--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -214,45 +214,69 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B8" s="4">
+        <v>2836.4</v>
+      </c>
+      <c r="C8" s="4">
+        <v>2168.8</v>
+      </c>
+      <c r="D8" s="4">
+        <v>3437.2</v>
+      </c>
+      <c r="E8" s="4">
+        <v>667.6</v>
+      </c>
+      <c r="F8" s="4">
+        <v>5605.9</v>
+      </c>
+      <c r="G8" s="5">
+        <f>IF(F8&gt;0,C8/F8,"")</f>
+        <v>0.3869</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B8" s="7">
-        <f>SUM(B5:B7)</f>
-        <v>8903.0</v>
-      </c>
-      <c r="C8" s="7">
-        <f>SUM(C5:C7)</f>
-        <v>7311.6</v>
-      </c>
-      <c r="D8" s="7">
-        <f>SUM(D5:D7)</f>
-        <v>19973.8</v>
-      </c>
-      <c r="E8" s="7">
-        <f>SUM(E5:E7)</f>
-        <v>1591.4</v>
-      </c>
-      <c r="F8" s="7">
-        <f>SUM(F5:F7)</f>
-        <v>27285.4</v>
-      </c>
-      <c r="G8" s="8">
-        <f>IF(F8&gt;0,C8/F8,"")</f>
-        <v>0.268</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B9" s="7">
+        <f>SUM(B5:B8)</f>
+        <v>11739.5</v>
+      </c>
+      <c r="C9" s="7">
+        <f>SUM(C5:C8)</f>
+        <v>9480.4</v>
+      </c>
+      <c r="D9" s="7">
+        <f>SUM(D5:D8)</f>
+        <v>23411.0</v>
+      </c>
+      <c r="E9" s="7">
+        <f>SUM(E5:E8)</f>
+        <v>2259.0</v>
+      </c>
+      <c r="F9" s="7">
+        <f>SUM(F5:F8)</f>
+        <v>32891.4</v>
+      </c>
+      <c r="G9" s="8">
+        <f>IF(F9&gt;0,C9/F9,"")</f>
+        <v>0.2882</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -7511,7 +7535,2407 @@
         <v>74.086</v>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C290" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D290" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E290" s="3">
+        <v>74.086</v>
+      </c>
+      <c r="F290" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G290" s="3">
+        <v>74.086</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C291" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D291" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E291" s="3">
+        <v>74.189</v>
+      </c>
+      <c r="F291" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G291" s="3">
+        <v>74.189</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C292" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D292" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E292" s="3">
+        <v>74.24</v>
+      </c>
+      <c r="F292" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G292" s="3">
+        <v>74.24</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B293" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C293" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D293" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E293" s="3">
+        <v>74.138</v>
+      </c>
+      <c r="F293" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G293" s="3">
+        <v>74.138</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B294" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C294" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D294" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E294" s="3">
+        <v>74.035</v>
+      </c>
+      <c r="F294" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G294" s="3">
+        <v>74.035</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B295" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C295" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D295" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E295" s="3">
+        <v>74.547</v>
+      </c>
+      <c r="F295" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G295" s="3">
+        <v>74.547</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B296" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C296" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D296" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E296" s="3">
+        <v>74.086</v>
+      </c>
+      <c r="F296" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G296" s="3">
+        <v>74.086</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B297" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C297" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D297" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E297" s="3">
+        <v>74.394</v>
+      </c>
+      <c r="F297" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G297" s="3">
+        <v>74.394</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B298" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C298" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D298" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E298" s="3">
+        <v>74.138</v>
+      </c>
+      <c r="F298" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G298" s="3">
+        <v>74.138</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B299" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C299" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D299" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E299" s="3">
+        <v>74.24</v>
+      </c>
+      <c r="F299" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G299" s="3">
+        <v>74.24</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B300" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C300" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D300" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E300" s="3">
+        <v>73.933</v>
+      </c>
+      <c r="F300" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G300" s="3">
+        <v>73.933</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B301" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C301" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D301" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E301" s="3">
+        <v>74.291</v>
+      </c>
+      <c r="F301" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G301" s="3">
+        <v>74.291</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B302" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C302" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D302" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E302" s="3">
+        <v>73.779</v>
+      </c>
+      <c r="F302" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G302" s="3">
+        <v>73.779</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B303" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C303" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D303" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E303" s="3">
+        <v>71.014</v>
+      </c>
+      <c r="F303" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G303" s="3">
+        <v>71.014</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B304" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C304" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D304" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E304" s="3">
+        <v>70.963</v>
+      </c>
+      <c r="F304" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G304" s="3">
+        <v>70.963</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B305" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C305" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D305" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E305" s="3">
+        <v>70.912</v>
+      </c>
+      <c r="F305" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G305" s="3">
+        <v>70.912</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B306" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C306" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D306" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E306" s="3">
+        <v>71.424</v>
+      </c>
+      <c r="F306" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G306" s="3">
+        <v>71.424</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B307" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C307" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D307" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E307" s="3">
+        <v>71.014</v>
+      </c>
+      <c r="F307" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G307" s="3">
+        <v>71.014</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B308" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C308" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D308" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E308" s="3">
+        <v>71.219</v>
+      </c>
+      <c r="F308" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G308" s="3">
+        <v>71.219</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B309" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C309" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D309" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E309" s="3">
+        <v>71.475</v>
+      </c>
+      <c r="F309" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G309" s="3">
+        <v>71.475</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B310" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C310" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D310" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E310" s="3">
+        <v>71.936</v>
+      </c>
+      <c r="F310" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G310" s="3">
+        <v>71.936</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B311" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C311" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D311" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E311" s="3">
+        <v>71.936</v>
+      </c>
+      <c r="F311" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G311" s="3">
+        <v>71.936</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B312" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C312" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D312" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E312" s="3">
+        <v>70.912</v>
+      </c>
+      <c r="F312" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G312" s="3">
+        <v>70.912</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B313" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C313" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D313" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E313" s="3">
+        <v>71.014</v>
+      </c>
+      <c r="F313" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G313" s="3">
+        <v>71.014</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B314" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C314" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D314" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E314" s="3">
+        <v>70.963</v>
+      </c>
+      <c r="F314" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G314" s="3">
+        <v>70.963</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B315" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C315" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D315" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E315" s="3">
+        <v>71.373</v>
+      </c>
+      <c r="F315" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G315" s="3">
+        <v>71.373</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B316" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C316" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D316" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E316" s="3">
+        <v>71.526</v>
+      </c>
+      <c r="F316" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G316" s="3">
+        <v>71.526</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B317" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C317" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D317" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E317" s="3">
+        <v>71.014</v>
+      </c>
+      <c r="F317" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G317" s="3">
+        <v>71.014</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B318" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C318" s="3">
+        <v>0.166</v>
+      </c>
+      <c r="D318" s="3">
+        <v>0.166</v>
+      </c>
+      <c r="E318" s="3">
+        <v>70.758</v>
+      </c>
+      <c r="F318" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G318" s="3">
+        <v>70.924</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B319" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C319" s="3">
+        <v>1.075</v>
+      </c>
+      <c r="D319" s="3">
+        <v>1.075</v>
+      </c>
+      <c r="E319" s="3">
+        <v>70.298</v>
+      </c>
+      <c r="F319" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G319" s="3">
+        <v>71.373</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B320" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C320" s="3">
+        <v>2.662</v>
+      </c>
+      <c r="D320" s="3">
+        <v>2.662</v>
+      </c>
+      <c r="E320" s="3">
+        <v>68.659</v>
+      </c>
+      <c r="F320" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G320" s="3">
+        <v>71.321</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B321" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C321" s="3">
+        <v>8.192</v>
+      </c>
+      <c r="D321" s="3">
+        <v>8.192</v>
+      </c>
+      <c r="E321" s="3">
+        <v>62.618</v>
+      </c>
+      <c r="F321" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G321" s="3">
+        <v>70.81</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B322" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C322" s="3">
+        <v>12.506</v>
+      </c>
+      <c r="D322" s="3">
+        <v>12.506</v>
+      </c>
+      <c r="E322" s="3">
+        <v>58.829</v>
+      </c>
+      <c r="F322" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G322" s="3">
+        <v>71.335</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B323" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C323" s="3">
+        <v>14.848</v>
+      </c>
+      <c r="D323" s="3">
+        <v>14.848</v>
+      </c>
+      <c r="E323" s="3">
+        <v>56.32</v>
+      </c>
+      <c r="F323" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G323" s="3">
+        <v>71.168</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B324" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C324" s="3">
+        <v>17.024</v>
+      </c>
+      <c r="D324" s="3">
+        <v>17.024</v>
+      </c>
+      <c r="E324" s="3">
+        <v>54.528</v>
+      </c>
+      <c r="F324" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G324" s="3">
+        <v>71.552</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B325" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C325" s="3">
+        <v>24.934</v>
+      </c>
+      <c r="D325" s="3">
+        <v>24.934</v>
+      </c>
+      <c r="E325" s="3">
+        <v>46.285</v>
+      </c>
+      <c r="F325" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G325" s="3">
+        <v>71.219</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B326" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C326" s="3">
+        <v>31.386</v>
+      </c>
+      <c r="D326" s="3">
+        <v>31.386</v>
+      </c>
+      <c r="E326" s="3">
+        <v>39.987</v>
+      </c>
+      <c r="F326" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G326" s="3">
+        <v>71.373</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B327" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C327" s="3">
+        <v>58.534</v>
+      </c>
+      <c r="D327" s="3">
+        <v>58.483</v>
+      </c>
+      <c r="E327" s="3">
+        <v>13.158</v>
+      </c>
+      <c r="F327" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G327" s="3">
+        <v>71.641</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B328" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C328" s="3">
+        <v>72.051</v>
+      </c>
+      <c r="D328" s="3">
+        <v>69.952</v>
+      </c>
+      <c r="E328" s="3">
+        <v>2.202</v>
+      </c>
+      <c r="F328" s="3">
+        <v>2.099</v>
+      </c>
+      <c r="G328" s="3">
+        <v>72.154</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B329" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C329" s="3">
+        <v>80.154</v>
+      </c>
+      <c r="D329" s="3">
+        <v>71.757</v>
+      </c>
+      <c r="E329" s="3">
+        <v>0.973</v>
+      </c>
+      <c r="F329" s="3">
+        <v>8.397</v>
+      </c>
+      <c r="G329" s="3">
+        <v>72.73</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B330" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C330" s="3">
+        <v>88.282</v>
+      </c>
+      <c r="D330" s="3">
+        <v>71.693</v>
+      </c>
+      <c r="E330" s="3">
+        <v>0.205</v>
+      </c>
+      <c r="F330" s="3">
+        <v>16.589</v>
+      </c>
+      <c r="G330" s="3">
+        <v>71.898</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B331" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C331" s="3">
+        <v>92.698</v>
+      </c>
+      <c r="D331" s="3">
+        <v>71.706</v>
+      </c>
+      <c r="E331" s="3">
+        <v>0.666</v>
+      </c>
+      <c r="F331" s="3">
+        <v>20.992</v>
+      </c>
+      <c r="G331" s="3">
+        <v>72.372</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B332" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C332" s="3">
+        <v>73.626</v>
+      </c>
+      <c r="D332" s="3">
+        <v>66.304</v>
+      </c>
+      <c r="E332" s="3">
+        <v>5.632</v>
+      </c>
+      <c r="F332" s="3">
+        <v>7.322</v>
+      </c>
+      <c r="G332" s="3">
+        <v>71.936</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B333" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C333" s="3">
+        <v>80.218</v>
+      </c>
+      <c r="D333" s="3">
+        <v>65.882</v>
+      </c>
+      <c r="E333" s="3">
+        <v>6.042</v>
+      </c>
+      <c r="F333" s="3">
+        <v>14.336</v>
+      </c>
+      <c r="G333" s="3">
+        <v>71.924</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B334" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C334" s="3">
+        <v>104.73</v>
+      </c>
+      <c r="D334" s="3">
+        <v>71.194</v>
+      </c>
+      <c r="E334" s="3">
+        <v>0.512</v>
+      </c>
+      <c r="F334" s="3">
+        <v>33.536</v>
+      </c>
+      <c r="G334" s="3">
+        <v>71.706</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B335" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C335" s="3">
+        <v>103.309</v>
+      </c>
+      <c r="D335" s="3">
+        <v>69.824</v>
+      </c>
+      <c r="E335" s="3">
+        <v>2.15</v>
+      </c>
+      <c r="F335" s="3">
+        <v>33.485</v>
+      </c>
+      <c r="G335" s="3">
+        <v>71.974</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B336" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C336" s="3">
+        <v>95.667</v>
+      </c>
+      <c r="D336" s="3">
+        <v>66.329</v>
+      </c>
+      <c r="E336" s="3">
+        <v>5.325</v>
+      </c>
+      <c r="F336" s="3">
+        <v>29.338</v>
+      </c>
+      <c r="G336" s="3">
+        <v>71.654</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B337" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C337" s="3">
+        <v>107.763</v>
+      </c>
+      <c r="D337" s="3">
+        <v>71.923</v>
+      </c>
+      <c r="E337" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F337" s="3">
+        <v>35.84</v>
+      </c>
+      <c r="G337" s="3">
+        <v>71.923</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B338" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C338" s="3">
+        <v>91.034</v>
+      </c>
+      <c r="D338" s="3">
+        <v>69.223</v>
+      </c>
+      <c r="E338" s="3">
+        <v>2.509</v>
+      </c>
+      <c r="F338" s="3">
+        <v>21.811</v>
+      </c>
+      <c r="G338" s="3">
+        <v>71.732</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B339" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C339" s="3">
+        <v>96.96</v>
+      </c>
+      <c r="D339" s="3">
+        <v>68.954</v>
+      </c>
+      <c r="E339" s="3">
+        <v>2.406</v>
+      </c>
+      <c r="F339" s="3">
+        <v>28.006</v>
+      </c>
+      <c r="G339" s="3">
+        <v>71.36</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B340" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C340" s="3">
+        <v>109.389</v>
+      </c>
+      <c r="D340" s="3">
+        <v>71.655</v>
+      </c>
+      <c r="E340" s="3">
+        <v>0.256</v>
+      </c>
+      <c r="F340" s="3">
+        <v>37.734</v>
+      </c>
+      <c r="G340" s="3">
+        <v>71.911</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B341" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C341" s="3">
+        <v>98.624</v>
+      </c>
+      <c r="D341" s="3">
+        <v>70.31</v>
+      </c>
+      <c r="E341" s="3">
+        <v>1.587</v>
+      </c>
+      <c r="F341" s="3">
+        <v>28.314</v>
+      </c>
+      <c r="G341" s="3">
+        <v>71.897</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B342" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C342" s="3">
+        <v>108.006</v>
+      </c>
+      <c r="D342" s="3">
+        <v>71.961</v>
+      </c>
+      <c r="E342" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F342" s="3">
+        <v>36.045</v>
+      </c>
+      <c r="G342" s="3">
+        <v>71.961</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B343" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C343" s="3">
+        <v>107.686</v>
+      </c>
+      <c r="D343" s="3">
+        <v>71.948</v>
+      </c>
+      <c r="E343" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F343" s="3">
+        <v>35.738</v>
+      </c>
+      <c r="G343" s="3">
+        <v>71.948</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B344" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C344" s="3">
+        <v>104.627</v>
+      </c>
+      <c r="D344" s="3">
+        <v>71.859</v>
+      </c>
+      <c r="E344" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="F344" s="3">
+        <v>32.768</v>
+      </c>
+      <c r="G344" s="3">
+        <v>71.91</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B345" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C345" s="3">
+        <v>108.237</v>
+      </c>
+      <c r="D345" s="3">
+        <v>71.475</v>
+      </c>
+      <c r="E345" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F345" s="3">
+        <v>36.762</v>
+      </c>
+      <c r="G345" s="3">
+        <v>71.475</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B346" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C346" s="3">
+        <v>90.445</v>
+      </c>
+      <c r="D346" s="3">
+        <v>71.501</v>
+      </c>
+      <c r="E346" s="3">
+        <v>0.666</v>
+      </c>
+      <c r="F346" s="3">
+        <v>18.944</v>
+      </c>
+      <c r="G346" s="3">
+        <v>72.167</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B347" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C347" s="3">
+        <v>94.528</v>
+      </c>
+      <c r="D347" s="3">
+        <v>72.307</v>
+      </c>
+      <c r="E347" s="3">
+        <v>0.205</v>
+      </c>
+      <c r="F347" s="3">
+        <v>22.221</v>
+      </c>
+      <c r="G347" s="3">
+        <v>72.512</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B348" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C348" s="3">
+        <v>106.522</v>
+      </c>
+      <c r="D348" s="3">
+        <v>72.884</v>
+      </c>
+      <c r="E348" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F348" s="3">
+        <v>33.638</v>
+      </c>
+      <c r="G348" s="3">
+        <v>72.884</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B349" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C349" s="3">
+        <v>98.957</v>
+      </c>
+      <c r="D349" s="3">
+        <v>71.258</v>
+      </c>
+      <c r="E349" s="3">
+        <v>1.075</v>
+      </c>
+      <c r="F349" s="3">
+        <v>27.699</v>
+      </c>
+      <c r="G349" s="3">
+        <v>72.333</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B350" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C350" s="3">
+        <v>82.483</v>
+      </c>
+      <c r="D350" s="3">
+        <v>69.478</v>
+      </c>
+      <c r="E350" s="3">
+        <v>2.662</v>
+      </c>
+      <c r="F350" s="3">
+        <v>13.005</v>
+      </c>
+      <c r="G350" s="3">
+        <v>72.14</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B351" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C351" s="3">
+        <v>84.826</v>
+      </c>
+      <c r="D351" s="3">
+        <v>64.039</v>
+      </c>
+      <c r="E351" s="3">
+        <v>3.994</v>
+      </c>
+      <c r="F351" s="3">
+        <v>20.787</v>
+      </c>
+      <c r="G351" s="3">
+        <v>68.033</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B352" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C352" s="3">
+        <v>70.067</v>
+      </c>
+      <c r="D352" s="3">
+        <v>38.118</v>
+      </c>
+      <c r="E352" s="3">
+        <v>0.205</v>
+      </c>
+      <c r="F352" s="3">
+        <v>31.949</v>
+      </c>
+      <c r="G352" s="3">
+        <v>38.323</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B353" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C353" s="3">
+        <v>70.234</v>
+      </c>
+      <c r="D353" s="3">
+        <v>38.183</v>
+      </c>
+      <c r="E353" s="3">
+        <v>0.358</v>
+      </c>
+      <c r="F353" s="3">
+        <v>32.051</v>
+      </c>
+      <c r="G353" s="3">
+        <v>38.541</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B354" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C354" s="3">
+        <v>40.806</v>
+      </c>
+      <c r="D354" s="3">
+        <v>37.068</v>
+      </c>
+      <c r="E354" s="3">
+        <v>0.768</v>
+      </c>
+      <c r="F354" s="3">
+        <v>3.738</v>
+      </c>
+      <c r="G354" s="3">
+        <v>37.836</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B355" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C355" s="3">
+        <v>38.106</v>
+      </c>
+      <c r="D355" s="3">
+        <v>36.365</v>
+      </c>
+      <c r="E355" s="3">
+        <v>1.536</v>
+      </c>
+      <c r="F355" s="3">
+        <v>1.741</v>
+      </c>
+      <c r="G355" s="3">
+        <v>37.901</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B356" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C356" s="3">
+        <v>38.656</v>
+      </c>
+      <c r="D356" s="3">
+        <v>36.352</v>
+      </c>
+      <c r="E356" s="3">
+        <v>1.331</v>
+      </c>
+      <c r="F356" s="3">
+        <v>2.304</v>
+      </c>
+      <c r="G356" s="3">
+        <v>37.683</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B357" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C357" s="3">
+        <v>32.038</v>
+      </c>
+      <c r="D357" s="3">
+        <v>31.628</v>
+      </c>
+      <c r="E357" s="3">
+        <v>6.093</v>
+      </c>
+      <c r="F357" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="G357" s="3">
+        <v>37.721</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B358" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C358" s="3">
+        <v>23.987</v>
+      </c>
+      <c r="D358" s="3">
+        <v>23.987</v>
+      </c>
+      <c r="E358" s="3">
+        <v>13.568</v>
+      </c>
+      <c r="F358" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G358" s="3">
+        <v>37.555</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B359" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C359" s="3">
+        <v>19.635</v>
+      </c>
+      <c r="D359" s="3">
+        <v>19.635</v>
+      </c>
+      <c r="E359" s="3">
+        <v>18.125</v>
+      </c>
+      <c r="F359" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G359" s="3">
+        <v>37.76</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B360" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C360" s="3">
+        <v>14.067</v>
+      </c>
+      <c r="D360" s="3">
+        <v>14.067</v>
+      </c>
+      <c r="E360" s="3">
+        <v>23.962</v>
+      </c>
+      <c r="F360" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G360" s="3">
+        <v>38.029</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B361" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C361" s="3">
+        <v>10.931</v>
+      </c>
+      <c r="D361" s="3">
+        <v>10.931</v>
+      </c>
+      <c r="E361" s="3">
+        <v>27.392</v>
+      </c>
+      <c r="F361" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G361" s="3">
+        <v>38.323</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B362" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C362" s="3">
+        <v>6.886</v>
+      </c>
+      <c r="D362" s="3">
+        <v>6.886</v>
+      </c>
+      <c r="E362" s="3">
+        <v>30.771</v>
+      </c>
+      <c r="F362" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G362" s="3">
+        <v>37.657</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B363" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C363" s="3">
+        <v>6.336</v>
+      </c>
+      <c r="D363" s="3">
+        <v>6.336</v>
+      </c>
+      <c r="E363" s="3">
+        <v>31.13</v>
+      </c>
+      <c r="F363" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G363" s="3">
+        <v>37.466</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B364" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C364" s="3">
+        <v>6.554</v>
+      </c>
+      <c r="D364" s="3">
+        <v>6.554</v>
+      </c>
+      <c r="E364" s="3">
+        <v>30.925</v>
+      </c>
+      <c r="F364" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G364" s="3">
+        <v>37.479</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B365" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C365" s="3">
+        <v>5.222</v>
+      </c>
+      <c r="D365" s="3">
+        <v>5.222</v>
+      </c>
+      <c r="E365" s="3">
+        <v>34.253</v>
+      </c>
+      <c r="F365" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G365" s="3">
+        <v>39.475</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B366" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C366" s="3">
+        <v>0.666</v>
+      </c>
+      <c r="D366" s="3">
+        <v>0.666</v>
+      </c>
+      <c r="E366" s="3">
+        <v>40.192</v>
+      </c>
+      <c r="F366" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G366" s="3">
+        <v>40.858</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B367" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C367" s="3">
+        <v>0.102</v>
+      </c>
+      <c r="D367" s="3">
+        <v>0.102</v>
+      </c>
+      <c r="E367" s="3">
+        <v>40.397</v>
+      </c>
+      <c r="F367" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G367" s="3">
+        <v>40.499</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B368" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C368" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D368" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E368" s="3">
+        <v>41.165</v>
+      </c>
+      <c r="F368" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G368" s="3">
+        <v>41.165</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B369" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C369" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D369" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E369" s="3">
+        <v>40.909</v>
+      </c>
+      <c r="F369" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G369" s="3">
+        <v>40.909</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B370" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C370" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D370" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E370" s="3">
+        <v>41.216</v>
+      </c>
+      <c r="F370" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G370" s="3">
+        <v>41.216</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B371" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C371" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D371" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E371" s="3">
+        <v>40.448</v>
+      </c>
+      <c r="F371" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G371" s="3">
+        <v>40.448</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B372" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C372" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D372" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E372" s="3">
+        <v>40.346</v>
+      </c>
+      <c r="F372" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G372" s="3">
+        <v>40.346</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B373" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C373" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D373" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E373" s="3">
+        <v>40.704</v>
+      </c>
+      <c r="F373" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G373" s="3">
+        <v>40.704</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B374" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C374" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D374" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E374" s="3">
+        <v>40.653</v>
+      </c>
+      <c r="F374" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G374" s="3">
+        <v>40.653</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B375" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C375" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D375" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E375" s="3">
+        <v>40.96</v>
+      </c>
+      <c r="F375" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G375" s="3">
+        <v>40.96</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B376" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C376" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D376" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E376" s="3">
+        <v>40.704</v>
+      </c>
+      <c r="F376" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G376" s="3">
+        <v>40.704</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B377" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C377" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D377" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E377" s="3">
+        <v>40.755</v>
+      </c>
+      <c r="F377" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G377" s="3">
+        <v>40.755</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B378" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C378" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D378" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E378" s="3">
+        <v>40.806</v>
+      </c>
+      <c r="F378" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G378" s="3">
+        <v>40.806</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B379" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C379" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D379" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E379" s="3">
+        <v>30.003</v>
+      </c>
+      <c r="F379" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G379" s="3">
+        <v>30.003</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B380" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C380" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D380" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E380" s="3">
+        <v>7.373</v>
+      </c>
+      <c r="F380" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G380" s="3">
+        <v>7.373</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B381" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C381" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D381" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E381" s="3">
+        <v>7.578</v>
+      </c>
+      <c r="F381" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G381" s="3">
+        <v>7.578</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B382" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C382" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D382" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E382" s="3">
+        <v>6.963</v>
+      </c>
+      <c r="F382" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G382" s="3">
+        <v>6.963</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B383" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C383" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D383" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E383" s="3">
+        <v>7.27</v>
+      </c>
+      <c r="F383" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G383" s="3">
+        <v>7.27</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B384" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C384" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D384" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E384" s="3">
+        <v>7.526</v>
+      </c>
+      <c r="F384" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G384" s="3">
+        <v>7.526</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B385" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C385" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D385" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E385" s="3">
+        <v>7.424</v>
+      </c>
+      <c r="F385" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G385" s="3">
+        <v>7.424</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G289"/>
+  <autoFilter ref="A1:G385"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -238,45 +238,69 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B9" s="4">
+        <v>2453.5</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2272.9</v>
+      </c>
+      <c r="D9" s="4">
+        <v>6068.6</v>
+      </c>
+      <c r="E9" s="4">
+        <v>180.6</v>
+      </c>
+      <c r="F9" s="4">
+        <v>8341.5</v>
+      </c>
+      <c r="G9" s="5">
+        <f>IF(F9&gt;0,C9/F9,"")</f>
+        <v>0.2725</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B9" s="7">
-        <f>SUM(B5:B8)</f>
-        <v>11739.5</v>
-      </c>
-      <c r="C9" s="7">
-        <f>SUM(C5:C8)</f>
-        <v>9480.4</v>
-      </c>
-      <c r="D9" s="7">
-        <f>SUM(D5:D8)</f>
-        <v>23411.0</v>
-      </c>
-      <c r="E9" s="7">
-        <f>SUM(E5:E8)</f>
-        <v>2259.0</v>
-      </c>
-      <c r="F9" s="7">
-        <f>SUM(F5:F8)</f>
-        <v>32891.4</v>
-      </c>
-      <c r="G9" s="8">
-        <f>IF(F9&gt;0,C9/F9,"")</f>
-        <v>0.2882</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B10" s="7">
+        <f>SUM(B5:B9)</f>
+        <v>14193.0</v>
+      </c>
+      <c r="C10" s="7">
+        <f>SUM(C5:C9)</f>
+        <v>11753.4</v>
+      </c>
+      <c r="D10" s="7">
+        <f>SUM(D5:D9)</f>
+        <v>29479.5</v>
+      </c>
+      <c r="E10" s="7">
+        <f>SUM(E5:E9)</f>
+        <v>2439.6</v>
+      </c>
+      <c r="F10" s="7">
+        <f>SUM(F5:F9)</f>
+        <v>41232.9</v>
+      </c>
+      <c r="G10" s="8">
+        <f>IF(F10&gt;0,C10/F10,"")</f>
+        <v>0.285</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -9935,7 +9959,2407 @@
         <v>7.424</v>
       </c>
     </row>
+    <row r="386">
+      <c r="A386" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B386" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C386" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D386" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E386" s="3">
+        <v>6.707</v>
+      </c>
+      <c r="F386" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G386" s="3">
+        <v>6.707</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B387" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C387" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D387" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E387" s="3">
+        <v>6.861</v>
+      </c>
+      <c r="F387" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G387" s="3">
+        <v>6.861</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B388" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C388" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D388" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E388" s="3">
+        <v>7.066</v>
+      </c>
+      <c r="F388" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G388" s="3">
+        <v>7.066</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B389" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C389" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D389" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E389" s="3">
+        <v>6.707</v>
+      </c>
+      <c r="F389" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G389" s="3">
+        <v>6.707</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B390" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C390" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D390" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E390" s="3">
+        <v>6.656</v>
+      </c>
+      <c r="F390" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G390" s="3">
+        <v>6.656</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B391" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C391" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D391" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E391" s="3">
+        <v>6.656</v>
+      </c>
+      <c r="F391" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G391" s="3">
+        <v>6.656</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B392" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C392" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D392" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E392" s="3">
+        <v>6.912</v>
+      </c>
+      <c r="F392" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G392" s="3">
+        <v>6.912</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B393" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C393" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D393" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E393" s="3">
+        <v>6.656</v>
+      </c>
+      <c r="F393" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G393" s="3">
+        <v>6.656</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B394" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C394" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D394" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E394" s="3">
+        <v>6.963</v>
+      </c>
+      <c r="F394" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G394" s="3">
+        <v>6.963</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B395" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C395" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D395" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E395" s="3">
+        <v>7.168</v>
+      </c>
+      <c r="F395" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G395" s="3">
+        <v>7.168</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B396" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C396" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D396" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E396" s="3">
+        <v>6.758</v>
+      </c>
+      <c r="F396" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G396" s="3">
+        <v>6.758</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B397" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C397" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D397" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E397" s="3">
+        <v>6.707</v>
+      </c>
+      <c r="F397" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G397" s="3">
+        <v>6.707</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B398" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C398" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D398" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E398" s="3">
+        <v>6.605</v>
+      </c>
+      <c r="F398" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G398" s="3">
+        <v>6.605</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B399" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C399" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D399" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E399" s="3">
+        <v>6.605</v>
+      </c>
+      <c r="F399" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G399" s="3">
+        <v>6.605</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B400" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C400" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D400" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E400" s="3">
+        <v>6.758</v>
+      </c>
+      <c r="F400" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G400" s="3">
+        <v>6.758</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B401" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C401" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D401" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E401" s="3">
+        <v>6.861</v>
+      </c>
+      <c r="F401" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G401" s="3">
+        <v>6.861</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B402" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C402" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D402" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E402" s="3">
+        <v>6.707</v>
+      </c>
+      <c r="F402" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G402" s="3">
+        <v>6.707</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B403" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C403" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D403" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E403" s="3">
+        <v>6.707</v>
+      </c>
+      <c r="F403" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G403" s="3">
+        <v>6.707</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B404" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C404" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D404" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E404" s="3">
+        <v>6.861</v>
+      </c>
+      <c r="F404" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G404" s="3">
+        <v>6.861</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B405" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C405" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D405" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E405" s="3">
+        <v>6.758</v>
+      </c>
+      <c r="F405" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G405" s="3">
+        <v>6.758</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B406" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C406" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D406" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E406" s="3">
+        <v>6.656</v>
+      </c>
+      <c r="F406" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G406" s="3">
+        <v>6.656</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B407" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C407" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D407" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E407" s="3">
+        <v>7.27</v>
+      </c>
+      <c r="F407" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G407" s="3">
+        <v>7.27</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B408" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C408" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D408" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E408" s="3">
+        <v>6.861</v>
+      </c>
+      <c r="F408" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G408" s="3">
+        <v>6.861</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B409" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C409" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D409" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E409" s="3">
+        <v>6.4</v>
+      </c>
+      <c r="F409" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G409" s="3">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B410" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C410" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D410" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E410" s="3">
+        <v>6.451</v>
+      </c>
+      <c r="F410" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G410" s="3">
+        <v>6.451</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B411" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C411" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D411" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E411" s="3">
+        <v>6.349</v>
+      </c>
+      <c r="F411" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G411" s="3">
+        <v>6.349</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B412" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C412" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D412" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E412" s="3">
+        <v>6.298</v>
+      </c>
+      <c r="F412" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G412" s="3">
+        <v>6.298</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B413" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C413" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D413" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E413" s="3">
+        <v>6.656</v>
+      </c>
+      <c r="F413" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G413" s="3">
+        <v>6.656</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B414" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C414" s="3">
+        <v>0.064</v>
+      </c>
+      <c r="D414" s="3">
+        <v>0.064</v>
+      </c>
+      <c r="E414" s="3">
+        <v>6.554</v>
+      </c>
+      <c r="F414" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G414" s="3">
+        <v>6.618</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B415" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C415" s="3">
+        <v>0.717</v>
+      </c>
+      <c r="D415" s="3">
+        <v>0.717</v>
+      </c>
+      <c r="E415" s="3">
+        <v>10.138</v>
+      </c>
+      <c r="F415" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G415" s="3">
+        <v>10.855</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B416" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C416" s="3">
+        <v>6.618</v>
+      </c>
+      <c r="D416" s="3">
+        <v>6.618</v>
+      </c>
+      <c r="E416" s="3">
+        <v>29.645</v>
+      </c>
+      <c r="F416" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G416" s="3">
+        <v>36.263</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B417" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C417" s="3">
+        <v>17.037</v>
+      </c>
+      <c r="D417" s="3">
+        <v>17.037</v>
+      </c>
+      <c r="E417" s="3">
+        <v>19.558</v>
+      </c>
+      <c r="F417" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G417" s="3">
+        <v>36.595</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B418" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C418" s="3">
+        <v>19.558</v>
+      </c>
+      <c r="D418" s="3">
+        <v>19.558</v>
+      </c>
+      <c r="E418" s="3">
+        <v>40.858</v>
+      </c>
+      <c r="F418" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G418" s="3">
+        <v>60.416</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B419" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C419" s="3">
+        <v>32.614</v>
+      </c>
+      <c r="D419" s="3">
+        <v>32.614</v>
+      </c>
+      <c r="E419" s="3">
+        <v>38.246</v>
+      </c>
+      <c r="F419" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G419" s="3">
+        <v>70.86</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B420" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C420" s="3">
+        <v>32.09</v>
+      </c>
+      <c r="D420" s="3">
+        <v>32.09</v>
+      </c>
+      <c r="E420" s="3">
+        <v>38.605</v>
+      </c>
+      <c r="F420" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G420" s="3">
+        <v>70.695</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B421" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C421" s="3">
+        <v>29.184</v>
+      </c>
+      <c r="D421" s="3">
+        <v>29.184</v>
+      </c>
+      <c r="E421" s="3">
+        <v>41.882</v>
+      </c>
+      <c r="F421" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G421" s="3">
+        <v>71.066</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B422" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C422" s="3">
+        <v>31.322</v>
+      </c>
+      <c r="D422" s="3">
+        <v>31.322</v>
+      </c>
+      <c r="E422" s="3">
+        <v>39.475</v>
+      </c>
+      <c r="F422" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G422" s="3">
+        <v>70.797</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B423" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C423" s="3">
+        <v>70.259</v>
+      </c>
+      <c r="D423" s="3">
+        <v>64.013</v>
+      </c>
+      <c r="E423" s="3">
+        <v>7.117</v>
+      </c>
+      <c r="F423" s="3">
+        <v>6.246</v>
+      </c>
+      <c r="G423" s="3">
+        <v>71.13</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B424" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C424" s="3">
+        <v>63.13</v>
+      </c>
+      <c r="D424" s="3">
+        <v>60.212</v>
+      </c>
+      <c r="E424" s="3">
+        <v>11.571</v>
+      </c>
+      <c r="F424" s="3">
+        <v>2.918</v>
+      </c>
+      <c r="G424" s="3">
+        <v>71.783</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B425" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C425" s="3">
+        <v>70.682</v>
+      </c>
+      <c r="D425" s="3">
+        <v>62.029</v>
+      </c>
+      <c r="E425" s="3">
+        <v>10.035</v>
+      </c>
+      <c r="F425" s="3">
+        <v>8.653</v>
+      </c>
+      <c r="G425" s="3">
+        <v>72.064</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B426" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C426" s="3">
+        <v>57.139</v>
+      </c>
+      <c r="D426" s="3">
+        <v>56.217</v>
+      </c>
+      <c r="E426" s="3">
+        <v>15.667</v>
+      </c>
+      <c r="F426" s="3">
+        <v>0.922</v>
+      </c>
+      <c r="G426" s="3">
+        <v>71.884</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B427" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C427" s="3">
+        <v>43.84</v>
+      </c>
+      <c r="D427" s="3">
+        <v>43.84</v>
+      </c>
+      <c r="E427" s="3">
+        <v>39.117</v>
+      </c>
+      <c r="F427" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G427" s="3">
+        <v>82.957</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B428" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C428" s="3">
+        <v>65.472</v>
+      </c>
+      <c r="D428" s="3">
+        <v>59.072</v>
+      </c>
+      <c r="E428" s="3">
+        <v>13.363</v>
+      </c>
+      <c r="F428" s="3">
+        <v>6.4</v>
+      </c>
+      <c r="G428" s="3">
+        <v>72.435</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B429" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C429" s="3">
+        <v>89.869</v>
+      </c>
+      <c r="D429" s="3">
+        <v>67.443</v>
+      </c>
+      <c r="E429" s="3">
+        <v>4.915</v>
+      </c>
+      <c r="F429" s="3">
+        <v>22.426</v>
+      </c>
+      <c r="G429" s="3">
+        <v>72.358</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B430" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C430" s="3">
+        <v>95.974</v>
+      </c>
+      <c r="D430" s="3">
+        <v>79.692</v>
+      </c>
+      <c r="E430" s="3">
+        <v>8.038</v>
+      </c>
+      <c r="F430" s="3">
+        <v>16.282</v>
+      </c>
+      <c r="G430" s="3">
+        <v>87.73</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B431" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C431" s="3">
+        <v>82.534</v>
+      </c>
+      <c r="D431" s="3">
+        <v>81.868</v>
+      </c>
+      <c r="E431" s="3">
+        <v>23.91</v>
+      </c>
+      <c r="F431" s="3">
+        <v>0.666</v>
+      </c>
+      <c r="G431" s="3">
+        <v>105.778</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B432" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C432" s="3">
+        <v>89.51</v>
+      </c>
+      <c r="D432" s="3">
+        <v>85.772</v>
+      </c>
+      <c r="E432" s="3">
+        <v>19.661</v>
+      </c>
+      <c r="F432" s="3">
+        <v>3.738</v>
+      </c>
+      <c r="G432" s="3">
+        <v>105.433</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B433" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C433" s="3">
+        <v>110.784</v>
+      </c>
+      <c r="D433" s="3">
+        <v>104.128</v>
+      </c>
+      <c r="E433" s="3">
+        <v>1.024</v>
+      </c>
+      <c r="F433" s="3">
+        <v>6.656</v>
+      </c>
+      <c r="G433" s="3">
+        <v>105.152</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B434" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C434" s="3">
+        <v>107.699</v>
+      </c>
+      <c r="D434" s="3">
+        <v>102.374</v>
+      </c>
+      <c r="E434" s="3">
+        <v>2.816</v>
+      </c>
+      <c r="F434" s="3">
+        <v>5.325</v>
+      </c>
+      <c r="G434" s="3">
+        <v>105.19</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B435" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C435" s="3">
+        <v>104.909</v>
+      </c>
+      <c r="D435" s="3">
+        <v>102.4</v>
+      </c>
+      <c r="E435" s="3">
+        <v>6.963</v>
+      </c>
+      <c r="F435" s="3">
+        <v>2.509</v>
+      </c>
+      <c r="G435" s="3">
+        <v>109.363</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B436" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C436" s="3">
+        <v>101.901</v>
+      </c>
+      <c r="D436" s="3">
+        <v>91.2</v>
+      </c>
+      <c r="E436" s="3">
+        <v>6.656</v>
+      </c>
+      <c r="F436" s="3">
+        <v>10.701</v>
+      </c>
+      <c r="G436" s="3">
+        <v>97.856</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B437" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C437" s="3">
+        <v>113.178</v>
+      </c>
+      <c r="D437" s="3">
+        <v>71.962</v>
+      </c>
+      <c r="E437" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F437" s="3">
+        <v>41.216</v>
+      </c>
+      <c r="G437" s="3">
+        <v>71.962</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B438" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C438" s="3">
+        <v>111.552</v>
+      </c>
+      <c r="D438" s="3">
+        <v>71.258</v>
+      </c>
+      <c r="E438" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F438" s="3">
+        <v>40.294</v>
+      </c>
+      <c r="G438" s="3">
+        <v>71.258</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B439" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C439" s="3">
+        <v>81.254</v>
+      </c>
+      <c r="D439" s="3">
+        <v>79.001</v>
+      </c>
+      <c r="E439" s="3">
+        <v>22.938</v>
+      </c>
+      <c r="F439" s="3">
+        <v>2.253</v>
+      </c>
+      <c r="G439" s="3">
+        <v>101.939</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B440" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C440" s="3">
+        <v>76.378</v>
+      </c>
+      <c r="D440" s="3">
+        <v>76.378</v>
+      </c>
+      <c r="E440" s="3">
+        <v>28.314</v>
+      </c>
+      <c r="F440" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G440" s="3">
+        <v>104.692</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B441" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C441" s="3">
+        <v>64.179</v>
+      </c>
+      <c r="D441" s="3">
+        <v>64.179</v>
+      </c>
+      <c r="E441" s="3">
+        <v>41.062</v>
+      </c>
+      <c r="F441" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G441" s="3">
+        <v>105.241</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B442" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C442" s="3">
+        <v>52.326</v>
+      </c>
+      <c r="D442" s="3">
+        <v>52.326</v>
+      </c>
+      <c r="E442" s="3">
+        <v>52.582</v>
+      </c>
+      <c r="F442" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G442" s="3">
+        <v>104.908</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B443" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C443" s="3">
+        <v>85.53</v>
+      </c>
+      <c r="D443" s="3">
+        <v>84.813</v>
+      </c>
+      <c r="E443" s="3">
+        <v>20.122</v>
+      </c>
+      <c r="F443" s="3">
+        <v>0.717</v>
+      </c>
+      <c r="G443" s="3">
+        <v>104.935</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B444" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C444" s="3">
+        <v>98.803</v>
+      </c>
+      <c r="D444" s="3">
+        <v>96.141</v>
+      </c>
+      <c r="E444" s="3">
+        <v>9.062</v>
+      </c>
+      <c r="F444" s="3">
+        <v>2.662</v>
+      </c>
+      <c r="G444" s="3">
+        <v>105.203</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B445" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C445" s="3">
+        <v>60.07</v>
+      </c>
+      <c r="D445" s="3">
+        <v>60.07</v>
+      </c>
+      <c r="E445" s="3">
+        <v>44.954</v>
+      </c>
+      <c r="F445" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G445" s="3">
+        <v>105.024</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B446" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C446" s="3">
+        <v>49.421</v>
+      </c>
+      <c r="D446" s="3">
+        <v>49.421</v>
+      </c>
+      <c r="E446" s="3">
+        <v>55.552</v>
+      </c>
+      <c r="F446" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G446" s="3">
+        <v>104.973</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B447" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C447" s="3">
+        <v>52.698</v>
+      </c>
+      <c r="D447" s="3">
+        <v>52.698</v>
+      </c>
+      <c r="E447" s="3">
+        <v>51.814</v>
+      </c>
+      <c r="F447" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G447" s="3">
+        <v>104.512</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B448" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C448" s="3">
+        <v>34.547</v>
+      </c>
+      <c r="D448" s="3">
+        <v>34.547</v>
+      </c>
+      <c r="E448" s="3">
+        <v>70.042</v>
+      </c>
+      <c r="F448" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G448" s="3">
+        <v>104.589</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B449" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C449" s="3">
+        <v>39.219</v>
+      </c>
+      <c r="D449" s="3">
+        <v>39.219</v>
+      </c>
+      <c r="E449" s="3">
+        <v>65.536</v>
+      </c>
+      <c r="F449" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G449" s="3">
+        <v>104.755</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B450" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C450" s="3">
+        <v>35.955</v>
+      </c>
+      <c r="D450" s="3">
+        <v>35.955</v>
+      </c>
+      <c r="E450" s="3">
+        <v>68.762</v>
+      </c>
+      <c r="F450" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G450" s="3">
+        <v>104.717</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B451" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C451" s="3">
+        <v>25.216</v>
+      </c>
+      <c r="D451" s="3">
+        <v>25.216</v>
+      </c>
+      <c r="E451" s="3">
+        <v>79.667</v>
+      </c>
+      <c r="F451" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G451" s="3">
+        <v>104.883</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B452" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C452" s="3">
+        <v>31.014</v>
+      </c>
+      <c r="D452" s="3">
+        <v>31.014</v>
+      </c>
+      <c r="E452" s="3">
+        <v>73.165</v>
+      </c>
+      <c r="F452" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G452" s="3">
+        <v>104.179</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B453" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C453" s="3">
+        <v>29.619</v>
+      </c>
+      <c r="D453" s="3">
+        <v>29.619</v>
+      </c>
+      <c r="E453" s="3">
+        <v>82.586</v>
+      </c>
+      <c r="F453" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G453" s="3">
+        <v>112.205</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B454" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C454" s="3">
+        <v>26.445</v>
+      </c>
+      <c r="D454" s="3">
+        <v>26.445</v>
+      </c>
+      <c r="E454" s="3">
+        <v>109.568</v>
+      </c>
+      <c r="F454" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G454" s="3">
+        <v>136.013</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B455" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C455" s="3">
+        <v>19.085</v>
+      </c>
+      <c r="D455" s="3">
+        <v>19.085</v>
+      </c>
+      <c r="E455" s="3">
+        <v>139.264</v>
+      </c>
+      <c r="F455" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G455" s="3">
+        <v>158.349</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B456" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C456" s="3">
+        <v>7.693</v>
+      </c>
+      <c r="D456" s="3">
+        <v>7.693</v>
+      </c>
+      <c r="E456" s="3">
+        <v>163.277</v>
+      </c>
+      <c r="F456" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G456" s="3">
+        <v>170.97</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B457" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C457" s="3">
+        <v>8.205</v>
+      </c>
+      <c r="D457" s="3">
+        <v>8.205</v>
+      </c>
+      <c r="E457" s="3">
+        <v>162.304</v>
+      </c>
+      <c r="F457" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G457" s="3">
+        <v>170.509</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B458" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C458" s="3">
+        <v>9.28</v>
+      </c>
+      <c r="D458" s="3">
+        <v>9.28</v>
+      </c>
+      <c r="E458" s="3">
+        <v>160.87</v>
+      </c>
+      <c r="F458" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G458" s="3">
+        <v>170.15</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B459" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C459" s="3">
+        <v>9.498</v>
+      </c>
+      <c r="D459" s="3">
+        <v>9.498</v>
+      </c>
+      <c r="E459" s="3">
+        <v>161.792</v>
+      </c>
+      <c r="F459" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G459" s="3">
+        <v>171.29</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B460" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C460" s="3">
+        <v>6.003</v>
+      </c>
+      <c r="D460" s="3">
+        <v>6.003</v>
+      </c>
+      <c r="E460" s="3">
+        <v>165.274</v>
+      </c>
+      <c r="F460" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G460" s="3">
+        <v>171.277</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B461" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C461" s="3">
+        <v>2.086</v>
+      </c>
+      <c r="D461" s="3">
+        <v>2.086</v>
+      </c>
+      <c r="E461" s="3">
+        <v>168.653</v>
+      </c>
+      <c r="F461" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G461" s="3">
+        <v>170.739</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B462" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C462" s="3">
+        <v>1.318</v>
+      </c>
+      <c r="D462" s="3">
+        <v>1.318</v>
+      </c>
+      <c r="E462" s="3">
+        <v>170.24</v>
+      </c>
+      <c r="F462" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G462" s="3">
+        <v>171.558</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B463" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C463" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="D463" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="E463" s="3">
+        <v>171.008</v>
+      </c>
+      <c r="F463" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G463" s="3">
+        <v>171.059</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B464" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C464" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D464" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E464" s="3">
+        <v>171.11</v>
+      </c>
+      <c r="F464" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G464" s="3">
+        <v>171.11</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B465" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C465" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D465" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E465" s="3">
+        <v>171.11</v>
+      </c>
+      <c r="F465" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G465" s="3">
+        <v>171.11</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B466" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C466" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D466" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E466" s="3">
+        <v>171.008</v>
+      </c>
+      <c r="F466" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G466" s="3">
+        <v>171.008</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B467" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C467" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D467" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E467" s="3">
+        <v>171.11</v>
+      </c>
+      <c r="F467" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G467" s="3">
+        <v>171.11</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B468" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C468" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D468" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E468" s="3">
+        <v>171.366</v>
+      </c>
+      <c r="F468" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G468" s="3">
+        <v>171.366</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B469" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C469" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D469" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E469" s="3">
+        <v>170.957</v>
+      </c>
+      <c r="F469" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G469" s="3">
+        <v>170.957</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B470" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C470" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D470" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E470" s="3">
+        <v>170.803</v>
+      </c>
+      <c r="F470" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G470" s="3">
+        <v>170.803</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B471" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C471" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D471" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E471" s="3">
+        <v>171.418</v>
+      </c>
+      <c r="F471" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G471" s="3">
+        <v>171.418</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B472" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C472" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D472" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E472" s="3">
+        <v>173.363</v>
+      </c>
+      <c r="F472" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G472" s="3">
+        <v>173.363</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B473" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C473" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D473" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E473" s="3">
+        <v>173.722</v>
+      </c>
+      <c r="F473" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G473" s="3">
+        <v>173.722</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B474" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C474" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D474" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E474" s="3">
+        <v>173.722</v>
+      </c>
+      <c r="F474" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G474" s="3">
+        <v>173.722</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B475" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C475" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D475" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E475" s="3">
+        <v>173.875</v>
+      </c>
+      <c r="F475" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G475" s="3">
+        <v>173.875</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B476" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C476" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D476" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E476" s="3">
+        <v>174.08</v>
+      </c>
+      <c r="F476" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G476" s="3">
+        <v>174.08</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B477" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C477" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D477" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E477" s="3">
+        <v>173.619</v>
+      </c>
+      <c r="F477" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G477" s="3">
+        <v>173.619</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B478" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C478" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D478" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E478" s="3">
+        <v>173.312</v>
+      </c>
+      <c r="F478" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G478" s="3">
+        <v>173.312</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B479" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C479" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D479" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E479" s="3">
+        <v>173.466</v>
+      </c>
+      <c r="F479" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G479" s="3">
+        <v>173.466</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B480" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C480" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D480" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E480" s="3">
+        <v>174.131</v>
+      </c>
+      <c r="F480" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G480" s="3">
+        <v>174.131</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B481" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C481" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D481" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E481" s="3">
+        <v>173.568</v>
+      </c>
+      <c r="F481" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G481" s="3">
+        <v>173.568</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G385"/>
+  <autoFilter ref="A1:G481"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -262,45 +262,69 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B10" s="4">
+        <v>2522.3</v>
+      </c>
+      <c r="C10" s="4">
+        <v>2322.5</v>
+      </c>
+      <c r="D10" s="4">
+        <v>8889.1</v>
+      </c>
+      <c r="E10" s="4">
+        <v>199.8</v>
+      </c>
+      <c r="F10" s="4">
+        <v>11211.6</v>
+      </c>
+      <c r="G10" s="5">
+        <f>IF(F10&gt;0,C10/F10,"")</f>
+        <v>0.2072</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B10" s="7">
-        <f>SUM(B5:B9)</f>
-        <v>14193.0</v>
-      </c>
-      <c r="C10" s="7">
-        <f>SUM(C5:C9)</f>
-        <v>11753.4</v>
-      </c>
-      <c r="D10" s="7">
-        <f>SUM(D5:D9)</f>
-        <v>29479.5</v>
-      </c>
-      <c r="E10" s="7">
-        <f>SUM(E5:E9)</f>
-        <v>2439.6</v>
-      </c>
-      <c r="F10" s="7">
-        <f>SUM(F5:F9)</f>
-        <v>41232.9</v>
-      </c>
-      <c r="G10" s="8">
-        <f>IF(F10&gt;0,C10/F10,"")</f>
-        <v>0.285</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B11" s="7">
+        <f>SUM(B5:B10)</f>
+        <v>16715.3</v>
+      </c>
+      <c r="C11" s="7">
+        <f>SUM(C5:C10)</f>
+        <v>14075.9</v>
+      </c>
+      <c r="D11" s="7">
+        <f>SUM(D5:D10)</f>
+        <v>38368.7</v>
+      </c>
+      <c r="E11" s="7">
+        <f>SUM(E5:E10)</f>
+        <v>2639.4</v>
+      </c>
+      <c r="F11" s="7">
+        <f>SUM(F5:F10)</f>
+        <v>52444.6</v>
+      </c>
+      <c r="G11" s="8">
+        <f>IF(F11&gt;0,C11/F11,"")</f>
+        <v>0.2684</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -12359,7 +12383,2407 @@
         <v>173.568</v>
       </c>
     </row>
+    <row r="482">
+      <c r="A482" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B482" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C482" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D482" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E482" s="3">
+        <v>173.312</v>
+      </c>
+      <c r="F482" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G482" s="3">
+        <v>173.312</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B483" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C483" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D483" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E483" s="3">
+        <v>173.312</v>
+      </c>
+      <c r="F483" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G483" s="3">
+        <v>173.312</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B484" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C484" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D484" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E484" s="3">
+        <v>173.414</v>
+      </c>
+      <c r="F484" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G484" s="3">
+        <v>173.414</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B485" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C485" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D485" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E485" s="3">
+        <v>173.568</v>
+      </c>
+      <c r="F485" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G485" s="3">
+        <v>173.568</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B486" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C486" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D486" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E486" s="3">
+        <v>173.312</v>
+      </c>
+      <c r="F486" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G486" s="3">
+        <v>173.312</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B487" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C487" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D487" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E487" s="3">
+        <v>173.312</v>
+      </c>
+      <c r="F487" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G487" s="3">
+        <v>173.312</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B488" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C488" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D488" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E488" s="3">
+        <v>173.466</v>
+      </c>
+      <c r="F488" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G488" s="3">
+        <v>173.466</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B489" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C489" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D489" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E489" s="3">
+        <v>173.414</v>
+      </c>
+      <c r="F489" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G489" s="3">
+        <v>173.414</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B490" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C490" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D490" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E490" s="3">
+        <v>173.363</v>
+      </c>
+      <c r="F490" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G490" s="3">
+        <v>173.363</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B491" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C491" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D491" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E491" s="3">
+        <v>173.261</v>
+      </c>
+      <c r="F491" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G491" s="3">
+        <v>173.261</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B492" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C492" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D492" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E492" s="3">
+        <v>173.363</v>
+      </c>
+      <c r="F492" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G492" s="3">
+        <v>173.363</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B493" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C493" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D493" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E493" s="3">
+        <v>173.824</v>
+      </c>
+      <c r="F493" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G493" s="3">
+        <v>173.824</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B494" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C494" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D494" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E494" s="3">
+        <v>173.568</v>
+      </c>
+      <c r="F494" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G494" s="3">
+        <v>173.568</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B495" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C495" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D495" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E495" s="3">
+        <v>173.312</v>
+      </c>
+      <c r="F495" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G495" s="3">
+        <v>173.312</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B496" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C496" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D496" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E496" s="3">
+        <v>173.466</v>
+      </c>
+      <c r="F496" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G496" s="3">
+        <v>173.466</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B497" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C497" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D497" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E497" s="3">
+        <v>174.131</v>
+      </c>
+      <c r="F497" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G497" s="3">
+        <v>174.131</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B498" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C498" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D498" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E498" s="3">
+        <v>174.234</v>
+      </c>
+      <c r="F498" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G498" s="3">
+        <v>174.234</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B499" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C499" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D499" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E499" s="3">
+        <v>173.722</v>
+      </c>
+      <c r="F499" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G499" s="3">
+        <v>173.722</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B500" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C500" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D500" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E500" s="3">
+        <v>173.363</v>
+      </c>
+      <c r="F500" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G500" s="3">
+        <v>173.363</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B501" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C501" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D501" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E501" s="3">
+        <v>173.363</v>
+      </c>
+      <c r="F501" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G501" s="3">
+        <v>173.363</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B502" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C502" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D502" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E502" s="3">
+        <v>173.363</v>
+      </c>
+      <c r="F502" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G502" s="3">
+        <v>173.363</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B503" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C503" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D503" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E503" s="3">
+        <v>173.875</v>
+      </c>
+      <c r="F503" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G503" s="3">
+        <v>173.875</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B504" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C504" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D504" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E504" s="3">
+        <v>173.312</v>
+      </c>
+      <c r="F504" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G504" s="3">
+        <v>173.312</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B505" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C505" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D505" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E505" s="3">
+        <v>173.312</v>
+      </c>
+      <c r="F505" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G505" s="3">
+        <v>173.312</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B506" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C506" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D506" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E506" s="3">
+        <v>173.568</v>
+      </c>
+      <c r="F506" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G506" s="3">
+        <v>173.568</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B507" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C507" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D507" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E507" s="3">
+        <v>174.95</v>
+      </c>
+      <c r="F507" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G507" s="3">
+        <v>174.95</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B508" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C508" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D508" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E508" s="3">
+        <v>174.95</v>
+      </c>
+      <c r="F508" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G508" s="3">
+        <v>174.95</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B509" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C509" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="D509" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="E509" s="3">
+        <v>171.981</v>
+      </c>
+      <c r="F509" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G509" s="3">
+        <v>171.994</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B510" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C510" s="3">
+        <v>0.717</v>
+      </c>
+      <c r="D510" s="3">
+        <v>0.717</v>
+      </c>
+      <c r="E510" s="3">
+        <v>139.827</v>
+      </c>
+      <c r="F510" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G510" s="3">
+        <v>140.544</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B511" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C511" s="3">
+        <v>1.933</v>
+      </c>
+      <c r="D511" s="3">
+        <v>1.933</v>
+      </c>
+      <c r="E511" s="3">
+        <v>138.342</v>
+      </c>
+      <c r="F511" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G511" s="3">
+        <v>140.275</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B512" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C512" s="3">
+        <v>6.285</v>
+      </c>
+      <c r="D512" s="3">
+        <v>6.285</v>
+      </c>
+      <c r="E512" s="3">
+        <v>133.939</v>
+      </c>
+      <c r="F512" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G512" s="3">
+        <v>140.224</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B513" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C513" s="3">
+        <v>12.429</v>
+      </c>
+      <c r="D513" s="3">
+        <v>12.429</v>
+      </c>
+      <c r="E513" s="3">
+        <v>128.563</v>
+      </c>
+      <c r="F513" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G513" s="3">
+        <v>140.992</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B514" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C514" s="3">
+        <v>12.045</v>
+      </c>
+      <c r="D514" s="3">
+        <v>12.045</v>
+      </c>
+      <c r="E514" s="3">
+        <v>129.024</v>
+      </c>
+      <c r="F514" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G514" s="3">
+        <v>141.069</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B515" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C515" s="3">
+        <v>13.35</v>
+      </c>
+      <c r="D515" s="3">
+        <v>13.35</v>
+      </c>
+      <c r="E515" s="3">
+        <v>128.922</v>
+      </c>
+      <c r="F515" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G515" s="3">
+        <v>142.272</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B516" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C516" s="3">
+        <v>28.838</v>
+      </c>
+      <c r="D516" s="3">
+        <v>28.838</v>
+      </c>
+      <c r="E516" s="3">
+        <v>105.933</v>
+      </c>
+      <c r="F516" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G516" s="3">
+        <v>134.771</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B517" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C517" s="3">
+        <v>45.606</v>
+      </c>
+      <c r="D517" s="3">
+        <v>45.606</v>
+      </c>
+      <c r="E517" s="3">
+        <v>58.522</v>
+      </c>
+      <c r="F517" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G517" s="3">
+        <v>104.128</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B518" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C518" s="3">
+        <v>43.853</v>
+      </c>
+      <c r="D518" s="3">
+        <v>43.853</v>
+      </c>
+      <c r="E518" s="3">
+        <v>59.494</v>
+      </c>
+      <c r="F518" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G518" s="3">
+        <v>103.347</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B519" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C519" s="3">
+        <v>54.349</v>
+      </c>
+      <c r="D519" s="3">
+        <v>54.349</v>
+      </c>
+      <c r="E519" s="3">
+        <v>48.384</v>
+      </c>
+      <c r="F519" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G519" s="3">
+        <v>102.733</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B520" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C520" s="3">
+        <v>60.134</v>
+      </c>
+      <c r="D520" s="3">
+        <v>60.134</v>
+      </c>
+      <c r="E520" s="3">
+        <v>42.752</v>
+      </c>
+      <c r="F520" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G520" s="3">
+        <v>102.886</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B521" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C521" s="3">
+        <v>76.134</v>
+      </c>
+      <c r="D521" s="3">
+        <v>76.134</v>
+      </c>
+      <c r="E521" s="3">
+        <v>27.341</v>
+      </c>
+      <c r="F521" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G521" s="3">
+        <v>103.475</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B522" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C522" s="3">
+        <v>68.544</v>
+      </c>
+      <c r="D522" s="3">
+        <v>68.544</v>
+      </c>
+      <c r="E522" s="3">
+        <v>34.509</v>
+      </c>
+      <c r="F522" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G522" s="3">
+        <v>103.053</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B523" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C523" s="3">
+        <v>69.837</v>
+      </c>
+      <c r="D523" s="3">
+        <v>69.837</v>
+      </c>
+      <c r="E523" s="3">
+        <v>32.973</v>
+      </c>
+      <c r="F523" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G523" s="3">
+        <v>102.81</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B524" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C524" s="3">
+        <v>87.424</v>
+      </c>
+      <c r="D524" s="3">
+        <v>87.27</v>
+      </c>
+      <c r="E524" s="3">
+        <v>15.309</v>
+      </c>
+      <c r="F524" s="3">
+        <v>0.154</v>
+      </c>
+      <c r="G524" s="3">
+        <v>102.579</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B525" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C525" s="3">
+        <v>89.766</v>
+      </c>
+      <c r="D525" s="3">
+        <v>88.896</v>
+      </c>
+      <c r="E525" s="3">
+        <v>18.534</v>
+      </c>
+      <c r="F525" s="3">
+        <v>0.87</v>
+      </c>
+      <c r="G525" s="3">
+        <v>107.43</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B526" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C526" s="3">
+        <v>107.174</v>
+      </c>
+      <c r="D526" s="3">
+        <v>99.955</v>
+      </c>
+      <c r="E526" s="3">
+        <v>2.406</v>
+      </c>
+      <c r="F526" s="3">
+        <v>7.219</v>
+      </c>
+      <c r="G526" s="3">
+        <v>102.361</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B527" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C527" s="3">
+        <v>58.048</v>
+      </c>
+      <c r="D527" s="3">
+        <v>57.843</v>
+      </c>
+      <c r="E527" s="3">
+        <v>43.981</v>
+      </c>
+      <c r="F527" s="3">
+        <v>0.205</v>
+      </c>
+      <c r="G527" s="3">
+        <v>101.824</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B528" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C528" s="3">
+        <v>54.963</v>
+      </c>
+      <c r="D528" s="3">
+        <v>54.656</v>
+      </c>
+      <c r="E528" s="3">
+        <v>47.565</v>
+      </c>
+      <c r="F528" s="3">
+        <v>0.307</v>
+      </c>
+      <c r="G528" s="3">
+        <v>102.221</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B529" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C529" s="3">
+        <v>35.546</v>
+      </c>
+      <c r="D529" s="3">
+        <v>35.546</v>
+      </c>
+      <c r="E529" s="3">
+        <v>66.15</v>
+      </c>
+      <c r="F529" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G529" s="3">
+        <v>101.696</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B530" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C530" s="3">
+        <v>27.763</v>
+      </c>
+      <c r="D530" s="3">
+        <v>27.763</v>
+      </c>
+      <c r="E530" s="3">
+        <v>74.086</v>
+      </c>
+      <c r="F530" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G530" s="3">
+        <v>101.849</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B531" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C531" s="3">
+        <v>45.76</v>
+      </c>
+      <c r="D531" s="3">
+        <v>45.76</v>
+      </c>
+      <c r="E531" s="3">
+        <v>56.166</v>
+      </c>
+      <c r="F531" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G531" s="3">
+        <v>101.926</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B532" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C532" s="3">
+        <v>73.216</v>
+      </c>
+      <c r="D532" s="3">
+        <v>72.55</v>
+      </c>
+      <c r="E532" s="3">
+        <v>24.934</v>
+      </c>
+      <c r="F532" s="3">
+        <v>0.666</v>
+      </c>
+      <c r="G532" s="3">
+        <v>97.484</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B533" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C533" s="3">
+        <v>49.562</v>
+      </c>
+      <c r="D533" s="3">
+        <v>49.152</v>
+      </c>
+      <c r="E533" s="3">
+        <v>22.63</v>
+      </c>
+      <c r="F533" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="G533" s="3">
+        <v>71.782</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B534" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C534" s="3">
+        <v>64.909</v>
+      </c>
+      <c r="D534" s="3">
+        <v>55.488</v>
+      </c>
+      <c r="E534" s="3">
+        <v>15.872</v>
+      </c>
+      <c r="F534" s="3">
+        <v>9.421</v>
+      </c>
+      <c r="G534" s="3">
+        <v>71.36</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B535" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C535" s="3">
+        <v>66.074</v>
+      </c>
+      <c r="D535" s="3">
+        <v>57.421</v>
+      </c>
+      <c r="E535" s="3">
+        <v>14.643</v>
+      </c>
+      <c r="F535" s="3">
+        <v>8.653</v>
+      </c>
+      <c r="G535" s="3">
+        <v>72.064</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B536" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C536" s="3">
+        <v>73.946</v>
+      </c>
+      <c r="D536" s="3">
+        <v>58.944</v>
+      </c>
+      <c r="E536" s="3">
+        <v>12.493</v>
+      </c>
+      <c r="F536" s="3">
+        <v>15.002</v>
+      </c>
+      <c r="G536" s="3">
+        <v>71.437</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B537" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C537" s="3">
+        <v>96.346</v>
+      </c>
+      <c r="D537" s="3">
+        <v>69.568</v>
+      </c>
+      <c r="E537" s="3">
+        <v>2.406</v>
+      </c>
+      <c r="F537" s="3">
+        <v>26.778</v>
+      </c>
+      <c r="G537" s="3">
+        <v>71.974</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B538" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C538" s="3">
+        <v>87.744</v>
+      </c>
+      <c r="D538" s="3">
+        <v>65.318</v>
+      </c>
+      <c r="E538" s="3">
+        <v>5.939</v>
+      </c>
+      <c r="F538" s="3">
+        <v>22.426</v>
+      </c>
+      <c r="G538" s="3">
+        <v>71.257</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B539" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C539" s="3">
+        <v>92.032</v>
+      </c>
+      <c r="D539" s="3">
+        <v>66.944</v>
+      </c>
+      <c r="E539" s="3">
+        <v>4.301</v>
+      </c>
+      <c r="F539" s="3">
+        <v>25.088</v>
+      </c>
+      <c r="G539" s="3">
+        <v>71.245</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B540" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C540" s="3">
+        <v>86.861</v>
+      </c>
+      <c r="D540" s="3">
+        <v>62.49</v>
+      </c>
+      <c r="E540" s="3">
+        <v>8.141</v>
+      </c>
+      <c r="F540" s="3">
+        <v>24.371</v>
+      </c>
+      <c r="G540" s="3">
+        <v>70.631</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B541" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C541" s="3">
+        <v>106.112</v>
+      </c>
+      <c r="D541" s="3">
+        <v>69.914</v>
+      </c>
+      <c r="E541" s="3">
+        <v>1.485</v>
+      </c>
+      <c r="F541" s="3">
+        <v>36.198</v>
+      </c>
+      <c r="G541" s="3">
+        <v>71.399</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B542" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C542" s="3">
+        <v>76.531</v>
+      </c>
+      <c r="D542" s="3">
+        <v>58.816</v>
+      </c>
+      <c r="E542" s="3">
+        <v>12.39</v>
+      </c>
+      <c r="F542" s="3">
+        <v>17.715</v>
+      </c>
+      <c r="G542" s="3">
+        <v>71.206</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B543" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C543" s="3">
+        <v>66.79</v>
+      </c>
+      <c r="D543" s="3">
+        <v>63.564</v>
+      </c>
+      <c r="E543" s="3">
+        <v>32.87</v>
+      </c>
+      <c r="F543" s="3">
+        <v>3.226</v>
+      </c>
+      <c r="G543" s="3">
+        <v>96.434</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B544" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C544" s="3">
+        <v>98.637</v>
+      </c>
+      <c r="D544" s="3">
+        <v>97.664</v>
+      </c>
+      <c r="E544" s="3">
+        <v>7.014</v>
+      </c>
+      <c r="F544" s="3">
+        <v>0.973</v>
+      </c>
+      <c r="G544" s="3">
+        <v>104.678</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B545" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C545" s="3">
+        <v>98.022</v>
+      </c>
+      <c r="D545" s="3">
+        <v>97.92</v>
+      </c>
+      <c r="E545" s="3">
+        <v>20.89</v>
+      </c>
+      <c r="F545" s="3">
+        <v>0.102</v>
+      </c>
+      <c r="G545" s="3">
+        <v>118.81</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B546" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C546" s="3">
+        <v>66.675</v>
+      </c>
+      <c r="D546" s="3">
+        <v>66.675</v>
+      </c>
+      <c r="E546" s="3">
+        <v>71.424</v>
+      </c>
+      <c r="F546" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G546" s="3">
+        <v>138.099</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B547" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C547" s="3">
+        <v>40.768</v>
+      </c>
+      <c r="D547" s="3">
+        <v>40.768</v>
+      </c>
+      <c r="E547" s="3">
+        <v>97.792</v>
+      </c>
+      <c r="F547" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G547" s="3">
+        <v>138.56</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B548" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C548" s="3">
+        <v>43.021</v>
+      </c>
+      <c r="D548" s="3">
+        <v>43.021</v>
+      </c>
+      <c r="E548" s="3">
+        <v>95.13</v>
+      </c>
+      <c r="F548" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G548" s="3">
+        <v>138.151</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B549" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C549" s="3">
+        <v>57.715</v>
+      </c>
+      <c r="D549" s="3">
+        <v>57.715</v>
+      </c>
+      <c r="E549" s="3">
+        <v>80.384</v>
+      </c>
+      <c r="F549" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G549" s="3">
+        <v>138.099</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B550" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C550" s="3">
+        <v>55.117</v>
+      </c>
+      <c r="D550" s="3">
+        <v>55.117</v>
+      </c>
+      <c r="E550" s="3">
+        <v>58.317</v>
+      </c>
+      <c r="F550" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G550" s="3">
+        <v>113.434</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B551" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C551" s="3">
+        <v>26.253</v>
+      </c>
+      <c r="D551" s="3">
+        <v>26.253</v>
+      </c>
+      <c r="E551" s="3">
+        <v>77.722</v>
+      </c>
+      <c r="F551" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G551" s="3">
+        <v>103.975</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B552" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C552" s="3">
+        <v>36.224</v>
+      </c>
+      <c r="D552" s="3">
+        <v>36.224</v>
+      </c>
+      <c r="E552" s="3">
+        <v>66.406</v>
+      </c>
+      <c r="F552" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G552" s="3">
+        <v>102.63</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B553" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C553" s="3">
+        <v>20.39</v>
+      </c>
+      <c r="D553" s="3">
+        <v>20.39</v>
+      </c>
+      <c r="E553" s="3">
+        <v>82.432</v>
+      </c>
+      <c r="F553" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G553" s="3">
+        <v>102.822</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B554" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C554" s="3">
+        <v>10.624</v>
+      </c>
+      <c r="D554" s="3">
+        <v>10.624</v>
+      </c>
+      <c r="E554" s="3">
+        <v>77.414</v>
+      </c>
+      <c r="F554" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G554" s="3">
+        <v>88.038</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B555" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C555" s="3">
+        <v>10.317</v>
+      </c>
+      <c r="D555" s="3">
+        <v>10.317</v>
+      </c>
+      <c r="E555" s="3">
+        <v>58.624</v>
+      </c>
+      <c r="F555" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G555" s="3">
+        <v>68.941</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B556" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C556" s="3">
+        <v>9.69</v>
+      </c>
+      <c r="D556" s="3">
+        <v>9.69</v>
+      </c>
+      <c r="E556" s="3">
+        <v>59.341</v>
+      </c>
+      <c r="F556" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G556" s="3">
+        <v>69.031</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B557" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C557" s="3">
+        <v>5.466</v>
+      </c>
+      <c r="D557" s="3">
+        <v>5.466</v>
+      </c>
+      <c r="E557" s="3">
+        <v>63.539</v>
+      </c>
+      <c r="F557" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G557" s="3">
+        <v>69.005</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B558" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C558" s="3">
+        <v>1.523</v>
+      </c>
+      <c r="D558" s="3">
+        <v>1.523</v>
+      </c>
+      <c r="E558" s="3">
+        <v>66.714</v>
+      </c>
+      <c r="F558" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G558" s="3">
+        <v>68.237</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B559" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C559" s="3">
+        <v>0.87</v>
+      </c>
+      <c r="D559" s="3">
+        <v>0.87</v>
+      </c>
+      <c r="E559" s="3">
+        <v>68.966</v>
+      </c>
+      <c r="F559" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G559" s="3">
+        <v>69.836</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B560" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C560" s="3">
+        <v>0.333</v>
+      </c>
+      <c r="D560" s="3">
+        <v>0.333</v>
+      </c>
+      <c r="E560" s="3">
+        <v>69.171</v>
+      </c>
+      <c r="F560" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G560" s="3">
+        <v>69.504</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B561" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C561" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="D561" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="E561" s="3">
+        <v>69.632</v>
+      </c>
+      <c r="F561" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G561" s="3">
+        <v>69.645</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B562" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C562" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D562" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E562" s="3">
+        <v>69.53</v>
+      </c>
+      <c r="F562" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G562" s="3">
+        <v>69.53</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B563" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C563" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D563" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E563" s="3">
+        <v>69.581</v>
+      </c>
+      <c r="F563" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G563" s="3">
+        <v>69.581</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B564" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C564" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D564" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E564" s="3">
+        <v>69.427</v>
+      </c>
+      <c r="F564" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G564" s="3">
+        <v>69.427</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B565" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C565" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D565" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E565" s="3">
+        <v>70.963</v>
+      </c>
+      <c r="F565" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G565" s="3">
+        <v>70.963</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B566" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C566" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D566" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E566" s="3">
+        <v>72.499</v>
+      </c>
+      <c r="F566" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G566" s="3">
+        <v>72.499</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B567" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C567" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D567" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E567" s="3">
+        <v>72.704</v>
+      </c>
+      <c r="F567" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G567" s="3">
+        <v>72.704</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B568" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C568" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D568" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E568" s="3">
+        <v>72.397</v>
+      </c>
+      <c r="F568" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G568" s="3">
+        <v>72.397</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B569" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C569" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D569" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E569" s="3">
+        <v>71.885</v>
+      </c>
+      <c r="F569" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G569" s="3">
+        <v>71.885</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B570" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C570" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D570" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E570" s="3">
+        <v>71.987</v>
+      </c>
+      <c r="F570" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G570" s="3">
+        <v>71.987</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B571" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C571" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D571" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E571" s="3">
+        <v>72.192</v>
+      </c>
+      <c r="F571" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G571" s="3">
+        <v>72.192</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B572" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C572" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D572" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E572" s="3">
+        <v>72.038</v>
+      </c>
+      <c r="F572" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G572" s="3">
+        <v>72.038</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B573" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C573" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D573" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E573" s="3">
+        <v>71.936</v>
+      </c>
+      <c r="F573" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G573" s="3">
+        <v>71.936</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B574" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C574" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D574" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E574" s="3">
+        <v>71.936</v>
+      </c>
+      <c r="F574" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G574" s="3">
+        <v>71.936</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B575" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C575" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D575" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E575" s="3">
+        <v>72.602</v>
+      </c>
+      <c r="F575" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G575" s="3">
+        <v>72.602</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B576" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C576" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D576" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E576" s="3">
+        <v>72.909</v>
+      </c>
+      <c r="F576" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G576" s="3">
+        <v>72.909</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B577" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C577" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D577" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E577" s="3">
+        <v>73.421</v>
+      </c>
+      <c r="F577" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G577" s="3">
+        <v>73.421</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G481"/>
+  <autoFilter ref="A1:G577"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -286,45 +286,69 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B11" s="4">
+        <v>1972.0</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1972.0</v>
+      </c>
+      <c r="D11" s="4">
+        <v>9361.6</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F11" s="4">
+        <v>11333.6</v>
+      </c>
+      <c r="G11" s="5">
+        <f>IF(F11&gt;0,C11/F11,"")</f>
+        <v>0.174</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B11" s="7">
-        <f>SUM(B5:B10)</f>
-        <v>16715.3</v>
-      </c>
-      <c r="C11" s="7">
-        <f>SUM(C5:C10)</f>
-        <v>14075.9</v>
-      </c>
-      <c r="D11" s="7">
-        <f>SUM(D5:D10)</f>
-        <v>38368.7</v>
-      </c>
-      <c r="E11" s="7">
-        <f>SUM(E5:E10)</f>
+      <c r="B12" s="7">
+        <f>SUM(B5:B11)</f>
+        <v>18687.3</v>
+      </c>
+      <c r="C12" s="7">
+        <f>SUM(C5:C11)</f>
+        <v>16047.9</v>
+      </c>
+      <c r="D12" s="7">
+        <f>SUM(D5:D11)</f>
+        <v>47730.2</v>
+      </c>
+      <c r="E12" s="7">
+        <f>SUM(E5:E11)</f>
         <v>2639.4</v>
       </c>
-      <c r="F11" s="7">
-        <f>SUM(F5:F10)</f>
-        <v>52444.6</v>
-      </c>
-      <c r="G11" s="8">
-        <f>IF(F11&gt;0,C11/F11,"")</f>
-        <v>0.2684</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="F12" s="7">
+        <f>SUM(F5:F11)</f>
+        <v>63778.1</v>
+      </c>
+      <c r="G12" s="8">
+        <f>IF(F12&gt;0,C12/F12,"")</f>
+        <v>0.2516</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -14783,7 +14807,2407 @@
         <v>73.421</v>
       </c>
     </row>
+    <row r="578">
+      <c r="A578" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B578" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C578" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D578" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E578" s="3">
+        <v>72.55</v>
+      </c>
+      <c r="F578" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G578" s="3">
+        <v>72.55</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B579" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C579" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D579" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E579" s="3">
+        <v>72.55</v>
+      </c>
+      <c r="F579" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G579" s="3">
+        <v>72.55</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B580" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C580" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D580" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E580" s="3">
+        <v>72.09</v>
+      </c>
+      <c r="F580" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G580" s="3">
+        <v>72.09</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B581" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C581" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D581" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E581" s="3">
+        <v>72.141</v>
+      </c>
+      <c r="F581" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G581" s="3">
+        <v>72.141</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B582" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C582" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D582" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E582" s="3">
+        <v>72.448</v>
+      </c>
+      <c r="F582" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G582" s="3">
+        <v>72.448</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B583" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C583" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D583" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E583" s="3">
+        <v>72.448</v>
+      </c>
+      <c r="F583" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G583" s="3">
+        <v>72.448</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B584" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C584" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D584" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E584" s="3">
+        <v>72.448</v>
+      </c>
+      <c r="F584" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G584" s="3">
+        <v>72.448</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B585" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C585" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D585" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E585" s="3">
+        <v>72.448</v>
+      </c>
+      <c r="F585" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G585" s="3">
+        <v>72.448</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B586" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C586" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D586" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E586" s="3">
+        <v>72.243</v>
+      </c>
+      <c r="F586" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G586" s="3">
+        <v>72.243</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B587" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C587" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D587" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E587" s="3">
+        <v>72.346</v>
+      </c>
+      <c r="F587" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G587" s="3">
+        <v>72.346</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B588" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C588" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D588" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E588" s="3">
+        <v>72.909</v>
+      </c>
+      <c r="F588" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G588" s="3">
+        <v>72.909</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B589" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C589" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D589" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E589" s="3">
+        <v>72.346</v>
+      </c>
+      <c r="F589" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G589" s="3">
+        <v>72.346</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B590" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C590" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D590" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E590" s="3">
+        <v>72.499</v>
+      </c>
+      <c r="F590" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G590" s="3">
+        <v>72.499</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B591" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C591" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D591" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E591" s="3">
+        <v>72.243</v>
+      </c>
+      <c r="F591" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G591" s="3">
+        <v>72.243</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B592" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C592" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D592" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E592" s="3">
+        <v>72.294</v>
+      </c>
+      <c r="F592" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G592" s="3">
+        <v>72.294</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B593" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C593" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D593" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E593" s="3">
+        <v>72.602</v>
+      </c>
+      <c r="F593" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G593" s="3">
+        <v>72.602</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B594" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C594" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D594" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E594" s="3">
+        <v>72.448</v>
+      </c>
+      <c r="F594" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G594" s="3">
+        <v>72.448</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B595" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C595" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D595" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E595" s="3">
+        <v>72.346</v>
+      </c>
+      <c r="F595" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G595" s="3">
+        <v>72.346</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B596" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C596" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D596" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E596" s="3">
+        <v>72.346</v>
+      </c>
+      <c r="F596" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G596" s="3">
+        <v>72.346</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B597" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C597" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D597" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E597" s="3">
+        <v>72.397</v>
+      </c>
+      <c r="F597" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G597" s="3">
+        <v>72.397</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B598" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C598" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D598" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E598" s="3">
+        <v>72.294</v>
+      </c>
+      <c r="F598" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G598" s="3">
+        <v>72.294</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B599" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C599" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D599" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E599" s="3">
+        <v>72.499</v>
+      </c>
+      <c r="F599" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G599" s="3">
+        <v>72.499</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B600" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C600" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D600" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E600" s="3">
+        <v>72.346</v>
+      </c>
+      <c r="F600" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G600" s="3">
+        <v>72.346</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B601" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C601" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D601" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E601" s="3">
+        <v>72.346</v>
+      </c>
+      <c r="F601" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G601" s="3">
+        <v>72.346</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B602" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C602" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D602" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E602" s="3">
+        <v>73.216</v>
+      </c>
+      <c r="F602" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G602" s="3">
+        <v>73.216</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B603" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C603" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D603" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E603" s="3">
+        <v>72.858</v>
+      </c>
+      <c r="F603" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G603" s="3">
+        <v>72.858</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B604" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C604" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D604" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E604" s="3">
+        <v>72.602</v>
+      </c>
+      <c r="F604" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G604" s="3">
+        <v>72.602</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B605" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C605" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D605" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E605" s="3">
+        <v>72.55</v>
+      </c>
+      <c r="F605" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G605" s="3">
+        <v>72.55</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B606" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C606" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D606" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E606" s="3">
+        <v>72.96</v>
+      </c>
+      <c r="F606" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G606" s="3">
+        <v>72.96</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B607" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C607" s="3">
+        <v>0.269</v>
+      </c>
+      <c r="D607" s="3">
+        <v>0.269</v>
+      </c>
+      <c r="E607" s="3">
+        <v>72.704</v>
+      </c>
+      <c r="F607" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G607" s="3">
+        <v>72.973</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B608" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C608" s="3">
+        <v>1.421</v>
+      </c>
+      <c r="D608" s="3">
+        <v>1.421</v>
+      </c>
+      <c r="E608" s="3">
+        <v>70.298</v>
+      </c>
+      <c r="F608" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G608" s="3">
+        <v>71.719</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B609" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C609" s="3">
+        <v>4.211</v>
+      </c>
+      <c r="D609" s="3">
+        <v>4.211</v>
+      </c>
+      <c r="E609" s="3">
+        <v>66.662</v>
+      </c>
+      <c r="F609" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G609" s="3">
+        <v>70.873</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B610" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C610" s="3">
+        <v>6.784</v>
+      </c>
+      <c r="D610" s="3">
+        <v>6.784</v>
+      </c>
+      <c r="E610" s="3">
+        <v>95.283</v>
+      </c>
+      <c r="F610" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G610" s="3">
+        <v>102.067</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B611" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C611" s="3">
+        <v>9.805</v>
+      </c>
+      <c r="D611" s="3">
+        <v>9.805</v>
+      </c>
+      <c r="E611" s="3">
+        <v>95.232</v>
+      </c>
+      <c r="F611" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G611" s="3">
+        <v>105.037</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B612" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C612" s="3">
+        <v>6.362</v>
+      </c>
+      <c r="D612" s="3">
+        <v>6.362</v>
+      </c>
+      <c r="E612" s="3">
+        <v>98.355</v>
+      </c>
+      <c r="F612" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G612" s="3">
+        <v>104.717</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B613" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C613" s="3">
+        <v>15.514</v>
+      </c>
+      <c r="D613" s="3">
+        <v>15.514</v>
+      </c>
+      <c r="E613" s="3">
+        <v>109.978</v>
+      </c>
+      <c r="F613" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G613" s="3">
+        <v>125.492</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B614" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C614" s="3">
+        <v>41.05</v>
+      </c>
+      <c r="D614" s="3">
+        <v>41.05</v>
+      </c>
+      <c r="E614" s="3">
+        <v>94.72</v>
+      </c>
+      <c r="F614" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G614" s="3">
+        <v>135.77</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B615" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C615" s="3">
+        <v>26.342</v>
+      </c>
+      <c r="D615" s="3">
+        <v>26.342</v>
+      </c>
+      <c r="E615" s="3">
+        <v>109.978</v>
+      </c>
+      <c r="F615" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G615" s="3">
+        <v>136.32</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B616" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C616" s="3">
+        <v>25.715</v>
+      </c>
+      <c r="D616" s="3">
+        <v>25.715</v>
+      </c>
+      <c r="E616" s="3">
+        <v>116.07</v>
+      </c>
+      <c r="F616" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G616" s="3">
+        <v>141.785</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B617" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C617" s="3">
+        <v>30.272</v>
+      </c>
+      <c r="D617" s="3">
+        <v>30.272</v>
+      </c>
+      <c r="E617" s="3">
+        <v>141.158</v>
+      </c>
+      <c r="F617" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G617" s="3">
+        <v>171.43</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B618" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C618" s="3">
+        <v>41.536</v>
+      </c>
+      <c r="D618" s="3">
+        <v>41.536</v>
+      </c>
+      <c r="E618" s="3">
+        <v>98.867</v>
+      </c>
+      <c r="F618" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G618" s="3">
+        <v>140.403</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B619" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C619" s="3">
+        <v>87.565</v>
+      </c>
+      <c r="D619" s="3">
+        <v>87.565</v>
+      </c>
+      <c r="E619" s="3">
+        <v>51.814</v>
+      </c>
+      <c r="F619" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G619" s="3">
+        <v>139.379</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B620" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C620" s="3">
+        <v>31.642</v>
+      </c>
+      <c r="D620" s="3">
+        <v>31.642</v>
+      </c>
+      <c r="E620" s="3">
+        <v>107.469</v>
+      </c>
+      <c r="F620" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G620" s="3">
+        <v>139.111</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B621" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C621" s="3">
+        <v>31.526</v>
+      </c>
+      <c r="D621" s="3">
+        <v>31.526</v>
+      </c>
+      <c r="E621" s="3">
+        <v>107.366</v>
+      </c>
+      <c r="F621" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G621" s="3">
+        <v>138.892</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B622" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C622" s="3">
+        <v>18.534</v>
+      </c>
+      <c r="D622" s="3">
+        <v>18.534</v>
+      </c>
+      <c r="E622" s="3">
+        <v>120.371</v>
+      </c>
+      <c r="F622" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G622" s="3">
+        <v>138.905</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B623" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C623" s="3">
+        <v>22.95</v>
+      </c>
+      <c r="D623" s="3">
+        <v>22.95</v>
+      </c>
+      <c r="E623" s="3">
+        <v>116.275</v>
+      </c>
+      <c r="F623" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G623" s="3">
+        <v>139.225</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B624" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C624" s="3">
+        <v>22.784</v>
+      </c>
+      <c r="D624" s="3">
+        <v>22.784</v>
+      </c>
+      <c r="E624" s="3">
+        <v>116.48</v>
+      </c>
+      <c r="F624" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G624" s="3">
+        <v>139.264</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B625" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C625" s="3">
+        <v>15.859</v>
+      </c>
+      <c r="D625" s="3">
+        <v>15.859</v>
+      </c>
+      <c r="E625" s="3">
+        <v>122.778</v>
+      </c>
+      <c r="F625" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G625" s="3">
+        <v>138.637</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B626" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C626" s="3">
+        <v>16.294</v>
+      </c>
+      <c r="D626" s="3">
+        <v>16.294</v>
+      </c>
+      <c r="E626" s="3">
+        <v>125.542</v>
+      </c>
+      <c r="F626" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G626" s="3">
+        <v>141.836</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B627" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C627" s="3">
+        <v>14.349</v>
+      </c>
+      <c r="D627" s="3">
+        <v>14.349</v>
+      </c>
+      <c r="E627" s="3">
+        <v>152.525</v>
+      </c>
+      <c r="F627" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G627" s="3">
+        <v>166.874</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B628" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C628" s="3">
+        <v>28.173</v>
+      </c>
+      <c r="D628" s="3">
+        <v>28.173</v>
+      </c>
+      <c r="E628" s="3">
+        <v>110.746</v>
+      </c>
+      <c r="F628" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G628" s="3">
+        <v>138.919</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B629" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C629" s="3">
+        <v>32.934</v>
+      </c>
+      <c r="D629" s="3">
+        <v>32.934</v>
+      </c>
+      <c r="E629" s="3">
+        <v>105.728</v>
+      </c>
+      <c r="F629" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G629" s="3">
+        <v>138.662</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B630" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C630" s="3">
+        <v>44.314</v>
+      </c>
+      <c r="D630" s="3">
+        <v>44.314</v>
+      </c>
+      <c r="E630" s="3">
+        <v>107.981</v>
+      </c>
+      <c r="F630" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G630" s="3">
+        <v>152.295</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B631" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C631" s="3">
+        <v>46.912</v>
+      </c>
+      <c r="D631" s="3">
+        <v>46.912</v>
+      </c>
+      <c r="E631" s="3">
+        <v>123.034</v>
+      </c>
+      <c r="F631" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G631" s="3">
+        <v>169.946</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B632" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C632" s="3">
+        <v>46.566</v>
+      </c>
+      <c r="D632" s="3">
+        <v>46.566</v>
+      </c>
+      <c r="E632" s="3">
+        <v>125.594</v>
+      </c>
+      <c r="F632" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G632" s="3">
+        <v>172.16</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B633" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C633" s="3">
+        <v>95.181</v>
+      </c>
+      <c r="D633" s="3">
+        <v>95.181</v>
+      </c>
+      <c r="E633" s="3">
+        <v>74.906</v>
+      </c>
+      <c r="F633" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G633" s="3">
+        <v>170.087</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B634" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C634" s="3">
+        <v>87.616</v>
+      </c>
+      <c r="D634" s="3">
+        <v>87.616</v>
+      </c>
+      <c r="E634" s="3">
+        <v>84.378</v>
+      </c>
+      <c r="F634" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G634" s="3">
+        <v>171.994</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B635" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C635" s="3">
+        <v>102.63</v>
+      </c>
+      <c r="D635" s="3">
+        <v>102.63</v>
+      </c>
+      <c r="E635" s="3">
+        <v>68.864</v>
+      </c>
+      <c r="F635" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G635" s="3">
+        <v>171.494</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B636" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C636" s="3">
+        <v>101.542</v>
+      </c>
+      <c r="D636" s="3">
+        <v>101.542</v>
+      </c>
+      <c r="E636" s="3">
+        <v>70.502</v>
+      </c>
+      <c r="F636" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G636" s="3">
+        <v>172.044</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B637" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C637" s="3">
+        <v>99.226</v>
+      </c>
+      <c r="D637" s="3">
+        <v>99.226</v>
+      </c>
+      <c r="E637" s="3">
+        <v>55.296</v>
+      </c>
+      <c r="F637" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G637" s="3">
+        <v>154.522</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B638" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C638" s="3">
+        <v>62.195</v>
+      </c>
+      <c r="D638" s="3">
+        <v>62.195</v>
+      </c>
+      <c r="E638" s="3">
+        <v>75.213</v>
+      </c>
+      <c r="F638" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G638" s="3">
+        <v>137.408</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B639" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C639" s="3">
+        <v>54.144</v>
+      </c>
+      <c r="D639" s="3">
+        <v>54.144</v>
+      </c>
+      <c r="E639" s="3">
+        <v>84.941</v>
+      </c>
+      <c r="F639" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G639" s="3">
+        <v>139.085</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B640" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C640" s="3">
+        <v>81.677</v>
+      </c>
+      <c r="D640" s="3">
+        <v>81.677</v>
+      </c>
+      <c r="E640" s="3">
+        <v>55.296</v>
+      </c>
+      <c r="F640" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G640" s="3">
+        <v>136.973</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B641" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C641" s="3">
+        <v>93.35</v>
+      </c>
+      <c r="D641" s="3">
+        <v>93.35</v>
+      </c>
+      <c r="E641" s="3">
+        <v>44.083</v>
+      </c>
+      <c r="F641" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G641" s="3">
+        <v>137.433</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B642" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C642" s="3">
+        <v>85.504</v>
+      </c>
+      <c r="D642" s="3">
+        <v>85.504</v>
+      </c>
+      <c r="E642" s="3">
+        <v>51.866</v>
+      </c>
+      <c r="F642" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G642" s="3">
+        <v>137.37</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B643" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C643" s="3">
+        <v>75.405</v>
+      </c>
+      <c r="D643" s="3">
+        <v>75.405</v>
+      </c>
+      <c r="E643" s="3">
+        <v>61.184</v>
+      </c>
+      <c r="F643" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G643" s="3">
+        <v>136.589</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B644" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C644" s="3">
+        <v>63.565</v>
+      </c>
+      <c r="D644" s="3">
+        <v>63.565</v>
+      </c>
+      <c r="E644" s="3">
+        <v>74.24</v>
+      </c>
+      <c r="F644" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G644" s="3">
+        <v>137.805</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B645" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C645" s="3">
+        <v>65.293</v>
+      </c>
+      <c r="D645" s="3">
+        <v>65.293</v>
+      </c>
+      <c r="E645" s="3">
+        <v>71.27</v>
+      </c>
+      <c r="F645" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G645" s="3">
+        <v>136.563</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B646" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C646" s="3">
+        <v>57.728</v>
+      </c>
+      <c r="D646" s="3">
+        <v>57.728</v>
+      </c>
+      <c r="E646" s="3">
+        <v>79.565</v>
+      </c>
+      <c r="F646" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G646" s="3">
+        <v>137.293</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B647" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C647" s="3">
+        <v>50.714</v>
+      </c>
+      <c r="D647" s="3">
+        <v>50.714</v>
+      </c>
+      <c r="E647" s="3">
+        <v>86.682</v>
+      </c>
+      <c r="F647" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G647" s="3">
+        <v>137.396</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B648" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C648" s="3">
+        <v>45.875</v>
+      </c>
+      <c r="D648" s="3">
+        <v>45.875</v>
+      </c>
+      <c r="E648" s="3">
+        <v>90.573</v>
+      </c>
+      <c r="F648" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G648" s="3">
+        <v>136.448</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B649" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C649" s="3">
+        <v>39.834</v>
+      </c>
+      <c r="D649" s="3">
+        <v>39.834</v>
+      </c>
+      <c r="E649" s="3">
+        <v>96.358</v>
+      </c>
+      <c r="F649" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G649" s="3">
+        <v>136.192</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B650" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C650" s="3">
+        <v>17.011</v>
+      </c>
+      <c r="D650" s="3">
+        <v>17.011</v>
+      </c>
+      <c r="E650" s="3">
+        <v>119.091</v>
+      </c>
+      <c r="F650" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G650" s="3">
+        <v>136.102</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B651" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C651" s="3">
+        <v>10.726</v>
+      </c>
+      <c r="D651" s="3">
+        <v>10.726</v>
+      </c>
+      <c r="E651" s="3">
+        <v>126.157</v>
+      </c>
+      <c r="F651" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G651" s="3">
+        <v>136.883</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B652" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C652" s="3">
+        <v>8.525</v>
+      </c>
+      <c r="D652" s="3">
+        <v>8.525</v>
+      </c>
+      <c r="E652" s="3">
+        <v>128.461</v>
+      </c>
+      <c r="F652" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G652" s="3">
+        <v>136.986</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B653" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C653" s="3">
+        <v>3.648</v>
+      </c>
+      <c r="D653" s="3">
+        <v>3.648</v>
+      </c>
+      <c r="E653" s="3">
+        <v>132.762</v>
+      </c>
+      <c r="F653" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G653" s="3">
+        <v>136.41</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B654" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C654" s="3">
+        <v>0.819</v>
+      </c>
+      <c r="D654" s="3">
+        <v>0.819</v>
+      </c>
+      <c r="E654" s="3">
+        <v>135.526</v>
+      </c>
+      <c r="F654" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G654" s="3">
+        <v>136.345</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B655" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C655" s="3">
+        <v>0.128</v>
+      </c>
+      <c r="D655" s="3">
+        <v>0.128</v>
+      </c>
+      <c r="E655" s="3">
+        <v>137.011</v>
+      </c>
+      <c r="F655" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G655" s="3">
+        <v>137.139</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B656" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C656" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D656" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E656" s="3">
+        <v>137.421</v>
+      </c>
+      <c r="F656" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G656" s="3">
+        <v>137.421</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B657" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C657" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D657" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E657" s="3">
+        <v>137.114</v>
+      </c>
+      <c r="F657" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G657" s="3">
+        <v>137.114</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B658" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C658" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D658" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E658" s="3">
+        <v>136.55</v>
+      </c>
+      <c r="F658" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G658" s="3">
+        <v>136.55</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B659" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C659" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D659" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E659" s="3">
+        <v>136.653</v>
+      </c>
+      <c r="F659" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G659" s="3">
+        <v>136.653</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B660" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C660" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D660" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E660" s="3">
+        <v>136.909</v>
+      </c>
+      <c r="F660" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G660" s="3">
+        <v>136.909</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B661" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C661" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D661" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E661" s="3">
+        <v>138.035</v>
+      </c>
+      <c r="F661" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G661" s="3">
+        <v>138.035</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B662" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C662" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D662" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E662" s="3">
+        <v>137.779</v>
+      </c>
+      <c r="F662" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G662" s="3">
+        <v>137.779</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B663" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C663" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D663" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E663" s="3">
+        <v>137.574</v>
+      </c>
+      <c r="F663" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G663" s="3">
+        <v>137.574</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B664" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C664" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D664" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E664" s="3">
+        <v>138.24</v>
+      </c>
+      <c r="F664" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G664" s="3">
+        <v>138.24</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B665" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C665" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D665" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E665" s="3">
+        <v>138.138</v>
+      </c>
+      <c r="F665" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G665" s="3">
+        <v>138.138</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B666" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C666" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D666" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E666" s="3">
+        <v>139.981</v>
+      </c>
+      <c r="F666" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G666" s="3">
+        <v>139.981</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B667" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C667" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D667" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E667" s="3">
+        <v>139.622</v>
+      </c>
+      <c r="F667" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G667" s="3">
+        <v>139.622</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B668" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C668" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D668" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E668" s="3">
+        <v>139.571</v>
+      </c>
+      <c r="F668" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G668" s="3">
+        <v>139.571</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B669" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C669" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D669" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E669" s="3">
+        <v>140.134</v>
+      </c>
+      <c r="F669" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G669" s="3">
+        <v>140.134</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B670" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C670" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D670" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E670" s="3">
+        <v>139.571</v>
+      </c>
+      <c r="F670" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G670" s="3">
+        <v>139.571</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B671" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C671" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D671" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E671" s="3">
+        <v>139.469</v>
+      </c>
+      <c r="F671" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G671" s="3">
+        <v>139.469</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B672" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C672" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D672" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E672" s="3">
+        <v>140.032</v>
+      </c>
+      <c r="F672" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G672" s="3">
+        <v>140.032</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B673" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C673" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D673" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E673" s="3">
+        <v>139.725</v>
+      </c>
+      <c r="F673" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G673" s="3">
+        <v>139.725</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G577"/>
+  <autoFilter ref="A1:G673"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -310,45 +310,69 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B12" s="4">
+        <v>3075.7</v>
+      </c>
+      <c r="C12" s="4">
+        <v>2939.3</v>
+      </c>
+      <c r="D12" s="4">
+        <v>7071.6</v>
+      </c>
+      <c r="E12" s="4">
+        <v>136.4</v>
+      </c>
+      <c r="F12" s="4">
+        <v>10010.9</v>
+      </c>
+      <c r="G12" s="5">
+        <f>IF(F12&gt;0,C12/F12,"")</f>
+        <v>0.2936</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B12" s="7">
-        <f>SUM(B5:B11)</f>
-        <v>18687.3</v>
-      </c>
-      <c r="C12" s="7">
-        <f>SUM(C5:C11)</f>
-        <v>16047.9</v>
-      </c>
-      <c r="D12" s="7">
-        <f>SUM(D5:D11)</f>
-        <v>47730.2</v>
-      </c>
-      <c r="E12" s="7">
-        <f>SUM(E5:E11)</f>
-        <v>2639.4</v>
-      </c>
-      <c r="F12" s="7">
-        <f>SUM(F5:F11)</f>
-        <v>63778.1</v>
-      </c>
-      <c r="G12" s="8">
-        <f>IF(F12&gt;0,C12/F12,"")</f>
-        <v>0.2516</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B13" s="7">
+        <f>SUM(B5:B12)</f>
+        <v>21763.0</v>
+      </c>
+      <c r="C13" s="7">
+        <f>SUM(C5:C12)</f>
+        <v>18987.2</v>
+      </c>
+      <c r="D13" s="7">
+        <f>SUM(D5:D12)</f>
+        <v>54801.8</v>
+      </c>
+      <c r="E13" s="7">
+        <f>SUM(E5:E12)</f>
+        <v>2775.9</v>
+      </c>
+      <c r="F13" s="7">
+        <f>SUM(F5:F12)</f>
+        <v>73789.0</v>
+      </c>
+      <c r="G13" s="8">
+        <f>IF(F13&gt;0,C13/F13,"")</f>
+        <v>0.2573</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -17207,7 +17231,2407 @@
         <v>139.725</v>
       </c>
     </row>
+    <row r="674">
+      <c r="A674" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B674" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C674" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D674" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E674" s="3">
+        <v>139.366</v>
+      </c>
+      <c r="F674" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G674" s="3">
+        <v>139.366</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B675" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C675" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D675" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E675" s="3">
+        <v>139.827</v>
+      </c>
+      <c r="F675" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G675" s="3">
+        <v>139.827</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B676" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C676" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D676" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E676" s="3">
+        <v>139.469</v>
+      </c>
+      <c r="F676" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G676" s="3">
+        <v>139.469</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B677" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C677" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D677" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E677" s="3">
+        <v>139.162</v>
+      </c>
+      <c r="F677" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G677" s="3">
+        <v>139.162</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B678" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C678" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D678" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E678" s="3">
+        <v>139.52</v>
+      </c>
+      <c r="F678" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G678" s="3">
+        <v>139.52</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B679" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C679" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D679" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E679" s="3">
+        <v>139.059</v>
+      </c>
+      <c r="F679" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G679" s="3">
+        <v>139.059</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B680" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C680" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D680" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E680" s="3">
+        <v>139.162</v>
+      </c>
+      <c r="F680" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G680" s="3">
+        <v>139.162</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B681" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C681" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D681" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E681" s="3">
+        <v>139.11</v>
+      </c>
+      <c r="F681" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G681" s="3">
+        <v>139.11</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B682" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C682" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D682" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E682" s="3">
+        <v>139.162</v>
+      </c>
+      <c r="F682" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G682" s="3">
+        <v>139.162</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B683" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C683" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D683" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E683" s="3">
+        <v>139.162</v>
+      </c>
+      <c r="F683" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G683" s="3">
+        <v>139.162</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B684" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C684" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D684" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E684" s="3">
+        <v>139.725</v>
+      </c>
+      <c r="F684" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G684" s="3">
+        <v>139.725</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B685" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C685" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D685" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E685" s="3">
+        <v>140.186</v>
+      </c>
+      <c r="F685" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G685" s="3">
+        <v>140.186</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B686" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C686" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D686" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E686" s="3">
+        <v>139.571</v>
+      </c>
+      <c r="F686" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G686" s="3">
+        <v>139.571</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B687" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C687" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D687" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E687" s="3">
+        <v>139.059</v>
+      </c>
+      <c r="F687" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G687" s="3">
+        <v>139.059</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B688" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C688" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D688" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E688" s="3">
+        <v>139.776</v>
+      </c>
+      <c r="F688" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G688" s="3">
+        <v>139.776</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B689" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C689" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D689" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E689" s="3">
+        <v>139.213</v>
+      </c>
+      <c r="F689" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G689" s="3">
+        <v>139.213</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B690" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C690" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D690" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E690" s="3">
+        <v>139.008</v>
+      </c>
+      <c r="F690" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G690" s="3">
+        <v>139.008</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B691" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C691" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D691" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E691" s="3">
+        <v>139.571</v>
+      </c>
+      <c r="F691" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G691" s="3">
+        <v>139.571</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B692" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C692" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D692" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E692" s="3">
+        <v>140.186</v>
+      </c>
+      <c r="F692" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G692" s="3">
+        <v>140.186</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B693" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C693" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D693" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E693" s="3">
+        <v>140.544</v>
+      </c>
+      <c r="F693" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G693" s="3">
+        <v>140.544</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B694" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C694" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D694" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E694" s="3">
+        <v>139.981</v>
+      </c>
+      <c r="F694" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G694" s="3">
+        <v>139.981</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B695" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C695" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D695" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E695" s="3">
+        <v>139.264</v>
+      </c>
+      <c r="F695" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G695" s="3">
+        <v>139.264</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B696" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C696" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D696" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E696" s="3">
+        <v>139.264</v>
+      </c>
+      <c r="F696" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G696" s="3">
+        <v>139.264</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B697" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C697" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D697" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E697" s="3">
+        <v>139.264</v>
+      </c>
+      <c r="F697" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G697" s="3">
+        <v>139.264</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B698" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C698" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D698" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E698" s="3">
+        <v>139.981</v>
+      </c>
+      <c r="F698" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G698" s="3">
+        <v>139.981</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B699" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C699" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D699" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E699" s="3">
+        <v>139.827</v>
+      </c>
+      <c r="F699" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G699" s="3">
+        <v>139.827</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B700" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C700" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D700" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E700" s="3">
+        <v>122.317</v>
+      </c>
+      <c r="F700" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G700" s="3">
+        <v>122.317</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B701" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C701" s="3">
+        <v>0.077</v>
+      </c>
+      <c r="D701" s="3">
+        <v>0.077</v>
+      </c>
+      <c r="E701" s="3">
+        <v>104.397</v>
+      </c>
+      <c r="F701" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G701" s="3">
+        <v>104.474</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B702" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C702" s="3">
+        <v>1.011</v>
+      </c>
+      <c r="D702" s="3">
+        <v>1.011</v>
+      </c>
+      <c r="E702" s="3">
+        <v>103.373</v>
+      </c>
+      <c r="F702" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G702" s="3">
+        <v>104.384</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B703" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C703" s="3">
+        <v>3.379</v>
+      </c>
+      <c r="D703" s="3">
+        <v>3.379</v>
+      </c>
+      <c r="E703" s="3">
+        <v>101.018</v>
+      </c>
+      <c r="F703" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G703" s="3">
+        <v>104.397</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B704" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C704" s="3">
+        <v>8.768</v>
+      </c>
+      <c r="D704" s="3">
+        <v>8.768</v>
+      </c>
+      <c r="E704" s="3">
+        <v>95.232</v>
+      </c>
+      <c r="F704" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G704" s="3">
+        <v>104.0</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B705" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C705" s="3">
+        <v>16.038</v>
+      </c>
+      <c r="D705" s="3">
+        <v>16.038</v>
+      </c>
+      <c r="E705" s="3">
+        <v>87.808</v>
+      </c>
+      <c r="F705" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G705" s="3">
+        <v>103.846</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B706" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C706" s="3">
+        <v>20.672</v>
+      </c>
+      <c r="D706" s="3">
+        <v>20.672</v>
+      </c>
+      <c r="E706" s="3">
+        <v>84.07</v>
+      </c>
+      <c r="F706" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G706" s="3">
+        <v>104.742</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B707" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C707" s="3">
+        <v>13.747</v>
+      </c>
+      <c r="D707" s="3">
+        <v>13.747</v>
+      </c>
+      <c r="E707" s="3">
+        <v>90.88</v>
+      </c>
+      <c r="F707" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G707" s="3">
+        <v>104.627</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B708" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C708" s="3">
+        <v>24.614</v>
+      </c>
+      <c r="D708" s="3">
+        <v>24.614</v>
+      </c>
+      <c r="E708" s="3">
+        <v>80.333</v>
+      </c>
+      <c r="F708" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G708" s="3">
+        <v>104.947</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B709" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C709" s="3">
+        <v>32.307</v>
+      </c>
+      <c r="D709" s="3">
+        <v>32.307</v>
+      </c>
+      <c r="E709" s="3">
+        <v>72.653</v>
+      </c>
+      <c r="F709" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G709" s="3">
+        <v>104.96</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B710" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C710" s="3">
+        <v>49.958</v>
+      </c>
+      <c r="D710" s="3">
+        <v>49.958</v>
+      </c>
+      <c r="E710" s="3">
+        <v>55.091</v>
+      </c>
+      <c r="F710" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G710" s="3">
+        <v>105.049</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B711" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C711" s="3">
+        <v>65.254</v>
+      </c>
+      <c r="D711" s="3">
+        <v>65.254</v>
+      </c>
+      <c r="E711" s="3">
+        <v>39.987</v>
+      </c>
+      <c r="F711" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G711" s="3">
+        <v>105.241</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B712" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C712" s="3">
+        <v>58.278</v>
+      </c>
+      <c r="D712" s="3">
+        <v>58.278</v>
+      </c>
+      <c r="E712" s="3">
+        <v>47.616</v>
+      </c>
+      <c r="F712" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G712" s="3">
+        <v>105.894</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B713" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C713" s="3">
+        <v>82.982</v>
+      </c>
+      <c r="D713" s="3">
+        <v>82.931</v>
+      </c>
+      <c r="E713" s="3">
+        <v>22.63</v>
+      </c>
+      <c r="F713" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G713" s="3">
+        <v>105.561</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B714" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C714" s="3">
+        <v>72.73</v>
+      </c>
+      <c r="D714" s="3">
+        <v>72.218</v>
+      </c>
+      <c r="E714" s="3">
+        <v>31.744</v>
+      </c>
+      <c r="F714" s="3">
+        <v>0.512</v>
+      </c>
+      <c r="G714" s="3">
+        <v>103.962</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B715" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C715" s="3">
+        <v>67.469</v>
+      </c>
+      <c r="D715" s="3">
+        <v>65.933</v>
+      </c>
+      <c r="E715" s="3">
+        <v>38.963</v>
+      </c>
+      <c r="F715" s="3">
+        <v>1.536</v>
+      </c>
+      <c r="G715" s="3">
+        <v>104.896</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B716" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C716" s="3">
+        <v>73.254</v>
+      </c>
+      <c r="D716" s="3">
+        <v>70.233</v>
+      </c>
+      <c r="E716" s="3">
+        <v>30.976</v>
+      </c>
+      <c r="F716" s="3">
+        <v>3.021</v>
+      </c>
+      <c r="G716" s="3">
+        <v>101.209</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B717" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C717" s="3">
+        <v>60.826</v>
+      </c>
+      <c r="D717" s="3">
+        <v>60.416</v>
+      </c>
+      <c r="E717" s="3">
+        <v>41.216</v>
+      </c>
+      <c r="F717" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="G717" s="3">
+        <v>101.632</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B718" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C718" s="3">
+        <v>55.194</v>
+      </c>
+      <c r="D718" s="3">
+        <v>54.784</v>
+      </c>
+      <c r="E718" s="3">
+        <v>46.694</v>
+      </c>
+      <c r="F718" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="G718" s="3">
+        <v>101.478</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B719" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C719" s="3">
+        <v>76.454</v>
+      </c>
+      <c r="D719" s="3">
+        <v>73.638</v>
+      </c>
+      <c r="E719" s="3">
+        <v>28.928</v>
+      </c>
+      <c r="F719" s="3">
+        <v>2.816</v>
+      </c>
+      <c r="G719" s="3">
+        <v>102.566</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B720" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C720" s="3">
+        <v>103.181</v>
+      </c>
+      <c r="D720" s="3">
+        <v>94.682</v>
+      </c>
+      <c r="E720" s="3">
+        <v>7.526</v>
+      </c>
+      <c r="F720" s="3">
+        <v>8.499</v>
+      </c>
+      <c r="G720" s="3">
+        <v>102.208</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B721" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C721" s="3">
+        <v>113.293</v>
+      </c>
+      <c r="D721" s="3">
+        <v>101.773</v>
+      </c>
+      <c r="E721" s="3">
+        <v>0.717</v>
+      </c>
+      <c r="F721" s="3">
+        <v>11.52</v>
+      </c>
+      <c r="G721" s="3">
+        <v>102.49</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B722" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C722" s="3">
+        <v>99.149</v>
+      </c>
+      <c r="D722" s="3">
+        <v>93.415</v>
+      </c>
+      <c r="E722" s="3">
+        <v>8.397</v>
+      </c>
+      <c r="F722" s="3">
+        <v>5.734</v>
+      </c>
+      <c r="G722" s="3">
+        <v>101.812</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B723" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C723" s="3">
+        <v>76.16</v>
+      </c>
+      <c r="D723" s="3">
+        <v>73.19</v>
+      </c>
+      <c r="E723" s="3">
+        <v>27.75</v>
+      </c>
+      <c r="F723" s="3">
+        <v>2.97</v>
+      </c>
+      <c r="G723" s="3">
+        <v>100.94</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B724" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C724" s="3">
+        <v>102.08</v>
+      </c>
+      <c r="D724" s="3">
+        <v>92.864</v>
+      </c>
+      <c r="E724" s="3">
+        <v>9.114</v>
+      </c>
+      <c r="F724" s="3">
+        <v>9.216</v>
+      </c>
+      <c r="G724" s="3">
+        <v>101.978</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B725" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C725" s="3">
+        <v>96.87</v>
+      </c>
+      <c r="D725" s="3">
+        <v>88.883</v>
+      </c>
+      <c r="E725" s="3">
+        <v>14.182</v>
+      </c>
+      <c r="F725" s="3">
+        <v>7.987</v>
+      </c>
+      <c r="G725" s="3">
+        <v>103.065</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B726" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C726" s="3">
+        <v>89.011</v>
+      </c>
+      <c r="D726" s="3">
+        <v>84.045</v>
+      </c>
+      <c r="E726" s="3">
+        <v>17.408</v>
+      </c>
+      <c r="F726" s="3">
+        <v>4.966</v>
+      </c>
+      <c r="G726" s="3">
+        <v>101.453</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B727" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C727" s="3">
+        <v>89.997</v>
+      </c>
+      <c r="D727" s="3">
+        <v>84.467</v>
+      </c>
+      <c r="E727" s="3">
+        <v>18.227</v>
+      </c>
+      <c r="F727" s="3">
+        <v>5.53</v>
+      </c>
+      <c r="G727" s="3">
+        <v>102.694</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B728" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C728" s="3">
+        <v>82.099</v>
+      </c>
+      <c r="D728" s="3">
+        <v>76.979</v>
+      </c>
+      <c r="E728" s="3">
+        <v>24.986</v>
+      </c>
+      <c r="F728" s="3">
+        <v>5.12</v>
+      </c>
+      <c r="G728" s="3">
+        <v>101.965</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B729" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C729" s="3">
+        <v>63.91</v>
+      </c>
+      <c r="D729" s="3">
+        <v>63.244</v>
+      </c>
+      <c r="E729" s="3">
+        <v>38.042</v>
+      </c>
+      <c r="F729" s="3">
+        <v>0.666</v>
+      </c>
+      <c r="G729" s="3">
+        <v>101.286</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B730" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C730" s="3">
+        <v>112.602</v>
+      </c>
+      <c r="D730" s="3">
+        <v>101.645</v>
+      </c>
+      <c r="E730" s="3">
+        <v>1.434</v>
+      </c>
+      <c r="F730" s="3">
+        <v>10.957</v>
+      </c>
+      <c r="G730" s="3">
+        <v>103.079</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B731" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C731" s="3">
+        <v>104.614</v>
+      </c>
+      <c r="D731" s="3">
+        <v>96.371</v>
+      </c>
+      <c r="E731" s="3">
+        <v>5.427</v>
+      </c>
+      <c r="F731" s="3">
+        <v>8.243</v>
+      </c>
+      <c r="G731" s="3">
+        <v>101.798</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B732" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C732" s="3">
+        <v>84.429</v>
+      </c>
+      <c r="D732" s="3">
+        <v>78.234</v>
+      </c>
+      <c r="E732" s="3">
+        <v>25.6</v>
+      </c>
+      <c r="F732" s="3">
+        <v>6.195</v>
+      </c>
+      <c r="G732" s="3">
+        <v>103.834</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B733" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C733" s="3">
+        <v>115.942</v>
+      </c>
+      <c r="D733" s="3">
+        <v>102.681</v>
+      </c>
+      <c r="E733" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F733" s="3">
+        <v>13.261</v>
+      </c>
+      <c r="G733" s="3">
+        <v>102.681</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B734" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C734" s="3">
+        <v>112.371</v>
+      </c>
+      <c r="D734" s="3">
+        <v>101.875</v>
+      </c>
+      <c r="E734" s="3">
+        <v>0.717</v>
+      </c>
+      <c r="F734" s="3">
+        <v>10.496</v>
+      </c>
+      <c r="G734" s="3">
+        <v>102.592</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B735" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C735" s="3">
+        <v>111.923</v>
+      </c>
+      <c r="D735" s="3">
+        <v>102.553</v>
+      </c>
+      <c r="E735" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F735" s="3">
+        <v>9.37</v>
+      </c>
+      <c r="G735" s="3">
+        <v>102.553</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B736" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C736" s="3">
+        <v>67.43</v>
+      </c>
+      <c r="D736" s="3">
+        <v>63.539</v>
+      </c>
+      <c r="E736" s="3">
+        <v>37.171</v>
+      </c>
+      <c r="F736" s="3">
+        <v>3.891</v>
+      </c>
+      <c r="G736" s="3">
+        <v>100.71</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B737" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C737" s="3">
+        <v>60.429</v>
+      </c>
+      <c r="D737" s="3">
+        <v>58.023</v>
+      </c>
+      <c r="E737" s="3">
+        <v>45.466</v>
+      </c>
+      <c r="F737" s="3">
+        <v>2.406</v>
+      </c>
+      <c r="G737" s="3">
+        <v>103.489</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B738" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C738" s="3">
+        <v>98.509</v>
+      </c>
+      <c r="D738" s="3">
+        <v>97.843</v>
+      </c>
+      <c r="E738" s="3">
+        <v>4.25</v>
+      </c>
+      <c r="F738" s="3">
+        <v>0.666</v>
+      </c>
+      <c r="G738" s="3">
+        <v>102.093</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B739" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C739" s="3">
+        <v>88.742</v>
+      </c>
+      <c r="D739" s="3">
+        <v>88.742</v>
+      </c>
+      <c r="E739" s="3">
+        <v>12.902</v>
+      </c>
+      <c r="F739" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G739" s="3">
+        <v>101.644</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B740" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C740" s="3">
+        <v>79.552</v>
+      </c>
+      <c r="D740" s="3">
+        <v>79.552</v>
+      </c>
+      <c r="E740" s="3">
+        <v>25.088</v>
+      </c>
+      <c r="F740" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G740" s="3">
+        <v>104.64</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B741" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C741" s="3">
+        <v>72.256</v>
+      </c>
+      <c r="D741" s="3">
+        <v>72.256</v>
+      </c>
+      <c r="E741" s="3">
+        <v>29.645</v>
+      </c>
+      <c r="F741" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G741" s="3">
+        <v>101.901</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B742" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C742" s="3">
+        <v>65.408</v>
+      </c>
+      <c r="D742" s="3">
+        <v>65.408</v>
+      </c>
+      <c r="E742" s="3">
+        <v>37.12</v>
+      </c>
+      <c r="F742" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G742" s="3">
+        <v>102.528</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B743" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C743" s="3">
+        <v>58.061</v>
+      </c>
+      <c r="D743" s="3">
+        <v>58.061</v>
+      </c>
+      <c r="E743" s="3">
+        <v>44.442</v>
+      </c>
+      <c r="F743" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G743" s="3">
+        <v>102.503</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B744" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C744" s="3">
+        <v>47.334</v>
+      </c>
+      <c r="D744" s="3">
+        <v>47.334</v>
+      </c>
+      <c r="E744" s="3">
+        <v>45.517</v>
+      </c>
+      <c r="F744" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G744" s="3">
+        <v>92.851</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B745" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C745" s="3">
+        <v>32.55</v>
+      </c>
+      <c r="D745" s="3">
+        <v>32.55</v>
+      </c>
+      <c r="E745" s="3">
+        <v>36.403</v>
+      </c>
+      <c r="F745" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G745" s="3">
+        <v>68.953</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B746" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C746" s="3">
+        <v>27.149</v>
+      </c>
+      <c r="D746" s="3">
+        <v>27.149</v>
+      </c>
+      <c r="E746" s="3">
+        <v>41.677</v>
+      </c>
+      <c r="F746" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G746" s="3">
+        <v>68.826</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B747" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C747" s="3">
+        <v>18.765</v>
+      </c>
+      <c r="D747" s="3">
+        <v>18.765</v>
+      </c>
+      <c r="E747" s="3">
+        <v>49.971</v>
+      </c>
+      <c r="F747" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G747" s="3">
+        <v>68.736</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B748" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C748" s="3">
+        <v>11.29</v>
+      </c>
+      <c r="D748" s="3">
+        <v>11.29</v>
+      </c>
+      <c r="E748" s="3">
+        <v>57.498</v>
+      </c>
+      <c r="F748" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G748" s="3">
+        <v>68.788</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B749" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C749" s="3">
+        <v>5.619</v>
+      </c>
+      <c r="D749" s="3">
+        <v>5.619</v>
+      </c>
+      <c r="E749" s="3">
+        <v>63.232</v>
+      </c>
+      <c r="F749" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G749" s="3">
+        <v>68.851</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B750" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C750" s="3">
+        <v>1.754</v>
+      </c>
+      <c r="D750" s="3">
+        <v>1.754</v>
+      </c>
+      <c r="E750" s="3">
+        <v>66.714</v>
+      </c>
+      <c r="F750" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G750" s="3">
+        <v>68.468</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B751" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C751" s="3">
+        <v>0.218</v>
+      </c>
+      <c r="D751" s="3">
+        <v>0.218</v>
+      </c>
+      <c r="E751" s="3">
+        <v>68.403</v>
+      </c>
+      <c r="F751" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G751" s="3">
+        <v>68.621</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B752" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C752" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D752" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E752" s="3">
+        <v>68.71</v>
+      </c>
+      <c r="F752" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G752" s="3">
+        <v>68.71</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B753" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C753" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D753" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E753" s="3">
+        <v>68.659</v>
+      </c>
+      <c r="F753" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G753" s="3">
+        <v>68.659</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B754" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C754" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D754" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E754" s="3">
+        <v>68.762</v>
+      </c>
+      <c r="F754" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G754" s="3">
+        <v>68.762</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B755" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C755" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D755" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E755" s="3">
+        <v>68.608</v>
+      </c>
+      <c r="F755" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G755" s="3">
+        <v>68.608</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B756" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C756" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D756" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E756" s="3">
+        <v>68.506</v>
+      </c>
+      <c r="F756" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G756" s="3">
+        <v>68.506</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B757" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C757" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D757" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E757" s="3">
+        <v>68.659</v>
+      </c>
+      <c r="F757" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G757" s="3">
+        <v>68.659</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B758" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C758" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D758" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E758" s="3">
+        <v>69.069</v>
+      </c>
+      <c r="F758" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G758" s="3">
+        <v>69.069</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B759" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C759" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D759" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E759" s="3">
+        <v>68.966</v>
+      </c>
+      <c r="F759" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G759" s="3">
+        <v>68.966</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B760" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C760" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D760" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E760" s="3">
+        <v>68.915</v>
+      </c>
+      <c r="F760" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G760" s="3">
+        <v>68.915</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B761" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C761" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D761" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E761" s="3">
+        <v>68.608</v>
+      </c>
+      <c r="F761" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G761" s="3">
+        <v>68.608</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B762" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C762" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D762" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E762" s="3">
+        <v>68.71</v>
+      </c>
+      <c r="F762" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G762" s="3">
+        <v>68.71</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B763" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C763" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D763" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E763" s="3">
+        <v>69.018</v>
+      </c>
+      <c r="F763" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G763" s="3">
+        <v>69.018</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B764" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C764" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D764" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E764" s="3">
+        <v>70.246</v>
+      </c>
+      <c r="F764" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G764" s="3">
+        <v>70.246</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B765" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C765" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D765" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E765" s="3">
+        <v>71.731</v>
+      </c>
+      <c r="F765" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G765" s="3">
+        <v>71.731</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B766" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C766" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D766" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E766" s="3">
+        <v>71.629</v>
+      </c>
+      <c r="F766" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G766" s="3">
+        <v>71.629</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B767" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C767" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D767" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E767" s="3">
+        <v>71.526</v>
+      </c>
+      <c r="F767" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G767" s="3">
+        <v>71.526</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B768" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C768" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D768" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E768" s="3">
+        <v>71.526</v>
+      </c>
+      <c r="F768" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G768" s="3">
+        <v>71.526</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B769" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C769" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D769" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E769" s="3">
+        <v>71.373</v>
+      </c>
+      <c r="F769" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G769" s="3">
+        <v>71.373</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G673"/>
+  <autoFilter ref="A1:G769"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -334,45 +334,69 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B13" s="4">
+        <v>1964.0</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1595.6</v>
+      </c>
+      <c r="D13" s="4">
+        <v>7909.7</v>
+      </c>
+      <c r="E13" s="4">
+        <v>368.4</v>
+      </c>
+      <c r="F13" s="4">
+        <v>9505.3</v>
+      </c>
+      <c r="G13" s="5">
+        <f>IF(F13&gt;0,C13/F13,"")</f>
+        <v>0.1679</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B13" s="7">
-        <f>SUM(B5:B12)</f>
-        <v>21763.0</v>
-      </c>
-      <c r="C13" s="7">
-        <f>SUM(C5:C12)</f>
-        <v>18987.2</v>
-      </c>
-      <c r="D13" s="7">
-        <f>SUM(D5:D12)</f>
-        <v>54801.8</v>
-      </c>
-      <c r="E13" s="7">
-        <f>SUM(E5:E12)</f>
-        <v>2775.9</v>
-      </c>
-      <c r="F13" s="7">
-        <f>SUM(F5:F12)</f>
-        <v>73789.0</v>
-      </c>
-      <c r="G13" s="8">
-        <f>IF(F13&gt;0,C13/F13,"")</f>
-        <v>0.2573</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B14" s="7">
+        <f>SUM(B5:B13)</f>
+        <v>23727.1</v>
+      </c>
+      <c r="C14" s="7">
+        <f>SUM(C5:C13)</f>
+        <v>20582.8</v>
+      </c>
+      <c r="D14" s="7">
+        <f>SUM(D5:D13)</f>
+        <v>62711.5</v>
+      </c>
+      <c r="E14" s="7">
+        <f>SUM(E5:E13)</f>
+        <v>3144.3</v>
+      </c>
+      <c r="F14" s="7">
+        <f>SUM(F5:F13)</f>
+        <v>83294.3</v>
+      </c>
+      <c r="G14" s="8">
+        <f>IF(F14&gt;0,C14/F14,"")</f>
+        <v>0.2471</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -19631,7 +19655,2407 @@
         <v>71.373</v>
       </c>
     </row>
+    <row r="770">
+      <c r="A770" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B770" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C770" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D770" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E770" s="3">
+        <v>71.526</v>
+      </c>
+      <c r="F770" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G770" s="3">
+        <v>71.526</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B771" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C771" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D771" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E771" s="3">
+        <v>71.475</v>
+      </c>
+      <c r="F771" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G771" s="3">
+        <v>71.475</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B772" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C772" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D772" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E772" s="3">
+        <v>72.294</v>
+      </c>
+      <c r="F772" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G772" s="3">
+        <v>72.294</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B773" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C773" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D773" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E773" s="3">
+        <v>72.499</v>
+      </c>
+      <c r="F773" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G773" s="3">
+        <v>72.499</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B774" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C774" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D774" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E774" s="3">
+        <v>71.629</v>
+      </c>
+      <c r="F774" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G774" s="3">
+        <v>71.629</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B775" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C775" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D775" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E775" s="3">
+        <v>71.424</v>
+      </c>
+      <c r="F775" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G775" s="3">
+        <v>71.424</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B776" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C776" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D776" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E776" s="3">
+        <v>71.629</v>
+      </c>
+      <c r="F776" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G776" s="3">
+        <v>71.629</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B777" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C777" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D777" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E777" s="3">
+        <v>71.27</v>
+      </c>
+      <c r="F777" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G777" s="3">
+        <v>71.27</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B778" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C778" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D778" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E778" s="3">
+        <v>71.322</v>
+      </c>
+      <c r="F778" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G778" s="3">
+        <v>71.322</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B779" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C779" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D779" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E779" s="3">
+        <v>71.629</v>
+      </c>
+      <c r="F779" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G779" s="3">
+        <v>71.629</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B780" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C780" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D780" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E780" s="3">
+        <v>72.09</v>
+      </c>
+      <c r="F780" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G780" s="3">
+        <v>72.09</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B781" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C781" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D781" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E781" s="3">
+        <v>71.373</v>
+      </c>
+      <c r="F781" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G781" s="3">
+        <v>71.373</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B782" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C782" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D782" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E782" s="3">
+        <v>71.322</v>
+      </c>
+      <c r="F782" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G782" s="3">
+        <v>71.322</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B783" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C783" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D783" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E783" s="3">
+        <v>71.322</v>
+      </c>
+      <c r="F783" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G783" s="3">
+        <v>71.322</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B784" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C784" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D784" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E784" s="3">
+        <v>71.578</v>
+      </c>
+      <c r="F784" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G784" s="3">
+        <v>71.578</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B785" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C785" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D785" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E785" s="3">
+        <v>71.322</v>
+      </c>
+      <c r="F785" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G785" s="3">
+        <v>71.322</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B786" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C786" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D786" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E786" s="3">
+        <v>71.322</v>
+      </c>
+      <c r="F786" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G786" s="3">
+        <v>71.322</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B787" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C787" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D787" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E787" s="3">
+        <v>71.629</v>
+      </c>
+      <c r="F787" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G787" s="3">
+        <v>71.629</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B788" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C788" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D788" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E788" s="3">
+        <v>71.526</v>
+      </c>
+      <c r="F788" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G788" s="3">
+        <v>71.526</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B789" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C789" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D789" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E789" s="3">
+        <v>71.322</v>
+      </c>
+      <c r="F789" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G789" s="3">
+        <v>71.322</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B790" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C790" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D790" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E790" s="3">
+        <v>71.373</v>
+      </c>
+      <c r="F790" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G790" s="3">
+        <v>71.373</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B791" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C791" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D791" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E791" s="3">
+        <v>71.578</v>
+      </c>
+      <c r="F791" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G791" s="3">
+        <v>71.578</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B792" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C792" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D792" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E792" s="3">
+        <v>71.68</v>
+      </c>
+      <c r="F792" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G792" s="3">
+        <v>71.68</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B793" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C793" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D793" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E793" s="3">
+        <v>71.68</v>
+      </c>
+      <c r="F793" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G793" s="3">
+        <v>71.68</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B794" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C794" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D794" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E794" s="3">
+        <v>71.885</v>
+      </c>
+      <c r="F794" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G794" s="3">
+        <v>71.885</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B795" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C795" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D795" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E795" s="3">
+        <v>71.629</v>
+      </c>
+      <c r="F795" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G795" s="3">
+        <v>71.629</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B796" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C796" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D796" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E796" s="3">
+        <v>71.424</v>
+      </c>
+      <c r="F796" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G796" s="3">
+        <v>71.424</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B797" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C797" s="3">
+        <v>0.026</v>
+      </c>
+      <c r="D797" s="3">
+        <v>0.026</v>
+      </c>
+      <c r="E797" s="3">
+        <v>71.629</v>
+      </c>
+      <c r="F797" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G797" s="3">
+        <v>71.655</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B798" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C798" s="3">
+        <v>0.538</v>
+      </c>
+      <c r="D798" s="3">
+        <v>0.538</v>
+      </c>
+      <c r="E798" s="3">
+        <v>70.758</v>
+      </c>
+      <c r="F798" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G798" s="3">
+        <v>71.296</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B799" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C799" s="3">
+        <v>2.445</v>
+      </c>
+      <c r="D799" s="3">
+        <v>2.445</v>
+      </c>
+      <c r="E799" s="3">
+        <v>68.966</v>
+      </c>
+      <c r="F799" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G799" s="3">
+        <v>71.411</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B800" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C800" s="3">
+        <v>3.981</v>
+      </c>
+      <c r="D800" s="3">
+        <v>3.981</v>
+      </c>
+      <c r="E800" s="3">
+        <v>68.403</v>
+      </c>
+      <c r="F800" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G800" s="3">
+        <v>72.384</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B801" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C801" s="3">
+        <v>13.363</v>
+      </c>
+      <c r="D801" s="3">
+        <v>13.363</v>
+      </c>
+      <c r="E801" s="3">
+        <v>86.118</v>
+      </c>
+      <c r="F801" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G801" s="3">
+        <v>99.481</v>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B802" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C802" s="3">
+        <v>8.602</v>
+      </c>
+      <c r="D802" s="3">
+        <v>8.602</v>
+      </c>
+      <c r="E802" s="3">
+        <v>96.102</v>
+      </c>
+      <c r="F802" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G802" s="3">
+        <v>104.704</v>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B803" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C803" s="3">
+        <v>13.274</v>
+      </c>
+      <c r="D803" s="3">
+        <v>13.274</v>
+      </c>
+      <c r="E803" s="3">
+        <v>91.546</v>
+      </c>
+      <c r="F803" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G803" s="3">
+        <v>104.82</v>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B804" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C804" s="3">
+        <v>24.474</v>
+      </c>
+      <c r="D804" s="3">
+        <v>24.474</v>
+      </c>
+      <c r="E804" s="3">
+        <v>80.64</v>
+      </c>
+      <c r="F804" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G804" s="3">
+        <v>105.114</v>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B805" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C805" s="3">
+        <v>33.613</v>
+      </c>
+      <c r="D805" s="3">
+        <v>33.613</v>
+      </c>
+      <c r="E805" s="3">
+        <v>71.014</v>
+      </c>
+      <c r="F805" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G805" s="3">
+        <v>104.627</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B806" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C806" s="3">
+        <v>21.798</v>
+      </c>
+      <c r="D806" s="3">
+        <v>21.798</v>
+      </c>
+      <c r="E806" s="3">
+        <v>83.405</v>
+      </c>
+      <c r="F806" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G806" s="3">
+        <v>105.203</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B807" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C807" s="3">
+        <v>41.818</v>
+      </c>
+      <c r="D807" s="3">
+        <v>41.818</v>
+      </c>
+      <c r="E807" s="3">
+        <v>63.898</v>
+      </c>
+      <c r="F807" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G807" s="3">
+        <v>105.716</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B808" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C808" s="3">
+        <v>64.768</v>
+      </c>
+      <c r="D808" s="3">
+        <v>64.768</v>
+      </c>
+      <c r="E808" s="3">
+        <v>40.243</v>
+      </c>
+      <c r="F808" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G808" s="3">
+        <v>105.011</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B809" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C809" s="3">
+        <v>46.067</v>
+      </c>
+      <c r="D809" s="3">
+        <v>46.067</v>
+      </c>
+      <c r="E809" s="3">
+        <v>58.675</v>
+      </c>
+      <c r="F809" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G809" s="3">
+        <v>104.742</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B810" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C810" s="3">
+        <v>36.429</v>
+      </c>
+      <c r="D810" s="3">
+        <v>36.429</v>
+      </c>
+      <c r="E810" s="3">
+        <v>68.25</v>
+      </c>
+      <c r="F810" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G810" s="3">
+        <v>104.679</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B811" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C811" s="3">
+        <v>28.467</v>
+      </c>
+      <c r="D811" s="3">
+        <v>19.661</v>
+      </c>
+      <c r="E811" s="3">
+        <v>28.058</v>
+      </c>
+      <c r="F811" s="3">
+        <v>8.806</v>
+      </c>
+      <c r="G811" s="3">
+        <v>47.719</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B812" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C812" s="3">
+        <v>80.96</v>
+      </c>
+      <c r="D812" s="3">
+        <v>9.485</v>
+      </c>
+      <c r="E812" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F812" s="3">
+        <v>71.475</v>
+      </c>
+      <c r="G812" s="3">
+        <v>9.485</v>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B813" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C813" s="3">
+        <v>48.192</v>
+      </c>
+      <c r="D813" s="3">
+        <v>8.358</v>
+      </c>
+      <c r="E813" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F813" s="3">
+        <v>39.834</v>
+      </c>
+      <c r="G813" s="3">
+        <v>8.358</v>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B814" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C814" s="3">
+        <v>90.829</v>
+      </c>
+      <c r="D814" s="3">
+        <v>9.831</v>
+      </c>
+      <c r="E814" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F814" s="3">
+        <v>80.998</v>
+      </c>
+      <c r="G814" s="3">
+        <v>9.831</v>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B815" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C815" s="3">
+        <v>66.752</v>
+      </c>
+      <c r="D815" s="3">
+        <v>6.438</v>
+      </c>
+      <c r="E815" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F815" s="3">
+        <v>60.314</v>
+      </c>
+      <c r="G815" s="3">
+        <v>6.438</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B816" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C816" s="3">
+        <v>76.198</v>
+      </c>
+      <c r="D816" s="3">
+        <v>38.156</v>
+      </c>
+      <c r="E816" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F816" s="3">
+        <v>38.042</v>
+      </c>
+      <c r="G816" s="3">
+        <v>38.156</v>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B817" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C817" s="3">
+        <v>59.149</v>
+      </c>
+      <c r="D817" s="3">
+        <v>38.362</v>
+      </c>
+      <c r="E817" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F817" s="3">
+        <v>20.787</v>
+      </c>
+      <c r="G817" s="3">
+        <v>38.362</v>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B818" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C818" s="3">
+        <v>59.008</v>
+      </c>
+      <c r="D818" s="3">
+        <v>43.392</v>
+      </c>
+      <c r="E818" s="3">
+        <v>0.154</v>
+      </c>
+      <c r="F818" s="3">
+        <v>15.616</v>
+      </c>
+      <c r="G818" s="3">
+        <v>43.546</v>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B819" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C819" s="3">
+        <v>92.57</v>
+      </c>
+      <c r="D819" s="3">
+        <v>70.503</v>
+      </c>
+      <c r="E819" s="3">
+        <v>0.512</v>
+      </c>
+      <c r="F819" s="3">
+        <v>22.067</v>
+      </c>
+      <c r="G819" s="3">
+        <v>71.015</v>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B820" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C820" s="3">
+        <v>70.272</v>
+      </c>
+      <c r="D820" s="3">
+        <v>69.862</v>
+      </c>
+      <c r="E820" s="3">
+        <v>30.515</v>
+      </c>
+      <c r="F820" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="G820" s="3">
+        <v>100.377</v>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B821" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C821" s="3">
+        <v>83.174</v>
+      </c>
+      <c r="D821" s="3">
+        <v>82.457</v>
+      </c>
+      <c r="E821" s="3">
+        <v>21.862</v>
+      </c>
+      <c r="F821" s="3">
+        <v>0.717</v>
+      </c>
+      <c r="G821" s="3">
+        <v>104.319</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B822" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C822" s="3">
+        <v>48.768</v>
+      </c>
+      <c r="D822" s="3">
+        <v>48.768</v>
+      </c>
+      <c r="E822" s="3">
+        <v>55.398</v>
+      </c>
+      <c r="F822" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G822" s="3">
+        <v>104.166</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B823" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C823" s="3">
+        <v>54.349</v>
+      </c>
+      <c r="D823" s="3">
+        <v>54.349</v>
+      </c>
+      <c r="E823" s="3">
+        <v>48.998</v>
+      </c>
+      <c r="F823" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G823" s="3">
+        <v>103.347</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B824" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C824" s="3">
+        <v>37.901</v>
+      </c>
+      <c r="D824" s="3">
+        <v>37.901</v>
+      </c>
+      <c r="E824" s="3">
+        <v>66.509</v>
+      </c>
+      <c r="F824" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G824" s="3">
+        <v>104.41</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B825" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C825" s="3">
+        <v>87.232</v>
+      </c>
+      <c r="D825" s="3">
+        <v>84.416</v>
+      </c>
+      <c r="E825" s="3">
+        <v>20.531</v>
+      </c>
+      <c r="F825" s="3">
+        <v>2.816</v>
+      </c>
+      <c r="G825" s="3">
+        <v>104.947</v>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B826" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C826" s="3">
+        <v>60.198</v>
+      </c>
+      <c r="D826" s="3">
+        <v>59.993</v>
+      </c>
+      <c r="E826" s="3">
+        <v>43.213</v>
+      </c>
+      <c r="F826" s="3">
+        <v>0.205</v>
+      </c>
+      <c r="G826" s="3">
+        <v>103.206</v>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B827" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C827" s="3">
+        <v>51.098</v>
+      </c>
+      <c r="D827" s="3">
+        <v>50.996</v>
+      </c>
+      <c r="E827" s="3">
+        <v>51.814</v>
+      </c>
+      <c r="F827" s="3">
+        <v>0.102</v>
+      </c>
+      <c r="G827" s="3">
+        <v>102.81</v>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B828" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C828" s="3">
+        <v>40.102</v>
+      </c>
+      <c r="D828" s="3">
+        <v>40.102</v>
+      </c>
+      <c r="E828" s="3">
+        <v>62.771</v>
+      </c>
+      <c r="F828" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G828" s="3">
+        <v>102.873</v>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B829" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C829" s="3">
+        <v>60.979</v>
+      </c>
+      <c r="D829" s="3">
+        <v>60.109</v>
+      </c>
+      <c r="E829" s="3">
+        <v>43.52</v>
+      </c>
+      <c r="F829" s="3">
+        <v>0.87</v>
+      </c>
+      <c r="G829" s="3">
+        <v>103.629</v>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B830" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C830" s="3">
+        <v>88.717</v>
+      </c>
+      <c r="D830" s="3">
+        <v>83.341</v>
+      </c>
+      <c r="E830" s="3">
+        <v>18.534</v>
+      </c>
+      <c r="F830" s="3">
+        <v>5.376</v>
+      </c>
+      <c r="G830" s="3">
+        <v>101.875</v>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B831" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C831" s="3">
+        <v>36.928</v>
+      </c>
+      <c r="D831" s="3">
+        <v>36.928</v>
+      </c>
+      <c r="E831" s="3">
+        <v>65.434</v>
+      </c>
+      <c r="F831" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G831" s="3">
+        <v>102.362</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B832" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C832" s="3">
+        <v>38.285</v>
+      </c>
+      <c r="D832" s="3">
+        <v>38.285</v>
+      </c>
+      <c r="E832" s="3">
+        <v>73.062</v>
+      </c>
+      <c r="F832" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G832" s="3">
+        <v>111.347</v>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B833" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C833" s="3">
+        <v>30.95</v>
+      </c>
+      <c r="D833" s="3">
+        <v>30.95</v>
+      </c>
+      <c r="E833" s="3">
+        <v>105.421</v>
+      </c>
+      <c r="F833" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G833" s="3">
+        <v>136.371</v>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B834" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C834" s="3">
+        <v>32.768</v>
+      </c>
+      <c r="D834" s="3">
+        <v>32.768</v>
+      </c>
+      <c r="E834" s="3">
+        <v>103.526</v>
+      </c>
+      <c r="F834" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G834" s="3">
+        <v>136.294</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B835" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C835" s="3">
+        <v>36.352</v>
+      </c>
+      <c r="D835" s="3">
+        <v>36.352</v>
+      </c>
+      <c r="E835" s="3">
+        <v>100.045</v>
+      </c>
+      <c r="F835" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G835" s="3">
+        <v>136.397</v>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B836" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C836" s="3">
+        <v>28.659</v>
+      </c>
+      <c r="D836" s="3">
+        <v>28.659</v>
+      </c>
+      <c r="E836" s="3">
+        <v>107.52</v>
+      </c>
+      <c r="F836" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G836" s="3">
+        <v>136.179</v>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B837" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C837" s="3">
+        <v>27.085</v>
+      </c>
+      <c r="D837" s="3">
+        <v>27.085</v>
+      </c>
+      <c r="E837" s="3">
+        <v>110.643</v>
+      </c>
+      <c r="F837" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G837" s="3">
+        <v>137.728</v>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B838" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C838" s="3">
+        <v>28.403</v>
+      </c>
+      <c r="D838" s="3">
+        <v>28.403</v>
+      </c>
+      <c r="E838" s="3">
+        <v>141.363</v>
+      </c>
+      <c r="F838" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G838" s="3">
+        <v>169.766</v>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B839" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C839" s="3">
+        <v>31.206</v>
+      </c>
+      <c r="D839" s="3">
+        <v>31.206</v>
+      </c>
+      <c r="E839" s="3">
+        <v>138.701</v>
+      </c>
+      <c r="F839" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G839" s="3">
+        <v>169.907</v>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B840" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C840" s="3">
+        <v>25.088</v>
+      </c>
+      <c r="D840" s="3">
+        <v>25.088</v>
+      </c>
+      <c r="E840" s="3">
+        <v>141.21</v>
+      </c>
+      <c r="F840" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G840" s="3">
+        <v>166.298</v>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B841" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C841" s="3">
+        <v>20.582</v>
+      </c>
+      <c r="D841" s="3">
+        <v>20.582</v>
+      </c>
+      <c r="E841" s="3">
+        <v>116.48</v>
+      </c>
+      <c r="F841" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G841" s="3">
+        <v>137.062</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B842" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C842" s="3">
+        <v>13.222</v>
+      </c>
+      <c r="D842" s="3">
+        <v>13.222</v>
+      </c>
+      <c r="E842" s="3">
+        <v>123.955</v>
+      </c>
+      <c r="F842" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G842" s="3">
+        <v>137.177</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B843" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C843" s="3">
+        <v>7.194</v>
+      </c>
+      <c r="D843" s="3">
+        <v>7.194</v>
+      </c>
+      <c r="E843" s="3">
+        <v>129.997</v>
+      </c>
+      <c r="F843" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G843" s="3">
+        <v>137.191</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B844" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C844" s="3">
+        <v>5.056</v>
+      </c>
+      <c r="D844" s="3">
+        <v>5.056</v>
+      </c>
+      <c r="E844" s="3">
+        <v>131.738</v>
+      </c>
+      <c r="F844" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G844" s="3">
+        <v>136.794</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B845" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C845" s="3">
+        <v>4.557</v>
+      </c>
+      <c r="D845" s="3">
+        <v>4.557</v>
+      </c>
+      <c r="E845" s="3">
+        <v>132.454</v>
+      </c>
+      <c r="F845" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G845" s="3">
+        <v>137.011</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B846" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C846" s="3">
+        <v>1.242</v>
+      </c>
+      <c r="D846" s="3">
+        <v>1.242</v>
+      </c>
+      <c r="E846" s="3">
+        <v>136.243</v>
+      </c>
+      <c r="F846" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G846" s="3">
+        <v>137.485</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B847" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C847" s="3">
+        <v>0.333</v>
+      </c>
+      <c r="D847" s="3">
+        <v>0.333</v>
+      </c>
+      <c r="E847" s="3">
+        <v>136.806</v>
+      </c>
+      <c r="F847" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G847" s="3">
+        <v>137.139</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B848" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C848" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D848" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E848" s="3">
+        <v>137.421</v>
+      </c>
+      <c r="F848" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G848" s="3">
+        <v>137.421</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B849" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C849" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D849" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E849" s="3">
+        <v>137.933</v>
+      </c>
+      <c r="F849" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G849" s="3">
+        <v>137.933</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B850" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C850" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D850" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E850" s="3">
+        <v>137.779</v>
+      </c>
+      <c r="F850" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G850" s="3">
+        <v>137.779</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B851" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C851" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D851" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E851" s="3">
+        <v>137.574</v>
+      </c>
+      <c r="F851" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G851" s="3">
+        <v>137.574</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B852" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C852" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D852" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E852" s="3">
+        <v>137.011</v>
+      </c>
+      <c r="F852" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G852" s="3">
+        <v>137.011</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B853" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C853" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D853" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E853" s="3">
+        <v>136.806</v>
+      </c>
+      <c r="F853" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G853" s="3">
+        <v>136.806</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B854" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C854" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D854" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E854" s="3">
+        <v>137.318</v>
+      </c>
+      <c r="F854" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G854" s="3">
+        <v>137.318</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B855" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C855" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D855" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E855" s="3">
+        <v>137.216</v>
+      </c>
+      <c r="F855" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G855" s="3">
+        <v>137.216</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B856" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C856" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D856" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E856" s="3">
+        <v>136.755</v>
+      </c>
+      <c r="F856" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G856" s="3">
+        <v>136.755</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B857" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C857" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D857" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E857" s="3">
+        <v>136.909</v>
+      </c>
+      <c r="F857" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G857" s="3">
+        <v>136.909</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B858" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C858" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D858" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E858" s="3">
+        <v>137.37</v>
+      </c>
+      <c r="F858" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G858" s="3">
+        <v>137.37</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B859" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C859" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D859" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E859" s="3">
+        <v>137.062</v>
+      </c>
+      <c r="F859" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G859" s="3">
+        <v>137.062</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B860" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C860" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D860" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E860" s="3">
+        <v>137.626</v>
+      </c>
+      <c r="F860" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G860" s="3">
+        <v>137.626</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B861" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C861" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D861" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E861" s="3">
+        <v>137.421</v>
+      </c>
+      <c r="F861" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G861" s="3">
+        <v>137.421</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B862" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C862" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D862" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E862" s="3">
+        <v>136.909</v>
+      </c>
+      <c r="F862" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G862" s="3">
+        <v>136.909</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B863" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C863" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D863" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E863" s="3">
+        <v>136.858</v>
+      </c>
+      <c r="F863" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G863" s="3">
+        <v>136.858</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B864" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C864" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D864" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E864" s="3">
+        <v>137.062</v>
+      </c>
+      <c r="F864" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G864" s="3">
+        <v>137.062</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="2">
+        <v>46304</v>
+      </c>
+      <c r="B865" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C865" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D865" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E865" s="3">
+        <v>137.267</v>
+      </c>
+      <c r="F865" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G865" s="3">
+        <v>137.267</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G769"/>
+  <autoFilter ref="A1:G865"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -358,45 +358,69 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B14" s="4">
+        <v>2235.1</v>
+      </c>
+      <c r="C14" s="4">
+        <v>2235.1</v>
+      </c>
+      <c r="D14" s="4">
+        <v>12165.5</v>
+      </c>
+      <c r="E14" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="4">
+        <v>14400.6</v>
+      </c>
+      <c r="G14" s="5">
+        <f>IF(F14&gt;0,C14/F14,"")</f>
+        <v>0.1552</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B14" s="7">
-        <f>SUM(B5:B13)</f>
-        <v>23727.1</v>
-      </c>
-      <c r="C14" s="7">
-        <f>SUM(C5:C13)</f>
-        <v>20582.8</v>
-      </c>
-      <c r="D14" s="7">
-        <f>SUM(D5:D13)</f>
-        <v>62711.5</v>
-      </c>
-      <c r="E14" s="7">
-        <f>SUM(E5:E13)</f>
+      <c r="B15" s="7">
+        <f>SUM(B5:B14)</f>
+        <v>25962.1</v>
+      </c>
+      <c r="C15" s="7">
+        <f>SUM(C5:C14)</f>
+        <v>22817.8</v>
+      </c>
+      <c r="D15" s="7">
+        <f>SUM(D5:D14)</f>
+        <v>74877.0</v>
+      </c>
+      <c r="E15" s="7">
+        <f>SUM(E5:E14)</f>
         <v>3144.3</v>
       </c>
-      <c r="F14" s="7">
-        <f>SUM(F5:F13)</f>
-        <v>83294.3</v>
-      </c>
-      <c r="G14" s="8">
-        <f>IF(F14&gt;0,C14/F14,"")</f>
-        <v>0.2471</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="F15" s="7">
+        <f>SUM(F5:F14)</f>
+        <v>97694.8</v>
+      </c>
+      <c r="G15" s="8">
+        <f>IF(F15&gt;0,C15/F15,"")</f>
+        <v>0.2336</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -22055,7 +22079,2407 @@
         <v>137.267</v>
       </c>
     </row>
+    <row r="866">
+      <c r="A866" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B866" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C866" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D866" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E866" s="3">
+        <v>137.421</v>
+      </c>
+      <c r="F866" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G866" s="3">
+        <v>137.421</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B867" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C867" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D867" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E867" s="3">
+        <v>137.472</v>
+      </c>
+      <c r="F867" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G867" s="3">
+        <v>137.472</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B868" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C868" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D868" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E868" s="3">
+        <v>137.062</v>
+      </c>
+      <c r="F868" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G868" s="3">
+        <v>137.062</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B869" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C869" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D869" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E869" s="3">
+        <v>137.165</v>
+      </c>
+      <c r="F869" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G869" s="3">
+        <v>137.165</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B870" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C870" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D870" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E870" s="3">
+        <v>139.264</v>
+      </c>
+      <c r="F870" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G870" s="3">
+        <v>139.264</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B871" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C871" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D871" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E871" s="3">
+        <v>139.878</v>
+      </c>
+      <c r="F871" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G871" s="3">
+        <v>139.878</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B872" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C872" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D872" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E872" s="3">
+        <v>139.93</v>
+      </c>
+      <c r="F872" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G872" s="3">
+        <v>139.93</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B873" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C873" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D873" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E873" s="3">
+        <v>140.544</v>
+      </c>
+      <c r="F873" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G873" s="3">
+        <v>140.544</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B874" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C874" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D874" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E874" s="3">
+        <v>139.827</v>
+      </c>
+      <c r="F874" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G874" s="3">
+        <v>139.827</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B875" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C875" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D875" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E875" s="3">
+        <v>139.827</v>
+      </c>
+      <c r="F875" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G875" s="3">
+        <v>139.827</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B876" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C876" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D876" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E876" s="3">
+        <v>139.93</v>
+      </c>
+      <c r="F876" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G876" s="3">
+        <v>139.93</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B877" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C877" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D877" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E877" s="3">
+        <v>140.032</v>
+      </c>
+      <c r="F877" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G877" s="3">
+        <v>140.032</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B878" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C878" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D878" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E878" s="3">
+        <v>139.469</v>
+      </c>
+      <c r="F878" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G878" s="3">
+        <v>139.469</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B879" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C879" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D879" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E879" s="3">
+        <v>139.469</v>
+      </c>
+      <c r="F879" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G879" s="3">
+        <v>139.469</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B880" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C880" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D880" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E880" s="3">
+        <v>139.827</v>
+      </c>
+      <c r="F880" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G880" s="3">
+        <v>139.827</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B881" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C881" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D881" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E881" s="3">
+        <v>139.776</v>
+      </c>
+      <c r="F881" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G881" s="3">
+        <v>139.776</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B882" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C882" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D882" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E882" s="3">
+        <v>139.622</v>
+      </c>
+      <c r="F882" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G882" s="3">
+        <v>139.622</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B883" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C883" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D883" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E883" s="3">
+        <v>139.571</v>
+      </c>
+      <c r="F883" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G883" s="3">
+        <v>139.571</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B884" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C884" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D884" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E884" s="3">
+        <v>139.622</v>
+      </c>
+      <c r="F884" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G884" s="3">
+        <v>139.622</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B885" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C885" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D885" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E885" s="3">
+        <v>139.93</v>
+      </c>
+      <c r="F885" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G885" s="3">
+        <v>139.93</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B886" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C886" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D886" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E886" s="3">
+        <v>139.981</v>
+      </c>
+      <c r="F886" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G886" s="3">
+        <v>139.981</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B887" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C887" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D887" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E887" s="3">
+        <v>139.674</v>
+      </c>
+      <c r="F887" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G887" s="3">
+        <v>139.674</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B888" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C888" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D888" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E888" s="3">
+        <v>140.39</v>
+      </c>
+      <c r="F888" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G888" s="3">
+        <v>140.39</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B889" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C889" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D889" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E889" s="3">
+        <v>140.493</v>
+      </c>
+      <c r="F889" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G889" s="3">
+        <v>140.493</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B890" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C890" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D890" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E890" s="3">
+        <v>139.776</v>
+      </c>
+      <c r="F890" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G890" s="3">
+        <v>139.776</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B891" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C891" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D891" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E891" s="3">
+        <v>139.878</v>
+      </c>
+      <c r="F891" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G891" s="3">
+        <v>139.878</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B892" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C892" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D892" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E892" s="3">
+        <v>140.288</v>
+      </c>
+      <c r="F892" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G892" s="3">
+        <v>140.288</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B893" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C893" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="D893" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="E893" s="3">
+        <v>140.595</v>
+      </c>
+      <c r="F893" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G893" s="3">
+        <v>140.608</v>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B894" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C894" s="3">
+        <v>0.371</v>
+      </c>
+      <c r="D894" s="3">
+        <v>0.371</v>
+      </c>
+      <c r="E894" s="3">
+        <v>139.366</v>
+      </c>
+      <c r="F894" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G894" s="3">
+        <v>139.737</v>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B895" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C895" s="3">
+        <v>2.227</v>
+      </c>
+      <c r="D895" s="3">
+        <v>2.227</v>
+      </c>
+      <c r="E895" s="3">
+        <v>137.421</v>
+      </c>
+      <c r="F895" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G895" s="3">
+        <v>139.648</v>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B896" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C896" s="3">
+        <v>4.147</v>
+      </c>
+      <c r="D896" s="3">
+        <v>4.147</v>
+      </c>
+      <c r="E896" s="3">
+        <v>135.578</v>
+      </c>
+      <c r="F896" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G896" s="3">
+        <v>139.725</v>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B897" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C897" s="3">
+        <v>7.872</v>
+      </c>
+      <c r="D897" s="3">
+        <v>7.872</v>
+      </c>
+      <c r="E897" s="3">
+        <v>131.84</v>
+      </c>
+      <c r="F897" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G897" s="3">
+        <v>139.712</v>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B898" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C898" s="3">
+        <v>11.366</v>
+      </c>
+      <c r="D898" s="3">
+        <v>11.366</v>
+      </c>
+      <c r="E898" s="3">
+        <v>128.819</v>
+      </c>
+      <c r="F898" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G898" s="3">
+        <v>140.185</v>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B899" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C899" s="3">
+        <v>10.88</v>
+      </c>
+      <c r="D899" s="3">
+        <v>10.88</v>
+      </c>
+      <c r="E899" s="3">
+        <v>129.485</v>
+      </c>
+      <c r="F899" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G899" s="3">
+        <v>140.365</v>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B900" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C900" s="3">
+        <v>11.712</v>
+      </c>
+      <c r="D900" s="3">
+        <v>11.712</v>
+      </c>
+      <c r="E900" s="3">
+        <v>137.062</v>
+      </c>
+      <c r="F900" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G900" s="3">
+        <v>148.774</v>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B901" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C901" s="3">
+        <v>11.469</v>
+      </c>
+      <c r="D901" s="3">
+        <v>11.469</v>
+      </c>
+      <c r="E901" s="3">
+        <v>129.126</v>
+      </c>
+      <c r="F901" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G901" s="3">
+        <v>140.595</v>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B902" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C902" s="3">
+        <v>10.829</v>
+      </c>
+      <c r="D902" s="3">
+        <v>10.829</v>
+      </c>
+      <c r="E902" s="3">
+        <v>155.494</v>
+      </c>
+      <c r="F902" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G902" s="3">
+        <v>166.323</v>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B903" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C903" s="3">
+        <v>19.699</v>
+      </c>
+      <c r="D903" s="3">
+        <v>19.699</v>
+      </c>
+      <c r="E903" s="3">
+        <v>162.509</v>
+      </c>
+      <c r="F903" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G903" s="3">
+        <v>182.208</v>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B904" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C904" s="3">
+        <v>17.856</v>
+      </c>
+      <c r="D904" s="3">
+        <v>17.856</v>
+      </c>
+      <c r="E904" s="3">
+        <v>154.88</v>
+      </c>
+      <c r="F904" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G904" s="3">
+        <v>172.736</v>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B905" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C905" s="3">
+        <v>18.726</v>
+      </c>
+      <c r="D905" s="3">
+        <v>18.726</v>
+      </c>
+      <c r="E905" s="3">
+        <v>153.651</v>
+      </c>
+      <c r="F905" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G905" s="3">
+        <v>172.377</v>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B906" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C906" s="3">
+        <v>14.362</v>
+      </c>
+      <c r="D906" s="3">
+        <v>14.362</v>
+      </c>
+      <c r="E906" s="3">
+        <v>158.054</v>
+      </c>
+      <c r="F906" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G906" s="3">
+        <v>172.416</v>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B907" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C907" s="3">
+        <v>28.25</v>
+      </c>
+      <c r="D907" s="3">
+        <v>28.25</v>
+      </c>
+      <c r="E907" s="3">
+        <v>144.538</v>
+      </c>
+      <c r="F907" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G907" s="3">
+        <v>172.788</v>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B908" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C908" s="3">
+        <v>37.299</v>
+      </c>
+      <c r="D908" s="3">
+        <v>37.299</v>
+      </c>
+      <c r="E908" s="3">
+        <v>134.81</v>
+      </c>
+      <c r="F908" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G908" s="3">
+        <v>172.109</v>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B909" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C909" s="3">
+        <v>49.165</v>
+      </c>
+      <c r="D909" s="3">
+        <v>49.165</v>
+      </c>
+      <c r="E909" s="3">
+        <v>123.187</v>
+      </c>
+      <c r="F909" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G909" s="3">
+        <v>172.352</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B910" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C910" s="3">
+        <v>73.216</v>
+      </c>
+      <c r="D910" s="3">
+        <v>73.216</v>
+      </c>
+      <c r="E910" s="3">
+        <v>100.096</v>
+      </c>
+      <c r="F910" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G910" s="3">
+        <v>173.312</v>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B911" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C911" s="3">
+        <v>93.901</v>
+      </c>
+      <c r="D911" s="3">
+        <v>93.901</v>
+      </c>
+      <c r="E911" s="3">
+        <v>78.49</v>
+      </c>
+      <c r="F911" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G911" s="3">
+        <v>172.391</v>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B912" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C912" s="3">
+        <v>76.173</v>
+      </c>
+      <c r="D912" s="3">
+        <v>76.173</v>
+      </c>
+      <c r="E912" s="3">
+        <v>95.898</v>
+      </c>
+      <c r="F912" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G912" s="3">
+        <v>172.071</v>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B913" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C913" s="3">
+        <v>46.336</v>
+      </c>
+      <c r="D913" s="3">
+        <v>46.336</v>
+      </c>
+      <c r="E913" s="3">
+        <v>125.798</v>
+      </c>
+      <c r="F913" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G913" s="3">
+        <v>172.134</v>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B914" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C914" s="3">
+        <v>52.672</v>
+      </c>
+      <c r="D914" s="3">
+        <v>52.672</v>
+      </c>
+      <c r="E914" s="3">
+        <v>119.757</v>
+      </c>
+      <c r="F914" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G914" s="3">
+        <v>172.429</v>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B915" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C915" s="3">
+        <v>57.946</v>
+      </c>
+      <c r="D915" s="3">
+        <v>57.946</v>
+      </c>
+      <c r="E915" s="3">
+        <v>114.176</v>
+      </c>
+      <c r="F915" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G915" s="3">
+        <v>172.122</v>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B916" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C916" s="3">
+        <v>66.739</v>
+      </c>
+      <c r="D916" s="3">
+        <v>66.739</v>
+      </c>
+      <c r="E916" s="3">
+        <v>105.779</v>
+      </c>
+      <c r="F916" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G916" s="3">
+        <v>172.518</v>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B917" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C917" s="3">
+        <v>72.282</v>
+      </c>
+      <c r="D917" s="3">
+        <v>72.282</v>
+      </c>
+      <c r="E917" s="3">
+        <v>99.891</v>
+      </c>
+      <c r="F917" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G917" s="3">
+        <v>172.173</v>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B918" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C918" s="3">
+        <v>76.634</v>
+      </c>
+      <c r="D918" s="3">
+        <v>76.634</v>
+      </c>
+      <c r="E918" s="3">
+        <v>95.181</v>
+      </c>
+      <c r="F918" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G918" s="3">
+        <v>171.815</v>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B919" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C919" s="3">
+        <v>55.462</v>
+      </c>
+      <c r="D919" s="3">
+        <v>55.462</v>
+      </c>
+      <c r="E919" s="3">
+        <v>116.582</v>
+      </c>
+      <c r="F919" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G919" s="3">
+        <v>172.044</v>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B920" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C920" s="3">
+        <v>57.216</v>
+      </c>
+      <c r="D920" s="3">
+        <v>57.216</v>
+      </c>
+      <c r="E920" s="3">
+        <v>115.302</v>
+      </c>
+      <c r="F920" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G920" s="3">
+        <v>172.518</v>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B921" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C921" s="3">
+        <v>77.286</v>
+      </c>
+      <c r="D921" s="3">
+        <v>77.286</v>
+      </c>
+      <c r="E921" s="3">
+        <v>93.901</v>
+      </c>
+      <c r="F921" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G921" s="3">
+        <v>171.187</v>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B922" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C922" s="3">
+        <v>84.326</v>
+      </c>
+      <c r="D922" s="3">
+        <v>84.326</v>
+      </c>
+      <c r="E922" s="3">
+        <v>84.941</v>
+      </c>
+      <c r="F922" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G922" s="3">
+        <v>169.267</v>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B923" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C923" s="3">
+        <v>69.043</v>
+      </c>
+      <c r="D923" s="3">
+        <v>69.043</v>
+      </c>
+      <c r="E923" s="3">
+        <v>99.789</v>
+      </c>
+      <c r="F923" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G923" s="3">
+        <v>168.832</v>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B924" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C924" s="3">
+        <v>68.045</v>
+      </c>
+      <c r="D924" s="3">
+        <v>68.045</v>
+      </c>
+      <c r="E924" s="3">
+        <v>100.915</v>
+      </c>
+      <c r="F924" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G924" s="3">
+        <v>168.96</v>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B925" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C925" s="3">
+        <v>94.131</v>
+      </c>
+      <c r="D925" s="3">
+        <v>94.131</v>
+      </c>
+      <c r="E925" s="3">
+        <v>75.162</v>
+      </c>
+      <c r="F925" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G925" s="3">
+        <v>169.293</v>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B926" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C926" s="3">
+        <v>108.518</v>
+      </c>
+      <c r="D926" s="3">
+        <v>108.518</v>
+      </c>
+      <c r="E926" s="3">
+        <v>61.594</v>
+      </c>
+      <c r="F926" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G926" s="3">
+        <v>170.112</v>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B927" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C927" s="3">
+        <v>100.595</v>
+      </c>
+      <c r="D927" s="3">
+        <v>100.595</v>
+      </c>
+      <c r="E927" s="3">
+        <v>69.222</v>
+      </c>
+      <c r="F927" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G927" s="3">
+        <v>169.817</v>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B928" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C928" s="3">
+        <v>85.197</v>
+      </c>
+      <c r="D928" s="3">
+        <v>85.197</v>
+      </c>
+      <c r="E928" s="3">
+        <v>84.122</v>
+      </c>
+      <c r="F928" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G928" s="3">
+        <v>169.319</v>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B929" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C929" s="3">
+        <v>101.491</v>
+      </c>
+      <c r="D929" s="3">
+        <v>101.491</v>
+      </c>
+      <c r="E929" s="3">
+        <v>67.635</v>
+      </c>
+      <c r="F929" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G929" s="3">
+        <v>169.126</v>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B930" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C930" s="3">
+        <v>73.459</v>
+      </c>
+      <c r="D930" s="3">
+        <v>73.459</v>
+      </c>
+      <c r="E930" s="3">
+        <v>95.078</v>
+      </c>
+      <c r="F930" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G930" s="3">
+        <v>168.537</v>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B931" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C931" s="3">
+        <v>73.254</v>
+      </c>
+      <c r="D931" s="3">
+        <v>73.254</v>
+      </c>
+      <c r="E931" s="3">
+        <v>95.488</v>
+      </c>
+      <c r="F931" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G931" s="3">
+        <v>168.742</v>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B932" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C932" s="3">
+        <v>41.779</v>
+      </c>
+      <c r="D932" s="3">
+        <v>41.779</v>
+      </c>
+      <c r="E932" s="3">
+        <v>126.259</v>
+      </c>
+      <c r="F932" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G932" s="3">
+        <v>168.038</v>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B933" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C933" s="3">
+        <v>44.019</v>
+      </c>
+      <c r="D933" s="3">
+        <v>44.019</v>
+      </c>
+      <c r="E933" s="3">
+        <v>125.85</v>
+      </c>
+      <c r="F933" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G933" s="3">
+        <v>169.869</v>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B934" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C934" s="3">
+        <v>60.71</v>
+      </c>
+      <c r="D934" s="3">
+        <v>60.71</v>
+      </c>
+      <c r="E934" s="3">
+        <v>107.674</v>
+      </c>
+      <c r="F934" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G934" s="3">
+        <v>168.384</v>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B935" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C935" s="3">
+        <v>43.2</v>
+      </c>
+      <c r="D935" s="3">
+        <v>43.2</v>
+      </c>
+      <c r="E935" s="3">
+        <v>125.542</v>
+      </c>
+      <c r="F935" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G935" s="3">
+        <v>168.742</v>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B936" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C936" s="3">
+        <v>31.45</v>
+      </c>
+      <c r="D936" s="3">
+        <v>31.45</v>
+      </c>
+      <c r="E936" s="3">
+        <v>137.523</v>
+      </c>
+      <c r="F936" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G936" s="3">
+        <v>168.973</v>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B937" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C937" s="3">
+        <v>41.779</v>
+      </c>
+      <c r="D937" s="3">
+        <v>41.779</v>
+      </c>
+      <c r="E937" s="3">
+        <v>98.56</v>
+      </c>
+      <c r="F937" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G937" s="3">
+        <v>140.339</v>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B938" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C938" s="3">
+        <v>23.309</v>
+      </c>
+      <c r="D938" s="3">
+        <v>23.309</v>
+      </c>
+      <c r="E938" s="3">
+        <v>111.104</v>
+      </c>
+      <c r="F938" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G938" s="3">
+        <v>134.413</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B939" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C939" s="3">
+        <v>9.19</v>
+      </c>
+      <c r="D939" s="3">
+        <v>9.19</v>
+      </c>
+      <c r="E939" s="3">
+        <v>125.798</v>
+      </c>
+      <c r="F939" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G939" s="3">
+        <v>134.988</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B940" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C940" s="3">
+        <v>10.022</v>
+      </c>
+      <c r="D940" s="3">
+        <v>10.022</v>
+      </c>
+      <c r="E940" s="3">
+        <v>124.979</v>
+      </c>
+      <c r="F940" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G940" s="3">
+        <v>135.001</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B941" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C941" s="3">
+        <v>7.616</v>
+      </c>
+      <c r="D941" s="3">
+        <v>7.616</v>
+      </c>
+      <c r="E941" s="3">
+        <v>127.181</v>
+      </c>
+      <c r="F941" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G941" s="3">
+        <v>134.797</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B942" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C942" s="3">
+        <v>1.651</v>
+      </c>
+      <c r="D942" s="3">
+        <v>1.651</v>
+      </c>
+      <c r="E942" s="3">
+        <v>133.171</v>
+      </c>
+      <c r="F942" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G942" s="3">
+        <v>134.822</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B943" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C943" s="3">
+        <v>0.192</v>
+      </c>
+      <c r="D943" s="3">
+        <v>0.192</v>
+      </c>
+      <c r="E943" s="3">
+        <v>134.605</v>
+      </c>
+      <c r="F943" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G943" s="3">
+        <v>134.797</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B944" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C944" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D944" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E944" s="3">
+        <v>135.27</v>
+      </c>
+      <c r="F944" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G944" s="3">
+        <v>135.27</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B945" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C945" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D945" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E945" s="3">
+        <v>135.322</v>
+      </c>
+      <c r="F945" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G945" s="3">
+        <v>135.322</v>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B946" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C946" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D946" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E946" s="3">
+        <v>134.963</v>
+      </c>
+      <c r="F946" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G946" s="3">
+        <v>134.963</v>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B947" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C947" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D947" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E947" s="3">
+        <v>134.861</v>
+      </c>
+      <c r="F947" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G947" s="3">
+        <v>134.861</v>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B948" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C948" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D948" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E948" s="3">
+        <v>135.117</v>
+      </c>
+      <c r="F948" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G948" s="3">
+        <v>135.117</v>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B949" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C949" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D949" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E949" s="3">
+        <v>135.373</v>
+      </c>
+      <c r="F949" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G949" s="3">
+        <v>135.373</v>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B950" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C950" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D950" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E950" s="3">
+        <v>134.707</v>
+      </c>
+      <c r="F950" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G950" s="3">
+        <v>134.707</v>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B951" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C951" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D951" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E951" s="3">
+        <v>134.861</v>
+      </c>
+      <c r="F951" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G951" s="3">
+        <v>134.861</v>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B952" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C952" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D952" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E952" s="3">
+        <v>134.656</v>
+      </c>
+      <c r="F952" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G952" s="3">
+        <v>134.656</v>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B953" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C953" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D953" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E953" s="3">
+        <v>134.707</v>
+      </c>
+      <c r="F953" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G953" s="3">
+        <v>134.707</v>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B954" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C954" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D954" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E954" s="3">
+        <v>135.066</v>
+      </c>
+      <c r="F954" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G954" s="3">
+        <v>135.066</v>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B955" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C955" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D955" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E955" s="3">
+        <v>134.656</v>
+      </c>
+      <c r="F955" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G955" s="3">
+        <v>134.656</v>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B956" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C956" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D956" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E956" s="3">
+        <v>134.758</v>
+      </c>
+      <c r="F956" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G956" s="3">
+        <v>134.758</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B957" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C957" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D957" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E957" s="3">
+        <v>135.117</v>
+      </c>
+      <c r="F957" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G957" s="3">
+        <v>135.117</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B958" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C958" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D958" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E958" s="3">
+        <v>135.27</v>
+      </c>
+      <c r="F958" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G958" s="3">
+        <v>135.27</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B959" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C959" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D959" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E959" s="3">
+        <v>134.912</v>
+      </c>
+      <c r="F959" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G959" s="3">
+        <v>134.912</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B960" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C960" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D960" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E960" s="3">
+        <v>134.963</v>
+      </c>
+      <c r="F960" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G960" s="3">
+        <v>134.963</v>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B961" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C961" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D961" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E961" s="3">
+        <v>135.322</v>
+      </c>
+      <c r="F961" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G961" s="3">
+        <v>135.322</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G865"/>
+  <autoFilter ref="A1:G961"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -382,45 +382,69 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B15" s="4">
+        <v>962.8</v>
+      </c>
+      <c r="C15" s="4">
+        <v>962.8</v>
+      </c>
+      <c r="D15" s="4">
+        <v>11940.7</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="4">
+        <v>12903.5</v>
+      </c>
+      <c r="G15" s="5">
+        <f>IF(F15&gt;0,C15/F15,"")</f>
+        <v>0.0746</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B15" s="7">
-        <f>SUM(B5:B14)</f>
-        <v>25962.1</v>
-      </c>
-      <c r="C15" s="7">
-        <f>SUM(C5:C14)</f>
-        <v>22817.8</v>
-      </c>
-      <c r="D15" s="7">
-        <f>SUM(D5:D14)</f>
-        <v>74877.0</v>
-      </c>
-      <c r="E15" s="7">
-        <f>SUM(E5:E14)</f>
+      <c r="B16" s="7">
+        <f>SUM(B5:B15)</f>
+        <v>26925.0</v>
+      </c>
+      <c r="C16" s="7">
+        <f>SUM(C5:C15)</f>
+        <v>23780.7</v>
+      </c>
+      <c r="D16" s="7">
+        <f>SUM(D5:D15)</f>
+        <v>86817.6</v>
+      </c>
+      <c r="E16" s="7">
+        <f>SUM(E5:E15)</f>
         <v>3144.3</v>
       </c>
-      <c r="F15" s="7">
-        <f>SUM(F5:F14)</f>
-        <v>97694.8</v>
-      </c>
-      <c r="G15" s="8">
-        <f>IF(F15&gt;0,C15/F15,"")</f>
-        <v>0.2336</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="F16" s="7">
+        <f>SUM(F5:F15)</f>
+        <v>110598.3</v>
+      </c>
+      <c r="G16" s="8">
+        <f>IF(F16&gt;0,C16/F16,"")</f>
+        <v>0.215</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -24479,7 +24503,2407 @@
         <v>135.322</v>
       </c>
     </row>
+    <row r="962">
+      <c r="A962" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B962" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C962" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D962" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E962" s="3">
+        <v>135.014</v>
+      </c>
+      <c r="F962" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G962" s="3">
+        <v>135.014</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B963" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C963" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D963" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E963" s="3">
+        <v>135.373</v>
+      </c>
+      <c r="F963" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G963" s="3">
+        <v>135.373</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B964" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C964" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D964" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E964" s="3">
+        <v>135.424</v>
+      </c>
+      <c r="F964" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G964" s="3">
+        <v>135.424</v>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B965" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C965" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D965" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E965" s="3">
+        <v>135.117</v>
+      </c>
+      <c r="F965" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G965" s="3">
+        <v>135.117</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B966" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C966" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D966" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E966" s="3">
+        <v>134.912</v>
+      </c>
+      <c r="F966" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G966" s="3">
+        <v>134.912</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B967" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C967" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D967" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E967" s="3">
+        <v>135.782</v>
+      </c>
+      <c r="F967" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G967" s="3">
+        <v>135.782</v>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B968" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C968" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D968" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E968" s="3">
+        <v>136.141</v>
+      </c>
+      <c r="F968" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G968" s="3">
+        <v>136.141</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B969" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C969" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D969" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E969" s="3">
+        <v>135.014</v>
+      </c>
+      <c r="F969" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G969" s="3">
+        <v>135.014</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B970" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C970" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D970" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E970" s="3">
+        <v>134.707</v>
+      </c>
+      <c r="F970" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G970" s="3">
+        <v>134.707</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B971" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C971" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D971" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E971" s="3">
+        <v>134.656</v>
+      </c>
+      <c r="F971" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G971" s="3">
+        <v>134.656</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B972" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C972" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D972" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E972" s="3">
+        <v>134.707</v>
+      </c>
+      <c r="F972" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G972" s="3">
+        <v>134.707</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B973" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C973" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D973" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E973" s="3">
+        <v>135.014</v>
+      </c>
+      <c r="F973" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G973" s="3">
+        <v>135.014</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B974" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C974" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D974" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E974" s="3">
+        <v>134.861</v>
+      </c>
+      <c r="F974" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G974" s="3">
+        <v>134.861</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B975" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C975" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D975" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E975" s="3">
+        <v>134.605</v>
+      </c>
+      <c r="F975" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G975" s="3">
+        <v>134.605</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B976" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C976" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D976" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E976" s="3">
+        <v>134.758</v>
+      </c>
+      <c r="F976" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G976" s="3">
+        <v>134.758</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B977" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C977" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D977" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E977" s="3">
+        <v>135.014</v>
+      </c>
+      <c r="F977" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G977" s="3">
+        <v>135.014</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B978" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C978" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D978" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E978" s="3">
+        <v>134.758</v>
+      </c>
+      <c r="F978" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G978" s="3">
+        <v>134.758</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B979" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C979" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D979" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E979" s="3">
+        <v>134.605</v>
+      </c>
+      <c r="F979" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G979" s="3">
+        <v>134.605</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B980" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C980" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D980" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E980" s="3">
+        <v>134.81</v>
+      </c>
+      <c r="F980" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G980" s="3">
+        <v>134.81</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B981" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C981" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D981" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E981" s="3">
+        <v>134.502</v>
+      </c>
+      <c r="F981" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G981" s="3">
+        <v>134.502</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B982" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C982" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D982" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E982" s="3">
+        <v>135.936</v>
+      </c>
+      <c r="F982" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G982" s="3">
+        <v>135.936</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B983" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C983" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D983" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E983" s="3">
+        <v>137.677</v>
+      </c>
+      <c r="F983" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G983" s="3">
+        <v>137.677</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B984" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C984" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D984" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E984" s="3">
+        <v>137.626</v>
+      </c>
+      <c r="F984" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G984" s="3">
+        <v>137.626</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B985" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C985" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D985" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E985" s="3">
+        <v>137.472</v>
+      </c>
+      <c r="F985" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G985" s="3">
+        <v>137.472</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B986" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C986" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D986" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E986" s="3">
+        <v>137.472</v>
+      </c>
+      <c r="F986" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G986" s="3">
+        <v>137.472</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B987" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C987" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D987" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E987" s="3">
+        <v>137.882</v>
+      </c>
+      <c r="F987" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G987" s="3">
+        <v>137.882</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B988" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C988" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D988" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E988" s="3">
+        <v>137.728</v>
+      </c>
+      <c r="F988" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G988" s="3">
+        <v>137.728</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B989" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C989" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D989" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E989" s="3">
+        <v>138.24</v>
+      </c>
+      <c r="F989" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G989" s="3">
+        <v>138.24</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B990" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C990" s="3">
+        <v>0.435</v>
+      </c>
+      <c r="D990" s="3">
+        <v>0.435</v>
+      </c>
+      <c r="E990" s="3">
+        <v>138.035</v>
+      </c>
+      <c r="F990" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G990" s="3">
+        <v>138.47</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B991" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C991" s="3">
+        <v>1.587</v>
+      </c>
+      <c r="D991" s="3">
+        <v>1.587</v>
+      </c>
+      <c r="E991" s="3">
+        <v>136.09</v>
+      </c>
+      <c r="F991" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G991" s="3">
+        <v>137.677</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B992" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C992" s="3">
+        <v>3.661</v>
+      </c>
+      <c r="D992" s="3">
+        <v>3.661</v>
+      </c>
+      <c r="E992" s="3">
+        <v>134.246</v>
+      </c>
+      <c r="F992" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G992" s="3">
+        <v>137.907</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B993" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C993" s="3">
+        <v>11.456</v>
+      </c>
+      <c r="D993" s="3">
+        <v>11.456</v>
+      </c>
+      <c r="E993" s="3">
+        <v>125.952</v>
+      </c>
+      <c r="F993" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G993" s="3">
+        <v>137.408</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B994" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C994" s="3">
+        <v>10.381</v>
+      </c>
+      <c r="D994" s="3">
+        <v>10.381</v>
+      </c>
+      <c r="E994" s="3">
+        <v>127.488</v>
+      </c>
+      <c r="F994" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G994" s="3">
+        <v>137.869</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B995" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C995" s="3">
+        <v>11.93</v>
+      </c>
+      <c r="D995" s="3">
+        <v>11.93</v>
+      </c>
+      <c r="E995" s="3">
+        <v>125.44</v>
+      </c>
+      <c r="F995" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G995" s="3">
+        <v>137.37</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B996" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C996" s="3">
+        <v>6.989</v>
+      </c>
+      <c r="D996" s="3">
+        <v>6.989</v>
+      </c>
+      <c r="E996" s="3">
+        <v>130.406</v>
+      </c>
+      <c r="F996" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G996" s="3">
+        <v>137.395</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B997" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C997" s="3">
+        <v>3.61</v>
+      </c>
+      <c r="D997" s="3">
+        <v>3.61</v>
+      </c>
+      <c r="E997" s="3">
+        <v>133.837</v>
+      </c>
+      <c r="F997" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G997" s="3">
+        <v>137.447</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B998" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C998" s="3">
+        <v>5.683</v>
+      </c>
+      <c r="D998" s="3">
+        <v>5.683</v>
+      </c>
+      <c r="E998" s="3">
+        <v>131.738</v>
+      </c>
+      <c r="F998" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G998" s="3">
+        <v>137.421</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B999" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C999" s="3">
+        <v>12.595</v>
+      </c>
+      <c r="D999" s="3">
+        <v>12.595</v>
+      </c>
+      <c r="E999" s="3">
+        <v>125.184</v>
+      </c>
+      <c r="F999" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G999" s="3">
+        <v>137.779</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1000" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C1000" s="3">
+        <v>14.989</v>
+      </c>
+      <c r="D1000" s="3">
+        <v>14.989</v>
+      </c>
+      <c r="E1000" s="3">
+        <v>122.317</v>
+      </c>
+      <c r="F1000" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1000" s="3">
+        <v>137.306</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1001" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C1001" s="3">
+        <v>16.384</v>
+      </c>
+      <c r="D1001" s="3">
+        <v>16.384</v>
+      </c>
+      <c r="E1001" s="3">
+        <v>121.088</v>
+      </c>
+      <c r="F1001" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1001" s="3">
+        <v>137.472</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1002" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C1002" s="3">
+        <v>24.858</v>
+      </c>
+      <c r="D1002" s="3">
+        <v>24.858</v>
+      </c>
+      <c r="E1002" s="3">
+        <v>112.845</v>
+      </c>
+      <c r="F1002" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1002" s="3">
+        <v>137.703</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1003" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C1003" s="3">
+        <v>34.867</v>
+      </c>
+      <c r="D1003" s="3">
+        <v>34.867</v>
+      </c>
+      <c r="E1003" s="3">
+        <v>103.014</v>
+      </c>
+      <c r="F1003" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1003" s="3">
+        <v>137.881</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1004" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C1004" s="3">
+        <v>28.224</v>
+      </c>
+      <c r="D1004" s="3">
+        <v>28.224</v>
+      </c>
+      <c r="E1004" s="3">
+        <v>110.234</v>
+      </c>
+      <c r="F1004" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1004" s="3">
+        <v>138.458</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1005" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C1005" s="3">
+        <v>33.728</v>
+      </c>
+      <c r="D1005" s="3">
+        <v>33.728</v>
+      </c>
+      <c r="E1005" s="3">
+        <v>105.267</v>
+      </c>
+      <c r="F1005" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1005" s="3">
+        <v>138.995</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1006" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C1006" s="3">
+        <v>45.248</v>
+      </c>
+      <c r="D1006" s="3">
+        <v>45.248</v>
+      </c>
+      <c r="E1006" s="3">
+        <v>92.467</v>
+      </c>
+      <c r="F1006" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1006" s="3">
+        <v>137.715</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1007" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C1007" s="3">
+        <v>40.794</v>
+      </c>
+      <c r="D1007" s="3">
+        <v>40.794</v>
+      </c>
+      <c r="E1007" s="3">
+        <v>97.331</v>
+      </c>
+      <c r="F1007" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1007" s="3">
+        <v>138.125</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1008" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C1008" s="3">
+        <v>30.4</v>
+      </c>
+      <c r="D1008" s="3">
+        <v>30.4</v>
+      </c>
+      <c r="E1008" s="3">
+        <v>107.11</v>
+      </c>
+      <c r="F1008" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1008" s="3">
+        <v>137.51</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1009" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C1009" s="3">
+        <v>39.821</v>
+      </c>
+      <c r="D1009" s="3">
+        <v>39.821</v>
+      </c>
+      <c r="E1009" s="3">
+        <v>97.382</v>
+      </c>
+      <c r="F1009" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1009" s="3">
+        <v>137.203</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1010" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C1010" s="3">
+        <v>30.912</v>
+      </c>
+      <c r="D1010" s="3">
+        <v>30.912</v>
+      </c>
+      <c r="E1010" s="3">
+        <v>106.752</v>
+      </c>
+      <c r="F1010" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1010" s="3">
+        <v>137.664</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1011" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C1011" s="3">
+        <v>22.003</v>
+      </c>
+      <c r="D1011" s="3">
+        <v>22.003</v>
+      </c>
+      <c r="E1011" s="3">
+        <v>115.456</v>
+      </c>
+      <c r="F1011" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1011" s="3">
+        <v>137.459</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1012" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C1012" s="3">
+        <v>23.962</v>
+      </c>
+      <c r="D1012" s="3">
+        <v>23.962</v>
+      </c>
+      <c r="E1012" s="3">
+        <v>113.254</v>
+      </c>
+      <c r="F1012" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1012" s="3">
+        <v>137.216</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1013" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C1013" s="3">
+        <v>31.066</v>
+      </c>
+      <c r="D1013" s="3">
+        <v>31.066</v>
+      </c>
+      <c r="E1013" s="3">
+        <v>106.291</v>
+      </c>
+      <c r="F1013" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1013" s="3">
+        <v>137.357</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1014" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C1014" s="3">
+        <v>22.438</v>
+      </c>
+      <c r="D1014" s="3">
+        <v>22.438</v>
+      </c>
+      <c r="E1014" s="3">
+        <v>115.2</v>
+      </c>
+      <c r="F1014" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1014" s="3">
+        <v>137.638</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1015" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C1015" s="3">
+        <v>17.101</v>
+      </c>
+      <c r="D1015" s="3">
+        <v>17.101</v>
+      </c>
+      <c r="E1015" s="3">
+        <v>120.627</v>
+      </c>
+      <c r="F1015" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1015" s="3">
+        <v>137.728</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1016" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C1016" s="3">
+        <v>18.842</v>
+      </c>
+      <c r="D1016" s="3">
+        <v>18.842</v>
+      </c>
+      <c r="E1016" s="3">
+        <v>119.142</v>
+      </c>
+      <c r="F1016" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1016" s="3">
+        <v>137.984</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1017" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C1017" s="3">
+        <v>11.968</v>
+      </c>
+      <c r="D1017" s="3">
+        <v>11.968</v>
+      </c>
+      <c r="E1017" s="3">
+        <v>126.413</v>
+      </c>
+      <c r="F1017" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1017" s="3">
+        <v>138.381</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1018" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C1018" s="3">
+        <v>17.51</v>
+      </c>
+      <c r="D1018" s="3">
+        <v>17.51</v>
+      </c>
+      <c r="E1018" s="3">
+        <v>120.73</v>
+      </c>
+      <c r="F1018" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1018" s="3">
+        <v>138.24</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1019" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C1019" s="3">
+        <v>39.885</v>
+      </c>
+      <c r="D1019" s="3">
+        <v>39.885</v>
+      </c>
+      <c r="E1019" s="3">
+        <v>98.253</v>
+      </c>
+      <c r="F1019" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1019" s="3">
+        <v>138.138</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1020" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C1020" s="3">
+        <v>48.794</v>
+      </c>
+      <c r="D1020" s="3">
+        <v>48.794</v>
+      </c>
+      <c r="E1020" s="3">
+        <v>89.242</v>
+      </c>
+      <c r="F1020" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1020" s="3">
+        <v>138.036</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1021" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C1021" s="3">
+        <v>39.526</v>
+      </c>
+      <c r="D1021" s="3">
+        <v>39.526</v>
+      </c>
+      <c r="E1021" s="3">
+        <v>98.509</v>
+      </c>
+      <c r="F1021" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1021" s="3">
+        <v>138.035</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1022" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C1022" s="3">
+        <v>25.485</v>
+      </c>
+      <c r="D1022" s="3">
+        <v>25.485</v>
+      </c>
+      <c r="E1022" s="3">
+        <v>112.333</v>
+      </c>
+      <c r="F1022" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1022" s="3">
+        <v>137.818</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1023" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C1023" s="3">
+        <v>37.645</v>
+      </c>
+      <c r="D1023" s="3">
+        <v>37.645</v>
+      </c>
+      <c r="E1023" s="3">
+        <v>100.71</v>
+      </c>
+      <c r="F1023" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1023" s="3">
+        <v>138.355</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1024" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C1024" s="3">
+        <v>38.72</v>
+      </c>
+      <c r="D1024" s="3">
+        <v>38.72</v>
+      </c>
+      <c r="E1024" s="3">
+        <v>99.072</v>
+      </c>
+      <c r="F1024" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1024" s="3">
+        <v>137.792</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1025" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C1025" s="3">
+        <v>35.123</v>
+      </c>
+      <c r="D1025" s="3">
+        <v>35.123</v>
+      </c>
+      <c r="E1025" s="3">
+        <v>102.451</v>
+      </c>
+      <c r="F1025" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1025" s="3">
+        <v>137.574</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1026" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C1026" s="3">
+        <v>23.923</v>
+      </c>
+      <c r="D1026" s="3">
+        <v>23.923</v>
+      </c>
+      <c r="E1026" s="3">
+        <v>113.664</v>
+      </c>
+      <c r="F1026" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1026" s="3">
+        <v>137.587</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1027" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C1027" s="3">
+        <v>21.21</v>
+      </c>
+      <c r="D1027" s="3">
+        <v>21.21</v>
+      </c>
+      <c r="E1027" s="3">
+        <v>117.402</v>
+      </c>
+      <c r="F1027" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1027" s="3">
+        <v>138.612</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1028" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C1028" s="3">
+        <v>20.8</v>
+      </c>
+      <c r="D1028" s="3">
+        <v>20.8</v>
+      </c>
+      <c r="E1028" s="3">
+        <v>116.941</v>
+      </c>
+      <c r="F1028" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1028" s="3">
+        <v>137.741</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1029" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C1029" s="3">
+        <v>18.163</v>
+      </c>
+      <c r="D1029" s="3">
+        <v>18.163</v>
+      </c>
+      <c r="E1029" s="3">
+        <v>119.398</v>
+      </c>
+      <c r="F1029" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1029" s="3">
+        <v>137.561</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1030" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C1030" s="3">
+        <v>10.803</v>
+      </c>
+      <c r="D1030" s="3">
+        <v>10.803</v>
+      </c>
+      <c r="E1030" s="3">
+        <v>126.72</v>
+      </c>
+      <c r="F1030" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1030" s="3">
+        <v>137.523</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1031" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C1031" s="3">
+        <v>7.091</v>
+      </c>
+      <c r="D1031" s="3">
+        <v>7.091</v>
+      </c>
+      <c r="E1031" s="3">
+        <v>131.174</v>
+      </c>
+      <c r="F1031" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1031" s="3">
+        <v>138.265</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1032" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C1032" s="3">
+        <v>6.374</v>
+      </c>
+      <c r="D1032" s="3">
+        <v>6.374</v>
+      </c>
+      <c r="E1032" s="3">
+        <v>131.738</v>
+      </c>
+      <c r="F1032" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1032" s="3">
+        <v>138.112</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1033" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C1033" s="3">
+        <v>4.07</v>
+      </c>
+      <c r="D1033" s="3">
+        <v>4.07</v>
+      </c>
+      <c r="E1033" s="3">
+        <v>133.734</v>
+      </c>
+      <c r="F1033" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1033" s="3">
+        <v>137.804</v>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1034" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C1034" s="3">
+        <v>0.947</v>
+      </c>
+      <c r="D1034" s="3">
+        <v>0.947</v>
+      </c>
+      <c r="E1034" s="3">
+        <v>136.858</v>
+      </c>
+      <c r="F1034" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1034" s="3">
+        <v>137.805</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1035" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C1035" s="3">
+        <v>0.794</v>
+      </c>
+      <c r="D1035" s="3">
+        <v>0.794</v>
+      </c>
+      <c r="E1035" s="3">
+        <v>136.294</v>
+      </c>
+      <c r="F1035" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1035" s="3">
+        <v>137.088</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1036" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C1036" s="3">
+        <v>5.478</v>
+      </c>
+      <c r="D1036" s="3">
+        <v>5.478</v>
+      </c>
+      <c r="E1036" s="3">
+        <v>130.867</v>
+      </c>
+      <c r="F1036" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1036" s="3">
+        <v>136.345</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1037" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C1037" s="3">
+        <v>4.39</v>
+      </c>
+      <c r="D1037" s="3">
+        <v>4.39</v>
+      </c>
+      <c r="E1037" s="3">
+        <v>130.867</v>
+      </c>
+      <c r="F1037" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1037" s="3">
+        <v>135.257</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1038" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C1038" s="3">
+        <v>0.166</v>
+      </c>
+      <c r="D1038" s="3">
+        <v>0.166</v>
+      </c>
+      <c r="E1038" s="3">
+        <v>134.912</v>
+      </c>
+      <c r="F1038" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1038" s="3">
+        <v>135.078</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1039" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C1039" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1039" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1039" s="3">
+        <v>135.117</v>
+      </c>
+      <c r="F1039" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1039" s="3">
+        <v>135.117</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1040" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C1040" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1040" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1040" s="3">
+        <v>135.27</v>
+      </c>
+      <c r="F1040" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1040" s="3">
+        <v>135.27</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1041" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C1041" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1041" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1041" s="3">
+        <v>135.117</v>
+      </c>
+      <c r="F1041" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1041" s="3">
+        <v>135.117</v>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1042" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C1042" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1042" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1042" s="3">
+        <v>135.27</v>
+      </c>
+      <c r="F1042" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1042" s="3">
+        <v>135.27</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1043" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C1043" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1043" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1043" s="3">
+        <v>135.578</v>
+      </c>
+      <c r="F1043" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1043" s="3">
+        <v>135.578</v>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1044" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C1044" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1044" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1044" s="3">
+        <v>135.885</v>
+      </c>
+      <c r="F1044" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1044" s="3">
+        <v>135.885</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1045" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C1045" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1045" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1045" s="3">
+        <v>136.141</v>
+      </c>
+      <c r="F1045" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1045" s="3">
+        <v>136.141</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1046" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C1046" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1046" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1046" s="3">
+        <v>135.117</v>
+      </c>
+      <c r="F1046" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1046" s="3">
+        <v>135.117</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1047" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C1047" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1047" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1047" s="3">
+        <v>135.117</v>
+      </c>
+      <c r="F1047" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1047" s="3">
+        <v>135.117</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1048" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C1048" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1048" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1048" s="3">
+        <v>135.117</v>
+      </c>
+      <c r="F1048" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1048" s="3">
+        <v>135.117</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1049" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C1049" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1049" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1049" s="3">
+        <v>135.27</v>
+      </c>
+      <c r="F1049" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1049" s="3">
+        <v>135.27</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1050" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C1050" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1050" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1050" s="3">
+        <v>135.168</v>
+      </c>
+      <c r="F1050" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1050" s="3">
+        <v>135.168</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1051" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C1051" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1051" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1051" s="3">
+        <v>121.549</v>
+      </c>
+      <c r="F1051" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1051" s="3">
+        <v>121.549</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1052" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C1052" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1052" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1052" s="3">
+        <v>102.144</v>
+      </c>
+      <c r="F1052" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1052" s="3">
+        <v>102.144</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1053" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C1053" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1053" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1053" s="3">
+        <v>102.042</v>
+      </c>
+      <c r="F1053" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1053" s="3">
+        <v>102.042</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1054" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C1054" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1054" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1054" s="3">
+        <v>101.888</v>
+      </c>
+      <c r="F1054" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1054" s="3">
+        <v>101.888</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1055" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C1055" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1055" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1055" s="3">
+        <v>102.093</v>
+      </c>
+      <c r="F1055" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1055" s="3">
+        <v>102.093</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1056" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C1056" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1056" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1056" s="3">
+        <v>102.144</v>
+      </c>
+      <c r="F1056" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1056" s="3">
+        <v>102.144</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="2">
+        <v>46306</v>
+      </c>
+      <c r="B1057" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C1057" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1057" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1057" s="3">
+        <v>102.349</v>
+      </c>
+      <c r="F1057" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1057" s="3">
+        <v>102.349</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G961"/>
+  <autoFilter ref="A1:G1057"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -406,45 +406,69 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B16" s="4">
+        <v>1635.6</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1556.5</v>
+      </c>
+      <c r="D16" s="4">
+        <v>7322.1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>79.1</v>
+      </c>
+      <c r="F16" s="4">
+        <v>8878.5</v>
+      </c>
+      <c r="G16" s="5">
+        <f>IF(F16&gt;0,C16/F16,"")</f>
+        <v>0.1753</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B16" s="7">
-        <f>SUM(B5:B15)</f>
-        <v>26925.0</v>
-      </c>
-      <c r="C16" s="7">
-        <f>SUM(C5:C15)</f>
-        <v>23780.7</v>
-      </c>
-      <c r="D16" s="7">
-        <f>SUM(D5:D15)</f>
-        <v>86817.6</v>
-      </c>
-      <c r="E16" s="7">
-        <f>SUM(E5:E15)</f>
-        <v>3144.3</v>
-      </c>
-      <c r="F16" s="7">
-        <f>SUM(F5:F15)</f>
-        <v>110598.3</v>
-      </c>
-      <c r="G16" s="8">
-        <f>IF(F16&gt;0,C16/F16,"")</f>
-        <v>0.215</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B17" s="7">
+        <f>SUM(B5:B16)</f>
+        <v>28560.5</v>
+      </c>
+      <c r="C17" s="7">
+        <f>SUM(C5:C16)</f>
+        <v>25337.1</v>
+      </c>
+      <c r="D17" s="7">
+        <f>SUM(D5:D16)</f>
+        <v>94139.7</v>
+      </c>
+      <c r="E17" s="7">
+        <f>SUM(E5:E16)</f>
+        <v>3223.4</v>
+      </c>
+      <c r="F17" s="7">
+        <f>SUM(F5:F16)</f>
+        <v>119476.8</v>
+      </c>
+      <c r="G17" s="8">
+        <f>IF(F17&gt;0,C17/F17,"")</f>
+        <v>0.2121</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -26903,7 +26927,2407 @@
         <v>102.349</v>
       </c>
     </row>
+    <row r="1058">
+      <c r="A1058" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1058" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C1058" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1058" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1058" s="3">
+        <v>102.502</v>
+      </c>
+      <c r="F1058" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1058" s="3">
+        <v>102.502</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1059" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C1059" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1059" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1059" s="3">
+        <v>101.939</v>
+      </c>
+      <c r="F1059" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1059" s="3">
+        <v>101.939</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1060" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C1060" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1060" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1060" s="3">
+        <v>101.837</v>
+      </c>
+      <c r="F1060" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1060" s="3">
+        <v>101.837</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1061" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C1061" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1061" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1061" s="3">
+        <v>101.581</v>
+      </c>
+      <c r="F1061" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1061" s="3">
+        <v>101.581</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1062" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C1062" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1062" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1062" s="3">
+        <v>101.786</v>
+      </c>
+      <c r="F1062" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1062" s="3">
+        <v>101.786</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1063" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C1063" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1063" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1063" s="3">
+        <v>101.734</v>
+      </c>
+      <c r="F1063" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1063" s="3">
+        <v>101.734</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1064" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C1064" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1064" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1064" s="3">
+        <v>101.939</v>
+      </c>
+      <c r="F1064" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1064" s="3">
+        <v>101.939</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1065" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C1065" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1065" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1065" s="3">
+        <v>101.734</v>
+      </c>
+      <c r="F1065" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1065" s="3">
+        <v>101.734</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1066" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C1066" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1066" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1066" s="3">
+        <v>101.632</v>
+      </c>
+      <c r="F1066" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1066" s="3">
+        <v>101.632</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1067" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C1067" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1067" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1067" s="3">
+        <v>101.888</v>
+      </c>
+      <c r="F1067" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1067" s="3">
+        <v>101.888</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1068" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C1068" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1068" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1068" s="3">
+        <v>101.888</v>
+      </c>
+      <c r="F1068" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1068" s="3">
+        <v>101.888</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1069" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C1069" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1069" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1069" s="3">
+        <v>102.144</v>
+      </c>
+      <c r="F1069" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1069" s="3">
+        <v>102.144</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1070" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C1070" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1070" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1070" s="3">
+        <v>102.144</v>
+      </c>
+      <c r="F1070" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1070" s="3">
+        <v>102.144</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1071" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C1071" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1071" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1071" s="3">
+        <v>102.195</v>
+      </c>
+      <c r="F1071" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1071" s="3">
+        <v>102.195</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1072" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C1072" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1072" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1072" s="3">
+        <v>102.042</v>
+      </c>
+      <c r="F1072" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1072" s="3">
+        <v>102.042</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1073" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C1073" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1073" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1073" s="3">
+        <v>101.99</v>
+      </c>
+      <c r="F1073" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1073" s="3">
+        <v>101.99</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1074" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C1074" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1074" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1074" s="3">
+        <v>102.298</v>
+      </c>
+      <c r="F1074" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1074" s="3">
+        <v>102.298</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1075" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C1075" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1075" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1075" s="3">
+        <v>101.939</v>
+      </c>
+      <c r="F1075" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1075" s="3">
+        <v>101.939</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1076" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C1076" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1076" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1076" s="3">
+        <v>101.99</v>
+      </c>
+      <c r="F1076" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1076" s="3">
+        <v>101.99</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1077" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C1077" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1077" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1077" s="3">
+        <v>101.99</v>
+      </c>
+      <c r="F1077" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1077" s="3">
+        <v>101.99</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1078" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C1078" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1078" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1078" s="3">
+        <v>102.144</v>
+      </c>
+      <c r="F1078" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1078" s="3">
+        <v>102.144</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1079" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C1079" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1079" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1079" s="3">
+        <v>101.99</v>
+      </c>
+      <c r="F1079" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1079" s="3">
+        <v>101.99</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1080" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C1080" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1080" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1080" s="3">
+        <v>102.042</v>
+      </c>
+      <c r="F1080" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1080" s="3">
+        <v>102.042</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1081" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C1081" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1081" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1081" s="3">
+        <v>102.298</v>
+      </c>
+      <c r="F1081" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1081" s="3">
+        <v>102.298</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1082" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C1082" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1082" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1082" s="3">
+        <v>102.246</v>
+      </c>
+      <c r="F1082" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1082" s="3">
+        <v>102.246</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1083" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C1083" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1083" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1083" s="3">
+        <v>104.909</v>
+      </c>
+      <c r="F1083" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1083" s="3">
+        <v>104.909</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1084" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C1084" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1084" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1084" s="3">
+        <v>105.677</v>
+      </c>
+      <c r="F1084" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1084" s="3">
+        <v>105.677</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1085" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C1085" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="D1085" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="E1085" s="3">
+        <v>105.779</v>
+      </c>
+      <c r="F1085" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1085" s="3">
+        <v>105.792</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1086" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C1086" s="3">
+        <v>0.384</v>
+      </c>
+      <c r="D1086" s="3">
+        <v>0.384</v>
+      </c>
+      <c r="E1086" s="3">
+        <v>105.165</v>
+      </c>
+      <c r="F1086" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1086" s="3">
+        <v>105.549</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1087" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C1087" s="3">
+        <v>1.677</v>
+      </c>
+      <c r="D1087" s="3">
+        <v>1.677</v>
+      </c>
+      <c r="E1087" s="3">
+        <v>103.27</v>
+      </c>
+      <c r="F1087" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1087" s="3">
+        <v>104.947</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1088" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C1088" s="3">
+        <v>3.674</v>
+      </c>
+      <c r="D1088" s="3">
+        <v>3.674</v>
+      </c>
+      <c r="E1088" s="3">
+        <v>101.171</v>
+      </c>
+      <c r="F1088" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1088" s="3">
+        <v>104.845</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1089" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C1089" s="3">
+        <v>5.811</v>
+      </c>
+      <c r="D1089" s="3">
+        <v>5.811</v>
+      </c>
+      <c r="E1089" s="3">
+        <v>99.43</v>
+      </c>
+      <c r="F1089" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1089" s="3">
+        <v>105.241</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1090" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C1090" s="3">
+        <v>8.013</v>
+      </c>
+      <c r="D1090" s="3">
+        <v>8.013</v>
+      </c>
+      <c r="E1090" s="3">
+        <v>66.662</v>
+      </c>
+      <c r="F1090" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1090" s="3">
+        <v>74.675</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1091" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C1091" s="3">
+        <v>9.203</v>
+      </c>
+      <c r="D1091" s="3">
+        <v>9.203</v>
+      </c>
+      <c r="E1091" s="3">
+        <v>63.386</v>
+      </c>
+      <c r="F1091" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1091" s="3">
+        <v>72.589</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1092" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C1092" s="3">
+        <v>11.635</v>
+      </c>
+      <c r="D1092" s="3">
+        <v>11.635</v>
+      </c>
+      <c r="E1092" s="3">
+        <v>60.621</v>
+      </c>
+      <c r="F1092" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1092" s="3">
+        <v>72.256</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1093" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C1093" s="3">
+        <v>9.421</v>
+      </c>
+      <c r="D1093" s="3">
+        <v>9.421</v>
+      </c>
+      <c r="E1093" s="3">
+        <v>62.822</v>
+      </c>
+      <c r="F1093" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1093" s="3">
+        <v>72.243</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1094" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C1094" s="3">
+        <v>14.298</v>
+      </c>
+      <c r="D1094" s="3">
+        <v>14.298</v>
+      </c>
+      <c r="E1094" s="3">
+        <v>58.061</v>
+      </c>
+      <c r="F1094" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1094" s="3">
+        <v>72.359</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1095" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C1095" s="3">
+        <v>14.746</v>
+      </c>
+      <c r="D1095" s="3">
+        <v>14.746</v>
+      </c>
+      <c r="E1095" s="3">
+        <v>57.754</v>
+      </c>
+      <c r="F1095" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1095" s="3">
+        <v>72.5</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1096" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C1096" s="3">
+        <v>24.205</v>
+      </c>
+      <c r="D1096" s="3">
+        <v>24.205</v>
+      </c>
+      <c r="E1096" s="3">
+        <v>48.384</v>
+      </c>
+      <c r="F1096" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1096" s="3">
+        <v>72.589</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1097" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C1097" s="3">
+        <v>22.49</v>
+      </c>
+      <c r="D1097" s="3">
+        <v>22.49</v>
+      </c>
+      <c r="E1097" s="3">
+        <v>49.92</v>
+      </c>
+      <c r="F1097" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1097" s="3">
+        <v>72.41</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1098" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C1098" s="3">
+        <v>25.037</v>
+      </c>
+      <c r="D1098" s="3">
+        <v>25.037</v>
+      </c>
+      <c r="E1098" s="3">
+        <v>47.36</v>
+      </c>
+      <c r="F1098" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1098" s="3">
+        <v>72.397</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1099" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C1099" s="3">
+        <v>16.576</v>
+      </c>
+      <c r="D1099" s="3">
+        <v>16.576</v>
+      </c>
+      <c r="E1099" s="3">
+        <v>55.962</v>
+      </c>
+      <c r="F1099" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1099" s="3">
+        <v>72.538</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C1100" s="3">
+        <v>25.536</v>
+      </c>
+      <c r="D1100" s="3">
+        <v>25.536</v>
+      </c>
+      <c r="E1100" s="3">
+        <v>46.95</v>
+      </c>
+      <c r="F1100" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1100" s="3">
+        <v>72.486</v>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C1101" s="3">
+        <v>20.762</v>
+      </c>
+      <c r="D1101" s="3">
+        <v>20.762</v>
+      </c>
+      <c r="E1101" s="3">
+        <v>51.405</v>
+      </c>
+      <c r="F1101" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1101" s="3">
+        <v>72.167</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C1102" s="3">
+        <v>16.922</v>
+      </c>
+      <c r="D1102" s="3">
+        <v>16.922</v>
+      </c>
+      <c r="E1102" s="3">
+        <v>55.296</v>
+      </c>
+      <c r="F1102" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1102" s="3">
+        <v>72.218</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C1103" s="3">
+        <v>16.166</v>
+      </c>
+      <c r="D1103" s="3">
+        <v>16.166</v>
+      </c>
+      <c r="E1103" s="3">
+        <v>56.32</v>
+      </c>
+      <c r="F1103" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1103" s="3">
+        <v>72.486</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C1104" s="3">
+        <v>19.046</v>
+      </c>
+      <c r="D1104" s="3">
+        <v>19.046</v>
+      </c>
+      <c r="E1104" s="3">
+        <v>53.35</v>
+      </c>
+      <c r="F1104" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1104" s="3">
+        <v>72.396</v>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C1105" s="3">
+        <v>19.251</v>
+      </c>
+      <c r="D1105" s="3">
+        <v>19.251</v>
+      </c>
+      <c r="E1105" s="3">
+        <v>53.094</v>
+      </c>
+      <c r="F1105" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1105" s="3">
+        <v>72.345</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C1106" s="3">
+        <v>26.867</v>
+      </c>
+      <c r="D1106" s="3">
+        <v>26.867</v>
+      </c>
+      <c r="E1106" s="3">
+        <v>45.466</v>
+      </c>
+      <c r="F1106" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1106" s="3">
+        <v>72.333</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C1107" s="3">
+        <v>26.432</v>
+      </c>
+      <c r="D1107" s="3">
+        <v>26.432</v>
+      </c>
+      <c r="E1107" s="3">
+        <v>46.08</v>
+      </c>
+      <c r="F1107" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1107" s="3">
+        <v>72.512</v>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C1108" s="3">
+        <v>33.843</v>
+      </c>
+      <c r="D1108" s="3">
+        <v>33.843</v>
+      </c>
+      <c r="E1108" s="3">
+        <v>38.349</v>
+      </c>
+      <c r="F1108" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1108" s="3">
+        <v>72.192</v>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C1109" s="3">
+        <v>25.19</v>
+      </c>
+      <c r="D1109" s="3">
+        <v>25.19</v>
+      </c>
+      <c r="E1109" s="3">
+        <v>47.77</v>
+      </c>
+      <c r="F1109" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1109" s="3">
+        <v>72.96</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C1110" s="3">
+        <v>49.203</v>
+      </c>
+      <c r="D1110" s="3">
+        <v>49.203</v>
+      </c>
+      <c r="E1110" s="3">
+        <v>23.91</v>
+      </c>
+      <c r="F1110" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1110" s="3">
+        <v>73.113</v>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C1111" s="3">
+        <v>83.725</v>
+      </c>
+      <c r="D1111" s="3">
+        <v>69.543</v>
+      </c>
+      <c r="E1111" s="3">
+        <v>3.942</v>
+      </c>
+      <c r="F1111" s="3">
+        <v>14.182</v>
+      </c>
+      <c r="G1111" s="3">
+        <v>73.485</v>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C1112" s="3">
+        <v>51.546</v>
+      </c>
+      <c r="D1112" s="3">
+        <v>46.477</v>
+      </c>
+      <c r="E1112" s="3">
+        <v>24.832</v>
+      </c>
+      <c r="F1112" s="3">
+        <v>5.069</v>
+      </c>
+      <c r="G1112" s="3">
+        <v>71.309</v>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C1113" s="3">
+        <v>27.648</v>
+      </c>
+      <c r="D1113" s="3">
+        <v>27.648</v>
+      </c>
+      <c r="E1113" s="3">
+        <v>44.954</v>
+      </c>
+      <c r="F1113" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1113" s="3">
+        <v>72.602</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C1114" s="3">
+        <v>59.302</v>
+      </c>
+      <c r="D1114" s="3">
+        <v>52.953</v>
+      </c>
+      <c r="E1114" s="3">
+        <v>19.558</v>
+      </c>
+      <c r="F1114" s="3">
+        <v>6.349</v>
+      </c>
+      <c r="G1114" s="3">
+        <v>72.511</v>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C1115" s="3">
+        <v>63.77</v>
+      </c>
+      <c r="D1115" s="3">
+        <v>58.752</v>
+      </c>
+      <c r="E1115" s="3">
+        <v>14.08</v>
+      </c>
+      <c r="F1115" s="3">
+        <v>5.018</v>
+      </c>
+      <c r="G1115" s="3">
+        <v>72.832</v>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C1116" s="3">
+        <v>51.533</v>
+      </c>
+      <c r="D1116" s="3">
+        <v>46.976</v>
+      </c>
+      <c r="E1116" s="3">
+        <v>25.498</v>
+      </c>
+      <c r="F1116" s="3">
+        <v>4.557</v>
+      </c>
+      <c r="G1116" s="3">
+        <v>72.474</v>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C1117" s="3">
+        <v>72.09</v>
+      </c>
+      <c r="D1117" s="3">
+        <v>55.552</v>
+      </c>
+      <c r="E1117" s="3">
+        <v>18.33</v>
+      </c>
+      <c r="F1117" s="3">
+        <v>16.538</v>
+      </c>
+      <c r="G1117" s="3">
+        <v>73.882</v>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1118" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C1118" s="3">
+        <v>57.664</v>
+      </c>
+      <c r="D1118" s="3">
+        <v>50.035</v>
+      </c>
+      <c r="E1118" s="3">
+        <v>22.118</v>
+      </c>
+      <c r="F1118" s="3">
+        <v>7.629</v>
+      </c>
+      <c r="G1118" s="3">
+        <v>72.153</v>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1119" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C1119" s="3">
+        <v>58.086</v>
+      </c>
+      <c r="D1119" s="3">
+        <v>51.481</v>
+      </c>
+      <c r="E1119" s="3">
+        <v>21.043</v>
+      </c>
+      <c r="F1119" s="3">
+        <v>6.605</v>
+      </c>
+      <c r="G1119" s="3">
+        <v>72.524</v>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1120" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C1120" s="3">
+        <v>48.589</v>
+      </c>
+      <c r="D1120" s="3">
+        <v>48.487</v>
+      </c>
+      <c r="E1120" s="3">
+        <v>23.398</v>
+      </c>
+      <c r="F1120" s="3">
+        <v>0.102</v>
+      </c>
+      <c r="G1120" s="3">
+        <v>71.885</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1121" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C1121" s="3">
+        <v>44.352</v>
+      </c>
+      <c r="D1121" s="3">
+        <v>44.352</v>
+      </c>
+      <c r="E1121" s="3">
+        <v>28.518</v>
+      </c>
+      <c r="F1121" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1121" s="3">
+        <v>72.87</v>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C1122" s="3">
+        <v>33.882</v>
+      </c>
+      <c r="D1122" s="3">
+        <v>33.882</v>
+      </c>
+      <c r="E1122" s="3">
+        <v>39.782</v>
+      </c>
+      <c r="F1122" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1122" s="3">
+        <v>73.664</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C1123" s="3">
+        <v>72.602</v>
+      </c>
+      <c r="D1123" s="3">
+        <v>62.464</v>
+      </c>
+      <c r="E1123" s="3">
+        <v>25.6</v>
+      </c>
+      <c r="F1123" s="3">
+        <v>10.138</v>
+      </c>
+      <c r="G1123" s="3">
+        <v>88.064</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C1124" s="3">
+        <v>70.323</v>
+      </c>
+      <c r="D1124" s="3">
+        <v>67.405</v>
+      </c>
+      <c r="E1124" s="3">
+        <v>25.856</v>
+      </c>
+      <c r="F1124" s="3">
+        <v>2.918</v>
+      </c>
+      <c r="G1124" s="3">
+        <v>93.261</v>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C1125" s="3">
+        <v>75.738</v>
+      </c>
+      <c r="D1125" s="3">
+        <v>75.738</v>
+      </c>
+      <c r="E1125" s="3">
+        <v>30.106</v>
+      </c>
+      <c r="F1125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1125" s="3">
+        <v>105.844</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1126" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C1126" s="3">
+        <v>73.331</v>
+      </c>
+      <c r="D1126" s="3">
+        <v>73.331</v>
+      </c>
+      <c r="E1126" s="3">
+        <v>32.666</v>
+      </c>
+      <c r="F1126" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1126" s="3">
+        <v>105.997</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C1127" s="3">
+        <v>45.082</v>
+      </c>
+      <c r="D1127" s="3">
+        <v>45.082</v>
+      </c>
+      <c r="E1127" s="3">
+        <v>60.928</v>
+      </c>
+      <c r="F1127" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1127" s="3">
+        <v>106.01</v>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C1128" s="3">
+        <v>63.053</v>
+      </c>
+      <c r="D1128" s="3">
+        <v>63.053</v>
+      </c>
+      <c r="E1128" s="3">
+        <v>43.622</v>
+      </c>
+      <c r="F1128" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1128" s="3">
+        <v>106.675</v>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C1129" s="3">
+        <v>48.141</v>
+      </c>
+      <c r="D1129" s="3">
+        <v>48.141</v>
+      </c>
+      <c r="E1129" s="3">
+        <v>58.726</v>
+      </c>
+      <c r="F1129" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1129" s="3">
+        <v>106.867</v>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1130" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C1130" s="3">
+        <v>37.555</v>
+      </c>
+      <c r="D1130" s="3">
+        <v>37.555</v>
+      </c>
+      <c r="E1130" s="3">
+        <v>68.352</v>
+      </c>
+      <c r="F1130" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1130" s="3">
+        <v>105.907</v>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C1131" s="3">
+        <v>27.533</v>
+      </c>
+      <c r="D1131" s="3">
+        <v>27.533</v>
+      </c>
+      <c r="E1131" s="3">
+        <v>77.056</v>
+      </c>
+      <c r="F1131" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1131" s="3">
+        <v>104.589</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C1132" s="3">
+        <v>14.554</v>
+      </c>
+      <c r="D1132" s="3">
+        <v>14.554</v>
+      </c>
+      <c r="E1132" s="3">
+        <v>88.627</v>
+      </c>
+      <c r="F1132" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1132" s="3">
+        <v>103.181</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1133" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C1133" s="3">
+        <v>6.387</v>
+      </c>
+      <c r="D1133" s="3">
+        <v>6.387</v>
+      </c>
+      <c r="E1133" s="3">
+        <v>96.666</v>
+      </c>
+      <c r="F1133" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1133" s="3">
+        <v>103.053</v>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1134" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C1134" s="3">
+        <v>2.368</v>
+      </c>
+      <c r="D1134" s="3">
+        <v>2.368</v>
+      </c>
+      <c r="E1134" s="3">
+        <v>100.966</v>
+      </c>
+      <c r="F1134" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1134" s="3">
+        <v>103.334</v>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C1135" s="3">
+        <v>0.294</v>
+      </c>
+      <c r="D1135" s="3">
+        <v>0.294</v>
+      </c>
+      <c r="E1135" s="3">
+        <v>102.963</v>
+      </c>
+      <c r="F1135" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1135" s="3">
+        <v>103.257</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C1136" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="D1136" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="E1136" s="3">
+        <v>103.219</v>
+      </c>
+      <c r="F1136" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1136" s="3">
+        <v>103.232</v>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C1137" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1137" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1137" s="3">
+        <v>103.475</v>
+      </c>
+      <c r="F1137" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1137" s="3">
+        <v>103.475</v>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C1138" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1138" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1138" s="3">
+        <v>103.322</v>
+      </c>
+      <c r="F1138" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1138" s="3">
+        <v>103.322</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1139" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C1139" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1139" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1139" s="3">
+        <v>103.475</v>
+      </c>
+      <c r="F1139" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1139" s="3">
+        <v>103.475</v>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C1140" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1140" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1140" s="3">
+        <v>103.219</v>
+      </c>
+      <c r="F1140" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1140" s="3">
+        <v>103.219</v>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1141" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C1141" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1141" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1141" s="3">
+        <v>103.117</v>
+      </c>
+      <c r="F1141" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1141" s="3">
+        <v>103.117</v>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1142" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C1142" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1142" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1142" s="3">
+        <v>103.117</v>
+      </c>
+      <c r="F1142" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1142" s="3">
+        <v>103.117</v>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1143" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C1143" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1143" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1143" s="3">
+        <v>103.475</v>
+      </c>
+      <c r="F1143" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1143" s="3">
+        <v>103.475</v>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C1144" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1144" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1144" s="3">
+        <v>103.27</v>
+      </c>
+      <c r="F1144" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1144" s="3">
+        <v>103.27</v>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1145" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C1145" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1145" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1145" s="3">
+        <v>103.168</v>
+      </c>
+      <c r="F1145" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1145" s="3">
+        <v>103.168</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1146" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C1146" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1146" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1146" s="3">
+        <v>103.014</v>
+      </c>
+      <c r="F1146" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1146" s="3">
+        <v>103.014</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1147" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C1147" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1147" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1147" s="3">
+        <v>103.168</v>
+      </c>
+      <c r="F1147" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1147" s="3">
+        <v>103.168</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C1148" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1148" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1148" s="3">
+        <v>103.68</v>
+      </c>
+      <c r="F1148" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1148" s="3">
+        <v>103.68</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C1149" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1149" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1149" s="3">
+        <v>103.322</v>
+      </c>
+      <c r="F1149" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1149" s="3">
+        <v>103.322</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1150" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C1150" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1150" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1150" s="3">
+        <v>103.68</v>
+      </c>
+      <c r="F1150" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1150" s="3">
+        <v>103.68</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1151" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C1151" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1151" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1151" s="3">
+        <v>103.168</v>
+      </c>
+      <c r="F1151" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1151" s="3">
+        <v>103.168</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1152" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C1152" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1152" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1152" s="3">
+        <v>103.219</v>
+      </c>
+      <c r="F1152" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1152" s="3">
+        <v>103.219</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B1153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C1153" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1153" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1153" s="3">
+        <v>103.526</v>
+      </c>
+      <c r="F1153" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1153" s="3">
+        <v>103.526</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1057"/>
+  <autoFilter ref="A1:G1153"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -430,45 +430,69 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B17" s="4">
+        <v>1713.9</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1580.1</v>
+      </c>
+      <c r="D17" s="4">
+        <v>7964.7</v>
+      </c>
+      <c r="E17" s="4">
+        <v>133.8</v>
+      </c>
+      <c r="F17" s="4">
+        <v>9544.7</v>
+      </c>
+      <c r="G17" s="5">
+        <f>IF(F17&gt;0,C17/F17,"")</f>
+        <v>0.1655</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B17" s="7">
-        <f>SUM(B5:B16)</f>
-        <v>28560.5</v>
-      </c>
-      <c r="C17" s="7">
-        <f>SUM(C5:C16)</f>
-        <v>25337.1</v>
-      </c>
-      <c r="D17" s="7">
-        <f>SUM(D5:D16)</f>
-        <v>94139.7</v>
-      </c>
-      <c r="E17" s="7">
-        <f>SUM(E5:E16)</f>
-        <v>3223.4</v>
-      </c>
-      <c r="F17" s="7">
-        <f>SUM(F5:F16)</f>
-        <v>119476.8</v>
-      </c>
-      <c r="G17" s="8">
-        <f>IF(F17&gt;0,C17/F17,"")</f>
-        <v>0.2121</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B18" s="7">
+        <f>SUM(B5:B17)</f>
+        <v>30274.4</v>
+      </c>
+      <c r="C18" s="7">
+        <f>SUM(C5:C17)</f>
+        <v>26917.2</v>
+      </c>
+      <c r="D18" s="7">
+        <f>SUM(D5:D17)</f>
+        <v>102104.4</v>
+      </c>
+      <c r="E18" s="7">
+        <f>SUM(E5:E17)</f>
+        <v>3357.2</v>
+      </c>
+      <c r="F18" s="7">
+        <f>SUM(F5:F17)</f>
+        <v>129021.6</v>
+      </c>
+      <c r="G18" s="8">
+        <f>IF(F18&gt;0,C18/F18,"")</f>
+        <v>0.2086</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -29327,7 +29351,2407 @@
         <v>103.526</v>
       </c>
     </row>
+    <row r="1154">
+      <c r="A1154" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C1154" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1154" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1154" s="3">
+        <v>103.68</v>
+      </c>
+      <c r="F1154" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1154" s="3">
+        <v>103.68</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C1155" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1155" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1155" s="3">
+        <v>103.526</v>
+      </c>
+      <c r="F1155" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1155" s="3">
+        <v>103.526</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1156" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C1156" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1156" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1156" s="3">
+        <v>103.322</v>
+      </c>
+      <c r="F1156" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1156" s="3">
+        <v>103.322</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1157" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C1157" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1157" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1157" s="3">
+        <v>103.322</v>
+      </c>
+      <c r="F1157" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1157" s="3">
+        <v>103.322</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C1158" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1158" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1158" s="3">
+        <v>103.526</v>
+      </c>
+      <c r="F1158" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1158" s="3">
+        <v>103.526</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C1159" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1159" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1159" s="3">
+        <v>103.987</v>
+      </c>
+      <c r="F1159" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1159" s="3">
+        <v>103.987</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C1160" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1160" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1160" s="3">
+        <v>103.629</v>
+      </c>
+      <c r="F1160" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1160" s="3">
+        <v>103.629</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1161" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C1161" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1161" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1161" s="3">
+        <v>103.066</v>
+      </c>
+      <c r="F1161" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1161" s="3">
+        <v>103.066</v>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C1162" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1162" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1162" s="3">
+        <v>103.066</v>
+      </c>
+      <c r="F1162" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1162" s="3">
+        <v>103.066</v>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C1163" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1163" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1163" s="3">
+        <v>103.219</v>
+      </c>
+      <c r="F1163" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1163" s="3">
+        <v>103.219</v>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C1164" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1164" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1164" s="3">
+        <v>103.117</v>
+      </c>
+      <c r="F1164" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1164" s="3">
+        <v>103.117</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C1165" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1165" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1165" s="3">
+        <v>103.066</v>
+      </c>
+      <c r="F1165" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1165" s="3">
+        <v>103.066</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C1166" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1166" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1166" s="3">
+        <v>103.066</v>
+      </c>
+      <c r="F1166" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1166" s="3">
+        <v>103.066</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C1167" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1167" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1167" s="3">
+        <v>103.373</v>
+      </c>
+      <c r="F1167" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1167" s="3">
+        <v>103.373</v>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C1168" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1168" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1168" s="3">
+        <v>103.219</v>
+      </c>
+      <c r="F1168" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1168" s="3">
+        <v>103.219</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C1169" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1169" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1169" s="3">
+        <v>103.27</v>
+      </c>
+      <c r="F1169" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1169" s="3">
+        <v>103.27</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C1170" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1170" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1170" s="3">
+        <v>103.27</v>
+      </c>
+      <c r="F1170" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1170" s="3">
+        <v>103.27</v>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C1171" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1171" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1171" s="3">
+        <v>103.014</v>
+      </c>
+      <c r="F1171" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1171" s="3">
+        <v>103.014</v>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C1172" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1172" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1172" s="3">
+        <v>102.963</v>
+      </c>
+      <c r="F1172" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1172" s="3">
+        <v>102.963</v>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C1173" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1173" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1173" s="3">
+        <v>103.373</v>
+      </c>
+      <c r="F1173" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1173" s="3">
+        <v>103.373</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C1174" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1174" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1174" s="3">
+        <v>102.963</v>
+      </c>
+      <c r="F1174" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1174" s="3">
+        <v>102.963</v>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C1175" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1175" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1175" s="3">
+        <v>103.066</v>
+      </c>
+      <c r="F1175" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1175" s="3">
+        <v>103.066</v>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C1176" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1176" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1176" s="3">
+        <v>103.066</v>
+      </c>
+      <c r="F1176" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1176" s="3">
+        <v>103.066</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C1177" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1177" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1177" s="3">
+        <v>103.168</v>
+      </c>
+      <c r="F1177" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1177" s="3">
+        <v>103.168</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C1178" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1178" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1178" s="3">
+        <v>103.885</v>
+      </c>
+      <c r="F1178" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1178" s="3">
+        <v>103.885</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1179" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C1179" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1179" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1179" s="3">
+        <v>103.168</v>
+      </c>
+      <c r="F1179" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1179" s="3">
+        <v>103.168</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1180" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C1180" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1180" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1180" s="3">
+        <v>103.424</v>
+      </c>
+      <c r="F1180" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1180" s="3">
+        <v>103.424</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C1181" s="3">
+        <v>0.064</v>
+      </c>
+      <c r="D1181" s="3">
+        <v>0.064</v>
+      </c>
+      <c r="E1181" s="3">
+        <v>103.219</v>
+      </c>
+      <c r="F1181" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1181" s="3">
+        <v>103.283</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C1182" s="3">
+        <v>1.28</v>
+      </c>
+      <c r="D1182" s="3">
+        <v>1.28</v>
+      </c>
+      <c r="E1182" s="3">
+        <v>101.939</v>
+      </c>
+      <c r="F1182" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1182" s="3">
+        <v>103.219</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1183" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C1183" s="3">
+        <v>3.546</v>
+      </c>
+      <c r="D1183" s="3">
+        <v>3.546</v>
+      </c>
+      <c r="E1183" s="3">
+        <v>99.789</v>
+      </c>
+      <c r="F1183" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1183" s="3">
+        <v>103.335</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1184" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C1184" s="3">
+        <v>3.597</v>
+      </c>
+      <c r="D1184" s="3">
+        <v>3.597</v>
+      </c>
+      <c r="E1184" s="3">
+        <v>99.584</v>
+      </c>
+      <c r="F1184" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1184" s="3">
+        <v>103.181</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C1185" s="3">
+        <v>3.622</v>
+      </c>
+      <c r="D1185" s="3">
+        <v>3.622</v>
+      </c>
+      <c r="E1185" s="3">
+        <v>110.336</v>
+      </c>
+      <c r="F1185" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1185" s="3">
+        <v>113.958</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1186" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C1186" s="3">
+        <v>5.926</v>
+      </c>
+      <c r="D1186" s="3">
+        <v>5.926</v>
+      </c>
+      <c r="E1186" s="3">
+        <v>132.454</v>
+      </c>
+      <c r="F1186" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1186" s="3">
+        <v>138.38</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1187" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C1187" s="3">
+        <v>6.477</v>
+      </c>
+      <c r="D1187" s="3">
+        <v>6.477</v>
+      </c>
+      <c r="E1187" s="3">
+        <v>132.506</v>
+      </c>
+      <c r="F1187" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1187" s="3">
+        <v>138.983</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C1188" s="3">
+        <v>12.262</v>
+      </c>
+      <c r="D1188" s="3">
+        <v>12.262</v>
+      </c>
+      <c r="E1188" s="3">
+        <v>95.795</v>
+      </c>
+      <c r="F1188" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1188" s="3">
+        <v>108.057</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C1189" s="3">
+        <v>6.221</v>
+      </c>
+      <c r="D1189" s="3">
+        <v>6.221</v>
+      </c>
+      <c r="E1189" s="3">
+        <v>101.734</v>
+      </c>
+      <c r="F1189" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1189" s="3">
+        <v>107.955</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C1190" s="3">
+        <v>14.758</v>
+      </c>
+      <c r="D1190" s="3">
+        <v>14.758</v>
+      </c>
+      <c r="E1190" s="3">
+        <v>93.491</v>
+      </c>
+      <c r="F1190" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1190" s="3">
+        <v>108.249</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1191" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C1191" s="3">
+        <v>13.632</v>
+      </c>
+      <c r="D1191" s="3">
+        <v>13.632</v>
+      </c>
+      <c r="E1191" s="3">
+        <v>94.566</v>
+      </c>
+      <c r="F1191" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1191" s="3">
+        <v>108.198</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C1192" s="3">
+        <v>14.976</v>
+      </c>
+      <c r="D1192" s="3">
+        <v>14.976</v>
+      </c>
+      <c r="E1192" s="3">
+        <v>141.619</v>
+      </c>
+      <c r="F1192" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1192" s="3">
+        <v>156.595</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1193" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C1193" s="3">
+        <v>11.277</v>
+      </c>
+      <c r="D1193" s="3">
+        <v>11.277</v>
+      </c>
+      <c r="E1193" s="3">
+        <v>137.728</v>
+      </c>
+      <c r="F1193" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1193" s="3">
+        <v>149.005</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C1194" s="3">
+        <v>13.632</v>
+      </c>
+      <c r="D1194" s="3">
+        <v>13.632</v>
+      </c>
+      <c r="E1194" s="3">
+        <v>129.638</v>
+      </c>
+      <c r="F1194" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1194" s="3">
+        <v>143.27</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C1195" s="3">
+        <v>15.974</v>
+      </c>
+      <c r="D1195" s="3">
+        <v>15.974</v>
+      </c>
+      <c r="E1195" s="3">
+        <v>107.469</v>
+      </c>
+      <c r="F1195" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1195" s="3">
+        <v>123.443</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C1196" s="3">
+        <v>23.258</v>
+      </c>
+      <c r="D1196" s="3">
+        <v>23.258</v>
+      </c>
+      <c r="E1196" s="3">
+        <v>86.374</v>
+      </c>
+      <c r="F1196" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1196" s="3">
+        <v>109.632</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1197" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C1197" s="3">
+        <v>18.752</v>
+      </c>
+      <c r="D1197" s="3">
+        <v>18.752</v>
+      </c>
+      <c r="E1197" s="3">
+        <v>91.238</v>
+      </c>
+      <c r="F1197" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1197" s="3">
+        <v>109.99</v>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1198" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C1198" s="3">
+        <v>29.53</v>
+      </c>
+      <c r="D1198" s="3">
+        <v>29.53</v>
+      </c>
+      <c r="E1198" s="3">
+        <v>81.05</v>
+      </c>
+      <c r="F1198" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1198" s="3">
+        <v>110.58</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1199" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C1199" s="3">
+        <v>44.262</v>
+      </c>
+      <c r="D1199" s="3">
+        <v>44.262</v>
+      </c>
+      <c r="E1199" s="3">
+        <v>37.734</v>
+      </c>
+      <c r="F1199" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1199" s="3">
+        <v>81.996</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1200" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C1200" s="3">
+        <v>43.174</v>
+      </c>
+      <c r="D1200" s="3">
+        <v>43.174</v>
+      </c>
+      <c r="E1200" s="3">
+        <v>32.666</v>
+      </c>
+      <c r="F1200" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1200" s="3">
+        <v>75.84</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1201" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C1201" s="3">
+        <v>53.414</v>
+      </c>
+      <c r="D1201" s="3">
+        <v>53.414</v>
+      </c>
+      <c r="E1201" s="3">
+        <v>21.965</v>
+      </c>
+      <c r="F1201" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1201" s="3">
+        <v>75.379</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1202" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C1202" s="3">
+        <v>65.766</v>
+      </c>
+      <c r="D1202" s="3">
+        <v>43.033</v>
+      </c>
+      <c r="E1202" s="3">
+        <v>0.922</v>
+      </c>
+      <c r="F1202" s="3">
+        <v>22.733</v>
+      </c>
+      <c r="G1202" s="3">
+        <v>43.955</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1203" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C1203" s="3">
+        <v>64.96</v>
+      </c>
+      <c r="D1203" s="3">
+        <v>44.275</v>
+      </c>
+      <c r="E1203" s="3">
+        <v>4.198</v>
+      </c>
+      <c r="F1203" s="3">
+        <v>20.685</v>
+      </c>
+      <c r="G1203" s="3">
+        <v>48.473</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1204" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C1204" s="3">
+        <v>58.931</v>
+      </c>
+      <c r="D1204" s="3">
+        <v>58.675</v>
+      </c>
+      <c r="E1204" s="3">
+        <v>14.131</v>
+      </c>
+      <c r="F1204" s="3">
+        <v>0.256</v>
+      </c>
+      <c r="G1204" s="3">
+        <v>72.806</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1205" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C1205" s="3">
+        <v>45.005</v>
+      </c>
+      <c r="D1205" s="3">
+        <v>45.005</v>
+      </c>
+      <c r="E1205" s="3">
+        <v>36.966</v>
+      </c>
+      <c r="F1205" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1205" s="3">
+        <v>81.971</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1206" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C1206" s="3">
+        <v>55.526</v>
+      </c>
+      <c r="D1206" s="3">
+        <v>55.526</v>
+      </c>
+      <c r="E1206" s="3">
+        <v>51.2</v>
+      </c>
+      <c r="F1206" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1206" s="3">
+        <v>106.726</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1207" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C1207" s="3">
+        <v>27.11</v>
+      </c>
+      <c r="D1207" s="3">
+        <v>27.11</v>
+      </c>
+      <c r="E1207" s="3">
+        <v>77.926</v>
+      </c>
+      <c r="F1207" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1207" s="3">
+        <v>105.036</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1208" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C1208" s="3">
+        <v>17.677</v>
+      </c>
+      <c r="D1208" s="3">
+        <v>17.677</v>
+      </c>
+      <c r="E1208" s="3">
+        <v>54.886</v>
+      </c>
+      <c r="F1208" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1208" s="3">
+        <v>72.563</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1209" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C1209" s="3">
+        <v>28.582</v>
+      </c>
+      <c r="D1209" s="3">
+        <v>28.582</v>
+      </c>
+      <c r="E1209" s="3">
+        <v>44.749</v>
+      </c>
+      <c r="F1209" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1209" s="3">
+        <v>73.331</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1210" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C1210" s="3">
+        <v>59.84</v>
+      </c>
+      <c r="D1210" s="3">
+        <v>57.178</v>
+      </c>
+      <c r="E1210" s="3">
+        <v>16.896</v>
+      </c>
+      <c r="F1210" s="3">
+        <v>2.662</v>
+      </c>
+      <c r="G1210" s="3">
+        <v>74.074</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1211" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C1211" s="3">
+        <v>72.998</v>
+      </c>
+      <c r="D1211" s="3">
+        <v>69.67</v>
+      </c>
+      <c r="E1211" s="3">
+        <v>2.458</v>
+      </c>
+      <c r="F1211" s="3">
+        <v>3.328</v>
+      </c>
+      <c r="G1211" s="3">
+        <v>72.128</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C1212" s="3">
+        <v>67.046</v>
+      </c>
+      <c r="D1212" s="3">
+        <v>55.526</v>
+      </c>
+      <c r="E1212" s="3">
+        <v>5.171</v>
+      </c>
+      <c r="F1212" s="3">
+        <v>11.52</v>
+      </c>
+      <c r="G1212" s="3">
+        <v>60.697</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1213" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C1213" s="3">
+        <v>70.822</v>
+      </c>
+      <c r="D1213" s="3">
+        <v>39.385</v>
+      </c>
+      <c r="E1213" s="3">
+        <v>0.154</v>
+      </c>
+      <c r="F1213" s="3">
+        <v>31.437</v>
+      </c>
+      <c r="G1213" s="3">
+        <v>39.539</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1214" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C1214" s="3">
+        <v>38.758</v>
+      </c>
+      <c r="D1214" s="3">
+        <v>38.758</v>
+      </c>
+      <c r="E1214" s="3">
+        <v>33.075</v>
+      </c>
+      <c r="F1214" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1214" s="3">
+        <v>71.833</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1215" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C1215" s="3">
+        <v>29.299</v>
+      </c>
+      <c r="D1215" s="3">
+        <v>29.299</v>
+      </c>
+      <c r="E1215" s="3">
+        <v>43.264</v>
+      </c>
+      <c r="F1215" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1215" s="3">
+        <v>72.563</v>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1216" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C1216" s="3">
+        <v>28.339</v>
+      </c>
+      <c r="D1216" s="3">
+        <v>28.339</v>
+      </c>
+      <c r="E1216" s="3">
+        <v>44.544</v>
+      </c>
+      <c r="F1216" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1216" s="3">
+        <v>72.883</v>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1217" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C1217" s="3">
+        <v>55.04</v>
+      </c>
+      <c r="D1217" s="3">
+        <v>52.736</v>
+      </c>
+      <c r="E1217" s="3">
+        <v>20.275</v>
+      </c>
+      <c r="F1217" s="3">
+        <v>2.304</v>
+      </c>
+      <c r="G1217" s="3">
+        <v>73.011</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1218" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C1218" s="3">
+        <v>94.246</v>
+      </c>
+      <c r="D1218" s="3">
+        <v>67.52</v>
+      </c>
+      <c r="E1218" s="3">
+        <v>4.864</v>
+      </c>
+      <c r="F1218" s="3">
+        <v>26.726</v>
+      </c>
+      <c r="G1218" s="3">
+        <v>72.384</v>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1219" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C1219" s="3">
+        <v>81.229</v>
+      </c>
+      <c r="D1219" s="3">
+        <v>69.043</v>
+      </c>
+      <c r="E1219" s="3">
+        <v>10.957</v>
+      </c>
+      <c r="F1219" s="3">
+        <v>12.186</v>
+      </c>
+      <c r="G1219" s="3">
+        <v>80.0</v>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1220" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C1220" s="3">
+        <v>84.134</v>
+      </c>
+      <c r="D1220" s="3">
+        <v>84.134</v>
+      </c>
+      <c r="E1220" s="3">
+        <v>23.296</v>
+      </c>
+      <c r="F1220" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1220" s="3">
+        <v>107.43</v>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1221" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C1221" s="3">
+        <v>69.453</v>
+      </c>
+      <c r="D1221" s="3">
+        <v>69.453</v>
+      </c>
+      <c r="E1221" s="3">
+        <v>38.144</v>
+      </c>
+      <c r="F1221" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1221" s="3">
+        <v>107.597</v>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1222" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C1222" s="3">
+        <v>61.85</v>
+      </c>
+      <c r="D1222" s="3">
+        <v>61.85</v>
+      </c>
+      <c r="E1222" s="3">
+        <v>46.182</v>
+      </c>
+      <c r="F1222" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1222" s="3">
+        <v>108.032</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1223" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C1223" s="3">
+        <v>52.07</v>
+      </c>
+      <c r="D1223" s="3">
+        <v>52.07</v>
+      </c>
+      <c r="E1223" s="3">
+        <v>55.552</v>
+      </c>
+      <c r="F1223" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1223" s="3">
+        <v>107.622</v>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1224" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C1224" s="3">
+        <v>44.646</v>
+      </c>
+      <c r="D1224" s="3">
+        <v>44.646</v>
+      </c>
+      <c r="E1224" s="3">
+        <v>62.669</v>
+      </c>
+      <c r="F1224" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1224" s="3">
+        <v>107.315</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1225" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C1225" s="3">
+        <v>36.198</v>
+      </c>
+      <c r="D1225" s="3">
+        <v>36.198</v>
+      </c>
+      <c r="E1225" s="3">
+        <v>71.168</v>
+      </c>
+      <c r="F1225" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1225" s="3">
+        <v>107.366</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1226" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C1226" s="3">
+        <v>27.814</v>
+      </c>
+      <c r="D1226" s="3">
+        <v>27.814</v>
+      </c>
+      <c r="E1226" s="3">
+        <v>80.589</v>
+      </c>
+      <c r="F1226" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1226" s="3">
+        <v>108.403</v>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1227" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C1227" s="3">
+        <v>19.315</v>
+      </c>
+      <c r="D1227" s="3">
+        <v>19.315</v>
+      </c>
+      <c r="E1227" s="3">
+        <v>89.6</v>
+      </c>
+      <c r="F1227" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1227" s="3">
+        <v>108.915</v>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1228" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C1228" s="3">
+        <v>11.917</v>
+      </c>
+      <c r="D1228" s="3">
+        <v>11.917</v>
+      </c>
+      <c r="E1228" s="3">
+        <v>96.358</v>
+      </c>
+      <c r="F1228" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1228" s="3">
+        <v>108.275</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1229" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C1229" s="3">
+        <v>4.403</v>
+      </c>
+      <c r="D1229" s="3">
+        <v>4.403</v>
+      </c>
+      <c r="E1229" s="3">
+        <v>103.117</v>
+      </c>
+      <c r="F1229" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1229" s="3">
+        <v>107.52</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1230" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C1230" s="3">
+        <v>0.998</v>
+      </c>
+      <c r="D1230" s="3">
+        <v>0.998</v>
+      </c>
+      <c r="E1230" s="3">
+        <v>85.76</v>
+      </c>
+      <c r="F1230" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1230" s="3">
+        <v>86.758</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1231" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C1231" s="3">
+        <v>0.294</v>
+      </c>
+      <c r="D1231" s="3">
+        <v>0.294</v>
+      </c>
+      <c r="E1231" s="3">
+        <v>23.142</v>
+      </c>
+      <c r="F1231" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1231" s="3">
+        <v>23.436</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1232" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C1232" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="D1232" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="E1232" s="3">
+        <v>107.366</v>
+      </c>
+      <c r="F1232" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1232" s="3">
+        <v>107.379</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1233" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C1233" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1233" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1233" s="3">
+        <v>108.032</v>
+      </c>
+      <c r="F1233" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1233" s="3">
+        <v>108.032</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1234" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C1234" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1234" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1234" s="3">
+        <v>107.776</v>
+      </c>
+      <c r="F1234" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1234" s="3">
+        <v>107.776</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1235" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C1235" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1235" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1235" s="3">
+        <v>105.216</v>
+      </c>
+      <c r="F1235" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1235" s="3">
+        <v>105.216</v>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C1236" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1236" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1236" s="3">
+        <v>105.267</v>
+      </c>
+      <c r="F1236" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1236" s="3">
+        <v>105.267</v>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1237" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C1237" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1237" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1237" s="3">
+        <v>105.779</v>
+      </c>
+      <c r="F1237" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1237" s="3">
+        <v>105.779</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1238" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C1238" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1238" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1238" s="3">
+        <v>104.755</v>
+      </c>
+      <c r="F1238" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1238" s="3">
+        <v>104.755</v>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1239" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C1239" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1239" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1239" s="3">
+        <v>104.755</v>
+      </c>
+      <c r="F1239" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1239" s="3">
+        <v>104.755</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1240" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C1240" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1240" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1240" s="3">
+        <v>104.909</v>
+      </c>
+      <c r="F1240" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1240" s="3">
+        <v>104.909</v>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1241" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C1241" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1241" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1241" s="3">
+        <v>105.267</v>
+      </c>
+      <c r="F1241" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1241" s="3">
+        <v>105.267</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1242" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C1242" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1242" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1242" s="3">
+        <v>105.626</v>
+      </c>
+      <c r="F1242" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1242" s="3">
+        <v>105.626</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1243" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C1243" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1243" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1243" s="3">
+        <v>105.728</v>
+      </c>
+      <c r="F1243" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1243" s="3">
+        <v>105.728</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1244" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C1244" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1244" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1244" s="3">
+        <v>104.96</v>
+      </c>
+      <c r="F1244" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1244" s="3">
+        <v>104.96</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1245" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C1245" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1245" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1245" s="3">
+        <v>104.858</v>
+      </c>
+      <c r="F1245" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1245" s="3">
+        <v>104.858</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1246" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C1246" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1246" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1246" s="3">
+        <v>104.909</v>
+      </c>
+      <c r="F1246" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1246" s="3">
+        <v>104.909</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1247" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C1247" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1247" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1247" s="3">
+        <v>104.909</v>
+      </c>
+      <c r="F1247" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1247" s="3">
+        <v>104.909</v>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1248" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C1248" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1248" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1248" s="3">
+        <v>105.472</v>
+      </c>
+      <c r="F1248" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1248" s="3">
+        <v>105.472</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B1249" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C1249" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1249" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1249" s="3">
+        <v>105.165</v>
+      </c>
+      <c r="F1249" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1249" s="3">
+        <v>105.165</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1153"/>
+  <autoFilter ref="A1:G1249"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -454,45 +454,69 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B18" s="4">
+        <v>1979.7</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1919.2</v>
+      </c>
+      <c r="D18" s="4">
+        <v>8019.7</v>
+      </c>
+      <c r="E18" s="4">
+        <v>60.5</v>
+      </c>
+      <c r="F18" s="4">
+        <v>9938.9</v>
+      </c>
+      <c r="G18" s="5">
+        <f>IF(F18&gt;0,C18/F18,"")</f>
+        <v>0.1931</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B18" s="7">
-        <f>SUM(B5:B17)</f>
-        <v>30274.4</v>
-      </c>
-      <c r="C18" s="7">
-        <f>SUM(C5:C17)</f>
-        <v>26917.2</v>
-      </c>
-      <c r="D18" s="7">
-        <f>SUM(D5:D17)</f>
-        <v>102104.4</v>
-      </c>
-      <c r="E18" s="7">
-        <f>SUM(E5:E17)</f>
-        <v>3357.2</v>
-      </c>
-      <c r="F18" s="7">
-        <f>SUM(F5:F17)</f>
-        <v>129021.6</v>
-      </c>
-      <c r="G18" s="8">
-        <f>IF(F18&gt;0,C18/F18,"")</f>
-        <v>0.2086</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B19" s="7">
+        <f>SUM(B5:B18)</f>
+        <v>32254.2</v>
+      </c>
+      <c r="C19" s="7">
+        <f>SUM(C5:C18)</f>
+        <v>28836.4</v>
+      </c>
+      <c r="D19" s="7">
+        <f>SUM(D5:D18)</f>
+        <v>110124.0</v>
+      </c>
+      <c r="E19" s="7">
+        <f>SUM(E5:E18)</f>
+        <v>3417.8</v>
+      </c>
+      <c r="F19" s="7">
+        <f>SUM(F5:F18)</f>
+        <v>138960.4</v>
+      </c>
+      <c r="G19" s="8">
+        <f>IF(F19&gt;0,C19/F19,"")</f>
+        <v>0.2075</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -31751,7 +31775,2407 @@
         <v>105.165</v>
       </c>
     </row>
+    <row r="1250">
+      <c r="A1250" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1250" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C1250" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1250" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1250" s="3">
+        <v>105.267</v>
+      </c>
+      <c r="F1250" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1250" s="3">
+        <v>105.267</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1251" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C1251" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1251" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1251" s="3">
+        <v>105.318</v>
+      </c>
+      <c r="F1251" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1251" s="3">
+        <v>105.318</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1252" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C1252" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1252" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1252" s="3">
+        <v>105.216</v>
+      </c>
+      <c r="F1252" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1252" s="3">
+        <v>105.216</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1253" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C1253" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1253" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1253" s="3">
+        <v>105.318</v>
+      </c>
+      <c r="F1253" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1253" s="3">
+        <v>105.318</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1254" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C1254" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1254" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1254" s="3">
+        <v>105.267</v>
+      </c>
+      <c r="F1254" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1254" s="3">
+        <v>105.267</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1255" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C1255" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1255" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1255" s="3">
+        <v>104.96</v>
+      </c>
+      <c r="F1255" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1255" s="3">
+        <v>104.96</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1256" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C1256" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1256" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1256" s="3">
+        <v>104.858</v>
+      </c>
+      <c r="F1256" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1256" s="3">
+        <v>104.858</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1257" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C1257" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1257" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1257" s="3">
+        <v>104.858</v>
+      </c>
+      <c r="F1257" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1257" s="3">
+        <v>104.858</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1258" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C1258" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1258" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1258" s="3">
+        <v>105.011</v>
+      </c>
+      <c r="F1258" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1258" s="3">
+        <v>105.011</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1259" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C1259" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1259" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1259" s="3">
+        <v>104.909</v>
+      </c>
+      <c r="F1259" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1259" s="3">
+        <v>104.909</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1260" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C1260" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1260" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1260" s="3">
+        <v>105.114</v>
+      </c>
+      <c r="F1260" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1260" s="3">
+        <v>105.114</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1261" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C1261" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1261" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1261" s="3">
+        <v>105.011</v>
+      </c>
+      <c r="F1261" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1261" s="3">
+        <v>105.011</v>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1262" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C1262" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1262" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1262" s="3">
+        <v>105.011</v>
+      </c>
+      <c r="F1262" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1262" s="3">
+        <v>105.011</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1263" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C1263" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1263" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1263" s="3">
+        <v>105.011</v>
+      </c>
+      <c r="F1263" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1263" s="3">
+        <v>105.011</v>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1264" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C1264" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1264" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1264" s="3">
+        <v>105.267</v>
+      </c>
+      <c r="F1264" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1264" s="3">
+        <v>105.267</v>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1265" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C1265" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1265" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1265" s="3">
+        <v>105.882</v>
+      </c>
+      <c r="F1265" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1265" s="3">
+        <v>105.882</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1266" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C1266" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1266" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1266" s="3">
+        <v>105.472</v>
+      </c>
+      <c r="F1266" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1266" s="3">
+        <v>105.472</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C1267" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1267" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1267" s="3">
+        <v>105.165</v>
+      </c>
+      <c r="F1267" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1267" s="3">
+        <v>105.165</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1268" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C1268" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1268" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1268" s="3">
+        <v>105.011</v>
+      </c>
+      <c r="F1268" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1268" s="3">
+        <v>105.011</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1269" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C1269" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1269" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1269" s="3">
+        <v>105.267</v>
+      </c>
+      <c r="F1269" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1269" s="3">
+        <v>105.267</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1270" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C1270" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1270" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1270" s="3">
+        <v>105.421</v>
+      </c>
+      <c r="F1270" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1270" s="3">
+        <v>105.421</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1271" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C1271" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1271" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1271" s="3">
+        <v>104.909</v>
+      </c>
+      <c r="F1271" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1271" s="3">
+        <v>104.909</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1272" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C1272" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1272" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1272" s="3">
+        <v>105.062</v>
+      </c>
+      <c r="F1272" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1272" s="3">
+        <v>105.062</v>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1273" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C1273" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1273" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1273" s="3">
+        <v>105.062</v>
+      </c>
+      <c r="F1273" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1273" s="3">
+        <v>105.062</v>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1274" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C1274" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1274" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1274" s="3">
+        <v>105.267</v>
+      </c>
+      <c r="F1274" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1274" s="3">
+        <v>105.267</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1275" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C1275" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1275" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1275" s="3">
+        <v>105.421</v>
+      </c>
+      <c r="F1275" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1275" s="3">
+        <v>105.421</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1276" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C1276" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1276" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1276" s="3">
+        <v>105.318</v>
+      </c>
+      <c r="F1276" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1276" s="3">
+        <v>105.318</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1277" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C1277" s="3">
+        <v>0.038</v>
+      </c>
+      <c r="D1277" s="3">
+        <v>0.038</v>
+      </c>
+      <c r="E1277" s="3">
+        <v>105.165</v>
+      </c>
+      <c r="F1277" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1277" s="3">
+        <v>105.203</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1278" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C1278" s="3">
+        <v>0.947</v>
+      </c>
+      <c r="D1278" s="3">
+        <v>0.947</v>
+      </c>
+      <c r="E1278" s="3">
+        <v>104.038</v>
+      </c>
+      <c r="F1278" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1278" s="3">
+        <v>104.985</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1279" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C1279" s="3">
+        <v>2.074</v>
+      </c>
+      <c r="D1279" s="3">
+        <v>2.074</v>
+      </c>
+      <c r="E1279" s="3">
+        <v>102.861</v>
+      </c>
+      <c r="F1279" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1279" s="3">
+        <v>104.935</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1280" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C1280" s="3">
+        <v>8.755</v>
+      </c>
+      <c r="D1280" s="3">
+        <v>8.755</v>
+      </c>
+      <c r="E1280" s="3">
+        <v>96.461</v>
+      </c>
+      <c r="F1280" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1280" s="3">
+        <v>105.216</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1281" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C1281" s="3">
+        <v>15.066</v>
+      </c>
+      <c r="D1281" s="3">
+        <v>15.066</v>
+      </c>
+      <c r="E1281" s="3">
+        <v>91.29</v>
+      </c>
+      <c r="F1281" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1281" s="3">
+        <v>106.356</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1282" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C1282" s="3">
+        <v>17.856</v>
+      </c>
+      <c r="D1282" s="3">
+        <v>17.856</v>
+      </c>
+      <c r="E1282" s="3">
+        <v>87.706</v>
+      </c>
+      <c r="F1282" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1282" s="3">
+        <v>105.562</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1283" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C1283" s="3">
+        <v>21.03</v>
+      </c>
+      <c r="D1283" s="3">
+        <v>21.03</v>
+      </c>
+      <c r="E1283" s="3">
+        <v>84.122</v>
+      </c>
+      <c r="F1283" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1283" s="3">
+        <v>105.152</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1284" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C1284" s="3">
+        <v>19.494</v>
+      </c>
+      <c r="D1284" s="3">
+        <v>19.494</v>
+      </c>
+      <c r="E1284" s="3">
+        <v>90.419</v>
+      </c>
+      <c r="F1284" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1284" s="3">
+        <v>109.913</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1285" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C1285" s="3">
+        <v>51.405</v>
+      </c>
+      <c r="D1285" s="3">
+        <v>51.405</v>
+      </c>
+      <c r="E1285" s="3">
+        <v>55.398</v>
+      </c>
+      <c r="F1285" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1285" s="3">
+        <v>106.803</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C1286" s="3">
+        <v>31.245</v>
+      </c>
+      <c r="D1286" s="3">
+        <v>31.245</v>
+      </c>
+      <c r="E1286" s="3">
+        <v>76.851</v>
+      </c>
+      <c r="F1286" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1286" s="3">
+        <v>108.096</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1287" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C1287" s="3">
+        <v>16.269</v>
+      </c>
+      <c r="D1287" s="3">
+        <v>16.269</v>
+      </c>
+      <c r="E1287" s="3">
+        <v>91.392</v>
+      </c>
+      <c r="F1287" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1287" s="3">
+        <v>107.661</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1288" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C1288" s="3">
+        <v>15.206</v>
+      </c>
+      <c r="D1288" s="3">
+        <v>15.206</v>
+      </c>
+      <c r="E1288" s="3">
+        <v>92.467</v>
+      </c>
+      <c r="F1288" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1288" s="3">
+        <v>107.673</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1289" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C1289" s="3">
+        <v>20.557</v>
+      </c>
+      <c r="D1289" s="3">
+        <v>20.557</v>
+      </c>
+      <c r="E1289" s="3">
+        <v>87.245</v>
+      </c>
+      <c r="F1289" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1289" s="3">
+        <v>107.802</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C1290" s="3">
+        <v>26.675</v>
+      </c>
+      <c r="D1290" s="3">
+        <v>26.675</v>
+      </c>
+      <c r="E1290" s="3">
+        <v>81.869</v>
+      </c>
+      <c r="F1290" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1290" s="3">
+        <v>108.544</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C1291" s="3">
+        <v>53.645</v>
+      </c>
+      <c r="D1291" s="3">
+        <v>53.645</v>
+      </c>
+      <c r="E1291" s="3">
+        <v>55.091</v>
+      </c>
+      <c r="F1291" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1291" s="3">
+        <v>108.736</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C1292" s="3">
+        <v>90.931</v>
+      </c>
+      <c r="D1292" s="3">
+        <v>90.214</v>
+      </c>
+      <c r="E1292" s="3">
+        <v>18.176</v>
+      </c>
+      <c r="F1292" s="3">
+        <v>0.717</v>
+      </c>
+      <c r="G1292" s="3">
+        <v>108.39</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1293" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C1293" s="3">
+        <v>83.405</v>
+      </c>
+      <c r="D1293" s="3">
+        <v>82.791</v>
+      </c>
+      <c r="E1293" s="3">
+        <v>26.01</v>
+      </c>
+      <c r="F1293" s="3">
+        <v>0.614</v>
+      </c>
+      <c r="G1293" s="3">
+        <v>108.801</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1294" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C1294" s="3">
+        <v>52.211</v>
+      </c>
+      <c r="D1294" s="3">
+        <v>52.16</v>
+      </c>
+      <c r="E1294" s="3">
+        <v>56.013</v>
+      </c>
+      <c r="F1294" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G1294" s="3">
+        <v>108.173</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1295" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C1295" s="3">
+        <v>70.669</v>
+      </c>
+      <c r="D1295" s="3">
+        <v>69.952</v>
+      </c>
+      <c r="E1295" s="3">
+        <v>38.502</v>
+      </c>
+      <c r="F1295" s="3">
+        <v>0.717</v>
+      </c>
+      <c r="G1295" s="3">
+        <v>108.454</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1296" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C1296" s="3">
+        <v>98.982</v>
+      </c>
+      <c r="D1296" s="3">
+        <v>96.115</v>
+      </c>
+      <c r="E1296" s="3">
+        <v>12.902</v>
+      </c>
+      <c r="F1296" s="3">
+        <v>2.867</v>
+      </c>
+      <c r="G1296" s="3">
+        <v>109.017</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1297" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C1297" s="3">
+        <v>46.784</v>
+      </c>
+      <c r="D1297" s="3">
+        <v>46.784</v>
+      </c>
+      <c r="E1297" s="3">
+        <v>61.133</v>
+      </c>
+      <c r="F1297" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1297" s="3">
+        <v>107.917</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1298" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C1298" s="3">
+        <v>102.067</v>
+      </c>
+      <c r="D1298" s="3">
+        <v>98.381</v>
+      </c>
+      <c r="E1298" s="3">
+        <v>9.728</v>
+      </c>
+      <c r="F1298" s="3">
+        <v>3.686</v>
+      </c>
+      <c r="G1298" s="3">
+        <v>108.109</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1299" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C1299" s="3">
+        <v>62.49</v>
+      </c>
+      <c r="D1299" s="3">
+        <v>60.237</v>
+      </c>
+      <c r="E1299" s="3">
+        <v>48.179</v>
+      </c>
+      <c r="F1299" s="3">
+        <v>2.253</v>
+      </c>
+      <c r="G1299" s="3">
+        <v>108.416</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1300" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C1300" s="3">
+        <v>43.341</v>
+      </c>
+      <c r="D1300" s="3">
+        <v>43.341</v>
+      </c>
+      <c r="E1300" s="3">
+        <v>64.41</v>
+      </c>
+      <c r="F1300" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1300" s="3">
+        <v>107.751</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1301" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C1301" s="3">
+        <v>67.226</v>
+      </c>
+      <c r="D1301" s="3">
+        <v>66.663</v>
+      </c>
+      <c r="E1301" s="3">
+        <v>40.909</v>
+      </c>
+      <c r="F1301" s="3">
+        <v>0.563</v>
+      </c>
+      <c r="G1301" s="3">
+        <v>107.572</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1302" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C1302" s="3">
+        <v>67.405</v>
+      </c>
+      <c r="D1302" s="3">
+        <v>67.251</v>
+      </c>
+      <c r="E1302" s="3">
+        <v>41.011</v>
+      </c>
+      <c r="F1302" s="3">
+        <v>0.154</v>
+      </c>
+      <c r="G1302" s="3">
+        <v>108.262</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1303" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C1303" s="3">
+        <v>49.997</v>
+      </c>
+      <c r="D1303" s="3">
+        <v>49.843</v>
+      </c>
+      <c r="E1303" s="3">
+        <v>58.368</v>
+      </c>
+      <c r="F1303" s="3">
+        <v>0.154</v>
+      </c>
+      <c r="G1303" s="3">
+        <v>108.211</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1304" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C1304" s="3">
+        <v>55.949</v>
+      </c>
+      <c r="D1304" s="3">
+        <v>55.744</v>
+      </c>
+      <c r="E1304" s="3">
+        <v>52.429</v>
+      </c>
+      <c r="F1304" s="3">
+        <v>0.205</v>
+      </c>
+      <c r="G1304" s="3">
+        <v>108.173</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1305" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C1305" s="3">
+        <v>50.624</v>
+      </c>
+      <c r="D1305" s="3">
+        <v>50.266</v>
+      </c>
+      <c r="E1305" s="3">
+        <v>58.214</v>
+      </c>
+      <c r="F1305" s="3">
+        <v>0.358</v>
+      </c>
+      <c r="G1305" s="3">
+        <v>108.48</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1306" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C1306" s="3">
+        <v>44.48</v>
+      </c>
+      <c r="D1306" s="3">
+        <v>44.48</v>
+      </c>
+      <c r="E1306" s="3">
+        <v>64.154</v>
+      </c>
+      <c r="F1306" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1306" s="3">
+        <v>108.634</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1307" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C1307" s="3">
+        <v>69.12</v>
+      </c>
+      <c r="D1307" s="3">
+        <v>67.738</v>
+      </c>
+      <c r="E1307" s="3">
+        <v>40.806</v>
+      </c>
+      <c r="F1307" s="3">
+        <v>1.382</v>
+      </c>
+      <c r="G1307" s="3">
+        <v>108.544</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1308" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C1308" s="3">
+        <v>46.848</v>
+      </c>
+      <c r="D1308" s="3">
+        <v>46.643</v>
+      </c>
+      <c r="E1308" s="3">
+        <v>61.747</v>
+      </c>
+      <c r="F1308" s="3">
+        <v>0.205</v>
+      </c>
+      <c r="G1308" s="3">
+        <v>108.39</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1309" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C1309" s="3">
+        <v>29.581</v>
+      </c>
+      <c r="D1309" s="3">
+        <v>29.581</v>
+      </c>
+      <c r="E1309" s="3">
+        <v>48.486</v>
+      </c>
+      <c r="F1309" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1309" s="3">
+        <v>78.067</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1310" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C1310" s="3">
+        <v>22.976</v>
+      </c>
+      <c r="D1310" s="3">
+        <v>22.976</v>
+      </c>
+      <c r="E1310" s="3">
+        <v>49.203</v>
+      </c>
+      <c r="F1310" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1310" s="3">
+        <v>72.179</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1311" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C1311" s="3">
+        <v>32.922</v>
+      </c>
+      <c r="D1311" s="3">
+        <v>32.922</v>
+      </c>
+      <c r="E1311" s="3">
+        <v>39.219</v>
+      </c>
+      <c r="F1311" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1311" s="3">
+        <v>72.141</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1312" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C1312" s="3">
+        <v>52.186</v>
+      </c>
+      <c r="D1312" s="3">
+        <v>49.626</v>
+      </c>
+      <c r="E1312" s="3">
+        <v>22.989</v>
+      </c>
+      <c r="F1312" s="3">
+        <v>2.56</v>
+      </c>
+      <c r="G1312" s="3">
+        <v>72.615</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1313" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C1313" s="3">
+        <v>105.728</v>
+      </c>
+      <c r="D1313" s="3">
+        <v>72.96</v>
+      </c>
+      <c r="E1313" s="3">
+        <v>0.512</v>
+      </c>
+      <c r="F1313" s="3">
+        <v>32.768</v>
+      </c>
+      <c r="G1313" s="3">
+        <v>73.472</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1314" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C1314" s="3">
+        <v>59.661</v>
+      </c>
+      <c r="D1314" s="3">
+        <v>48.653</v>
+      </c>
+      <c r="E1314" s="3">
+        <v>24.883</v>
+      </c>
+      <c r="F1314" s="3">
+        <v>11.008</v>
+      </c>
+      <c r="G1314" s="3">
+        <v>73.536</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1315" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C1315" s="3">
+        <v>38.797</v>
+      </c>
+      <c r="D1315" s="3">
+        <v>38.541</v>
+      </c>
+      <c r="E1315" s="3">
+        <v>33.894</v>
+      </c>
+      <c r="F1315" s="3">
+        <v>0.256</v>
+      </c>
+      <c r="G1315" s="3">
+        <v>72.435</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1316" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C1316" s="3">
+        <v>32.781</v>
+      </c>
+      <c r="D1316" s="3">
+        <v>32.781</v>
+      </c>
+      <c r="E1316" s="3">
+        <v>40.038</v>
+      </c>
+      <c r="F1316" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1316" s="3">
+        <v>72.819</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1317" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C1317" s="3">
+        <v>32.538</v>
+      </c>
+      <c r="D1317" s="3">
+        <v>32.538</v>
+      </c>
+      <c r="E1317" s="3">
+        <v>71.27</v>
+      </c>
+      <c r="F1317" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1317" s="3">
+        <v>103.808</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1318" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C1318" s="3">
+        <v>54.554</v>
+      </c>
+      <c r="D1318" s="3">
+        <v>54.554</v>
+      </c>
+      <c r="E1318" s="3">
+        <v>52.326</v>
+      </c>
+      <c r="F1318" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1318" s="3">
+        <v>106.88</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1319" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C1319" s="3">
+        <v>43.277</v>
+      </c>
+      <c r="D1319" s="3">
+        <v>43.277</v>
+      </c>
+      <c r="E1319" s="3">
+        <v>64.256</v>
+      </c>
+      <c r="F1319" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1319" s="3">
+        <v>107.533</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1320" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C1320" s="3">
+        <v>23.885</v>
+      </c>
+      <c r="D1320" s="3">
+        <v>23.885</v>
+      </c>
+      <c r="E1320" s="3">
+        <v>82.995</v>
+      </c>
+      <c r="F1320" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1320" s="3">
+        <v>106.88</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1321" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C1321" s="3">
+        <v>10.496</v>
+      </c>
+      <c r="D1321" s="3">
+        <v>10.496</v>
+      </c>
+      <c r="E1321" s="3">
+        <v>97.638</v>
+      </c>
+      <c r="F1321" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1321" s="3">
+        <v>108.134</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1322" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C1322" s="3">
+        <v>11.072</v>
+      </c>
+      <c r="D1322" s="3">
+        <v>11.072</v>
+      </c>
+      <c r="E1322" s="3">
+        <v>96.768</v>
+      </c>
+      <c r="F1322" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1322" s="3">
+        <v>107.84</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1323" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C1323" s="3">
+        <v>11.315</v>
+      </c>
+      <c r="D1323" s="3">
+        <v>11.315</v>
+      </c>
+      <c r="E1323" s="3">
+        <v>95.642</v>
+      </c>
+      <c r="F1323" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1323" s="3">
+        <v>106.957</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1324" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C1324" s="3">
+        <v>6.285</v>
+      </c>
+      <c r="D1324" s="3">
+        <v>6.285</v>
+      </c>
+      <c r="E1324" s="3">
+        <v>100.71</v>
+      </c>
+      <c r="F1324" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1324" s="3">
+        <v>106.995</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1325" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C1325" s="3">
+        <v>5.901</v>
+      </c>
+      <c r="D1325" s="3">
+        <v>5.901</v>
+      </c>
+      <c r="E1325" s="3">
+        <v>100.608</v>
+      </c>
+      <c r="F1325" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1325" s="3">
+        <v>106.509</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1326" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C1326" s="3">
+        <v>2.778</v>
+      </c>
+      <c r="D1326" s="3">
+        <v>2.778</v>
+      </c>
+      <c r="E1326" s="3">
+        <v>103.834</v>
+      </c>
+      <c r="F1326" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1326" s="3">
+        <v>106.612</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1327" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C1327" s="3">
+        <v>0.218</v>
+      </c>
+      <c r="D1327" s="3">
+        <v>0.218</v>
+      </c>
+      <c r="E1327" s="3">
+        <v>106.138</v>
+      </c>
+      <c r="F1327" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1327" s="3">
+        <v>106.356</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1328" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C1328" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1328" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1328" s="3">
+        <v>106.342</v>
+      </c>
+      <c r="F1328" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1328" s="3">
+        <v>106.342</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1329" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C1329" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1329" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1329" s="3">
+        <v>106.445</v>
+      </c>
+      <c r="F1329" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1329" s="3">
+        <v>106.445</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1330" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C1330" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1330" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1330" s="3">
+        <v>106.598</v>
+      </c>
+      <c r="F1330" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1330" s="3">
+        <v>106.598</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1331" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C1331" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1331" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1331" s="3">
+        <v>106.496</v>
+      </c>
+      <c r="F1331" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1331" s="3">
+        <v>106.496</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1332" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C1332" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1332" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1332" s="3">
+        <v>106.496</v>
+      </c>
+      <c r="F1332" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1332" s="3">
+        <v>106.496</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1333" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C1333" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1333" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1333" s="3">
+        <v>106.445</v>
+      </c>
+      <c r="F1333" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1333" s="3">
+        <v>106.445</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1334" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C1334" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1334" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1334" s="3">
+        <v>106.65</v>
+      </c>
+      <c r="F1334" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1334" s="3">
+        <v>106.65</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1335" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C1335" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1335" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1335" s="3">
+        <v>106.445</v>
+      </c>
+      <c r="F1335" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1335" s="3">
+        <v>106.445</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1336" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C1336" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1336" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1336" s="3">
+        <v>103.987</v>
+      </c>
+      <c r="F1336" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1336" s="3">
+        <v>103.987</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1337" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C1337" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1337" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1337" s="3">
+        <v>103.526</v>
+      </c>
+      <c r="F1337" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1337" s="3">
+        <v>103.526</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1338" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C1338" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1338" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1338" s="3">
+        <v>103.782</v>
+      </c>
+      <c r="F1338" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1338" s="3">
+        <v>103.782</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1339" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C1339" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1339" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1339" s="3">
+        <v>104.141</v>
+      </c>
+      <c r="F1339" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1339" s="3">
+        <v>104.141</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1340" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C1340" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1340" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1340" s="3">
+        <v>104.192</v>
+      </c>
+      <c r="F1340" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1340" s="3">
+        <v>104.192</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1341" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C1341" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1341" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1341" s="3">
+        <v>104.55</v>
+      </c>
+      <c r="F1341" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1341" s="3">
+        <v>104.55</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1342" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C1342" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1342" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1342" s="3">
+        <v>103.987</v>
+      </c>
+      <c r="F1342" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1342" s="3">
+        <v>103.987</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1343" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C1343" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1343" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1343" s="3">
+        <v>104.243</v>
+      </c>
+      <c r="F1343" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1343" s="3">
+        <v>104.243</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1344" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C1344" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1344" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1344" s="3">
+        <v>104.806</v>
+      </c>
+      <c r="F1344" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1344" s="3">
+        <v>104.806</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="2">
+        <v>46309</v>
+      </c>
+      <c r="B1345" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C1345" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1345" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1345" s="3">
+        <v>104.397</v>
+      </c>
+      <c r="F1345" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1345" s="3">
+        <v>104.397</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1249"/>
+  <autoFilter ref="A1:G1345"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -478,45 +478,69 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B19" s="4">
+        <v>2710.3</v>
+      </c>
+      <c r="C19" s="4">
+        <v>2489.5</v>
+      </c>
+      <c r="D19" s="4">
+        <v>5901.2</v>
+      </c>
+      <c r="E19" s="4">
+        <v>220.8</v>
+      </c>
+      <c r="F19" s="4">
+        <v>8390.7</v>
+      </c>
+      <c r="G19" s="5">
+        <f>IF(F19&gt;0,C19/F19,"")</f>
+        <v>0.2967</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B19" s="7">
-        <f>SUM(B5:B18)</f>
-        <v>32254.2</v>
-      </c>
-      <c r="C19" s="7">
-        <f>SUM(C5:C18)</f>
-        <v>28836.4</v>
-      </c>
-      <c r="D19" s="7">
-        <f>SUM(D5:D18)</f>
-        <v>110124.0</v>
-      </c>
-      <c r="E19" s="7">
-        <f>SUM(E5:E18)</f>
-        <v>3417.8</v>
-      </c>
-      <c r="F19" s="7">
-        <f>SUM(F5:F18)</f>
-        <v>138960.4</v>
-      </c>
-      <c r="G19" s="8">
-        <f>IF(F19&gt;0,C19/F19,"")</f>
-        <v>0.2075</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B20" s="7">
+        <f>SUM(B5:B19)</f>
+        <v>34964.5</v>
+      </c>
+      <c r="C20" s="7">
+        <f>SUM(C5:C19)</f>
+        <v>31325.9</v>
+      </c>
+      <c r="D20" s="7">
+        <f>SUM(D5:D19)</f>
+        <v>116025.2</v>
+      </c>
+      <c r="E20" s="7">
+        <f>SUM(E5:E19)</f>
+        <v>3638.5</v>
+      </c>
+      <c r="F20" s="7">
+        <f>SUM(F5:F19)</f>
+        <v>147351.1</v>
+      </c>
+      <c r="G20" s="8">
+        <f>IF(F20&gt;0,C20/F20,"")</f>
+        <v>0.2126</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -34175,7 +34199,2407 @@
         <v>104.397</v>
       </c>
     </row>
+    <row r="1346">
+      <c r="A1346" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1346" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C1346" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1346" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1346" s="3">
+        <v>104.397</v>
+      </c>
+      <c r="F1346" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1346" s="3">
+        <v>104.397</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1347" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C1347" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1347" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1347" s="3">
+        <v>104.294</v>
+      </c>
+      <c r="F1347" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1347" s="3">
+        <v>104.294</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1348" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C1348" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1348" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1348" s="3">
+        <v>103.987</v>
+      </c>
+      <c r="F1348" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1348" s="3">
+        <v>103.987</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1349" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C1349" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1349" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1349" s="3">
+        <v>103.68</v>
+      </c>
+      <c r="F1349" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1349" s="3">
+        <v>103.68</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1350" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C1350" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1350" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1350" s="3">
+        <v>103.322</v>
+      </c>
+      <c r="F1350" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1350" s="3">
+        <v>103.322</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1351" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C1351" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1351" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1351" s="3">
+        <v>103.629</v>
+      </c>
+      <c r="F1351" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1351" s="3">
+        <v>103.629</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1352" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C1352" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1352" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1352" s="3">
+        <v>103.629</v>
+      </c>
+      <c r="F1352" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1352" s="3">
+        <v>103.629</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1353" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C1353" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1353" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1353" s="3">
+        <v>103.322</v>
+      </c>
+      <c r="F1353" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1353" s="3">
+        <v>103.322</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1354" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C1354" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1354" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1354" s="3">
+        <v>103.27</v>
+      </c>
+      <c r="F1354" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1354" s="3">
+        <v>103.27</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1355" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C1355" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1355" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1355" s="3">
+        <v>103.322</v>
+      </c>
+      <c r="F1355" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1355" s="3">
+        <v>103.322</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1356" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C1356" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1356" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1356" s="3">
+        <v>103.322</v>
+      </c>
+      <c r="F1356" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1356" s="3">
+        <v>103.322</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1357" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C1357" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1357" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1357" s="3">
+        <v>103.322</v>
+      </c>
+      <c r="F1357" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1357" s="3">
+        <v>103.322</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1358" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C1358" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1358" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1358" s="3">
+        <v>84.326</v>
+      </c>
+      <c r="F1358" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1358" s="3">
+        <v>84.326</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1359" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C1359" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1359" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1359" s="3">
+        <v>69.274</v>
+      </c>
+      <c r="F1359" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1359" s="3">
+        <v>69.274</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1360" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C1360" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1360" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1360" s="3">
+        <v>69.325</v>
+      </c>
+      <c r="F1360" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1360" s="3">
+        <v>69.325</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1361" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C1361" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1361" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1361" s="3">
+        <v>69.581</v>
+      </c>
+      <c r="F1361" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1361" s="3">
+        <v>69.581</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1362" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C1362" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1362" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1362" s="3">
+        <v>70.349</v>
+      </c>
+      <c r="F1362" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1362" s="3">
+        <v>70.349</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1363" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C1363" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1363" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1363" s="3">
+        <v>70.554</v>
+      </c>
+      <c r="F1363" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1363" s="3">
+        <v>70.554</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1364" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C1364" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1364" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1364" s="3">
+        <v>69.427</v>
+      </c>
+      <c r="F1364" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1364" s="3">
+        <v>69.427</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1365" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C1365" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1365" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1365" s="3">
+        <v>69.478</v>
+      </c>
+      <c r="F1365" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1365" s="3">
+        <v>69.478</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1366" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C1366" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1366" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1366" s="3">
+        <v>69.325</v>
+      </c>
+      <c r="F1366" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1366" s="3">
+        <v>69.325</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1367" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C1367" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1367" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1367" s="3">
+        <v>69.427</v>
+      </c>
+      <c r="F1367" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1367" s="3">
+        <v>69.427</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1368" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C1368" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1368" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1368" s="3">
+        <v>69.376</v>
+      </c>
+      <c r="F1368" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1368" s="3">
+        <v>69.376</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1369" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C1369" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1369" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1369" s="3">
+        <v>69.581</v>
+      </c>
+      <c r="F1369" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1369" s="3">
+        <v>69.581</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1370" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C1370" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1370" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1370" s="3">
+        <v>69.888</v>
+      </c>
+      <c r="F1370" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1370" s="3">
+        <v>69.888</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1371" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C1371" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1371" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1371" s="3">
+        <v>69.53</v>
+      </c>
+      <c r="F1371" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1371" s="3">
+        <v>69.53</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1372" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C1372" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="D1372" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="E1372" s="3">
+        <v>69.888</v>
+      </c>
+      <c r="F1372" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1372" s="3">
+        <v>69.901</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1373" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C1373" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="D1373" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="E1373" s="3">
+        <v>69.734</v>
+      </c>
+      <c r="F1373" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1373" s="3">
+        <v>70.144</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1374" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C1374" s="3">
+        <v>1.293</v>
+      </c>
+      <c r="D1374" s="3">
+        <v>1.293</v>
+      </c>
+      <c r="E1374" s="3">
+        <v>68.25</v>
+      </c>
+      <c r="F1374" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1374" s="3">
+        <v>69.543</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1375" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C1375" s="3">
+        <v>4.646</v>
+      </c>
+      <c r="D1375" s="3">
+        <v>4.646</v>
+      </c>
+      <c r="E1375" s="3">
+        <v>65.024</v>
+      </c>
+      <c r="F1375" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1375" s="3">
+        <v>69.67</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1376" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C1376" s="3">
+        <v>10.714</v>
+      </c>
+      <c r="D1376" s="3">
+        <v>10.714</v>
+      </c>
+      <c r="E1376" s="3">
+        <v>59.341</v>
+      </c>
+      <c r="F1376" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1376" s="3">
+        <v>70.055</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1377" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C1377" s="3">
+        <v>18.944</v>
+      </c>
+      <c r="D1377" s="3">
+        <v>18.944</v>
+      </c>
+      <c r="E1377" s="3">
+        <v>62.259</v>
+      </c>
+      <c r="F1377" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1377" s="3">
+        <v>81.203</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1378" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C1378" s="3">
+        <v>27.648</v>
+      </c>
+      <c r="D1378" s="3">
+        <v>27.648</v>
+      </c>
+      <c r="E1378" s="3">
+        <v>98.509</v>
+      </c>
+      <c r="F1378" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1378" s="3">
+        <v>126.157</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1379" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C1379" s="3">
+        <v>36.403</v>
+      </c>
+      <c r="D1379" s="3">
+        <v>36.403</v>
+      </c>
+      <c r="E1379" s="3">
+        <v>102.758</v>
+      </c>
+      <c r="F1379" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1379" s="3">
+        <v>139.161</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1380" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C1380" s="3">
+        <v>45.056</v>
+      </c>
+      <c r="D1380" s="3">
+        <v>45.056</v>
+      </c>
+      <c r="E1380" s="3">
+        <v>96.819</v>
+      </c>
+      <c r="F1380" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1380" s="3">
+        <v>141.875</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1381" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C1381" s="3">
+        <v>53.504</v>
+      </c>
+      <c r="D1381" s="3">
+        <v>53.504</v>
+      </c>
+      <c r="E1381" s="3">
+        <v>84.429</v>
+      </c>
+      <c r="F1381" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1381" s="3">
+        <v>137.933</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1382" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C1382" s="3">
+        <v>61.466</v>
+      </c>
+      <c r="D1382" s="3">
+        <v>61.466</v>
+      </c>
+      <c r="E1382" s="3">
+        <v>76.493</v>
+      </c>
+      <c r="F1382" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1382" s="3">
+        <v>137.959</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1383" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C1383" s="3">
+        <v>69.005</v>
+      </c>
+      <c r="D1383" s="3">
+        <v>69.005</v>
+      </c>
+      <c r="E1383" s="3">
+        <v>68.608</v>
+      </c>
+      <c r="F1383" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1383" s="3">
+        <v>137.613</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1384" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C1384" s="3">
+        <v>76.275</v>
+      </c>
+      <c r="D1384" s="3">
+        <v>76.275</v>
+      </c>
+      <c r="E1384" s="3">
+        <v>61.286</v>
+      </c>
+      <c r="F1384" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1384" s="3">
+        <v>137.561</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1385" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C1385" s="3">
+        <v>83.021</v>
+      </c>
+      <c r="D1385" s="3">
+        <v>83.021</v>
+      </c>
+      <c r="E1385" s="3">
+        <v>61.542</v>
+      </c>
+      <c r="F1385" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1385" s="3">
+        <v>144.563</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1386" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C1386" s="3">
+        <v>89.19</v>
+      </c>
+      <c r="D1386" s="3">
+        <v>89.19</v>
+      </c>
+      <c r="E1386" s="3">
+        <v>48.589</v>
+      </c>
+      <c r="F1386" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1386" s="3">
+        <v>137.779</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1387" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C1387" s="3">
+        <v>95.488</v>
+      </c>
+      <c r="D1387" s="3">
+        <v>95.488</v>
+      </c>
+      <c r="E1387" s="3">
+        <v>42.291</v>
+      </c>
+      <c r="F1387" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1387" s="3">
+        <v>137.779</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1388" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C1388" s="3">
+        <v>106.803</v>
+      </c>
+      <c r="D1388" s="3">
+        <v>106.803</v>
+      </c>
+      <c r="E1388" s="3">
+        <v>30.822</v>
+      </c>
+      <c r="F1388" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1388" s="3">
+        <v>137.625</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1389" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C1389" s="3">
+        <v>106.202</v>
+      </c>
+      <c r="D1389" s="3">
+        <v>102.618</v>
+      </c>
+      <c r="E1389" s="3">
+        <v>15.36</v>
+      </c>
+      <c r="F1389" s="3">
+        <v>3.584</v>
+      </c>
+      <c r="G1389" s="3">
+        <v>117.978</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1390" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C1390" s="3">
+        <v>57.306</v>
+      </c>
+      <c r="D1390" s="3">
+        <v>56.743</v>
+      </c>
+      <c r="E1390" s="3">
+        <v>48.64</v>
+      </c>
+      <c r="F1390" s="3">
+        <v>0.563</v>
+      </c>
+      <c r="G1390" s="3">
+        <v>105.383</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1391" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C1391" s="3">
+        <v>67.981</v>
+      </c>
+      <c r="D1391" s="3">
+        <v>65.523</v>
+      </c>
+      <c r="E1391" s="3">
+        <v>42.24</v>
+      </c>
+      <c r="F1391" s="3">
+        <v>2.458</v>
+      </c>
+      <c r="G1391" s="3">
+        <v>107.763</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1392" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C1392" s="3">
+        <v>112.384</v>
+      </c>
+      <c r="D1392" s="3">
+        <v>105.472</v>
+      </c>
+      <c r="E1392" s="3">
+        <v>2.56</v>
+      </c>
+      <c r="F1392" s="3">
+        <v>6.912</v>
+      </c>
+      <c r="G1392" s="3">
+        <v>108.032</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1393" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C1393" s="3">
+        <v>102.528</v>
+      </c>
+      <c r="D1393" s="3">
+        <v>96.742</v>
+      </c>
+      <c r="E1393" s="3">
+        <v>11.162</v>
+      </c>
+      <c r="F1393" s="3">
+        <v>5.786</v>
+      </c>
+      <c r="G1393" s="3">
+        <v>107.904</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1394" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C1394" s="3">
+        <v>54.694</v>
+      </c>
+      <c r="D1394" s="3">
+        <v>54.489</v>
+      </c>
+      <c r="E1394" s="3">
+        <v>52.736</v>
+      </c>
+      <c r="F1394" s="3">
+        <v>0.205</v>
+      </c>
+      <c r="G1394" s="3">
+        <v>107.225</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1395" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C1395" s="3">
+        <v>35.046</v>
+      </c>
+      <c r="D1395" s="3">
+        <v>35.046</v>
+      </c>
+      <c r="E1395" s="3">
+        <v>71.936</v>
+      </c>
+      <c r="F1395" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1395" s="3">
+        <v>106.982</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1396" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C1396" s="3">
+        <v>115.674</v>
+      </c>
+      <c r="D1396" s="3">
+        <v>107.328</v>
+      </c>
+      <c r="E1396" s="3">
+        <v>0.102</v>
+      </c>
+      <c r="F1396" s="3">
+        <v>8.346</v>
+      </c>
+      <c r="G1396" s="3">
+        <v>107.43</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1397" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C1397" s="3">
+        <v>87.322</v>
+      </c>
+      <c r="D1397" s="3">
+        <v>82.048</v>
+      </c>
+      <c r="E1397" s="3">
+        <v>25.498</v>
+      </c>
+      <c r="F1397" s="3">
+        <v>5.274</v>
+      </c>
+      <c r="G1397" s="3">
+        <v>107.546</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1398" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C1398" s="3">
+        <v>55.782</v>
+      </c>
+      <c r="D1398" s="3">
+        <v>47.948</v>
+      </c>
+      <c r="E1398" s="3">
+        <v>35.021</v>
+      </c>
+      <c r="F1398" s="3">
+        <v>7.834</v>
+      </c>
+      <c r="G1398" s="3">
+        <v>82.969</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1399" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C1399" s="3">
+        <v>36.685</v>
+      </c>
+      <c r="D1399" s="3">
+        <v>36.327</v>
+      </c>
+      <c r="E1399" s="3">
+        <v>37.171</v>
+      </c>
+      <c r="F1399" s="3">
+        <v>0.358</v>
+      </c>
+      <c r="G1399" s="3">
+        <v>73.498</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1400" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C1400" s="3">
+        <v>62.349</v>
+      </c>
+      <c r="D1400" s="3">
+        <v>50.163</v>
+      </c>
+      <c r="E1400" s="3">
+        <v>24.166</v>
+      </c>
+      <c r="F1400" s="3">
+        <v>12.186</v>
+      </c>
+      <c r="G1400" s="3">
+        <v>74.329</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1401" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C1401" s="3">
+        <v>95.782</v>
+      </c>
+      <c r="D1401" s="3">
+        <v>65.318</v>
+      </c>
+      <c r="E1401" s="3">
+        <v>8.397</v>
+      </c>
+      <c r="F1401" s="3">
+        <v>30.464</v>
+      </c>
+      <c r="G1401" s="3">
+        <v>73.715</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1402" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C1402" s="3">
+        <v>116.723</v>
+      </c>
+      <c r="D1402" s="3">
+        <v>73.92</v>
+      </c>
+      <c r="E1402" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1402" s="3">
+        <v>42.803</v>
+      </c>
+      <c r="G1402" s="3">
+        <v>73.92</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1403" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C1403" s="3">
+        <v>105.818</v>
+      </c>
+      <c r="D1403" s="3">
+        <v>69.824</v>
+      </c>
+      <c r="E1403" s="3">
+        <v>3.379</v>
+      </c>
+      <c r="F1403" s="3">
+        <v>35.994</v>
+      </c>
+      <c r="G1403" s="3">
+        <v>73.203</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1404" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C1404" s="3">
+        <v>39.603</v>
+      </c>
+      <c r="D1404" s="3">
+        <v>33.305</v>
+      </c>
+      <c r="E1404" s="3">
+        <v>40.09</v>
+      </c>
+      <c r="F1404" s="3">
+        <v>6.298</v>
+      </c>
+      <c r="G1404" s="3">
+        <v>73.395</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1405" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C1405" s="3">
+        <v>25.216</v>
+      </c>
+      <c r="D1405" s="3">
+        <v>25.216</v>
+      </c>
+      <c r="E1405" s="3">
+        <v>48.23</v>
+      </c>
+      <c r="F1405" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1405" s="3">
+        <v>73.446</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1406" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C1406" s="3">
+        <v>27.29</v>
+      </c>
+      <c r="D1406" s="3">
+        <v>27.29</v>
+      </c>
+      <c r="E1406" s="3">
+        <v>46.182</v>
+      </c>
+      <c r="F1406" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1406" s="3">
+        <v>73.472</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1407" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C1407" s="3">
+        <v>43.738</v>
+      </c>
+      <c r="D1407" s="3">
+        <v>38.925</v>
+      </c>
+      <c r="E1407" s="3">
+        <v>34.099</v>
+      </c>
+      <c r="F1407" s="3">
+        <v>4.813</v>
+      </c>
+      <c r="G1407" s="3">
+        <v>73.024</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1408" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C1408" s="3">
+        <v>39.706</v>
+      </c>
+      <c r="D1408" s="3">
+        <v>35.661</v>
+      </c>
+      <c r="E1408" s="3">
+        <v>37.99</v>
+      </c>
+      <c r="F1408" s="3">
+        <v>4.045</v>
+      </c>
+      <c r="G1408" s="3">
+        <v>73.651</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1409" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C1409" s="3">
+        <v>53.978</v>
+      </c>
+      <c r="D1409" s="3">
+        <v>45.735</v>
+      </c>
+      <c r="E1409" s="3">
+        <v>27.238</v>
+      </c>
+      <c r="F1409" s="3">
+        <v>8.243</v>
+      </c>
+      <c r="G1409" s="3">
+        <v>72.973</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1410" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C1410" s="3">
+        <v>76.57</v>
+      </c>
+      <c r="D1410" s="3">
+        <v>58.804</v>
+      </c>
+      <c r="E1410" s="3">
+        <v>15.309</v>
+      </c>
+      <c r="F1410" s="3">
+        <v>17.766</v>
+      </c>
+      <c r="G1410" s="3">
+        <v>74.113</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1411" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C1411" s="3">
+        <v>47.667</v>
+      </c>
+      <c r="D1411" s="3">
+        <v>41.779</v>
+      </c>
+      <c r="E1411" s="3">
+        <v>31.13</v>
+      </c>
+      <c r="F1411" s="3">
+        <v>5.888</v>
+      </c>
+      <c r="G1411" s="3">
+        <v>72.909</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1412" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C1412" s="3">
+        <v>83.917</v>
+      </c>
+      <c r="D1412" s="3">
+        <v>73.831</v>
+      </c>
+      <c r="E1412" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="F1412" s="3">
+        <v>10.086</v>
+      </c>
+      <c r="G1412" s="3">
+        <v>74.241</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1413" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C1413" s="3">
+        <v>68.826</v>
+      </c>
+      <c r="D1413" s="3">
+        <v>67.956</v>
+      </c>
+      <c r="E1413" s="3">
+        <v>6.093</v>
+      </c>
+      <c r="F1413" s="3">
+        <v>0.87</v>
+      </c>
+      <c r="G1413" s="3">
+        <v>74.049</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1414" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C1414" s="3">
+        <v>62.195</v>
+      </c>
+      <c r="D1414" s="3">
+        <v>62.195</v>
+      </c>
+      <c r="E1414" s="3">
+        <v>11.213</v>
+      </c>
+      <c r="F1414" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1414" s="3">
+        <v>73.408</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1415" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C1415" s="3">
+        <v>60.173</v>
+      </c>
+      <c r="D1415" s="3">
+        <v>60.173</v>
+      </c>
+      <c r="E1415" s="3">
+        <v>13.312</v>
+      </c>
+      <c r="F1415" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1415" s="3">
+        <v>73.485</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1416" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C1416" s="3">
+        <v>36.787</v>
+      </c>
+      <c r="D1416" s="3">
+        <v>36.787</v>
+      </c>
+      <c r="E1416" s="3">
+        <v>37.069</v>
+      </c>
+      <c r="F1416" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1416" s="3">
+        <v>73.856</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1417" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C1417" s="3">
+        <v>16.09</v>
+      </c>
+      <c r="D1417" s="3">
+        <v>16.09</v>
+      </c>
+      <c r="E1417" s="3">
+        <v>57.037</v>
+      </c>
+      <c r="F1417" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1417" s="3">
+        <v>73.127</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1418" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C1418" s="3">
+        <v>10.035</v>
+      </c>
+      <c r="D1418" s="3">
+        <v>10.035</v>
+      </c>
+      <c r="E1418" s="3">
+        <v>62.976</v>
+      </c>
+      <c r="F1418" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1418" s="3">
+        <v>73.011</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1419" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C1419" s="3">
+        <v>7.757</v>
+      </c>
+      <c r="D1419" s="3">
+        <v>7.757</v>
+      </c>
+      <c r="E1419" s="3">
+        <v>65.587</v>
+      </c>
+      <c r="F1419" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1419" s="3">
+        <v>73.344</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1420" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C1420" s="3">
+        <v>9.434</v>
+      </c>
+      <c r="D1420" s="3">
+        <v>9.434</v>
+      </c>
+      <c r="E1420" s="3">
+        <v>63.283</v>
+      </c>
+      <c r="F1420" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1420" s="3">
+        <v>72.717</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1421" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C1421" s="3">
+        <v>7.027</v>
+      </c>
+      <c r="D1421" s="3">
+        <v>7.027</v>
+      </c>
+      <c r="E1421" s="3">
+        <v>66.099</v>
+      </c>
+      <c r="F1421" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1421" s="3">
+        <v>73.126</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1422" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C1422" s="3">
+        <v>1.728</v>
+      </c>
+      <c r="D1422" s="3">
+        <v>1.728</v>
+      </c>
+      <c r="E1422" s="3">
+        <v>71.014</v>
+      </c>
+      <c r="F1422" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1422" s="3">
+        <v>72.742</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1423" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C1423" s="3">
+        <v>0.358</v>
+      </c>
+      <c r="D1423" s="3">
+        <v>0.358</v>
+      </c>
+      <c r="E1423" s="3">
+        <v>72.346</v>
+      </c>
+      <c r="F1423" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1423" s="3">
+        <v>72.704</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1424" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C1424" s="3">
+        <v>0.026</v>
+      </c>
+      <c r="D1424" s="3">
+        <v>0.026</v>
+      </c>
+      <c r="E1424" s="3">
+        <v>72.755</v>
+      </c>
+      <c r="F1424" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1424" s="3">
+        <v>72.781</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1425" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C1425" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1425" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1425" s="3">
+        <v>73.267</v>
+      </c>
+      <c r="F1425" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1425" s="3">
+        <v>73.267</v>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1426" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C1426" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1426" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1426" s="3">
+        <v>72.96</v>
+      </c>
+      <c r="F1426" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1426" s="3">
+        <v>72.96</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1427" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C1427" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1427" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1427" s="3">
+        <v>72.755</v>
+      </c>
+      <c r="F1427" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1427" s="3">
+        <v>72.755</v>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1428" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C1428" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1428" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1428" s="3">
+        <v>72.858</v>
+      </c>
+      <c r="F1428" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1428" s="3">
+        <v>72.858</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1429" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C1429" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1429" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1429" s="3">
+        <v>73.062</v>
+      </c>
+      <c r="F1429" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1429" s="3">
+        <v>73.062</v>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1430" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C1430" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1430" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1430" s="3">
+        <v>72.909</v>
+      </c>
+      <c r="F1430" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1430" s="3">
+        <v>72.909</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1431" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C1431" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1431" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1431" s="3">
+        <v>73.011</v>
+      </c>
+      <c r="F1431" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1431" s="3">
+        <v>73.011</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1432" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C1432" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1432" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1432" s="3">
+        <v>73.114</v>
+      </c>
+      <c r="F1432" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1432" s="3">
+        <v>73.114</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1433" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C1433" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1433" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1433" s="3">
+        <v>72.704</v>
+      </c>
+      <c r="F1433" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1433" s="3">
+        <v>72.704</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1434" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C1434" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1434" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1434" s="3">
+        <v>72.909</v>
+      </c>
+      <c r="F1434" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1434" s="3">
+        <v>72.909</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1435" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C1435" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1435" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1435" s="3">
+        <v>72.858</v>
+      </c>
+      <c r="F1435" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1435" s="3">
+        <v>72.858</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1436" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C1436" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1436" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1436" s="3">
+        <v>73.267</v>
+      </c>
+      <c r="F1436" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1436" s="3">
+        <v>73.267</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1437" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C1437" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1437" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1437" s="3">
+        <v>73.472</v>
+      </c>
+      <c r="F1437" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1437" s="3">
+        <v>73.472</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1438" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C1438" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1438" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1438" s="3">
+        <v>73.37</v>
+      </c>
+      <c r="F1438" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1438" s="3">
+        <v>73.37</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1439" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C1439" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1439" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1439" s="3">
+        <v>73.37</v>
+      </c>
+      <c r="F1439" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1439" s="3">
+        <v>73.37</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1440" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C1440" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1440" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1440" s="3">
+        <v>73.626</v>
+      </c>
+      <c r="F1440" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1440" s="3">
+        <v>73.626</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B1441" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C1441" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1441" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1441" s="3">
+        <v>74.24</v>
+      </c>
+      <c r="F1441" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1441" s="3">
+        <v>74.24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1345"/>
+  <autoFilter ref="A1:G1441"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -502,45 +502,69 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B20" s="4">
+        <v>1070.8</v>
+      </c>
+      <c r="C20" s="4">
+        <v>774.6</v>
+      </c>
+      <c r="D20" s="4">
+        <v>2477.3</v>
+      </c>
+      <c r="E20" s="4">
+        <v>296.2</v>
+      </c>
+      <c r="F20" s="4">
+        <v>3251.9</v>
+      </c>
+      <c r="G20" s="5">
+        <f>IF(F20&gt;0,C20/F20,"")</f>
+        <v>0.2382</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B20" s="7">
-        <f>SUM(B5:B19)</f>
-        <v>34964.5</v>
-      </c>
-      <c r="C20" s="7">
-        <f>SUM(C5:C19)</f>
-        <v>31325.9</v>
-      </c>
-      <c r="D20" s="7">
-        <f>SUM(D5:D19)</f>
-        <v>116025.2</v>
-      </c>
-      <c r="E20" s="7">
-        <f>SUM(E5:E19)</f>
-        <v>3638.5</v>
-      </c>
-      <c r="F20" s="7">
-        <f>SUM(F5:F19)</f>
-        <v>147351.1</v>
-      </c>
-      <c r="G20" s="8">
-        <f>IF(F20&gt;0,C20/F20,"")</f>
-        <v>0.2126</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B21" s="7">
+        <f>SUM(B5:B20)</f>
+        <v>36035.3</v>
+      </c>
+      <c r="C21" s="7">
+        <f>SUM(C5:C20)</f>
+        <v>32100.5</v>
+      </c>
+      <c r="D21" s="7">
+        <f>SUM(D5:D20)</f>
+        <v>118502.4</v>
+      </c>
+      <c r="E21" s="7">
+        <f>SUM(E5:E20)</f>
+        <v>3934.8</v>
+      </c>
+      <c r="F21" s="7">
+        <f>SUM(F5:F20)</f>
+        <v>150603.0</v>
+      </c>
+      <c r="G21" s="8">
+        <f>IF(F21&gt;0,C21/F21,"")</f>
+        <v>0.2131</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -36599,7 +36623,2407 @@
         <v>74.24</v>
       </c>
     </row>
+    <row r="1442">
+      <c r="A1442" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1442" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C1442" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1442" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1442" s="3">
+        <v>52.992</v>
+      </c>
+      <c r="F1442" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1442" s="3">
+        <v>52.992</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1443" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C1443" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1443" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1443" s="3">
+        <v>36.608</v>
+      </c>
+      <c r="F1443" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1443" s="3">
+        <v>36.608</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1444" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C1444" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1444" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1444" s="3">
+        <v>36.096</v>
+      </c>
+      <c r="F1444" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1444" s="3">
+        <v>36.096</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1445" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C1445" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1445" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1445" s="3">
+        <v>36.096</v>
+      </c>
+      <c r="F1445" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1445" s="3">
+        <v>36.096</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1446" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C1446" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1446" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1446" s="3">
+        <v>36.147</v>
+      </c>
+      <c r="F1446" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1446" s="3">
+        <v>36.147</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1447" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C1447" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1447" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1447" s="3">
+        <v>36.096</v>
+      </c>
+      <c r="F1447" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1447" s="3">
+        <v>36.096</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1448" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C1448" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1448" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1448" s="3">
+        <v>36.045</v>
+      </c>
+      <c r="F1448" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1448" s="3">
+        <v>36.045</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1449" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C1449" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1449" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1449" s="3">
+        <v>36.403</v>
+      </c>
+      <c r="F1449" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1449" s="3">
+        <v>36.403</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1450" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C1450" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1450" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1450" s="3">
+        <v>36.045</v>
+      </c>
+      <c r="F1450" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1450" s="3">
+        <v>36.045</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1451" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C1451" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1451" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1451" s="3">
+        <v>36.096</v>
+      </c>
+      <c r="F1451" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1451" s="3">
+        <v>36.096</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1452" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C1452" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1452" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1452" s="3">
+        <v>36.045</v>
+      </c>
+      <c r="F1452" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1452" s="3">
+        <v>36.045</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1453" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C1453" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1453" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1453" s="3">
+        <v>36.096</v>
+      </c>
+      <c r="F1453" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1453" s="3">
+        <v>36.096</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1454" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C1454" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1454" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1454" s="3">
+        <v>36.403</v>
+      </c>
+      <c r="F1454" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1454" s="3">
+        <v>36.403</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1455" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C1455" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1455" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1455" s="3">
+        <v>35.994</v>
+      </c>
+      <c r="F1455" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1455" s="3">
+        <v>35.994</v>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1456" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C1456" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1456" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1456" s="3">
+        <v>36.25</v>
+      </c>
+      <c r="F1456" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1456" s="3">
+        <v>36.25</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1457" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C1457" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1457" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1457" s="3">
+        <v>36.147</v>
+      </c>
+      <c r="F1457" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1457" s="3">
+        <v>36.147</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1458" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C1458" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1458" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1458" s="3">
+        <v>36.045</v>
+      </c>
+      <c r="F1458" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1458" s="3">
+        <v>36.045</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1459" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C1459" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1459" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1459" s="3">
+        <v>36.045</v>
+      </c>
+      <c r="F1459" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1459" s="3">
+        <v>36.045</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1460" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C1460" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1460" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1460" s="3">
+        <v>36.096</v>
+      </c>
+      <c r="F1460" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1460" s="3">
+        <v>36.096</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1461" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C1461" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1461" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1461" s="3">
+        <v>36.25</v>
+      </c>
+      <c r="F1461" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1461" s="3">
+        <v>36.25</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1462" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C1462" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1462" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1462" s="3">
+        <v>36.301</v>
+      </c>
+      <c r="F1462" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1462" s="3">
+        <v>36.301</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1463" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C1463" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1463" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1463" s="3">
+        <v>36.147</v>
+      </c>
+      <c r="F1463" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1463" s="3">
+        <v>36.147</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1464" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C1464" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1464" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1464" s="3">
+        <v>36.096</v>
+      </c>
+      <c r="F1464" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1464" s="3">
+        <v>36.096</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1465" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C1465" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1465" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1465" s="3">
+        <v>36.25</v>
+      </c>
+      <c r="F1465" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1465" s="3">
+        <v>36.25</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1466" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C1466" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1466" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1466" s="3">
+        <v>36.301</v>
+      </c>
+      <c r="F1466" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1466" s="3">
+        <v>36.301</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1467" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C1467" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1467" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1467" s="3">
+        <v>36.608</v>
+      </c>
+      <c r="F1467" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1467" s="3">
+        <v>36.608</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1468" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C1468" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1468" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1468" s="3">
+        <v>36.966</v>
+      </c>
+      <c r="F1468" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1468" s="3">
+        <v>36.966</v>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1469" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C1469" s="3">
+        <v>0.205</v>
+      </c>
+      <c r="D1469" s="3">
+        <v>0.205</v>
+      </c>
+      <c r="E1469" s="3">
+        <v>36.71</v>
+      </c>
+      <c r="F1469" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1469" s="3">
+        <v>36.915</v>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1470" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C1470" s="3">
+        <v>1.126</v>
+      </c>
+      <c r="D1470" s="3">
+        <v>1.126</v>
+      </c>
+      <c r="E1470" s="3">
+        <v>35.174</v>
+      </c>
+      <c r="F1470" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1470" s="3">
+        <v>36.3</v>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1471" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C1471" s="3">
+        <v>1.37</v>
+      </c>
+      <c r="D1471" s="3">
+        <v>1.37</v>
+      </c>
+      <c r="E1471" s="3">
+        <v>34.765</v>
+      </c>
+      <c r="F1471" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1471" s="3">
+        <v>36.135</v>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1472" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C1472" s="3">
+        <v>2.752</v>
+      </c>
+      <c r="D1472" s="3">
+        <v>2.752</v>
+      </c>
+      <c r="E1472" s="3">
+        <v>33.382</v>
+      </c>
+      <c r="F1472" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1472" s="3">
+        <v>36.134</v>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1473" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C1473" s="3">
+        <v>3.75</v>
+      </c>
+      <c r="D1473" s="3">
+        <v>3.75</v>
+      </c>
+      <c r="E1473" s="3">
+        <v>32.358</v>
+      </c>
+      <c r="F1473" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1473" s="3">
+        <v>36.108</v>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1474" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C1474" s="3">
+        <v>8.858</v>
+      </c>
+      <c r="D1474" s="3">
+        <v>8.858</v>
+      </c>
+      <c r="E1474" s="3">
+        <v>50.33</v>
+      </c>
+      <c r="F1474" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1474" s="3">
+        <v>59.188</v>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1475" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C1475" s="3">
+        <v>14.989</v>
+      </c>
+      <c r="D1475" s="3">
+        <v>14.989</v>
+      </c>
+      <c r="E1475" s="3">
+        <v>85.709</v>
+      </c>
+      <c r="F1475" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1475" s="3">
+        <v>100.698</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1476" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C1476" s="3">
+        <v>15.642</v>
+      </c>
+      <c r="D1476" s="3">
+        <v>15.642</v>
+      </c>
+      <c r="E1476" s="3">
+        <v>70.298</v>
+      </c>
+      <c r="F1476" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1476" s="3">
+        <v>85.94</v>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1477" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C1477" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1477" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1477" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1477" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1477" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1478" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C1478" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1478" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1478" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1478" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1478" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1479" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C1479" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1479" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1479" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1479" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1479" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1480" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C1480" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1480" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1480" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1480" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1480" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1481" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C1481" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1481" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1481" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1481" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1481" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1482" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C1482" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1482" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1482" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1482" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1482" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1483" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C1483" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1483" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1483" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1483" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1483" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1484" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C1484" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1484" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1484" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1484" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1484" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1485" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C1485" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1485" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1485" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1485" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1485" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1486" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C1486" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1486" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1486" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1486" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1486" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1487" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C1487" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1487" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1487" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1487" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1487" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1488" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C1488" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1488" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1488" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1488" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1488" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1489" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C1489" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1489" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1489" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1489" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1489" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1490" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C1490" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1490" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1490" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1490" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1490" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1491" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C1491" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1491" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1491" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1491" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1491" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1492" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C1492" s="3">
+        <v>8.026</v>
+      </c>
+      <c r="D1492" s="3">
+        <v>8.026</v>
+      </c>
+      <c r="E1492" s="3">
+        <v>32.307</v>
+      </c>
+      <c r="F1492" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1492" s="3">
+        <v>40.333</v>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1493" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C1493" s="3">
+        <v>17.92</v>
+      </c>
+      <c r="D1493" s="3">
+        <v>17.869</v>
+      </c>
+      <c r="E1493" s="3">
+        <v>15.155</v>
+      </c>
+      <c r="F1493" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G1493" s="3">
+        <v>33.024</v>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1494" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C1494" s="3">
+        <v>91.264</v>
+      </c>
+      <c r="D1494" s="3">
+        <v>38.528</v>
+      </c>
+      <c r="E1494" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="F1494" s="3">
+        <v>52.736</v>
+      </c>
+      <c r="G1494" s="3">
+        <v>38.579</v>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1495" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C1495" s="3">
+        <v>82.074</v>
+      </c>
+      <c r="D1495" s="3">
+        <v>40.756</v>
+      </c>
+      <c r="E1495" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1495" s="3">
+        <v>41.318</v>
+      </c>
+      <c r="G1495" s="3">
+        <v>40.756</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1496" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C1496" s="3">
+        <v>74.022</v>
+      </c>
+      <c r="D1496" s="3">
+        <v>40.435</v>
+      </c>
+      <c r="E1496" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1496" s="3">
+        <v>33.587</v>
+      </c>
+      <c r="G1496" s="3">
+        <v>40.435</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1497" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C1497" s="3">
+        <v>56.691</v>
+      </c>
+      <c r="D1497" s="3">
+        <v>40.102</v>
+      </c>
+      <c r="E1497" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1497" s="3">
+        <v>16.589</v>
+      </c>
+      <c r="G1497" s="3">
+        <v>40.102</v>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1498" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C1498" s="3">
+        <v>60.006</v>
+      </c>
+      <c r="D1498" s="3">
+        <v>40.601</v>
+      </c>
+      <c r="E1498" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1498" s="3">
+        <v>19.405</v>
+      </c>
+      <c r="G1498" s="3">
+        <v>40.601</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1499" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C1499" s="3">
+        <v>80.243</v>
+      </c>
+      <c r="D1499" s="3">
+        <v>40.409</v>
+      </c>
+      <c r="E1499" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1499" s="3">
+        <v>39.834</v>
+      </c>
+      <c r="G1499" s="3">
+        <v>40.409</v>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1500" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C1500" s="3">
+        <v>70.758</v>
+      </c>
+      <c r="D1500" s="3">
+        <v>39.987</v>
+      </c>
+      <c r="E1500" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1500" s="3">
+        <v>30.771</v>
+      </c>
+      <c r="G1500" s="3">
+        <v>39.987</v>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1501" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C1501" s="3">
+        <v>53.773</v>
+      </c>
+      <c r="D1501" s="3">
+        <v>40.359</v>
+      </c>
+      <c r="E1501" s="3">
+        <v>0.154</v>
+      </c>
+      <c r="F1501" s="3">
+        <v>13.414</v>
+      </c>
+      <c r="G1501" s="3">
+        <v>40.513</v>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1502" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C1502" s="3">
+        <v>64.922</v>
+      </c>
+      <c r="D1502" s="3">
+        <v>39.834</v>
+      </c>
+      <c r="E1502" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1502" s="3">
+        <v>25.088</v>
+      </c>
+      <c r="G1502" s="3">
+        <v>39.834</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1503" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C1503" s="3">
+        <v>61.824</v>
+      </c>
+      <c r="D1503" s="3">
+        <v>40.166</v>
+      </c>
+      <c r="E1503" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1503" s="3">
+        <v>21.658</v>
+      </c>
+      <c r="G1503" s="3">
+        <v>40.166</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1504" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C1504" s="3">
+        <v>37.402</v>
+      </c>
+      <c r="D1504" s="3">
+        <v>36.071</v>
+      </c>
+      <c r="E1504" s="3">
+        <v>4.045</v>
+      </c>
+      <c r="F1504" s="3">
+        <v>1.331</v>
+      </c>
+      <c r="G1504" s="3">
+        <v>40.116</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1505" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C1505" s="3">
+        <v>30.413</v>
+      </c>
+      <c r="D1505" s="3">
+        <v>30.413</v>
+      </c>
+      <c r="E1505" s="3">
+        <v>8.96</v>
+      </c>
+      <c r="F1505" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1505" s="3">
+        <v>39.373</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1506" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C1506" s="3">
+        <v>24.435</v>
+      </c>
+      <c r="D1506" s="3">
+        <v>24.435</v>
+      </c>
+      <c r="E1506" s="3">
+        <v>15.309</v>
+      </c>
+      <c r="F1506" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1506" s="3">
+        <v>39.744</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1507" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C1507" s="3">
+        <v>21.926</v>
+      </c>
+      <c r="D1507" s="3">
+        <v>21.926</v>
+      </c>
+      <c r="E1507" s="3">
+        <v>18.125</v>
+      </c>
+      <c r="F1507" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1507" s="3">
+        <v>40.051</v>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1508" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C1508" s="3">
+        <v>27.942</v>
+      </c>
+      <c r="D1508" s="3">
+        <v>27.942</v>
+      </c>
+      <c r="E1508" s="3">
+        <v>11.059</v>
+      </c>
+      <c r="F1508" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1508" s="3">
+        <v>39.001</v>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1509" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C1509" s="3">
+        <v>21.389</v>
+      </c>
+      <c r="D1509" s="3">
+        <v>21.389</v>
+      </c>
+      <c r="E1509" s="3">
+        <v>18.381</v>
+      </c>
+      <c r="F1509" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1509" s="3">
+        <v>39.77</v>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1510" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C1510" s="3">
+        <v>19.046</v>
+      </c>
+      <c r="D1510" s="3">
+        <v>19.046</v>
+      </c>
+      <c r="E1510" s="3">
+        <v>20.326</v>
+      </c>
+      <c r="F1510" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1510" s="3">
+        <v>39.372</v>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1511" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C1511" s="3">
+        <v>29.107</v>
+      </c>
+      <c r="D1511" s="3">
+        <v>29.107</v>
+      </c>
+      <c r="E1511" s="3">
+        <v>28.416</v>
+      </c>
+      <c r="F1511" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1511" s="3">
+        <v>57.523</v>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1512" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C1512" s="3">
+        <v>30.528</v>
+      </c>
+      <c r="D1512" s="3">
+        <v>30.323</v>
+      </c>
+      <c r="E1512" s="3">
+        <v>19.405</v>
+      </c>
+      <c r="F1512" s="3">
+        <v>0.205</v>
+      </c>
+      <c r="G1512" s="3">
+        <v>49.728</v>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1513" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C1513" s="3">
+        <v>23.603</v>
+      </c>
+      <c r="D1513" s="3">
+        <v>23.347</v>
+      </c>
+      <c r="E1513" s="3">
+        <v>15.462</v>
+      </c>
+      <c r="F1513" s="3">
+        <v>0.256</v>
+      </c>
+      <c r="G1513" s="3">
+        <v>38.809</v>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1514" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C1514" s="3">
+        <v>14.682</v>
+      </c>
+      <c r="D1514" s="3">
+        <v>14.682</v>
+      </c>
+      <c r="E1514" s="3">
+        <v>24.166</v>
+      </c>
+      <c r="F1514" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1514" s="3">
+        <v>38.848</v>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1515" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C1515" s="3">
+        <v>7.629</v>
+      </c>
+      <c r="D1515" s="3">
+        <v>7.629</v>
+      </c>
+      <c r="E1515" s="3">
+        <v>30.925</v>
+      </c>
+      <c r="F1515" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1515" s="3">
+        <v>38.554</v>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1516" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C1516" s="3">
+        <v>7.424</v>
+      </c>
+      <c r="D1516" s="3">
+        <v>7.424</v>
+      </c>
+      <c r="E1516" s="3">
+        <v>31.078</v>
+      </c>
+      <c r="F1516" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1516" s="3">
+        <v>38.502</v>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1517" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C1517" s="3">
+        <v>3.622</v>
+      </c>
+      <c r="D1517" s="3">
+        <v>3.622</v>
+      </c>
+      <c r="E1517" s="3">
+        <v>34.867</v>
+      </c>
+      <c r="F1517" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1517" s="3">
+        <v>38.489</v>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1518" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C1518" s="3">
+        <v>1.254</v>
+      </c>
+      <c r="D1518" s="3">
+        <v>1.254</v>
+      </c>
+      <c r="E1518" s="3">
+        <v>37.478</v>
+      </c>
+      <c r="F1518" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1518" s="3">
+        <v>38.732</v>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1519" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C1519" s="3">
+        <v>0.218</v>
+      </c>
+      <c r="D1519" s="3">
+        <v>0.218</v>
+      </c>
+      <c r="E1519" s="3">
+        <v>38.451</v>
+      </c>
+      <c r="F1519" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1519" s="3">
+        <v>38.669</v>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1520" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C1520" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1520" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1520" s="3">
+        <v>38.81</v>
+      </c>
+      <c r="F1520" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1520" s="3">
+        <v>38.81</v>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1521" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C1521" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1521" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1521" s="3">
+        <v>38.758</v>
+      </c>
+      <c r="F1521" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1521" s="3">
+        <v>38.758</v>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1522" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C1522" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1522" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1522" s="3">
+        <v>38.758</v>
+      </c>
+      <c r="F1522" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1522" s="3">
+        <v>38.758</v>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1523" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C1523" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1523" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1523" s="3">
+        <v>38.554</v>
+      </c>
+      <c r="F1523" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1523" s="3">
+        <v>38.554</v>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1524" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C1524" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1524" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1524" s="3">
+        <v>38.605</v>
+      </c>
+      <c r="F1524" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1524" s="3">
+        <v>38.605</v>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1525" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C1525" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1525" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1525" s="3">
+        <v>38.963</v>
+      </c>
+      <c r="F1525" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1525" s="3">
+        <v>38.963</v>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1526" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C1526" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1526" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1526" s="3">
+        <v>38.81</v>
+      </c>
+      <c r="F1526" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1526" s="3">
+        <v>38.81</v>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1527" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C1527" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1527" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1527" s="3">
+        <v>39.066</v>
+      </c>
+      <c r="F1527" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1527" s="3">
+        <v>39.066</v>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1528" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C1528" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1528" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1528" s="3">
+        <v>38.554</v>
+      </c>
+      <c r="F1528" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1528" s="3">
+        <v>38.554</v>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1529" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C1529" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1529" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1529" s="3">
+        <v>38.554</v>
+      </c>
+      <c r="F1529" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1529" s="3">
+        <v>38.554</v>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1530" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C1530" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1530" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1530" s="3">
+        <v>38.554</v>
+      </c>
+      <c r="F1530" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1530" s="3">
+        <v>38.554</v>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1531" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C1531" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1531" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1531" s="3">
+        <v>38.707</v>
+      </c>
+      <c r="F1531" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1531" s="3">
+        <v>38.707</v>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1532" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C1532" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1532" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1532" s="3">
+        <v>38.963</v>
+      </c>
+      <c r="F1532" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1532" s="3">
+        <v>38.963</v>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1533" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C1533" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1533" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1533" s="3">
+        <v>38.81</v>
+      </c>
+      <c r="F1533" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1533" s="3">
+        <v>38.81</v>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1534" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C1534" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1534" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1534" s="3">
+        <v>38.912</v>
+      </c>
+      <c r="F1534" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1534" s="3">
+        <v>38.912</v>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1535" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C1535" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1535" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1535" s="3">
+        <v>39.578</v>
+      </c>
+      <c r="F1535" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1535" s="3">
+        <v>39.578</v>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1536" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C1536" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1536" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1536" s="3">
+        <v>39.424</v>
+      </c>
+      <c r="F1536" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1536" s="3">
+        <v>39.424</v>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" s="2">
+        <v>46311</v>
+      </c>
+      <c r="B1537" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C1537" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1537" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1537" s="3">
+        <v>39.373</v>
+      </c>
+      <c r="F1537" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1537" s="3">
+        <v>39.373</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1441"/>
+  <autoFilter ref="A1:G1537"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -526,45 +526,69 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B21" s="4">
+        <v>2143.3</v>
+      </c>
+      <c r="C21" s="4">
+        <v>538.5</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1396.9</v>
+      </c>
+      <c r="E21" s="4">
+        <v>1604.8</v>
+      </c>
+      <c r="F21" s="4">
+        <v>1935.4</v>
+      </c>
+      <c r="G21" s="5">
+        <f>IF(F21&gt;0,C21/F21,"")</f>
+        <v>0.2782</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B21" s="7">
-        <f>SUM(B5:B20)</f>
-        <v>36035.3</v>
-      </c>
-      <c r="C21" s="7">
-        <f>SUM(C5:C20)</f>
-        <v>32100.5</v>
-      </c>
-      <c r="D21" s="7">
-        <f>SUM(D5:D20)</f>
-        <v>118502.4</v>
-      </c>
-      <c r="E21" s="7">
-        <f>SUM(E5:E20)</f>
-        <v>3934.8</v>
-      </c>
-      <c r="F21" s="7">
-        <f>SUM(F5:F20)</f>
-        <v>150603.0</v>
-      </c>
-      <c r="G21" s="8">
-        <f>IF(F21&gt;0,C21/F21,"")</f>
-        <v>0.2131</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B22" s="7">
+        <f>SUM(B5:B21)</f>
+        <v>38178.6</v>
+      </c>
+      <c r="C22" s="7">
+        <f>SUM(C5:C21)</f>
+        <v>32639.0</v>
+      </c>
+      <c r="D22" s="7">
+        <f>SUM(D5:D21)</f>
+        <v>119899.3</v>
+      </c>
+      <c r="E22" s="7">
+        <f>SUM(E5:E21)</f>
+        <v>5539.5</v>
+      </c>
+      <c r="F22" s="7">
+        <f>SUM(F5:F21)</f>
+        <v>152538.4</v>
+      </c>
+      <c r="G22" s="8">
+        <f>IF(F22&gt;0,C22/F22,"")</f>
+        <v>0.214</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -39023,7 +39047,2407 @@
         <v>39.373</v>
       </c>
     </row>
+    <row r="1538">
+      <c r="A1538" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1538" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C1538" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1538" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1538" s="3">
+        <v>38.758</v>
+      </c>
+      <c r="F1538" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1538" s="3">
+        <v>38.758</v>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1539" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C1539" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1539" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1539" s="3">
+        <v>38.349</v>
+      </c>
+      <c r="F1539" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1539" s="3">
+        <v>38.349</v>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1540" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C1540" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1540" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1540" s="3">
+        <v>38.349</v>
+      </c>
+      <c r="F1540" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1540" s="3">
+        <v>38.349</v>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1541" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C1541" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1541" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1541" s="3">
+        <v>38.195</v>
+      </c>
+      <c r="F1541" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1541" s="3">
+        <v>38.195</v>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1542" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C1542" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1542" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1542" s="3">
+        <v>38.144</v>
+      </c>
+      <c r="F1542" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1542" s="3">
+        <v>38.144</v>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1543" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C1543" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1543" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1543" s="3">
+        <v>38.093</v>
+      </c>
+      <c r="F1543" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1543" s="3">
+        <v>38.093</v>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1544" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C1544" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1544" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1544" s="3">
+        <v>38.246</v>
+      </c>
+      <c r="F1544" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1544" s="3">
+        <v>38.246</v>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1545" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C1545" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1545" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1545" s="3">
+        <v>38.298</v>
+      </c>
+      <c r="F1545" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1545" s="3">
+        <v>38.298</v>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1546" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C1546" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1546" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1546" s="3">
+        <v>38.451</v>
+      </c>
+      <c r="F1546" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1546" s="3">
+        <v>38.451</v>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1547" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C1547" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1547" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1547" s="3">
+        <v>38.656</v>
+      </c>
+      <c r="F1547" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1547" s="3">
+        <v>38.656</v>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1548" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C1548" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1548" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1548" s="3">
+        <v>37.325</v>
+      </c>
+      <c r="F1548" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1548" s="3">
+        <v>37.325</v>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1549" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C1549" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1549" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1549" s="3">
+        <v>35.226</v>
+      </c>
+      <c r="F1549" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1549" s="3">
+        <v>35.226</v>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1550" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C1550" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1550" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1550" s="3">
+        <v>35.277</v>
+      </c>
+      <c r="F1550" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1550" s="3">
+        <v>35.277</v>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1551" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C1551" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1551" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1551" s="3">
+        <v>35.226</v>
+      </c>
+      <c r="F1551" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1551" s="3">
+        <v>35.226</v>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1552" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C1552" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1552" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1552" s="3">
+        <v>35.277</v>
+      </c>
+      <c r="F1552" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1552" s="3">
+        <v>35.277</v>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1553" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C1553" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1553" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1553" s="3">
+        <v>35.482</v>
+      </c>
+      <c r="F1553" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1553" s="3">
+        <v>35.482</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1554" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C1554" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1554" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1554" s="3">
+        <v>35.482</v>
+      </c>
+      <c r="F1554" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1554" s="3">
+        <v>35.482</v>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1555" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C1555" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1555" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1555" s="3">
+        <v>35.226</v>
+      </c>
+      <c r="F1555" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1555" s="3">
+        <v>35.226</v>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1556" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C1556" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1556" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1556" s="3">
+        <v>35.226</v>
+      </c>
+      <c r="F1556" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1556" s="3">
+        <v>35.226</v>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1557" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C1557" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1557" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1557" s="3">
+        <v>35.328</v>
+      </c>
+      <c r="F1557" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1557" s="3">
+        <v>35.328</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1558" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C1558" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1558" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1558" s="3">
+        <v>35.328</v>
+      </c>
+      <c r="F1558" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1558" s="3">
+        <v>35.328</v>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1559" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C1559" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1559" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1559" s="3">
+        <v>35.482</v>
+      </c>
+      <c r="F1559" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1559" s="3">
+        <v>35.482</v>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1560" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C1560" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1560" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1560" s="3">
+        <v>35.379</v>
+      </c>
+      <c r="F1560" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1560" s="3">
+        <v>35.379</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1561" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C1561" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1561" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1561" s="3">
+        <v>35.584</v>
+      </c>
+      <c r="F1561" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1561" s="3">
+        <v>35.584</v>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1562" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C1562" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1562" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1562" s="3">
+        <v>35.277</v>
+      </c>
+      <c r="F1562" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1562" s="3">
+        <v>35.277</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1563" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C1563" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1563" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1563" s="3">
+        <v>35.123</v>
+      </c>
+      <c r="F1563" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1563" s="3">
+        <v>35.123</v>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1564" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C1564" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1564" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1564" s="3">
+        <v>35.328</v>
+      </c>
+      <c r="F1564" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1564" s="3">
+        <v>35.328</v>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1565" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C1565" s="3">
+        <v>0.09</v>
+      </c>
+      <c r="D1565" s="3">
+        <v>0.09</v>
+      </c>
+      <c r="E1565" s="3">
+        <v>35.84</v>
+      </c>
+      <c r="F1565" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1565" s="3">
+        <v>35.93</v>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1566" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C1566" s="3">
+        <v>1.101</v>
+      </c>
+      <c r="D1566" s="3">
+        <v>1.101</v>
+      </c>
+      <c r="E1566" s="3">
+        <v>34.611</v>
+      </c>
+      <c r="F1566" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1566" s="3">
+        <v>35.712</v>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1567" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C1567" s="3">
+        <v>1.715</v>
+      </c>
+      <c r="D1567" s="3">
+        <v>1.715</v>
+      </c>
+      <c r="E1567" s="3">
+        <v>33.485</v>
+      </c>
+      <c r="F1567" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1567" s="3">
+        <v>35.2</v>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1568" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C1568" s="3">
+        <v>2.342</v>
+      </c>
+      <c r="D1568" s="3">
+        <v>2.342</v>
+      </c>
+      <c r="E1568" s="3">
+        <v>32.819</v>
+      </c>
+      <c r="F1568" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1568" s="3">
+        <v>35.161</v>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1569" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C1569" s="3">
+        <v>5.146</v>
+      </c>
+      <c r="D1569" s="3">
+        <v>5.146</v>
+      </c>
+      <c r="E1569" s="3">
+        <v>38.042</v>
+      </c>
+      <c r="F1569" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1569" s="3">
+        <v>43.188</v>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1570" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C1570" s="3">
+        <v>8.013</v>
+      </c>
+      <c r="D1570" s="3">
+        <v>8.013</v>
+      </c>
+      <c r="E1570" s="3">
+        <v>40.141</v>
+      </c>
+      <c r="F1570" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1570" s="3">
+        <v>48.154</v>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1571" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C1571" s="3">
+        <v>23.45</v>
+      </c>
+      <c r="D1571" s="3">
+        <v>19.098</v>
+      </c>
+      <c r="E1571" s="3">
+        <v>17.203</v>
+      </c>
+      <c r="F1571" s="3">
+        <v>4.352</v>
+      </c>
+      <c r="G1571" s="3">
+        <v>36.301</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1572" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C1572" s="3">
+        <v>58.381</v>
+      </c>
+      <c r="D1572" s="3">
+        <v>35.341</v>
+      </c>
+      <c r="E1572" s="3">
+        <v>0.87</v>
+      </c>
+      <c r="F1572" s="3">
+        <v>23.04</v>
+      </c>
+      <c r="G1572" s="3">
+        <v>36.211</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1573" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C1573" s="3">
+        <v>24.435</v>
+      </c>
+      <c r="D1573" s="3">
+        <v>24.435</v>
+      </c>
+      <c r="E1573" s="3">
+        <v>11.366</v>
+      </c>
+      <c r="F1573" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1573" s="3">
+        <v>35.801</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1574" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C1574" s="3">
+        <v>29.082</v>
+      </c>
+      <c r="D1574" s="3">
+        <v>29.031</v>
+      </c>
+      <c r="E1574" s="3">
+        <v>7.014</v>
+      </c>
+      <c r="F1574" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G1574" s="3">
+        <v>36.045</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1575" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C1575" s="3">
+        <v>30.886</v>
+      </c>
+      <c r="D1575" s="3">
+        <v>30.835</v>
+      </c>
+      <c r="E1575" s="3">
+        <v>6.195</v>
+      </c>
+      <c r="F1575" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G1575" s="3">
+        <v>37.03</v>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1576" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C1576" s="3">
+        <v>29.773</v>
+      </c>
+      <c r="D1576" s="3">
+        <v>28.8</v>
+      </c>
+      <c r="E1576" s="3">
+        <v>7.424</v>
+      </c>
+      <c r="F1576" s="3">
+        <v>0.973</v>
+      </c>
+      <c r="G1576" s="3">
+        <v>36.224</v>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1577" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C1577" s="3">
+        <v>41.165</v>
+      </c>
+      <c r="D1577" s="3">
+        <v>35.789</v>
+      </c>
+      <c r="E1577" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1577" s="3">
+        <v>5.376</v>
+      </c>
+      <c r="G1577" s="3">
+        <v>35.789</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1578" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C1578" s="3">
+        <v>46.502</v>
+      </c>
+      <c r="D1578" s="3">
+        <v>33.958</v>
+      </c>
+      <c r="E1578" s="3">
+        <v>1.229</v>
+      </c>
+      <c r="F1578" s="3">
+        <v>12.544</v>
+      </c>
+      <c r="G1578" s="3">
+        <v>35.187</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1579" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C1579" s="3">
+        <v>59.213</v>
+      </c>
+      <c r="D1579" s="3">
+        <v>35.507</v>
+      </c>
+      <c r="E1579" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1579" s="3">
+        <v>23.706</v>
+      </c>
+      <c r="G1579" s="3">
+        <v>35.507</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1580" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C1580" s="3">
+        <v>68.864</v>
+      </c>
+      <c r="D1580" s="3">
+        <v>63.283</v>
+      </c>
+      <c r="E1580" s="3">
+        <v>4.762</v>
+      </c>
+      <c r="F1580" s="3">
+        <v>5.581</v>
+      </c>
+      <c r="G1580" s="3">
+        <v>68.045</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1581" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C1581" s="3">
+        <v>71.117</v>
+      </c>
+      <c r="D1581" s="3">
+        <v>17.92</v>
+      </c>
+      <c r="E1581" s="3">
+        <v>0.256</v>
+      </c>
+      <c r="F1581" s="3">
+        <v>53.197</v>
+      </c>
+      <c r="G1581" s="3">
+        <v>18.176</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1582" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C1582" s="3">
+        <v>58.957</v>
+      </c>
+      <c r="D1582" s="3">
+        <v>3.815</v>
+      </c>
+      <c r="E1582" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1582" s="3">
+        <v>55.142</v>
+      </c>
+      <c r="G1582" s="3">
+        <v>3.815</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1583" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C1583" s="3">
+        <v>72.013</v>
+      </c>
+      <c r="D1583" s="3">
+        <v>4.173</v>
+      </c>
+      <c r="E1583" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1583" s="3">
+        <v>67.84</v>
+      </c>
+      <c r="G1583" s="3">
+        <v>4.173</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1584" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C1584" s="3">
+        <v>85.491</v>
+      </c>
+      <c r="D1584" s="3">
+        <v>4.39</v>
+      </c>
+      <c r="E1584" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1584" s="3">
+        <v>81.101</v>
+      </c>
+      <c r="G1584" s="3">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1585" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C1585" s="3">
+        <v>97.267</v>
+      </c>
+      <c r="D1585" s="3">
+        <v>4.493</v>
+      </c>
+      <c r="E1585" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1585" s="3">
+        <v>92.774</v>
+      </c>
+      <c r="G1585" s="3">
+        <v>4.493</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1586" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C1586" s="3">
+        <v>96.077</v>
+      </c>
+      <c r="D1586" s="3">
+        <v>4.429</v>
+      </c>
+      <c r="E1586" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1586" s="3">
+        <v>91.648</v>
+      </c>
+      <c r="G1586" s="3">
+        <v>4.429</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1587" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C1587" s="3">
+        <v>111.501</v>
+      </c>
+      <c r="D1587" s="3">
+        <v>4.851</v>
+      </c>
+      <c r="E1587" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1587" s="3">
+        <v>106.65</v>
+      </c>
+      <c r="G1587" s="3">
+        <v>4.851</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1588" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C1588" s="3">
+        <v>81.114</v>
+      </c>
+      <c r="D1588" s="3">
+        <v>4.826</v>
+      </c>
+      <c r="E1588" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1588" s="3">
+        <v>76.288</v>
+      </c>
+      <c r="G1588" s="3">
+        <v>4.826</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1589" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C1589" s="3">
+        <v>40.102</v>
+      </c>
+      <c r="D1589" s="3">
+        <v>3.955</v>
+      </c>
+      <c r="E1589" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1589" s="3">
+        <v>36.147</v>
+      </c>
+      <c r="G1589" s="3">
+        <v>3.955</v>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1590" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C1590" s="3">
+        <v>63.053</v>
+      </c>
+      <c r="D1590" s="3">
+        <v>3.763</v>
+      </c>
+      <c r="E1590" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1590" s="3">
+        <v>59.29</v>
+      </c>
+      <c r="G1590" s="3">
+        <v>3.763</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1591" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C1591" s="3">
+        <v>74.202</v>
+      </c>
+      <c r="D1591" s="3">
+        <v>3.802</v>
+      </c>
+      <c r="E1591" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1591" s="3">
+        <v>70.4</v>
+      </c>
+      <c r="G1591" s="3">
+        <v>3.802</v>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1592" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C1592" s="3">
+        <v>79.206</v>
+      </c>
+      <c r="D1592" s="3">
+        <v>4.556</v>
+      </c>
+      <c r="E1592" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1592" s="3">
+        <v>74.65</v>
+      </c>
+      <c r="G1592" s="3">
+        <v>4.556</v>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1593" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C1593" s="3">
+        <v>104.717</v>
+      </c>
+      <c r="D1593" s="3">
+        <v>4.519</v>
+      </c>
+      <c r="E1593" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1593" s="3">
+        <v>100.198</v>
+      </c>
+      <c r="G1593" s="3">
+        <v>4.519</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1594" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C1594" s="3">
+        <v>79.386</v>
+      </c>
+      <c r="D1594" s="3">
+        <v>5.453</v>
+      </c>
+      <c r="E1594" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1594" s="3">
+        <v>73.933</v>
+      </c>
+      <c r="G1594" s="3">
+        <v>5.453</v>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1595" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C1595" s="3">
+        <v>70.042</v>
+      </c>
+      <c r="D1595" s="3">
+        <v>35.482</v>
+      </c>
+      <c r="E1595" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1595" s="3">
+        <v>34.56</v>
+      </c>
+      <c r="G1595" s="3">
+        <v>35.482</v>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1596" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C1596" s="3">
+        <v>86.042</v>
+      </c>
+      <c r="D1596" s="3">
+        <v>4.89</v>
+      </c>
+      <c r="E1596" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1596" s="3">
+        <v>81.152</v>
+      </c>
+      <c r="G1596" s="3">
+        <v>4.89</v>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1597" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C1597" s="3">
+        <v>98.509</v>
+      </c>
+      <c r="D1597" s="3">
+        <v>4.352</v>
+      </c>
+      <c r="E1597" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1597" s="3">
+        <v>94.157</v>
+      </c>
+      <c r="G1597" s="3">
+        <v>4.352</v>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1598" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C1598" s="3">
+        <v>70.029</v>
+      </c>
+      <c r="D1598" s="3">
+        <v>4.442</v>
+      </c>
+      <c r="E1598" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1598" s="3">
+        <v>65.587</v>
+      </c>
+      <c r="G1598" s="3">
+        <v>4.442</v>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1599" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C1599" s="3">
+        <v>83.226</v>
+      </c>
+      <c r="D1599" s="3">
+        <v>4.48</v>
+      </c>
+      <c r="E1599" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1599" s="3">
+        <v>78.746</v>
+      </c>
+      <c r="G1599" s="3">
+        <v>4.48</v>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1600" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C1600" s="3">
+        <v>79.206</v>
+      </c>
+      <c r="D1600" s="3">
+        <v>4.096</v>
+      </c>
+      <c r="E1600" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1600" s="3">
+        <v>75.11</v>
+      </c>
+      <c r="G1600" s="3">
+        <v>4.096</v>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1601" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C1601" s="3">
+        <v>26.368</v>
+      </c>
+      <c r="D1601" s="3">
+        <v>3.738</v>
+      </c>
+      <c r="E1601" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1601" s="3">
+        <v>22.63</v>
+      </c>
+      <c r="G1601" s="3">
+        <v>3.738</v>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1602" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C1602" s="3">
+        <v>2.189</v>
+      </c>
+      <c r="D1602" s="3">
+        <v>1.523</v>
+      </c>
+      <c r="E1602" s="3">
+        <v>1.997</v>
+      </c>
+      <c r="F1602" s="3">
+        <v>0.666</v>
+      </c>
+      <c r="G1602" s="3">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1603" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C1603" s="3">
+        <v>1.382</v>
+      </c>
+      <c r="D1603" s="3">
+        <v>1.075</v>
+      </c>
+      <c r="E1603" s="3">
+        <v>2.611</v>
+      </c>
+      <c r="F1603" s="3">
+        <v>0.307</v>
+      </c>
+      <c r="G1603" s="3">
+        <v>3.686</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1604" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C1604" s="3">
+        <v>1.434</v>
+      </c>
+      <c r="D1604" s="3">
+        <v>1.178</v>
+      </c>
+      <c r="E1604" s="3">
+        <v>2.765</v>
+      </c>
+      <c r="F1604" s="3">
+        <v>0.256</v>
+      </c>
+      <c r="G1604" s="3">
+        <v>3.943</v>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1605" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C1605" s="3">
+        <v>2.547</v>
+      </c>
+      <c r="D1605" s="3">
+        <v>1.779</v>
+      </c>
+      <c r="E1605" s="3">
+        <v>1.741</v>
+      </c>
+      <c r="F1605" s="3">
+        <v>0.768</v>
+      </c>
+      <c r="G1605" s="3">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1606" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C1606" s="3">
+        <v>5.581</v>
+      </c>
+      <c r="D1606" s="3">
+        <v>3.072</v>
+      </c>
+      <c r="E1606" s="3">
+        <v>0.307</v>
+      </c>
+      <c r="F1606" s="3">
+        <v>2.509</v>
+      </c>
+      <c r="G1606" s="3">
+        <v>3.379</v>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1607" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C1607" s="3">
+        <v>12.928</v>
+      </c>
+      <c r="D1607" s="3">
+        <v>3.558</v>
+      </c>
+      <c r="E1607" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1607" s="3">
+        <v>9.37</v>
+      </c>
+      <c r="G1607" s="3">
+        <v>3.558</v>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1608" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C1608" s="3">
+        <v>8.307</v>
+      </c>
+      <c r="D1608" s="3">
+        <v>3.443</v>
+      </c>
+      <c r="E1608" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1608" s="3">
+        <v>4.864</v>
+      </c>
+      <c r="G1608" s="3">
+        <v>3.443</v>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1609" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C1609" s="3">
+        <v>8.73</v>
+      </c>
+      <c r="D1609" s="3">
+        <v>4.788</v>
+      </c>
+      <c r="E1609" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="F1609" s="3">
+        <v>3.942</v>
+      </c>
+      <c r="G1609" s="3">
+        <v>4.839</v>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1610" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C1610" s="3">
+        <v>8.282</v>
+      </c>
+      <c r="D1610" s="3">
+        <v>6.08</v>
+      </c>
+      <c r="E1610" s="3">
+        <v>0.205</v>
+      </c>
+      <c r="F1610" s="3">
+        <v>2.202</v>
+      </c>
+      <c r="G1610" s="3">
+        <v>6.285</v>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1611" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C1611" s="3">
+        <v>8.896</v>
+      </c>
+      <c r="D1611" s="3">
+        <v>6.541</v>
+      </c>
+      <c r="E1611" s="3">
+        <v>0.256</v>
+      </c>
+      <c r="F1611" s="3">
+        <v>2.355</v>
+      </c>
+      <c r="G1611" s="3">
+        <v>6.797</v>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1612" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C1612" s="3">
+        <v>14.323</v>
+      </c>
+      <c r="D1612" s="3">
+        <v>6.541</v>
+      </c>
+      <c r="E1612" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1612" s="3">
+        <v>7.782</v>
+      </c>
+      <c r="G1612" s="3">
+        <v>6.541</v>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1613" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C1613" s="3">
+        <v>8.218</v>
+      </c>
+      <c r="D1613" s="3">
+        <v>5.351</v>
+      </c>
+      <c r="E1613" s="3">
+        <v>0.819</v>
+      </c>
+      <c r="F1613" s="3">
+        <v>2.867</v>
+      </c>
+      <c r="G1613" s="3">
+        <v>6.17</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1614" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C1614" s="3">
+        <v>2.074</v>
+      </c>
+      <c r="D1614" s="3">
+        <v>2.074</v>
+      </c>
+      <c r="E1614" s="3">
+        <v>4.198</v>
+      </c>
+      <c r="F1614" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1614" s="3">
+        <v>6.272</v>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1615" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C1615" s="3">
+        <v>0.563</v>
+      </c>
+      <c r="D1615" s="3">
+        <v>0.563</v>
+      </c>
+      <c r="E1615" s="3">
+        <v>6.758</v>
+      </c>
+      <c r="F1615" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1615" s="3">
+        <v>7.321</v>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1616" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C1616" s="3">
+        <v>0.038</v>
+      </c>
+      <c r="D1616" s="3">
+        <v>0.038</v>
+      </c>
+      <c r="E1616" s="3">
+        <v>7.578</v>
+      </c>
+      <c r="F1616" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1616" s="3">
+        <v>7.616</v>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1617" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C1617" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1617" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1617" s="3">
+        <v>7.168</v>
+      </c>
+      <c r="F1617" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1617" s="3">
+        <v>7.168</v>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1618" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C1618" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1618" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1618" s="3">
+        <v>6.4</v>
+      </c>
+      <c r="F1618" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1618" s="3">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1619" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C1619" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1619" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1619" s="3">
+        <v>6.298</v>
+      </c>
+      <c r="F1619" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1619" s="3">
+        <v>6.298</v>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1620" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C1620" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1620" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1620" s="3">
+        <v>6.707</v>
+      </c>
+      <c r="F1620" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1620" s="3">
+        <v>6.707</v>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1621" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C1621" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1621" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1621" s="3">
+        <v>6.502</v>
+      </c>
+      <c r="F1621" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1621" s="3">
+        <v>6.502</v>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1622" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C1622" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1622" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1622" s="3">
+        <v>6.4</v>
+      </c>
+      <c r="F1622" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1622" s="3">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1623" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C1623" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1623" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1623" s="3">
+        <v>6.4</v>
+      </c>
+      <c r="F1623" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1623" s="3">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1624" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C1624" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1624" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1624" s="3">
+        <v>6.758</v>
+      </c>
+      <c r="F1624" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1624" s="3">
+        <v>6.758</v>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1625" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C1625" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1625" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1625" s="3">
+        <v>6.4</v>
+      </c>
+      <c r="F1625" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1625" s="3">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1626" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C1626" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1626" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1626" s="3">
+        <v>6.298</v>
+      </c>
+      <c r="F1626" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1626" s="3">
+        <v>6.298</v>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1627" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C1627" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1627" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1627" s="3">
+        <v>6.298</v>
+      </c>
+      <c r="F1627" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1627" s="3">
+        <v>6.298</v>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1628" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C1628" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1628" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1628" s="3">
+        <v>6.298</v>
+      </c>
+      <c r="F1628" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1628" s="3">
+        <v>6.298</v>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1629" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C1629" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1629" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1629" s="3">
+        <v>6.605</v>
+      </c>
+      <c r="F1629" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1629" s="3">
+        <v>6.605</v>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1630" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C1630" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1630" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1630" s="3">
+        <v>6.298</v>
+      </c>
+      <c r="F1630" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1630" s="3">
+        <v>6.298</v>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1631" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C1631" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1631" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1631" s="3">
+        <v>6.349</v>
+      </c>
+      <c r="F1631" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1631" s="3">
+        <v>6.349</v>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1632" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C1632" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1632" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1632" s="3">
+        <v>6.502</v>
+      </c>
+      <c r="F1632" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1632" s="3">
+        <v>6.502</v>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" s="2">
+        <v>46312</v>
+      </c>
+      <c r="B1633" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C1633" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1633" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1633" s="3">
+        <v>6.554</v>
+      </c>
+      <c r="F1633" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1633" s="3">
+        <v>6.554</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1537"/>
+  <autoFilter ref="A1:G1633"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -550,45 +550,69 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B22" s="4">
+        <v>2067.7</v>
+      </c>
+      <c r="C22" s="4">
+        <v>237.9</v>
+      </c>
+      <c r="D22" s="4">
+        <v>282.1</v>
+      </c>
+      <c r="E22" s="4">
+        <v>1829.9</v>
+      </c>
+      <c r="F22" s="4">
+        <v>520.0</v>
+      </c>
+      <c r="G22" s="5">
+        <f>IF(F22&gt;0,C22/F22,"")</f>
+        <v>0.4575</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B22" s="7">
-        <f>SUM(B5:B21)</f>
-        <v>38178.6</v>
-      </c>
-      <c r="C22" s="7">
-        <f>SUM(C5:C21)</f>
-        <v>32639.0</v>
-      </c>
-      <c r="D22" s="7">
-        <f>SUM(D5:D21)</f>
-        <v>119899.3</v>
-      </c>
-      <c r="E22" s="7">
-        <f>SUM(E5:E21)</f>
-        <v>5539.5</v>
-      </c>
-      <c r="F22" s="7">
-        <f>SUM(F5:F21)</f>
-        <v>152538.4</v>
-      </c>
-      <c r="G22" s="8">
-        <f>IF(F22&gt;0,C22/F22,"")</f>
-        <v>0.214</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B23" s="7">
+        <f>SUM(B5:B22)</f>
+        <v>40246.2</v>
+      </c>
+      <c r="C23" s="7">
+        <f>SUM(C5:C22)</f>
+        <v>32876.9</v>
+      </c>
+      <c r="D23" s="7">
+        <f>SUM(D5:D22)</f>
+        <v>120181.5</v>
+      </c>
+      <c r="E23" s="7">
+        <f>SUM(E5:E22)</f>
+        <v>7369.4</v>
+      </c>
+      <c r="F23" s="7">
+        <f>SUM(F5:F22)</f>
+        <v>153058.4</v>
+      </c>
+      <c r="G23" s="8">
+        <f>IF(F23&gt;0,C23/F23,"")</f>
+        <v>0.2148</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -41447,7 +41471,2407 @@
         <v>6.554</v>
       </c>
     </row>
+    <row r="1634">
+      <c r="A1634" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1634" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C1634" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1634" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1634" s="3">
+        <v>6.861</v>
+      </c>
+      <c r="F1634" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1634" s="3">
+        <v>6.861</v>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1635" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C1635" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1635" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1635" s="3">
+        <v>6.707</v>
+      </c>
+      <c r="F1635" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1635" s="3">
+        <v>6.707</v>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1636" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C1636" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1636" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1636" s="3">
+        <v>6.656</v>
+      </c>
+      <c r="F1636" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1636" s="3">
+        <v>6.656</v>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1637" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C1637" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1637" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1637" s="3">
+        <v>6.349</v>
+      </c>
+      <c r="F1637" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1637" s="3">
+        <v>6.349</v>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1638" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C1638" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1638" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1638" s="3">
+        <v>6.298</v>
+      </c>
+      <c r="F1638" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1638" s="3">
+        <v>6.298</v>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1639" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C1639" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1639" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1639" s="3">
+        <v>6.195</v>
+      </c>
+      <c r="F1639" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1639" s="3">
+        <v>6.195</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1640" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C1640" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1640" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1640" s="3">
+        <v>6.195</v>
+      </c>
+      <c r="F1640" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1640" s="3">
+        <v>6.195</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1641" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C1641" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1641" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1641" s="3">
+        <v>6.246</v>
+      </c>
+      <c r="F1641" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1641" s="3">
+        <v>6.246</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1642" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C1642" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1642" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1642" s="3">
+        <v>6.246</v>
+      </c>
+      <c r="F1642" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1642" s="3">
+        <v>6.246</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1643" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C1643" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1643" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1643" s="3">
+        <v>6.451</v>
+      </c>
+      <c r="F1643" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1643" s="3">
+        <v>6.451</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1644" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C1644" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1644" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1644" s="3">
+        <v>6.195</v>
+      </c>
+      <c r="F1644" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1644" s="3">
+        <v>6.195</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1645" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C1645" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1645" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1645" s="3">
+        <v>6.298</v>
+      </c>
+      <c r="F1645" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1645" s="3">
+        <v>6.298</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1646" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C1646" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1646" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1646" s="3">
+        <v>6.298</v>
+      </c>
+      <c r="F1646" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1646" s="3">
+        <v>6.298</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1647" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C1647" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1647" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1647" s="3">
+        <v>6.349</v>
+      </c>
+      <c r="F1647" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1647" s="3">
+        <v>6.349</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1648" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C1648" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1648" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1648" s="3">
+        <v>5.325</v>
+      </c>
+      <c r="F1648" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1648" s="3">
+        <v>5.325</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1649" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C1649" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1649" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1649" s="3">
+        <v>3.738</v>
+      </c>
+      <c r="F1649" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1649" s="3">
+        <v>3.738</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1650" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C1650" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1650" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1650" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F1650" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1650" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1651" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C1651" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1651" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1651" s="3">
+        <v>3.328</v>
+      </c>
+      <c r="F1651" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1651" s="3">
+        <v>3.328</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1652" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C1652" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1652" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1652" s="3">
+        <v>3.379</v>
+      </c>
+      <c r="F1652" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1652" s="3">
+        <v>3.379</v>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1653" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C1653" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1653" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1653" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F1653" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1653" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1654" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C1654" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1654" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1654" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F1654" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G1654" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1655" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C1655" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1655" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1655" s="3">
+        <v>3.482</v>
+      </c>
+      <c r="F1655" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G1655" s="3">
+        <v>3.482</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1656" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C1656" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1656" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1656" s="3">
+        <v>3.994</v>
+      </c>
+      <c r="F1656" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1656" s="3">
+        <v>3.994</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1657" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C1657" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1657" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1657" s="3">
+        <v>4.096</v>
+      </c>
+      <c r="F1657" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1657" s="3">
+        <v>4.096</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1658" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C1658" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1658" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1658" s="3">
+        <v>3.994</v>
+      </c>
+      <c r="F1658" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1658" s="3">
+        <v>3.994</v>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1659" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C1659" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1659" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1659" s="3">
+        <v>3.738</v>
+      </c>
+      <c r="F1659" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1659" s="3">
+        <v>3.738</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1660" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C1660" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1660" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1660" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F1660" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1660" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1661" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C1661" s="3">
+        <v>0.115</v>
+      </c>
+      <c r="D1661" s="3">
+        <v>0.115</v>
+      </c>
+      <c r="E1661" s="3">
+        <v>3.072</v>
+      </c>
+      <c r="F1661" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1661" s="3">
+        <v>3.187</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1662" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C1662" s="3">
+        <v>0.653</v>
+      </c>
+      <c r="D1662" s="3">
+        <v>0.653</v>
+      </c>
+      <c r="E1662" s="3">
+        <v>2.867</v>
+      </c>
+      <c r="F1662" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1662" s="3">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1663" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C1663" s="3">
+        <v>1.894</v>
+      </c>
+      <c r="D1663" s="3">
+        <v>1.587</v>
+      </c>
+      <c r="E1663" s="3">
+        <v>1.946</v>
+      </c>
+      <c r="F1663" s="3">
+        <v>0.307</v>
+      </c>
+      <c r="G1663" s="3">
+        <v>3.533</v>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1664" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C1664" s="3">
+        <v>4.736</v>
+      </c>
+      <c r="D1664" s="3">
+        <v>2.944</v>
+      </c>
+      <c r="E1664" s="3">
+        <v>0.307</v>
+      </c>
+      <c r="F1664" s="3">
+        <v>1.792</v>
+      </c>
+      <c r="G1664" s="3">
+        <v>3.251</v>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1665" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C1665" s="3">
+        <v>6.426</v>
+      </c>
+      <c r="D1665" s="3">
+        <v>2.996</v>
+      </c>
+      <c r="E1665" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1665" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G1665" s="3">
+        <v>2.996</v>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1666" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C1666" s="3">
+        <v>5.939</v>
+      </c>
+      <c r="D1666" s="3">
+        <v>3.021</v>
+      </c>
+      <c r="E1666" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1666" s="3">
+        <v>2.918</v>
+      </c>
+      <c r="G1666" s="3">
+        <v>3.021</v>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1667" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C1667" s="3">
+        <v>7.347</v>
+      </c>
+      <c r="D1667" s="3">
+        <v>2.944</v>
+      </c>
+      <c r="E1667" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1667" s="3">
+        <v>4.403</v>
+      </c>
+      <c r="G1667" s="3">
+        <v>2.944</v>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1668" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C1668" s="3">
+        <v>12.544</v>
+      </c>
+      <c r="D1668" s="3">
+        <v>3.226</v>
+      </c>
+      <c r="E1668" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1668" s="3">
+        <v>9.318</v>
+      </c>
+      <c r="G1668" s="3">
+        <v>3.226</v>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1669" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C1669" s="3">
+        <v>9.766</v>
+      </c>
+      <c r="D1669" s="3">
+        <v>3.161</v>
+      </c>
+      <c r="E1669" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1669" s="3">
+        <v>6.605</v>
+      </c>
+      <c r="G1669" s="3">
+        <v>3.161</v>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1670" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C1670" s="3">
+        <v>14.195</v>
+      </c>
+      <c r="D1670" s="3">
+        <v>3.033</v>
+      </c>
+      <c r="E1670" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1670" s="3">
+        <v>11.162</v>
+      </c>
+      <c r="G1670" s="3">
+        <v>3.033</v>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1671" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C1671" s="3">
+        <v>18.931</v>
+      </c>
+      <c r="D1671" s="3">
+        <v>3.161</v>
+      </c>
+      <c r="E1671" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1671" s="3">
+        <v>15.77</v>
+      </c>
+      <c r="G1671" s="3">
+        <v>3.161</v>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1672" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C1672" s="3">
+        <v>22.758</v>
+      </c>
+      <c r="D1672" s="3">
+        <v>3.302</v>
+      </c>
+      <c r="E1672" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1672" s="3">
+        <v>19.456</v>
+      </c>
+      <c r="G1672" s="3">
+        <v>3.302</v>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1673" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C1673" s="3">
+        <v>27.866</v>
+      </c>
+      <c r="D1673" s="3">
+        <v>3.444</v>
+      </c>
+      <c r="E1673" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1673" s="3">
+        <v>24.422</v>
+      </c>
+      <c r="G1673" s="3">
+        <v>3.444</v>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1674" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C1674" s="3">
+        <v>26.752</v>
+      </c>
+      <c r="D1674" s="3">
+        <v>3.405</v>
+      </c>
+      <c r="E1674" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1674" s="3">
+        <v>23.347</v>
+      </c>
+      <c r="G1674" s="3">
+        <v>3.405</v>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1675" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C1675" s="3">
+        <v>29.862</v>
+      </c>
+      <c r="D1675" s="3">
+        <v>3.699</v>
+      </c>
+      <c r="E1675" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1675" s="3">
+        <v>26.163</v>
+      </c>
+      <c r="G1675" s="3">
+        <v>3.699</v>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1676" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C1676" s="3">
+        <v>32.397</v>
+      </c>
+      <c r="D1676" s="3">
+        <v>3.571</v>
+      </c>
+      <c r="E1676" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1676" s="3">
+        <v>28.826</v>
+      </c>
+      <c r="G1676" s="3">
+        <v>3.571</v>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1677" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C1677" s="3">
+        <v>38.566</v>
+      </c>
+      <c r="D1677" s="3">
+        <v>3.443</v>
+      </c>
+      <c r="E1677" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1677" s="3">
+        <v>35.123</v>
+      </c>
+      <c r="G1677" s="3">
+        <v>3.443</v>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1678" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C1678" s="3">
+        <v>39.718</v>
+      </c>
+      <c r="D1678" s="3">
+        <v>4.032</v>
+      </c>
+      <c r="E1678" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1678" s="3">
+        <v>35.686</v>
+      </c>
+      <c r="G1678" s="3">
+        <v>4.032</v>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1679" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C1679" s="3">
+        <v>52.672</v>
+      </c>
+      <c r="D1679" s="3">
+        <v>4.134</v>
+      </c>
+      <c r="E1679" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1679" s="3">
+        <v>48.538</v>
+      </c>
+      <c r="G1679" s="3">
+        <v>4.134</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1680" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C1680" s="3">
+        <v>64.192</v>
+      </c>
+      <c r="D1680" s="3">
+        <v>4.493</v>
+      </c>
+      <c r="E1680" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1680" s="3">
+        <v>59.699</v>
+      </c>
+      <c r="G1680" s="3">
+        <v>4.493</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1681" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C1681" s="3">
+        <v>60.147</v>
+      </c>
+      <c r="D1681" s="3">
+        <v>4.288</v>
+      </c>
+      <c r="E1681" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1681" s="3">
+        <v>55.859</v>
+      </c>
+      <c r="G1681" s="3">
+        <v>4.288</v>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1682" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C1682" s="3">
+        <v>30.426</v>
+      </c>
+      <c r="D1682" s="3">
+        <v>4.416</v>
+      </c>
+      <c r="E1682" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1682" s="3">
+        <v>26.01</v>
+      </c>
+      <c r="G1682" s="3">
+        <v>4.416</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1683" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C1683" s="3">
+        <v>36.198</v>
+      </c>
+      <c r="D1683" s="3">
+        <v>3.584</v>
+      </c>
+      <c r="E1683" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1683" s="3">
+        <v>32.614</v>
+      </c>
+      <c r="G1683" s="3">
+        <v>3.584</v>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1684" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C1684" s="3">
+        <v>37.21</v>
+      </c>
+      <c r="D1684" s="3">
+        <v>4.135</v>
+      </c>
+      <c r="E1684" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1684" s="3">
+        <v>33.075</v>
+      </c>
+      <c r="G1684" s="3">
+        <v>4.135</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1685" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C1685" s="3">
+        <v>77.21</v>
+      </c>
+      <c r="D1685" s="3">
+        <v>4.25</v>
+      </c>
+      <c r="E1685" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1685" s="3">
+        <v>72.96</v>
+      </c>
+      <c r="G1685" s="3">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1686" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C1686" s="3">
+        <v>81.997</v>
+      </c>
+      <c r="D1686" s="3">
+        <v>4.224</v>
+      </c>
+      <c r="E1686" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1686" s="3">
+        <v>77.773</v>
+      </c>
+      <c r="G1686" s="3">
+        <v>4.224</v>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1687" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C1687" s="3">
+        <v>72.525</v>
+      </c>
+      <c r="D1687" s="3">
+        <v>4.685</v>
+      </c>
+      <c r="E1687" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1687" s="3">
+        <v>67.84</v>
+      </c>
+      <c r="G1687" s="3">
+        <v>4.685</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1688" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C1688" s="3">
+        <v>99.866</v>
+      </c>
+      <c r="D1688" s="3">
+        <v>4.89</v>
+      </c>
+      <c r="E1688" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1688" s="3">
+        <v>94.976</v>
+      </c>
+      <c r="G1688" s="3">
+        <v>4.89</v>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1689" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C1689" s="3">
+        <v>68.442</v>
+      </c>
+      <c r="D1689" s="3">
+        <v>4.544</v>
+      </c>
+      <c r="E1689" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1689" s="3">
+        <v>63.898</v>
+      </c>
+      <c r="G1689" s="3">
+        <v>4.544</v>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1690" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C1690" s="3">
+        <v>74.867</v>
+      </c>
+      <c r="D1690" s="3">
+        <v>4.057</v>
+      </c>
+      <c r="E1690" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1690" s="3">
+        <v>70.81</v>
+      </c>
+      <c r="G1690" s="3">
+        <v>4.057</v>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1691" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C1691" s="3">
+        <v>62.976</v>
+      </c>
+      <c r="D1691" s="3">
+        <v>3.942</v>
+      </c>
+      <c r="E1691" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1691" s="3">
+        <v>59.034</v>
+      </c>
+      <c r="G1691" s="3">
+        <v>3.942</v>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1692" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C1692" s="3">
+        <v>101.12</v>
+      </c>
+      <c r="D1692" s="3">
+        <v>7.373</v>
+      </c>
+      <c r="E1692" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1692" s="3">
+        <v>93.747</v>
+      </c>
+      <c r="G1692" s="3">
+        <v>7.373</v>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1693" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C1693" s="3">
+        <v>109.696</v>
+      </c>
+      <c r="D1693" s="3">
+        <v>7.603</v>
+      </c>
+      <c r="E1693" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1693" s="3">
+        <v>102.093</v>
+      </c>
+      <c r="G1693" s="3">
+        <v>7.603</v>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1694" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C1694" s="3">
+        <v>74.061</v>
+      </c>
+      <c r="D1694" s="3">
+        <v>7.347</v>
+      </c>
+      <c r="E1694" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1694" s="3">
+        <v>66.714</v>
+      </c>
+      <c r="G1694" s="3">
+        <v>7.347</v>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1695" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C1695" s="3">
+        <v>36.493</v>
+      </c>
+      <c r="D1695" s="3">
+        <v>7.463</v>
+      </c>
+      <c r="E1695" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1695" s="3">
+        <v>29.03</v>
+      </c>
+      <c r="G1695" s="3">
+        <v>7.463</v>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1696" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C1696" s="3">
+        <v>88.934</v>
+      </c>
+      <c r="D1696" s="3">
+        <v>8.396</v>
+      </c>
+      <c r="E1696" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1696" s="3">
+        <v>80.538</v>
+      </c>
+      <c r="G1696" s="3">
+        <v>8.396</v>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1697" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C1697" s="3">
+        <v>75.341</v>
+      </c>
+      <c r="D1697" s="3">
+        <v>7.655</v>
+      </c>
+      <c r="E1697" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1697" s="3">
+        <v>67.686</v>
+      </c>
+      <c r="G1697" s="3">
+        <v>7.655</v>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1698" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C1698" s="3">
+        <v>92.941</v>
+      </c>
+      <c r="D1698" s="3">
+        <v>7.949</v>
+      </c>
+      <c r="E1698" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1698" s="3">
+        <v>84.992</v>
+      </c>
+      <c r="G1698" s="3">
+        <v>7.949</v>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1699" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C1699" s="3">
+        <v>63.59</v>
+      </c>
+      <c r="D1699" s="3">
+        <v>7.475</v>
+      </c>
+      <c r="E1699" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1699" s="3">
+        <v>56.115</v>
+      </c>
+      <c r="G1699" s="3">
+        <v>7.475</v>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1700" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C1700" s="3">
+        <v>57.229</v>
+      </c>
+      <c r="D1700" s="3">
+        <v>7.719</v>
+      </c>
+      <c r="E1700" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1700" s="3">
+        <v>49.51</v>
+      </c>
+      <c r="G1700" s="3">
+        <v>7.719</v>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1701" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C1701" s="3">
+        <v>35.046</v>
+      </c>
+      <c r="D1701" s="3">
+        <v>6.835</v>
+      </c>
+      <c r="E1701" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1701" s="3">
+        <v>28.211</v>
+      </c>
+      <c r="G1701" s="3">
+        <v>6.835</v>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1702" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C1702" s="3">
+        <v>42.701</v>
+      </c>
+      <c r="D1702" s="3">
+        <v>6.963</v>
+      </c>
+      <c r="E1702" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1702" s="3">
+        <v>35.738</v>
+      </c>
+      <c r="G1702" s="3">
+        <v>6.963</v>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1703" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C1703" s="3">
+        <v>45.594</v>
+      </c>
+      <c r="D1703" s="3">
+        <v>7.194</v>
+      </c>
+      <c r="E1703" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1703" s="3">
+        <v>38.4</v>
+      </c>
+      <c r="G1703" s="3">
+        <v>7.194</v>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1704" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C1704" s="3">
+        <v>37.875</v>
+      </c>
+      <c r="D1704" s="3">
+        <v>6.899</v>
+      </c>
+      <c r="E1704" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1704" s="3">
+        <v>30.976</v>
+      </c>
+      <c r="G1704" s="3">
+        <v>6.899</v>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1705" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C1705" s="3">
+        <v>35.661</v>
+      </c>
+      <c r="D1705" s="3">
+        <v>7.143</v>
+      </c>
+      <c r="E1705" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1705" s="3">
+        <v>28.518</v>
+      </c>
+      <c r="G1705" s="3">
+        <v>7.143</v>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1706" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C1706" s="3">
+        <v>24.358</v>
+      </c>
+      <c r="D1706" s="3">
+        <v>6.489</v>
+      </c>
+      <c r="E1706" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1706" s="3">
+        <v>17.869</v>
+      </c>
+      <c r="G1706" s="3">
+        <v>6.489</v>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1707" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C1707" s="3">
+        <v>11.571</v>
+      </c>
+      <c r="D1707" s="3">
+        <v>6.502</v>
+      </c>
+      <c r="E1707" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1707" s="3">
+        <v>5.069</v>
+      </c>
+      <c r="G1707" s="3">
+        <v>6.502</v>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1708" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C1708" s="3">
+        <v>7.974</v>
+      </c>
+      <c r="D1708" s="3">
+        <v>5.977</v>
+      </c>
+      <c r="E1708" s="3">
+        <v>0.461</v>
+      </c>
+      <c r="F1708" s="3">
+        <v>1.997</v>
+      </c>
+      <c r="G1708" s="3">
+        <v>6.438</v>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1709" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C1709" s="3">
+        <v>5.171</v>
+      </c>
+      <c r="D1709" s="3">
+        <v>4.454</v>
+      </c>
+      <c r="E1709" s="3">
+        <v>1.894</v>
+      </c>
+      <c r="F1709" s="3">
+        <v>0.717</v>
+      </c>
+      <c r="G1709" s="3">
+        <v>6.348</v>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1710" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C1710" s="3">
+        <v>2.637</v>
+      </c>
+      <c r="D1710" s="3">
+        <v>2.586</v>
+      </c>
+      <c r="E1710" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="F1710" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G1710" s="3">
+        <v>6.426</v>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1711" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C1711" s="3">
+        <v>0.461</v>
+      </c>
+      <c r="D1711" s="3">
+        <v>0.461</v>
+      </c>
+      <c r="E1711" s="3">
+        <v>5.888</v>
+      </c>
+      <c r="F1711" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1711" s="3">
+        <v>6.349</v>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1712" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C1712" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="D1712" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="E1712" s="3">
+        <v>6.81</v>
+      </c>
+      <c r="F1712" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1712" s="3">
+        <v>6.823</v>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1713" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C1713" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1713" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1713" s="3">
+        <v>7.117</v>
+      </c>
+      <c r="F1713" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1713" s="3">
+        <v>7.117</v>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1714" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C1714" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1714" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1714" s="3">
+        <v>6.81</v>
+      </c>
+      <c r="F1714" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1714" s="3">
+        <v>6.81</v>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1715" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C1715" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1715" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1715" s="3">
+        <v>7.066</v>
+      </c>
+      <c r="F1715" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1715" s="3">
+        <v>7.066</v>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1716" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C1716" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1716" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1716" s="3">
+        <v>6.605</v>
+      </c>
+      <c r="F1716" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1716" s="3">
+        <v>6.605</v>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1717" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C1717" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1717" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1717" s="3">
+        <v>6.451</v>
+      </c>
+      <c r="F1717" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1717" s="3">
+        <v>6.451</v>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1718" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C1718" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1718" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1718" s="3">
+        <v>6.912</v>
+      </c>
+      <c r="F1718" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1718" s="3">
+        <v>6.912</v>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1719" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C1719" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1719" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1719" s="3">
+        <v>6.4</v>
+      </c>
+      <c r="F1719" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1719" s="3">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1720" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C1720" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1720" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1720" s="3">
+        <v>6.554</v>
+      </c>
+      <c r="F1720" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1720" s="3">
+        <v>6.554</v>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1721" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C1721" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1721" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1721" s="3">
+        <v>6.912</v>
+      </c>
+      <c r="F1721" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1721" s="3">
+        <v>6.912</v>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1722" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C1722" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1722" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1722" s="3">
+        <v>7.219</v>
+      </c>
+      <c r="F1722" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1722" s="3">
+        <v>7.219</v>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1723" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C1723" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1723" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1723" s="3">
+        <v>7.066</v>
+      </c>
+      <c r="F1723" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1723" s="3">
+        <v>7.066</v>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1724" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C1724" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1724" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1724" s="3">
+        <v>7.219</v>
+      </c>
+      <c r="F1724" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1724" s="3">
+        <v>7.219</v>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1725" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C1725" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1725" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1725" s="3">
+        <v>6.861</v>
+      </c>
+      <c r="F1725" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1725" s="3">
+        <v>6.861</v>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1726" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C1726" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1726" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1726" s="3">
+        <v>7.322</v>
+      </c>
+      <c r="F1726" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1726" s="3">
+        <v>7.322</v>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1727" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C1727" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1727" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1727" s="3">
+        <v>7.066</v>
+      </c>
+      <c r="F1727" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1727" s="3">
+        <v>7.066</v>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1728" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C1728" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1728" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1728" s="3">
+        <v>6.758</v>
+      </c>
+      <c r="F1728" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1728" s="3">
+        <v>6.758</v>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" s="2">
+        <v>46313</v>
+      </c>
+      <c r="B1729" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C1729" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1729" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1729" s="3">
+        <v>6.554</v>
+      </c>
+      <c r="F1729" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1729" s="3">
+        <v>6.554</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1633"/>
+  <autoFilter ref="A1:G1729"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -574,45 +574,69 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B23" s="4">
+        <v>1511.1</v>
+      </c>
+      <c r="C23" s="4">
+        <v>434.4</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1057.2</v>
+      </c>
+      <c r="E23" s="4">
+        <v>1076.7</v>
+      </c>
+      <c r="F23" s="4">
+        <v>1491.6</v>
+      </c>
+      <c r="G23" s="5">
+        <f>IF(F23&gt;0,C23/F23,"")</f>
+        <v>0.2912</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B23" s="7">
-        <f>SUM(B5:B22)</f>
-        <v>40246.2</v>
-      </c>
-      <c r="C23" s="7">
-        <f>SUM(C5:C22)</f>
-        <v>32876.9</v>
-      </c>
-      <c r="D23" s="7">
-        <f>SUM(D5:D22)</f>
-        <v>120181.5</v>
-      </c>
-      <c r="E23" s="7">
-        <f>SUM(E5:E22)</f>
-        <v>7369.4</v>
-      </c>
-      <c r="F23" s="7">
-        <f>SUM(F5:F22)</f>
-        <v>153058.4</v>
-      </c>
-      <c r="G23" s="8">
-        <f>IF(F23&gt;0,C23/F23,"")</f>
-        <v>0.2148</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B24" s="7">
+        <f>SUM(B5:B23)</f>
+        <v>41757.3</v>
+      </c>
+      <c r="C24" s="7">
+        <f>SUM(C5:C23)</f>
+        <v>33311.3</v>
+      </c>
+      <c r="D24" s="7">
+        <f>SUM(D5:D23)</f>
+        <v>121238.6</v>
+      </c>
+      <c r="E24" s="7">
+        <f>SUM(E5:E23)</f>
+        <v>8446.2</v>
+      </c>
+      <c r="F24" s="7">
+        <f>SUM(F5:F23)</f>
+        <v>154550.0</v>
+      </c>
+      <c r="G24" s="8">
+        <f>IF(F24&gt;0,C24/F24,"")</f>
+        <v>0.2155</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -43871,7 +43895,2407 @@
         <v>6.554</v>
       </c>
     </row>
+    <row r="1730">
+      <c r="A1730" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1730" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C1730" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1730" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1730" s="3">
+        <v>3.789</v>
+      </c>
+      <c r="F1730" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1730" s="3">
+        <v>3.789</v>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1731" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C1731" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1731" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1731" s="3">
+        <v>3.738</v>
+      </c>
+      <c r="F1731" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G1731" s="3">
+        <v>3.738</v>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1732" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C1732" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1732" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1732" s="3">
+        <v>4.352</v>
+      </c>
+      <c r="F1732" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1732" s="3">
+        <v>4.352</v>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1733" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C1733" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1733" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1733" s="3">
+        <v>4.454</v>
+      </c>
+      <c r="F1733" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1733" s="3">
+        <v>4.454</v>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1734" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C1734" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1734" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1734" s="3">
+        <v>3.738</v>
+      </c>
+      <c r="F1734" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1734" s="3">
+        <v>3.738</v>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1735" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C1735" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1735" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1735" s="3">
+        <v>3.482</v>
+      </c>
+      <c r="F1735" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1735" s="3">
+        <v>3.482</v>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1736" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C1736" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1736" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1736" s="3">
+        <v>3.482</v>
+      </c>
+      <c r="F1736" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1736" s="3">
+        <v>3.482</v>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1737" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C1737" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1737" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1737" s="3">
+        <v>3.686</v>
+      </c>
+      <c r="F1737" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1737" s="3">
+        <v>3.686</v>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1738" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C1738" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1738" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1738" s="3">
+        <v>3.533</v>
+      </c>
+      <c r="F1738" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1738" s="3">
+        <v>3.533</v>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1739" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C1739" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1739" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1739" s="3">
+        <v>3.994</v>
+      </c>
+      <c r="F1739" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G1739" s="3">
+        <v>3.994</v>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1740" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C1740" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1740" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1740" s="3">
+        <v>3.738</v>
+      </c>
+      <c r="F1740" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1740" s="3">
+        <v>3.738</v>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1741" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C1741" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1741" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1741" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F1741" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1741" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1742" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C1742" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1742" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1742" s="3">
+        <v>3.686</v>
+      </c>
+      <c r="F1742" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1742" s="3">
+        <v>3.686</v>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1743" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C1743" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1743" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1743" s="3">
+        <v>3.584</v>
+      </c>
+      <c r="F1743" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1743" s="3">
+        <v>3.584</v>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1744" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C1744" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1744" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1744" s="3">
+        <v>3.635</v>
+      </c>
+      <c r="F1744" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1744" s="3">
+        <v>3.635</v>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1745" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C1745" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1745" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1745" s="3">
+        <v>3.891</v>
+      </c>
+      <c r="F1745" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1745" s="3">
+        <v>3.891</v>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1746" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C1746" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1746" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1746" s="3">
+        <v>3.379</v>
+      </c>
+      <c r="F1746" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1746" s="3">
+        <v>3.379</v>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1747" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C1747" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1747" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1747" s="3">
+        <v>3.533</v>
+      </c>
+      <c r="F1747" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1747" s="3">
+        <v>3.533</v>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1748" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C1748" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1748" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1748" s="3">
+        <v>3.635</v>
+      </c>
+      <c r="F1748" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1748" s="3">
+        <v>3.635</v>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1749" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C1749" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1749" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1749" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F1749" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1749" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1750" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C1750" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1750" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1750" s="3">
+        <v>3.686</v>
+      </c>
+      <c r="F1750" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1750" s="3">
+        <v>3.686</v>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1751" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C1751" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1751" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1751" s="3">
+        <v>3.891</v>
+      </c>
+      <c r="F1751" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1751" s="3">
+        <v>3.891</v>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1752" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C1752" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1752" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1752" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F1752" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1752" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1753" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C1753" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1753" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1753" s="3">
+        <v>3.994</v>
+      </c>
+      <c r="F1753" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1753" s="3">
+        <v>3.994</v>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1754" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C1754" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1754" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1754" s="3">
+        <v>3.738</v>
+      </c>
+      <c r="F1754" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1754" s="3">
+        <v>3.738</v>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1755" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C1755" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1755" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1755" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F1755" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1755" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1756" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C1756" s="3">
+        <v>0.026</v>
+      </c>
+      <c r="D1756" s="3">
+        <v>0.026</v>
+      </c>
+      <c r="E1756" s="3">
+        <v>4.25</v>
+      </c>
+      <c r="F1756" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1756" s="3">
+        <v>4.276</v>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1757" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C1757" s="3">
+        <v>0.781</v>
+      </c>
+      <c r="D1757" s="3">
+        <v>0.73</v>
+      </c>
+      <c r="E1757" s="3">
+        <v>3.328</v>
+      </c>
+      <c r="F1757" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G1757" s="3">
+        <v>4.058</v>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1758" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C1758" s="3">
+        <v>1.229</v>
+      </c>
+      <c r="D1758" s="3">
+        <v>0.973</v>
+      </c>
+      <c r="E1758" s="3">
+        <v>2.611</v>
+      </c>
+      <c r="F1758" s="3">
+        <v>0.256</v>
+      </c>
+      <c r="G1758" s="3">
+        <v>3.584</v>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1759" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C1759" s="3">
+        <v>1.28</v>
+      </c>
+      <c r="D1759" s="3">
+        <v>1.178</v>
+      </c>
+      <c r="E1759" s="3">
+        <v>2.97</v>
+      </c>
+      <c r="F1759" s="3">
+        <v>0.102</v>
+      </c>
+      <c r="G1759" s="3">
+        <v>4.148</v>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1760" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C1760" s="3">
+        <v>5.056</v>
+      </c>
+      <c r="D1760" s="3">
+        <v>3.264</v>
+      </c>
+      <c r="E1760" s="3">
+        <v>0.307</v>
+      </c>
+      <c r="F1760" s="3">
+        <v>1.792</v>
+      </c>
+      <c r="G1760" s="3">
+        <v>3.571</v>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1761" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C1761" s="3">
+        <v>10.176</v>
+      </c>
+      <c r="D1761" s="3">
+        <v>3.571</v>
+      </c>
+      <c r="E1761" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="F1761" s="3">
+        <v>6.605</v>
+      </c>
+      <c r="G1761" s="3">
+        <v>3.622</v>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1762" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C1762" s="3">
+        <v>8.806</v>
+      </c>
+      <c r="D1762" s="3">
+        <v>3.891</v>
+      </c>
+      <c r="E1762" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1762" s="3">
+        <v>4.915</v>
+      </c>
+      <c r="G1762" s="3">
+        <v>3.891</v>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1763" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C1763" s="3">
+        <v>9.267</v>
+      </c>
+      <c r="D1763" s="3">
+        <v>4.249</v>
+      </c>
+      <c r="E1763" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1763" s="3">
+        <v>5.018</v>
+      </c>
+      <c r="G1763" s="3">
+        <v>4.249</v>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1764" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C1764" s="3">
+        <v>11.469</v>
+      </c>
+      <c r="D1764" s="3">
+        <v>4.096</v>
+      </c>
+      <c r="E1764" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1764" s="3">
+        <v>7.373</v>
+      </c>
+      <c r="G1764" s="3">
+        <v>4.096</v>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1765" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C1765" s="3">
+        <v>17.536</v>
+      </c>
+      <c r="D1765" s="3">
+        <v>3.814</v>
+      </c>
+      <c r="E1765" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1765" s="3">
+        <v>13.722</v>
+      </c>
+      <c r="G1765" s="3">
+        <v>3.814</v>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1766" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C1766" s="3">
+        <v>13.286</v>
+      </c>
+      <c r="D1766" s="3">
+        <v>3.968</v>
+      </c>
+      <c r="E1766" s="3">
+        <v>0.205</v>
+      </c>
+      <c r="F1766" s="3">
+        <v>9.318</v>
+      </c>
+      <c r="G1766" s="3">
+        <v>4.173</v>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1767" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C1767" s="3">
+        <v>18.163</v>
+      </c>
+      <c r="D1767" s="3">
+        <v>4.288</v>
+      </c>
+      <c r="E1767" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1767" s="3">
+        <v>13.875</v>
+      </c>
+      <c r="G1767" s="3">
+        <v>4.288</v>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1768" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C1768" s="3">
+        <v>20.928</v>
+      </c>
+      <c r="D1768" s="3">
+        <v>3.622</v>
+      </c>
+      <c r="E1768" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1768" s="3">
+        <v>17.306</v>
+      </c>
+      <c r="G1768" s="3">
+        <v>3.622</v>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1769" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C1769" s="3">
+        <v>16.102</v>
+      </c>
+      <c r="D1769" s="3">
+        <v>4.07</v>
+      </c>
+      <c r="E1769" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1769" s="3">
+        <v>12.032</v>
+      </c>
+      <c r="G1769" s="3">
+        <v>4.07</v>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1770" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C1770" s="3">
+        <v>15.923</v>
+      </c>
+      <c r="D1770" s="3">
+        <v>3.993</v>
+      </c>
+      <c r="E1770" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1770" s="3">
+        <v>11.93</v>
+      </c>
+      <c r="G1770" s="3">
+        <v>3.993</v>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1771" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C1771" s="3">
+        <v>18.381</v>
+      </c>
+      <c r="D1771" s="3">
+        <v>6.656</v>
+      </c>
+      <c r="E1771" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1771" s="3">
+        <v>11.725</v>
+      </c>
+      <c r="G1771" s="3">
+        <v>6.656</v>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1772" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C1772" s="3">
+        <v>22.541</v>
+      </c>
+      <c r="D1772" s="3">
+        <v>8.307</v>
+      </c>
+      <c r="E1772" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1772" s="3">
+        <v>14.234</v>
+      </c>
+      <c r="G1772" s="3">
+        <v>8.307</v>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1773" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C1773" s="3">
+        <v>30.003</v>
+      </c>
+      <c r="D1773" s="3">
+        <v>8.243</v>
+      </c>
+      <c r="E1773" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1773" s="3">
+        <v>21.76</v>
+      </c>
+      <c r="G1773" s="3">
+        <v>8.243</v>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1774" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C1774" s="3">
+        <v>29.274</v>
+      </c>
+      <c r="D1774" s="3">
+        <v>7.053</v>
+      </c>
+      <c r="E1774" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1774" s="3">
+        <v>22.221</v>
+      </c>
+      <c r="G1774" s="3">
+        <v>7.053</v>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1775" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C1775" s="3">
+        <v>50.97</v>
+      </c>
+      <c r="D1775" s="3">
+        <v>7.296</v>
+      </c>
+      <c r="E1775" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1775" s="3">
+        <v>43.674</v>
+      </c>
+      <c r="G1775" s="3">
+        <v>7.296</v>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1776" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C1776" s="3">
+        <v>47.386</v>
+      </c>
+      <c r="D1776" s="3">
+        <v>7.348</v>
+      </c>
+      <c r="E1776" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1776" s="3">
+        <v>40.038</v>
+      </c>
+      <c r="G1776" s="3">
+        <v>7.348</v>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1777" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C1777" s="3">
+        <v>47.309</v>
+      </c>
+      <c r="D1777" s="3">
+        <v>6.963</v>
+      </c>
+      <c r="E1777" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1777" s="3">
+        <v>40.346</v>
+      </c>
+      <c r="G1777" s="3">
+        <v>6.963</v>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1778" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C1778" s="3">
+        <v>63.155</v>
+      </c>
+      <c r="D1778" s="3">
+        <v>8.013</v>
+      </c>
+      <c r="E1778" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1778" s="3">
+        <v>55.142</v>
+      </c>
+      <c r="G1778" s="3">
+        <v>8.013</v>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1779" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C1779" s="3">
+        <v>43.366</v>
+      </c>
+      <c r="D1779" s="3">
+        <v>7.628</v>
+      </c>
+      <c r="E1779" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1779" s="3">
+        <v>35.738</v>
+      </c>
+      <c r="G1779" s="3">
+        <v>7.628</v>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1780" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C1780" s="3">
+        <v>39.795</v>
+      </c>
+      <c r="D1780" s="3">
+        <v>7.437</v>
+      </c>
+      <c r="E1780" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1780" s="3">
+        <v>32.358</v>
+      </c>
+      <c r="G1780" s="3">
+        <v>7.437</v>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1781" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C1781" s="3">
+        <v>33.357</v>
+      </c>
+      <c r="D1781" s="3">
+        <v>7.399</v>
+      </c>
+      <c r="E1781" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1781" s="3">
+        <v>25.958</v>
+      </c>
+      <c r="G1781" s="3">
+        <v>7.399</v>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1782" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C1782" s="3">
+        <v>41.6</v>
+      </c>
+      <c r="D1782" s="3">
+        <v>8.269</v>
+      </c>
+      <c r="E1782" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1782" s="3">
+        <v>33.331</v>
+      </c>
+      <c r="G1782" s="3">
+        <v>8.269</v>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1783" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C1783" s="3">
+        <v>39.347</v>
+      </c>
+      <c r="D1783" s="3">
+        <v>8.473</v>
+      </c>
+      <c r="E1783" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1783" s="3">
+        <v>30.874</v>
+      </c>
+      <c r="G1783" s="3">
+        <v>8.473</v>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1784" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C1784" s="3">
+        <v>49.549</v>
+      </c>
+      <c r="D1784" s="3">
+        <v>8.384</v>
+      </c>
+      <c r="E1784" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1784" s="3">
+        <v>41.165</v>
+      </c>
+      <c r="G1784" s="3">
+        <v>8.384</v>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1785" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C1785" s="3">
+        <v>61.581</v>
+      </c>
+      <c r="D1785" s="3">
+        <v>8.691</v>
+      </c>
+      <c r="E1785" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1785" s="3">
+        <v>52.89</v>
+      </c>
+      <c r="G1785" s="3">
+        <v>8.691</v>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1786" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C1786" s="3">
+        <v>77.837</v>
+      </c>
+      <c r="D1786" s="3">
+        <v>8.666</v>
+      </c>
+      <c r="E1786" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1786" s="3">
+        <v>69.171</v>
+      </c>
+      <c r="G1786" s="3">
+        <v>8.666</v>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1787" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C1787" s="3">
+        <v>71.27</v>
+      </c>
+      <c r="D1787" s="3">
+        <v>8.345</v>
+      </c>
+      <c r="E1787" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1787" s="3">
+        <v>62.925</v>
+      </c>
+      <c r="G1787" s="3">
+        <v>8.345</v>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1788" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C1788" s="3">
+        <v>70.464</v>
+      </c>
+      <c r="D1788" s="3">
+        <v>7.59</v>
+      </c>
+      <c r="E1788" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1788" s="3">
+        <v>62.874</v>
+      </c>
+      <c r="G1788" s="3">
+        <v>7.59</v>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1789" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C1789" s="3">
+        <v>65.472</v>
+      </c>
+      <c r="D1789" s="3">
+        <v>7.258</v>
+      </c>
+      <c r="E1789" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1789" s="3">
+        <v>58.214</v>
+      </c>
+      <c r="G1789" s="3">
+        <v>7.258</v>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1790" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C1790" s="3">
+        <v>60.288</v>
+      </c>
+      <c r="D1790" s="3">
+        <v>7.194</v>
+      </c>
+      <c r="E1790" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1790" s="3">
+        <v>53.094</v>
+      </c>
+      <c r="G1790" s="3">
+        <v>7.194</v>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1791" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C1791" s="3">
+        <v>47.014</v>
+      </c>
+      <c r="D1791" s="3">
+        <v>6.976</v>
+      </c>
+      <c r="E1791" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1791" s="3">
+        <v>40.038</v>
+      </c>
+      <c r="G1791" s="3">
+        <v>6.976</v>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1792" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C1792" s="3">
+        <v>43.443</v>
+      </c>
+      <c r="D1792" s="3">
+        <v>6.733</v>
+      </c>
+      <c r="E1792" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1792" s="3">
+        <v>36.71</v>
+      </c>
+      <c r="G1792" s="3">
+        <v>6.733</v>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1793" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C1793" s="3">
+        <v>47.13</v>
+      </c>
+      <c r="D1793" s="3">
+        <v>6.58</v>
+      </c>
+      <c r="E1793" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1793" s="3">
+        <v>40.55</v>
+      </c>
+      <c r="G1793" s="3">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1794" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C1794" s="3">
+        <v>41.075</v>
+      </c>
+      <c r="D1794" s="3">
+        <v>6.617</v>
+      </c>
+      <c r="E1794" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1794" s="3">
+        <v>34.458</v>
+      </c>
+      <c r="G1794" s="3">
+        <v>6.617</v>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1795" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C1795" s="3">
+        <v>29.581</v>
+      </c>
+      <c r="D1795" s="3">
+        <v>22.055</v>
+      </c>
+      <c r="E1795" s="3">
+        <v>7.424</v>
+      </c>
+      <c r="F1795" s="3">
+        <v>7.526</v>
+      </c>
+      <c r="G1795" s="3">
+        <v>29.479</v>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1796" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C1796" s="3">
+        <v>32.282</v>
+      </c>
+      <c r="D1796" s="3">
+        <v>32.282</v>
+      </c>
+      <c r="E1796" s="3">
+        <v>6.246</v>
+      </c>
+      <c r="F1796" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1796" s="3">
+        <v>38.528</v>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1797" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C1797" s="3">
+        <v>29.12</v>
+      </c>
+      <c r="D1797" s="3">
+        <v>29.12</v>
+      </c>
+      <c r="E1797" s="3">
+        <v>9.062</v>
+      </c>
+      <c r="F1797" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1797" s="3">
+        <v>38.182</v>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1798" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C1798" s="3">
+        <v>35.776</v>
+      </c>
+      <c r="D1798" s="3">
+        <v>30.451</v>
+      </c>
+      <c r="E1798" s="3">
+        <v>7.885</v>
+      </c>
+      <c r="F1798" s="3">
+        <v>5.325</v>
+      </c>
+      <c r="G1798" s="3">
+        <v>38.336</v>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1799" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C1799" s="3">
+        <v>20.403</v>
+      </c>
+      <c r="D1799" s="3">
+        <v>20.403</v>
+      </c>
+      <c r="E1799" s="3">
+        <v>18.637</v>
+      </c>
+      <c r="F1799" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1799" s="3">
+        <v>39.04</v>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1800" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C1800" s="3">
+        <v>19.904</v>
+      </c>
+      <c r="D1800" s="3">
+        <v>19.904</v>
+      </c>
+      <c r="E1800" s="3">
+        <v>19.251</v>
+      </c>
+      <c r="F1800" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1800" s="3">
+        <v>39.155</v>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1801" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C1801" s="3">
+        <v>12.147</v>
+      </c>
+      <c r="D1801" s="3">
+        <v>12.147</v>
+      </c>
+      <c r="E1801" s="3">
+        <v>26.778</v>
+      </c>
+      <c r="F1801" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1801" s="3">
+        <v>38.925</v>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1802" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C1802" s="3">
+        <v>11.085</v>
+      </c>
+      <c r="D1802" s="3">
+        <v>11.085</v>
+      </c>
+      <c r="E1802" s="3">
+        <v>27.546</v>
+      </c>
+      <c r="F1802" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1802" s="3">
+        <v>38.631</v>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1803" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C1803" s="3">
+        <v>12.134</v>
+      </c>
+      <c r="D1803" s="3">
+        <v>12.134</v>
+      </c>
+      <c r="E1803" s="3">
+        <v>26.112</v>
+      </c>
+      <c r="F1803" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1803" s="3">
+        <v>38.246</v>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1804" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C1804" s="3">
+        <v>8.704</v>
+      </c>
+      <c r="D1804" s="3">
+        <v>8.704</v>
+      </c>
+      <c r="E1804" s="3">
+        <v>29.338</v>
+      </c>
+      <c r="F1804" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1804" s="3">
+        <v>38.042</v>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="A1805" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1805" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C1805" s="3">
+        <v>6.054</v>
+      </c>
+      <c r="D1805" s="3">
+        <v>6.054</v>
+      </c>
+      <c r="E1805" s="3">
+        <v>32.256</v>
+      </c>
+      <c r="F1805" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1805" s="3">
+        <v>38.31</v>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1806" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C1806" s="3">
+        <v>1.946</v>
+      </c>
+      <c r="D1806" s="3">
+        <v>1.946</v>
+      </c>
+      <c r="E1806" s="3">
+        <v>36.301</v>
+      </c>
+      <c r="F1806" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1806" s="3">
+        <v>38.247</v>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1807" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C1807" s="3">
+        <v>0.282</v>
+      </c>
+      <c r="D1807" s="3">
+        <v>0.282</v>
+      </c>
+      <c r="E1807" s="3">
+        <v>38.093</v>
+      </c>
+      <c r="F1807" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1807" s="3">
+        <v>38.375</v>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1808" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C1808" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="D1808" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="E1808" s="3">
+        <v>38.81</v>
+      </c>
+      <c r="F1808" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1808" s="3">
+        <v>38.823</v>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="A1809" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1809" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C1809" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1809" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1809" s="3">
+        <v>39.066</v>
+      </c>
+      <c r="F1809" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1809" s="3">
+        <v>39.066</v>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="A1810" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1810" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C1810" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1810" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1810" s="3">
+        <v>39.322</v>
+      </c>
+      <c r="F1810" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1810" s="3">
+        <v>39.322</v>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="A1811" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1811" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C1811" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1811" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1811" s="3">
+        <v>39.322</v>
+      </c>
+      <c r="F1811" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1811" s="3">
+        <v>39.322</v>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1812" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C1812" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1812" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1812" s="3">
+        <v>38.605</v>
+      </c>
+      <c r="F1812" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1812" s="3">
+        <v>38.605</v>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1813" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C1813" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1813" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1813" s="3">
+        <v>38.554</v>
+      </c>
+      <c r="F1813" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1813" s="3">
+        <v>38.554</v>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1814" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C1814" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1814" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1814" s="3">
+        <v>35.789</v>
+      </c>
+      <c r="F1814" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1814" s="3">
+        <v>35.789</v>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1815" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C1815" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1815" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1815" s="3">
+        <v>35.738</v>
+      </c>
+      <c r="F1815" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1815" s="3">
+        <v>35.738</v>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1816" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C1816" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1816" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1816" s="3">
+        <v>35.994</v>
+      </c>
+      <c r="F1816" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1816" s="3">
+        <v>35.994</v>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1817" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C1817" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1817" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1817" s="3">
+        <v>35.533</v>
+      </c>
+      <c r="F1817" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1817" s="3">
+        <v>35.533</v>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1818" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C1818" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1818" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1818" s="3">
+        <v>35.328</v>
+      </c>
+      <c r="F1818" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1818" s="3">
+        <v>35.328</v>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1819" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C1819" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1819" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1819" s="3">
+        <v>35.277</v>
+      </c>
+      <c r="F1819" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1819" s="3">
+        <v>35.277</v>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1820" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C1820" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1820" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1820" s="3">
+        <v>35.584</v>
+      </c>
+      <c r="F1820" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1820" s="3">
+        <v>35.584</v>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="A1821" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1821" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C1821" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1821" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1821" s="3">
+        <v>35.942</v>
+      </c>
+      <c r="F1821" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1821" s="3">
+        <v>35.942</v>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1822" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C1822" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1822" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1822" s="3">
+        <v>35.891</v>
+      </c>
+      <c r="F1822" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1822" s="3">
+        <v>35.891</v>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1823" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C1823" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1823" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1823" s="3">
+        <v>35.738</v>
+      </c>
+      <c r="F1823" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1823" s="3">
+        <v>35.738</v>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1824" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C1824" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1824" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1824" s="3">
+        <v>35.994</v>
+      </c>
+      <c r="F1824" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1824" s="3">
+        <v>35.994</v>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="A1825" s="2">
+        <v>46314</v>
+      </c>
+      <c r="B1825" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C1825" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1825" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1825" s="3">
+        <v>35.686</v>
+      </c>
+      <c r="F1825" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1825" s="3">
+        <v>35.686</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1729"/>
+  <autoFilter ref="A1:G1825"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -598,45 +598,69 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B24" s="4">
+        <v>2064.1</v>
+      </c>
+      <c r="C24" s="4">
+        <v>921.2</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1480.8</v>
+      </c>
+      <c r="E24" s="4">
+        <v>1142.9</v>
+      </c>
+      <c r="F24" s="4">
+        <v>2402.0</v>
+      </c>
+      <c r="G24" s="5">
+        <f>IF(F24&gt;0,C24/F24,"")</f>
+        <v>0.3835</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B24" s="7">
-        <f>SUM(B5:B23)</f>
-        <v>41757.3</v>
-      </c>
-      <c r="C24" s="7">
-        <f>SUM(C5:C23)</f>
-        <v>33311.3</v>
-      </c>
-      <c r="D24" s="7">
-        <f>SUM(D5:D23)</f>
-        <v>121238.6</v>
-      </c>
-      <c r="E24" s="7">
-        <f>SUM(E5:E23)</f>
-        <v>8446.2</v>
-      </c>
-      <c r="F24" s="7">
-        <f>SUM(F5:F23)</f>
-        <v>154550.0</v>
-      </c>
-      <c r="G24" s="8">
-        <f>IF(F24&gt;0,C24/F24,"")</f>
-        <v>0.2155</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B25" s="7">
+        <f>SUM(B5:B24)</f>
+        <v>43821.4</v>
+      </c>
+      <c r="C25" s="7">
+        <f>SUM(C5:C24)</f>
+        <v>34232.5</v>
+      </c>
+      <c r="D25" s="7">
+        <f>SUM(D5:D24)</f>
+        <v>122719.4</v>
+      </c>
+      <c r="E25" s="7">
+        <f>SUM(E5:E24)</f>
+        <v>9589.1</v>
+      </c>
+      <c r="F25" s="7">
+        <f>SUM(F5:F24)</f>
+        <v>156952.0</v>
+      </c>
+      <c r="G25" s="8">
+        <f>IF(F25&gt;0,C25/F25,"")</f>
+        <v>0.2181</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -46295,7 +46319,2407 @@
         <v>35.686</v>
       </c>
     </row>
+    <row r="1826">
+      <c r="A1826" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1826" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C1826" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1826" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1826" s="3">
+        <v>36.096</v>
+      </c>
+      <c r="F1826" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1826" s="3">
+        <v>36.096</v>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1827" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C1827" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1827" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1827" s="3">
+        <v>35.328</v>
+      </c>
+      <c r="F1827" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1827" s="3">
+        <v>35.328</v>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1828" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C1828" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1828" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1828" s="3">
+        <v>35.277</v>
+      </c>
+      <c r="F1828" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1828" s="3">
+        <v>35.277</v>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1829" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C1829" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1829" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1829" s="3">
+        <v>35.174</v>
+      </c>
+      <c r="F1829" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1829" s="3">
+        <v>35.174</v>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1830" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C1830" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1830" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1830" s="3">
+        <v>35.584</v>
+      </c>
+      <c r="F1830" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1830" s="3">
+        <v>35.584</v>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1831" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C1831" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1831" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1831" s="3">
+        <v>35.174</v>
+      </c>
+      <c r="F1831" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1831" s="3">
+        <v>35.174</v>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1832" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C1832" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1832" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1832" s="3">
+        <v>35.226</v>
+      </c>
+      <c r="F1832" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1832" s="3">
+        <v>35.226</v>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1833" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C1833" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1833" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1833" s="3">
+        <v>35.43</v>
+      </c>
+      <c r="F1833" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1833" s="3">
+        <v>35.43</v>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1834" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C1834" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1834" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1834" s="3">
+        <v>35.482</v>
+      </c>
+      <c r="F1834" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1834" s="3">
+        <v>35.482</v>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1835" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C1835" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1835" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1835" s="3">
+        <v>35.43</v>
+      </c>
+      <c r="F1835" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1835" s="3">
+        <v>35.43</v>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1836" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C1836" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1836" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1836" s="3">
+        <v>35.686</v>
+      </c>
+      <c r="F1836" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1836" s="3">
+        <v>35.686</v>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1837" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C1837" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1837" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1837" s="3">
+        <v>35.379</v>
+      </c>
+      <c r="F1837" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1837" s="3">
+        <v>35.379</v>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1838" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C1838" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1838" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1838" s="3">
+        <v>35.379</v>
+      </c>
+      <c r="F1838" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1838" s="3">
+        <v>35.379</v>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1839" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C1839" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1839" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1839" s="3">
+        <v>35.277</v>
+      </c>
+      <c r="F1839" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1839" s="3">
+        <v>35.277</v>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1840" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C1840" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1840" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1840" s="3">
+        <v>35.277</v>
+      </c>
+      <c r="F1840" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1840" s="3">
+        <v>35.277</v>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1841" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C1841" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1841" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1841" s="3">
+        <v>35.226</v>
+      </c>
+      <c r="F1841" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1841" s="3">
+        <v>35.226</v>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1842" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C1842" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1842" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1842" s="3">
+        <v>35.635</v>
+      </c>
+      <c r="F1842" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1842" s="3">
+        <v>35.635</v>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1843" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C1843" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1843" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1843" s="3">
+        <v>35.277</v>
+      </c>
+      <c r="F1843" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1843" s="3">
+        <v>35.277</v>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1844" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C1844" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1844" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1844" s="3">
+        <v>35.174</v>
+      </c>
+      <c r="F1844" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1844" s="3">
+        <v>35.174</v>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1845" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C1845" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1845" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1845" s="3">
+        <v>35.277</v>
+      </c>
+      <c r="F1845" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1845" s="3">
+        <v>35.277</v>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1846" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C1846" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1846" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1846" s="3">
+        <v>36.147</v>
+      </c>
+      <c r="F1846" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1846" s="3">
+        <v>36.147</v>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1847" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C1847" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1847" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1847" s="3">
+        <v>36.147</v>
+      </c>
+      <c r="F1847" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1847" s="3">
+        <v>36.147</v>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1848" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C1848" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1848" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1848" s="3">
+        <v>35.84</v>
+      </c>
+      <c r="F1848" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1848" s="3">
+        <v>35.84</v>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1849" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C1849" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1849" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1849" s="3">
+        <v>35.635</v>
+      </c>
+      <c r="F1849" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1849" s="3">
+        <v>35.635</v>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1850" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C1850" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1850" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1850" s="3">
+        <v>35.635</v>
+      </c>
+      <c r="F1850" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1850" s="3">
+        <v>35.635</v>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1851" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C1851" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1851" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1851" s="3">
+        <v>35.738</v>
+      </c>
+      <c r="F1851" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1851" s="3">
+        <v>35.738</v>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1852" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C1852" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1852" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1852" s="3">
+        <v>35.891</v>
+      </c>
+      <c r="F1852" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1852" s="3">
+        <v>35.891</v>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1853" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C1853" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1853" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1853" s="3">
+        <v>36.25</v>
+      </c>
+      <c r="F1853" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1853" s="3">
+        <v>36.25</v>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1854" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C1854" s="3">
+        <v>0.115</v>
+      </c>
+      <c r="D1854" s="3">
+        <v>0.115</v>
+      </c>
+      <c r="E1854" s="3">
+        <v>35.84</v>
+      </c>
+      <c r="F1854" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1854" s="3">
+        <v>35.955</v>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1855" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C1855" s="3">
+        <v>0.358</v>
+      </c>
+      <c r="D1855" s="3">
+        <v>0.358</v>
+      </c>
+      <c r="E1855" s="3">
+        <v>35.328</v>
+      </c>
+      <c r="F1855" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1855" s="3">
+        <v>35.686</v>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1856" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C1856" s="3">
+        <v>0.806</v>
+      </c>
+      <c r="D1856" s="3">
+        <v>0.806</v>
+      </c>
+      <c r="E1856" s="3">
+        <v>34.765</v>
+      </c>
+      <c r="F1856" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1856" s="3">
+        <v>35.571</v>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1857" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C1857" s="3">
+        <v>1.19</v>
+      </c>
+      <c r="D1857" s="3">
+        <v>1.19</v>
+      </c>
+      <c r="E1857" s="3">
+        <v>34.458</v>
+      </c>
+      <c r="F1857" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1857" s="3">
+        <v>35.648</v>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1858" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C1858" s="3">
+        <v>1.626</v>
+      </c>
+      <c r="D1858" s="3">
+        <v>1.626</v>
+      </c>
+      <c r="E1858" s="3">
+        <v>34.355</v>
+      </c>
+      <c r="F1858" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1858" s="3">
+        <v>35.981</v>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1859" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C1859" s="3">
+        <v>2.432</v>
+      </c>
+      <c r="D1859" s="3">
+        <v>2.432</v>
+      </c>
+      <c r="E1859" s="3">
+        <v>34.202</v>
+      </c>
+      <c r="F1859" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1859" s="3">
+        <v>36.634</v>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1860" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C1860" s="3">
+        <v>4.57</v>
+      </c>
+      <c r="D1860" s="3">
+        <v>4.57</v>
+      </c>
+      <c r="E1860" s="3">
+        <v>32.154</v>
+      </c>
+      <c r="F1860" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1860" s="3">
+        <v>36.724</v>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1861" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C1861" s="3">
+        <v>8.128</v>
+      </c>
+      <c r="D1861" s="3">
+        <v>8.128</v>
+      </c>
+      <c r="E1861" s="3">
+        <v>28.314</v>
+      </c>
+      <c r="F1861" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1861" s="3">
+        <v>36.442</v>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1862" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C1862" s="3">
+        <v>13.299</v>
+      </c>
+      <c r="D1862" s="3">
+        <v>13.299</v>
+      </c>
+      <c r="E1862" s="3">
+        <v>25.344</v>
+      </c>
+      <c r="F1862" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1862" s="3">
+        <v>38.643</v>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1863" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C1863" s="3">
+        <v>17.984</v>
+      </c>
+      <c r="D1863" s="3">
+        <v>17.984</v>
+      </c>
+      <c r="E1863" s="3">
+        <v>20.736</v>
+      </c>
+      <c r="F1863" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1863" s="3">
+        <v>38.72</v>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1864" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C1864" s="3">
+        <v>21.146</v>
+      </c>
+      <c r="D1864" s="3">
+        <v>21.146</v>
+      </c>
+      <c r="E1864" s="3">
+        <v>17.203</v>
+      </c>
+      <c r="F1864" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1864" s="3">
+        <v>38.349</v>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1865" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C1865" s="3">
+        <v>18.573</v>
+      </c>
+      <c r="D1865" s="3">
+        <v>18.573</v>
+      </c>
+      <c r="E1865" s="3">
+        <v>19.558</v>
+      </c>
+      <c r="F1865" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1865" s="3">
+        <v>38.131</v>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1866" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C1866" s="3">
+        <v>21.389</v>
+      </c>
+      <c r="D1866" s="3">
+        <v>21.389</v>
+      </c>
+      <c r="E1866" s="3">
+        <v>16.947</v>
+      </c>
+      <c r="F1866" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1866" s="3">
+        <v>38.336</v>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1867" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C1867" s="3">
+        <v>25.562</v>
+      </c>
+      <c r="D1867" s="3">
+        <v>25.562</v>
+      </c>
+      <c r="E1867" s="3">
+        <v>13.005</v>
+      </c>
+      <c r="F1867" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1867" s="3">
+        <v>38.567</v>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1868" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C1868" s="3">
+        <v>24.218</v>
+      </c>
+      <c r="D1868" s="3">
+        <v>24.218</v>
+      </c>
+      <c r="E1868" s="3">
+        <v>14.029</v>
+      </c>
+      <c r="F1868" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1868" s="3">
+        <v>38.247</v>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1869" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C1869" s="3">
+        <v>34.483</v>
+      </c>
+      <c r="D1869" s="3">
+        <v>34.022</v>
+      </c>
+      <c r="E1869" s="3">
+        <v>4.403</v>
+      </c>
+      <c r="F1869" s="3">
+        <v>0.461</v>
+      </c>
+      <c r="G1869" s="3">
+        <v>38.425</v>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1870" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C1870" s="3">
+        <v>38.797</v>
+      </c>
+      <c r="D1870" s="3">
+        <v>37.363</v>
+      </c>
+      <c r="E1870" s="3">
+        <v>1.638</v>
+      </c>
+      <c r="F1870" s="3">
+        <v>1.434</v>
+      </c>
+      <c r="G1870" s="3">
+        <v>39.001</v>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1871" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C1871" s="3">
+        <v>46.106</v>
+      </c>
+      <c r="D1871" s="3">
+        <v>38.221</v>
+      </c>
+      <c r="E1871" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="F1871" s="3">
+        <v>7.885</v>
+      </c>
+      <c r="G1871" s="3">
+        <v>38.272</v>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1872" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C1872" s="3">
+        <v>51.738</v>
+      </c>
+      <c r="D1872" s="3">
+        <v>38.375</v>
+      </c>
+      <c r="E1872" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1872" s="3">
+        <v>13.363</v>
+      </c>
+      <c r="G1872" s="3">
+        <v>38.375</v>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1873" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C1873" s="3">
+        <v>61.619</v>
+      </c>
+      <c r="D1873" s="3">
+        <v>38.784</v>
+      </c>
+      <c r="E1873" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1873" s="3">
+        <v>22.835</v>
+      </c>
+      <c r="G1873" s="3">
+        <v>38.784</v>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1874" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C1874" s="3">
+        <v>61.824</v>
+      </c>
+      <c r="D1874" s="3">
+        <v>38.733</v>
+      </c>
+      <c r="E1874" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1874" s="3">
+        <v>23.091</v>
+      </c>
+      <c r="G1874" s="3">
+        <v>38.733</v>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1875" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C1875" s="3">
+        <v>71.795</v>
+      </c>
+      <c r="D1875" s="3">
+        <v>38.669</v>
+      </c>
+      <c r="E1875" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1875" s="3">
+        <v>33.126</v>
+      </c>
+      <c r="G1875" s="3">
+        <v>38.669</v>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1876" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C1876" s="3">
+        <v>73.664</v>
+      </c>
+      <c r="D1876" s="3">
+        <v>38.541</v>
+      </c>
+      <c r="E1876" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1876" s="3">
+        <v>35.123</v>
+      </c>
+      <c r="G1876" s="3">
+        <v>38.541</v>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1877" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C1877" s="3">
+        <v>84.083</v>
+      </c>
+      <c r="D1877" s="3">
+        <v>38.771</v>
+      </c>
+      <c r="E1877" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1877" s="3">
+        <v>45.312</v>
+      </c>
+      <c r="G1877" s="3">
+        <v>38.771</v>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1878" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C1878" s="3">
+        <v>69.466</v>
+      </c>
+      <c r="D1878" s="3">
+        <v>38.951</v>
+      </c>
+      <c r="E1878" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1878" s="3">
+        <v>30.515</v>
+      </c>
+      <c r="G1878" s="3">
+        <v>38.951</v>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1879" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C1879" s="3">
+        <v>51.482</v>
+      </c>
+      <c r="D1879" s="3">
+        <v>38.989</v>
+      </c>
+      <c r="E1879" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1879" s="3">
+        <v>12.493</v>
+      </c>
+      <c r="G1879" s="3">
+        <v>38.989</v>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1880" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C1880" s="3">
+        <v>46.336</v>
+      </c>
+      <c r="D1880" s="3">
+        <v>38.605</v>
+      </c>
+      <c r="E1880" s="3">
+        <v>0.102</v>
+      </c>
+      <c r="F1880" s="3">
+        <v>7.731</v>
+      </c>
+      <c r="G1880" s="3">
+        <v>38.707</v>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1881" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C1881" s="3">
+        <v>63.27</v>
+      </c>
+      <c r="D1881" s="3">
+        <v>38.694</v>
+      </c>
+      <c r="E1881" s="3">
+        <v>0.256</v>
+      </c>
+      <c r="F1881" s="3">
+        <v>24.576</v>
+      </c>
+      <c r="G1881" s="3">
+        <v>38.95</v>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1882" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C1882" s="3">
+        <v>49.83</v>
+      </c>
+      <c r="D1882" s="3">
+        <v>38.412</v>
+      </c>
+      <c r="E1882" s="3">
+        <v>0.256</v>
+      </c>
+      <c r="F1882" s="3">
+        <v>11.418</v>
+      </c>
+      <c r="G1882" s="3">
+        <v>38.668</v>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1883" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C1883" s="3">
+        <v>62.234</v>
+      </c>
+      <c r="D1883" s="3">
+        <v>38.784</v>
+      </c>
+      <c r="E1883" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1883" s="3">
+        <v>23.45</v>
+      </c>
+      <c r="G1883" s="3">
+        <v>38.784</v>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1884" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C1884" s="3">
+        <v>89.651</v>
+      </c>
+      <c r="D1884" s="3">
+        <v>39.577</v>
+      </c>
+      <c r="E1884" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1884" s="3">
+        <v>50.074</v>
+      </c>
+      <c r="G1884" s="3">
+        <v>39.577</v>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1885" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C1885" s="3">
+        <v>76.198</v>
+      </c>
+      <c r="D1885" s="3">
+        <v>24.742</v>
+      </c>
+      <c r="E1885" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1885" s="3">
+        <v>51.456</v>
+      </c>
+      <c r="G1885" s="3">
+        <v>24.742</v>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1886" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C1886" s="3">
+        <v>60.902</v>
+      </c>
+      <c r="D1886" s="3">
+        <v>7.603</v>
+      </c>
+      <c r="E1886" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1886" s="3">
+        <v>53.299</v>
+      </c>
+      <c r="G1886" s="3">
+        <v>7.603</v>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1887" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C1887" s="3">
+        <v>66.022</v>
+      </c>
+      <c r="D1887" s="3">
+        <v>6.988</v>
+      </c>
+      <c r="E1887" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1887" s="3">
+        <v>59.034</v>
+      </c>
+      <c r="G1887" s="3">
+        <v>6.988</v>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1888" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C1888" s="3">
+        <v>108.224</v>
+      </c>
+      <c r="D1888" s="3">
+        <v>8.026</v>
+      </c>
+      <c r="E1888" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1888" s="3">
+        <v>100.198</v>
+      </c>
+      <c r="G1888" s="3">
+        <v>8.026</v>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1889" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C1889" s="3">
+        <v>99.968</v>
+      </c>
+      <c r="D1889" s="3">
+        <v>8.115</v>
+      </c>
+      <c r="E1889" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1889" s="3">
+        <v>91.853</v>
+      </c>
+      <c r="G1889" s="3">
+        <v>8.115</v>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1890" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C1890" s="3">
+        <v>93.222</v>
+      </c>
+      <c r="D1890" s="3">
+        <v>7.616</v>
+      </c>
+      <c r="E1890" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1890" s="3">
+        <v>85.606</v>
+      </c>
+      <c r="G1890" s="3">
+        <v>7.616</v>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1891" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C1891" s="3">
+        <v>43.558</v>
+      </c>
+      <c r="D1891" s="3">
+        <v>7.001</v>
+      </c>
+      <c r="E1891" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1891" s="3">
+        <v>36.557</v>
+      </c>
+      <c r="G1891" s="3">
+        <v>7.001</v>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1892" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C1892" s="3">
+        <v>69.722</v>
+      </c>
+      <c r="D1892" s="3">
+        <v>6.797</v>
+      </c>
+      <c r="E1892" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1892" s="3">
+        <v>62.925</v>
+      </c>
+      <c r="G1892" s="3">
+        <v>6.797</v>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1893" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C1893" s="3">
+        <v>71.373</v>
+      </c>
+      <c r="D1893" s="3">
+        <v>7.475</v>
+      </c>
+      <c r="E1893" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1893" s="3">
+        <v>63.898</v>
+      </c>
+      <c r="G1893" s="3">
+        <v>7.475</v>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1894" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C1894" s="3">
+        <v>64.013</v>
+      </c>
+      <c r="D1894" s="3">
+        <v>8.154</v>
+      </c>
+      <c r="E1894" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1894" s="3">
+        <v>55.859</v>
+      </c>
+      <c r="G1894" s="3">
+        <v>8.154</v>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1895" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C1895" s="3">
+        <v>54.989</v>
+      </c>
+      <c r="D1895" s="3">
+        <v>7.731</v>
+      </c>
+      <c r="E1895" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1895" s="3">
+        <v>47.258</v>
+      </c>
+      <c r="G1895" s="3">
+        <v>7.731</v>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1896" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C1896" s="3">
+        <v>44.8</v>
+      </c>
+      <c r="D1896" s="3">
+        <v>7.629</v>
+      </c>
+      <c r="E1896" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1896" s="3">
+        <v>37.171</v>
+      </c>
+      <c r="G1896" s="3">
+        <v>7.629</v>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1897" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C1897" s="3">
+        <v>30.362</v>
+      </c>
+      <c r="D1897" s="3">
+        <v>7.373</v>
+      </c>
+      <c r="E1897" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1897" s="3">
+        <v>22.989</v>
+      </c>
+      <c r="G1897" s="3">
+        <v>7.373</v>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1898" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C1898" s="3">
+        <v>14.848</v>
+      </c>
+      <c r="D1898" s="3">
+        <v>6.093</v>
+      </c>
+      <c r="E1898" s="3">
+        <v>0.154</v>
+      </c>
+      <c r="F1898" s="3">
+        <v>8.755</v>
+      </c>
+      <c r="G1898" s="3">
+        <v>6.247</v>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1899" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C1899" s="3">
+        <v>17.101</v>
+      </c>
+      <c r="D1899" s="3">
+        <v>6.4</v>
+      </c>
+      <c r="E1899" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1899" s="3">
+        <v>10.701</v>
+      </c>
+      <c r="G1899" s="3">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1900" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C1900" s="3">
+        <v>15.782</v>
+      </c>
+      <c r="D1900" s="3">
+        <v>6.72</v>
+      </c>
+      <c r="E1900" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1900" s="3">
+        <v>9.062</v>
+      </c>
+      <c r="G1900" s="3">
+        <v>6.72</v>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1901" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C1901" s="3">
+        <v>9.498</v>
+      </c>
+      <c r="D1901" s="3">
+        <v>6.682</v>
+      </c>
+      <c r="E1901" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1901" s="3">
+        <v>2.816</v>
+      </c>
+      <c r="G1901" s="3">
+        <v>6.682</v>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1902" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C1902" s="3">
+        <v>4.966</v>
+      </c>
+      <c r="D1902" s="3">
+        <v>4.403</v>
+      </c>
+      <c r="E1902" s="3">
+        <v>2.458</v>
+      </c>
+      <c r="F1902" s="3">
+        <v>0.563</v>
+      </c>
+      <c r="G1902" s="3">
+        <v>6.861</v>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1903" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C1903" s="3">
+        <v>0.742</v>
+      </c>
+      <c r="D1903" s="3">
+        <v>0.742</v>
+      </c>
+      <c r="E1903" s="3">
+        <v>5.99</v>
+      </c>
+      <c r="F1903" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1903" s="3">
+        <v>6.732</v>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1904" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C1904" s="3">
+        <v>0.026</v>
+      </c>
+      <c r="D1904" s="3">
+        <v>0.026</v>
+      </c>
+      <c r="E1904" s="3">
+        <v>6.656</v>
+      </c>
+      <c r="F1904" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1904" s="3">
+        <v>6.682</v>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1905" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C1905" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1905" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1905" s="3">
+        <v>6.758</v>
+      </c>
+      <c r="F1905" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1905" s="3">
+        <v>6.758</v>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1906" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C1906" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1906" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1906" s="3">
+        <v>5.632</v>
+      </c>
+      <c r="F1906" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1906" s="3">
+        <v>5.632</v>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1907" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C1907" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1907" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1907" s="3">
+        <v>4.301</v>
+      </c>
+      <c r="F1907" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1907" s="3">
+        <v>4.301</v>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1908" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C1908" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1908" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1908" s="3">
+        <v>3.942</v>
+      </c>
+      <c r="F1908" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1908" s="3">
+        <v>3.942</v>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1909" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C1909" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1909" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1909" s="3">
+        <v>3.635</v>
+      </c>
+      <c r="F1909" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1909" s="3">
+        <v>3.635</v>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1910" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C1910" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1910" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1910" s="3">
+        <v>3.686</v>
+      </c>
+      <c r="F1910" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1910" s="3">
+        <v>3.686</v>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1911" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C1911" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1911" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1911" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F1911" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1911" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1912" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C1912" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1912" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1912" s="3">
+        <v>3.482</v>
+      </c>
+      <c r="F1912" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1912" s="3">
+        <v>3.482</v>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1913" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C1913" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1913" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1913" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F1913" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1913" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1914" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C1914" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1914" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1914" s="3">
+        <v>3.584</v>
+      </c>
+      <c r="F1914" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1914" s="3">
+        <v>3.584</v>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1915" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C1915" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1915" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1915" s="3">
+        <v>3.686</v>
+      </c>
+      <c r="F1915" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1915" s="3">
+        <v>3.686</v>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1916" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C1916" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1916" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1916" s="3">
+        <v>3.379</v>
+      </c>
+      <c r="F1916" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1916" s="3">
+        <v>3.379</v>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1917" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C1917" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1917" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1917" s="3">
+        <v>3.482</v>
+      </c>
+      <c r="F1917" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1917" s="3">
+        <v>3.482</v>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1918" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C1918" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1918" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1918" s="3">
+        <v>3.533</v>
+      </c>
+      <c r="F1918" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1918" s="3">
+        <v>3.533</v>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1919" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C1919" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1919" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1919" s="3">
+        <v>4.096</v>
+      </c>
+      <c r="F1919" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1919" s="3">
+        <v>4.096</v>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1920" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C1920" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1920" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1920" s="3">
+        <v>3.635</v>
+      </c>
+      <c r="F1920" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1920" s="3">
+        <v>3.635</v>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" s="2">
+        <v>46315</v>
+      </c>
+      <c r="B1921" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C1921" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1921" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1921" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="F1921" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1921" s="3">
+        <v>3.84</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1825"/>
+  <autoFilter ref="A1:G1921"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -622,45 +622,69 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B25" s="4">
+        <v>3374.8</v>
+      </c>
+      <c r="C25" s="4">
+        <v>826.5</v>
+      </c>
+      <c r="D25" s="4">
+        <v>950.5</v>
+      </c>
+      <c r="E25" s="4">
+        <v>2548.4</v>
+      </c>
+      <c r="F25" s="4">
+        <v>1776.9</v>
+      </c>
+      <c r="G25" s="5">
+        <f>IF(F25&gt;0,C25/F25,"")</f>
+        <v>0.4651</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B25" s="7">
-        <f>SUM(B5:B24)</f>
-        <v>43821.4</v>
-      </c>
-      <c r="C25" s="7">
-        <f>SUM(C5:C24)</f>
-        <v>34232.5</v>
-      </c>
-      <c r="D25" s="7">
-        <f>SUM(D5:D24)</f>
-        <v>122719.4</v>
-      </c>
-      <c r="E25" s="7">
-        <f>SUM(E5:E24)</f>
-        <v>9589.1</v>
-      </c>
-      <c r="F25" s="7">
-        <f>SUM(F5:F24)</f>
-        <v>156952.0</v>
-      </c>
-      <c r="G25" s="8">
-        <f>IF(F25&gt;0,C25/F25,"")</f>
-        <v>0.2181</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B26" s="7">
+        <f>SUM(B5:B25)</f>
+        <v>47196.2</v>
+      </c>
+      <c r="C26" s="7">
+        <f>SUM(C5:C25)</f>
+        <v>35059.0</v>
+      </c>
+      <c r="D26" s="7">
+        <f>SUM(D5:D25)</f>
+        <v>123669.9</v>
+      </c>
+      <c r="E26" s="7">
+        <f>SUM(E5:E25)</f>
+        <v>12137.5</v>
+      </c>
+      <c r="F26" s="7">
+        <f>SUM(F5:F25)</f>
+        <v>158728.9</v>
+      </c>
+      <c r="G26" s="8">
+        <f>IF(F26&gt;0,C26/F26,"")</f>
+        <v>0.2209</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -48719,7 +48743,2407 @@
         <v>3.84</v>
       </c>
     </row>
+    <row r="1922">
+      <c r="A1922" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1922" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C1922" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1922" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1922" s="3">
+        <v>3.994</v>
+      </c>
+      <c r="F1922" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1922" s="3">
+        <v>3.994</v>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1923" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C1923" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1923" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1923" s="3">
+        <v>4.301</v>
+      </c>
+      <c r="F1923" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1923" s="3">
+        <v>4.301</v>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1924" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C1924" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1924" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1924" s="3">
+        <v>3.942</v>
+      </c>
+      <c r="F1924" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1924" s="3">
+        <v>3.942</v>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1925" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C1925" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1925" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1925" s="3">
+        <v>4.198</v>
+      </c>
+      <c r="F1925" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1925" s="3">
+        <v>4.198</v>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1926" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C1926" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1926" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1926" s="3">
+        <v>4.25</v>
+      </c>
+      <c r="F1926" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1926" s="3">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1927" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C1927" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1927" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1927" s="3">
+        <v>3.584</v>
+      </c>
+      <c r="F1927" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G1927" s="3">
+        <v>3.584</v>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1928" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C1928" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1928" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1928" s="3">
+        <v>3.635</v>
+      </c>
+      <c r="F1928" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1928" s="3">
+        <v>3.635</v>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1929" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C1929" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1929" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1929" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F1929" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1929" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1930" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C1930" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1930" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1930" s="3">
+        <v>3.482</v>
+      </c>
+      <c r="F1930" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1930" s="3">
+        <v>3.482</v>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1931" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C1931" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1931" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1931" s="3">
+        <v>3.379</v>
+      </c>
+      <c r="F1931" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1931" s="3">
+        <v>3.379</v>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1932" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C1932" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1932" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1932" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="F1932" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1932" s="3">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1933" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C1933" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1933" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1933" s="3">
+        <v>3.942</v>
+      </c>
+      <c r="F1933" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1933" s="3">
+        <v>3.942</v>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1934" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C1934" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1934" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1934" s="3">
+        <v>3.533</v>
+      </c>
+      <c r="F1934" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1934" s="3">
+        <v>3.533</v>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1935" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C1935" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1935" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1935" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F1935" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G1935" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1936" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C1936" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1936" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1936" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F1936" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1936" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1937" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C1937" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1937" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1937" s="3">
+        <v>3.482</v>
+      </c>
+      <c r="F1937" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1937" s="3">
+        <v>3.482</v>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1938" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C1938" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1938" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1938" s="3">
+        <v>3.584</v>
+      </c>
+      <c r="F1938" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1938" s="3">
+        <v>3.584</v>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1939" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C1939" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1939" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1939" s="3">
+        <v>3.686</v>
+      </c>
+      <c r="F1939" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1939" s="3">
+        <v>3.686</v>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1940" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C1940" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1940" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1940" s="3">
+        <v>3.686</v>
+      </c>
+      <c r="F1940" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1940" s="3">
+        <v>3.686</v>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1941" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C1941" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1941" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1941" s="3">
+        <v>3.533</v>
+      </c>
+      <c r="F1941" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1941" s="3">
+        <v>3.533</v>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1942" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C1942" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1942" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1942" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F1942" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1942" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1943" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C1943" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1943" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1943" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F1943" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1943" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1944" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C1944" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1944" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1944" s="3">
+        <v>3.635</v>
+      </c>
+      <c r="F1944" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1944" s="3">
+        <v>3.635</v>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1945" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C1945" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1945" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1945" s="3">
+        <v>3.891</v>
+      </c>
+      <c r="F1945" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1945" s="3">
+        <v>3.891</v>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1946" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C1946" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1946" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1946" s="3">
+        <v>4.25</v>
+      </c>
+      <c r="F1946" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1946" s="3">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1947" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C1947" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D1947" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E1947" s="3">
+        <v>4.045</v>
+      </c>
+      <c r="F1947" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1947" s="3">
+        <v>4.045</v>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1948" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C1948" s="3">
+        <v>0.115</v>
+      </c>
+      <c r="D1948" s="3">
+        <v>0.115</v>
+      </c>
+      <c r="E1948" s="3">
+        <v>3.738</v>
+      </c>
+      <c r="F1948" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1948" s="3">
+        <v>3.853</v>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1949" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C1949" s="3">
+        <v>0.806</v>
+      </c>
+      <c r="D1949" s="3">
+        <v>0.806</v>
+      </c>
+      <c r="E1949" s="3">
+        <v>3.533</v>
+      </c>
+      <c r="F1949" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1949" s="3">
+        <v>4.339</v>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1950" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C1950" s="3">
+        <v>2.086</v>
+      </c>
+      <c r="D1950" s="3">
+        <v>1.881</v>
+      </c>
+      <c r="E1950" s="3">
+        <v>2.509</v>
+      </c>
+      <c r="F1950" s="3">
+        <v>0.205</v>
+      </c>
+      <c r="G1950" s="3">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1951" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C1951" s="3">
+        <v>5.734</v>
+      </c>
+      <c r="D1951" s="3">
+        <v>3.532</v>
+      </c>
+      <c r="E1951" s="3">
+        <v>0.256</v>
+      </c>
+      <c r="F1951" s="3">
+        <v>2.202</v>
+      </c>
+      <c r="G1951" s="3">
+        <v>3.788</v>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1952" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C1952" s="3">
+        <v>11.264</v>
+      </c>
+      <c r="D1952" s="3">
+        <v>3.789</v>
+      </c>
+      <c r="E1952" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1952" s="3">
+        <v>7.475</v>
+      </c>
+      <c r="G1952" s="3">
+        <v>3.789</v>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1953" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C1953" s="3">
+        <v>18.714</v>
+      </c>
+      <c r="D1953" s="3">
+        <v>3.508</v>
+      </c>
+      <c r="E1953" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1953" s="3">
+        <v>15.206</v>
+      </c>
+      <c r="G1953" s="3">
+        <v>3.508</v>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1954" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C1954" s="3">
+        <v>26.906</v>
+      </c>
+      <c r="D1954" s="3">
+        <v>6.682</v>
+      </c>
+      <c r="E1954" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1954" s="3">
+        <v>20.224</v>
+      </c>
+      <c r="G1954" s="3">
+        <v>6.682</v>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1955" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C1955" s="3">
+        <v>35.456</v>
+      </c>
+      <c r="D1955" s="3">
+        <v>7.142</v>
+      </c>
+      <c r="E1955" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1955" s="3">
+        <v>28.314</v>
+      </c>
+      <c r="G1955" s="3">
+        <v>7.142</v>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1956" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C1956" s="3">
+        <v>44.032</v>
+      </c>
+      <c r="D1956" s="3">
+        <v>6.963</v>
+      </c>
+      <c r="E1956" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1956" s="3">
+        <v>37.069</v>
+      </c>
+      <c r="G1956" s="3">
+        <v>6.963</v>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1957" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C1957" s="3">
+        <v>52.378</v>
+      </c>
+      <c r="D1957" s="3">
+        <v>6.964</v>
+      </c>
+      <c r="E1957" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1957" s="3">
+        <v>45.414</v>
+      </c>
+      <c r="G1957" s="3">
+        <v>6.964</v>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1958" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C1958" s="3">
+        <v>60.544</v>
+      </c>
+      <c r="D1958" s="3">
+        <v>7.04</v>
+      </c>
+      <c r="E1958" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1958" s="3">
+        <v>53.504</v>
+      </c>
+      <c r="G1958" s="3">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1959" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C1959" s="3">
+        <v>67.942</v>
+      </c>
+      <c r="D1959" s="3">
+        <v>7.168</v>
+      </c>
+      <c r="E1959" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1959" s="3">
+        <v>60.774</v>
+      </c>
+      <c r="G1959" s="3">
+        <v>7.168</v>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1960" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C1960" s="3">
+        <v>65.843</v>
+      </c>
+      <c r="D1960" s="3">
+        <v>7.731</v>
+      </c>
+      <c r="E1960" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1960" s="3">
+        <v>58.112</v>
+      </c>
+      <c r="G1960" s="3">
+        <v>7.731</v>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1961" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C1961" s="3">
+        <v>77.645</v>
+      </c>
+      <c r="D1961" s="3">
+        <v>7.603</v>
+      </c>
+      <c r="E1961" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1961" s="3">
+        <v>70.042</v>
+      </c>
+      <c r="G1961" s="3">
+        <v>7.603</v>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1962" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C1962" s="3">
+        <v>86.08</v>
+      </c>
+      <c r="D1962" s="3">
+        <v>7.488</v>
+      </c>
+      <c r="E1962" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1962" s="3">
+        <v>78.592</v>
+      </c>
+      <c r="G1962" s="3">
+        <v>7.488</v>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1963" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C1963" s="3">
+        <v>94.221</v>
+      </c>
+      <c r="D1963" s="3">
+        <v>8.461</v>
+      </c>
+      <c r="E1963" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1963" s="3">
+        <v>85.76</v>
+      </c>
+      <c r="G1963" s="3">
+        <v>8.461</v>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1964" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C1964" s="3">
+        <v>96.166</v>
+      </c>
+      <c r="D1964" s="3">
+        <v>9.024</v>
+      </c>
+      <c r="E1964" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1964" s="3">
+        <v>87.142</v>
+      </c>
+      <c r="G1964" s="3">
+        <v>9.024</v>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1965" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C1965" s="3">
+        <v>101.888</v>
+      </c>
+      <c r="D1965" s="3">
+        <v>8.96</v>
+      </c>
+      <c r="E1965" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1965" s="3">
+        <v>92.928</v>
+      </c>
+      <c r="G1965" s="3">
+        <v>8.96</v>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1966" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C1966" s="3">
+        <v>97.728</v>
+      </c>
+      <c r="D1966" s="3">
+        <v>8.691</v>
+      </c>
+      <c r="E1966" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1966" s="3">
+        <v>89.037</v>
+      </c>
+      <c r="G1966" s="3">
+        <v>8.691</v>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1967" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C1967" s="3">
+        <v>110.976</v>
+      </c>
+      <c r="D1967" s="3">
+        <v>8.115</v>
+      </c>
+      <c r="E1967" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1967" s="3">
+        <v>102.861</v>
+      </c>
+      <c r="G1967" s="3">
+        <v>8.115</v>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1968" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C1968" s="3">
+        <v>113.216</v>
+      </c>
+      <c r="D1968" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="E1968" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1968" s="3">
+        <v>105.216</v>
+      </c>
+      <c r="G1968" s="3">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1969" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C1969" s="3">
+        <v>102.221</v>
+      </c>
+      <c r="D1969" s="3">
+        <v>7.45</v>
+      </c>
+      <c r="E1969" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1969" s="3">
+        <v>94.771</v>
+      </c>
+      <c r="G1969" s="3">
+        <v>7.45</v>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1970" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C1970" s="3">
+        <v>78.234</v>
+      </c>
+      <c r="D1970" s="3">
+        <v>7.22</v>
+      </c>
+      <c r="E1970" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1970" s="3">
+        <v>71.014</v>
+      </c>
+      <c r="G1970" s="3">
+        <v>7.22</v>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1971" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C1971" s="3">
+        <v>100.966</v>
+      </c>
+      <c r="D1971" s="3">
+        <v>7.884</v>
+      </c>
+      <c r="E1971" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1971" s="3">
+        <v>93.082</v>
+      </c>
+      <c r="G1971" s="3">
+        <v>7.884</v>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1972" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C1972" s="3">
+        <v>91.11</v>
+      </c>
+      <c r="D1972" s="3">
+        <v>8.115</v>
+      </c>
+      <c r="E1972" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1972" s="3">
+        <v>82.995</v>
+      </c>
+      <c r="G1972" s="3">
+        <v>8.115</v>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1973" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C1973" s="3">
+        <v>96.947</v>
+      </c>
+      <c r="D1973" s="3">
+        <v>8.013</v>
+      </c>
+      <c r="E1973" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1973" s="3">
+        <v>88.934</v>
+      </c>
+      <c r="G1973" s="3">
+        <v>8.013</v>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1974" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C1974" s="3">
+        <v>103.04</v>
+      </c>
+      <c r="D1974" s="3">
+        <v>7.501</v>
+      </c>
+      <c r="E1974" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1974" s="3">
+        <v>95.539</v>
+      </c>
+      <c r="G1974" s="3">
+        <v>7.501</v>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1975" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C1975" s="3">
+        <v>113.651</v>
+      </c>
+      <c r="D1975" s="3">
+        <v>8.179</v>
+      </c>
+      <c r="E1975" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1975" s="3">
+        <v>105.472</v>
+      </c>
+      <c r="G1975" s="3">
+        <v>8.179</v>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1976" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C1976" s="3">
+        <v>115.494</v>
+      </c>
+      <c r="D1976" s="3">
+        <v>8.025</v>
+      </c>
+      <c r="E1976" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1976" s="3">
+        <v>107.469</v>
+      </c>
+      <c r="G1976" s="3">
+        <v>8.025</v>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1977" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C1977" s="3">
+        <v>95.194</v>
+      </c>
+      <c r="D1977" s="3">
+        <v>7.232</v>
+      </c>
+      <c r="E1977" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1977" s="3">
+        <v>87.962</v>
+      </c>
+      <c r="G1977" s="3">
+        <v>7.232</v>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1978" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C1978" s="3">
+        <v>72.064</v>
+      </c>
+      <c r="D1978" s="3">
+        <v>7.245</v>
+      </c>
+      <c r="E1978" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1978" s="3">
+        <v>64.819</v>
+      </c>
+      <c r="G1978" s="3">
+        <v>7.245</v>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1979" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C1979" s="3">
+        <v>108.032</v>
+      </c>
+      <c r="D1979" s="3">
+        <v>7.782</v>
+      </c>
+      <c r="E1979" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1979" s="3">
+        <v>100.25</v>
+      </c>
+      <c r="G1979" s="3">
+        <v>7.782</v>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1980" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C1980" s="3">
+        <v>75.763</v>
+      </c>
+      <c r="D1980" s="3">
+        <v>13.197</v>
+      </c>
+      <c r="E1980" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="F1980" s="3">
+        <v>62.566</v>
+      </c>
+      <c r="G1980" s="3">
+        <v>13.248</v>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1981" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C1981" s="3">
+        <v>110.554</v>
+      </c>
+      <c r="D1981" s="3">
+        <v>40.82</v>
+      </c>
+      <c r="E1981" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1981" s="3">
+        <v>69.734</v>
+      </c>
+      <c r="G1981" s="3">
+        <v>40.82</v>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1982" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C1982" s="3">
+        <v>80.026</v>
+      </c>
+      <c r="D1982" s="3">
+        <v>37.53</v>
+      </c>
+      <c r="E1982" s="3">
+        <v>3.174</v>
+      </c>
+      <c r="F1982" s="3">
+        <v>42.496</v>
+      </c>
+      <c r="G1982" s="3">
+        <v>40.704</v>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1983" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C1983" s="3">
+        <v>102.746</v>
+      </c>
+      <c r="D1983" s="3">
+        <v>40.743</v>
+      </c>
+      <c r="E1983" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1983" s="3">
+        <v>62.003</v>
+      </c>
+      <c r="G1983" s="3">
+        <v>40.743</v>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1984" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C1984" s="3">
+        <v>95.347</v>
+      </c>
+      <c r="D1984" s="3">
+        <v>40.153</v>
+      </c>
+      <c r="E1984" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1984" s="3">
+        <v>55.194</v>
+      </c>
+      <c r="G1984" s="3">
+        <v>40.153</v>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1985" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C1985" s="3">
+        <v>90.56</v>
+      </c>
+      <c r="D1985" s="3">
+        <v>40.333</v>
+      </c>
+      <c r="E1985" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1985" s="3">
+        <v>50.227</v>
+      </c>
+      <c r="G1985" s="3">
+        <v>40.333</v>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1986" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C1986" s="3">
+        <v>84.634</v>
+      </c>
+      <c r="D1986" s="3">
+        <v>40.039</v>
+      </c>
+      <c r="E1986" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1986" s="3">
+        <v>44.595</v>
+      </c>
+      <c r="G1986" s="3">
+        <v>40.039</v>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1987" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C1987" s="3">
+        <v>78.963</v>
+      </c>
+      <c r="D1987" s="3">
+        <v>40.563</v>
+      </c>
+      <c r="E1987" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1987" s="3">
+        <v>38.4</v>
+      </c>
+      <c r="G1987" s="3">
+        <v>40.563</v>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1988" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C1988" s="3">
+        <v>72.55</v>
+      </c>
+      <c r="D1988" s="3">
+        <v>40.499</v>
+      </c>
+      <c r="E1988" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1988" s="3">
+        <v>32.051</v>
+      </c>
+      <c r="G1988" s="3">
+        <v>40.499</v>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1989" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C1989" s="3">
+        <v>66.112</v>
+      </c>
+      <c r="D1989" s="3">
+        <v>40.256</v>
+      </c>
+      <c r="E1989" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1989" s="3">
+        <v>25.856</v>
+      </c>
+      <c r="G1989" s="3">
+        <v>40.256</v>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1990" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C1990" s="3">
+        <v>58.854</v>
+      </c>
+      <c r="D1990" s="3">
+        <v>40.166</v>
+      </c>
+      <c r="E1990" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1990" s="3">
+        <v>18.688</v>
+      </c>
+      <c r="G1990" s="3">
+        <v>40.166</v>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1991" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C1991" s="3">
+        <v>51.11</v>
+      </c>
+      <c r="D1991" s="3">
+        <v>40.512</v>
+      </c>
+      <c r="E1991" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F1991" s="3">
+        <v>10.598</v>
+      </c>
+      <c r="G1991" s="3">
+        <v>40.512</v>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1992" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C1992" s="3">
+        <v>43.456</v>
+      </c>
+      <c r="D1992" s="3">
+        <v>40.026</v>
+      </c>
+      <c r="E1992" s="3">
+        <v>0.768</v>
+      </c>
+      <c r="F1992" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="G1992" s="3">
+        <v>40.794</v>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1993" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C1993" s="3">
+        <v>35.482</v>
+      </c>
+      <c r="D1993" s="3">
+        <v>35.38</v>
+      </c>
+      <c r="E1993" s="3">
+        <v>5.581</v>
+      </c>
+      <c r="F1993" s="3">
+        <v>0.102</v>
+      </c>
+      <c r="G1993" s="3">
+        <v>40.961</v>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1994" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C1994" s="3">
+        <v>28.096</v>
+      </c>
+      <c r="D1994" s="3">
+        <v>28.096</v>
+      </c>
+      <c r="E1994" s="3">
+        <v>12.595</v>
+      </c>
+      <c r="F1994" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1994" s="3">
+        <v>40.691</v>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1995" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C1995" s="3">
+        <v>20.339</v>
+      </c>
+      <c r="D1995" s="3">
+        <v>20.339</v>
+      </c>
+      <c r="E1995" s="3">
+        <v>20.224</v>
+      </c>
+      <c r="F1995" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1995" s="3">
+        <v>40.563</v>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1996" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C1996" s="3">
+        <v>15.77</v>
+      </c>
+      <c r="D1996" s="3">
+        <v>15.77</v>
+      </c>
+      <c r="E1996" s="3">
+        <v>24.525</v>
+      </c>
+      <c r="F1996" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1996" s="3">
+        <v>40.295</v>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1997" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C1997" s="3">
+        <v>10.867</v>
+      </c>
+      <c r="D1997" s="3">
+        <v>10.867</v>
+      </c>
+      <c r="E1997" s="3">
+        <v>28.877</v>
+      </c>
+      <c r="F1997" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1997" s="3">
+        <v>39.744</v>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1998" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C1998" s="3">
+        <v>5.414</v>
+      </c>
+      <c r="D1998" s="3">
+        <v>5.414</v>
+      </c>
+      <c r="E1998" s="3">
+        <v>34.15</v>
+      </c>
+      <c r="F1998" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1998" s="3">
+        <v>39.564</v>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B1999" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C1999" s="3">
+        <v>1.382</v>
+      </c>
+      <c r="D1999" s="3">
+        <v>1.382</v>
+      </c>
+      <c r="E1999" s="3">
+        <v>38.246</v>
+      </c>
+      <c r="F1999" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G1999" s="3">
+        <v>39.628</v>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B2000" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C2000" s="3">
+        <v>0.077</v>
+      </c>
+      <c r="D2000" s="3">
+        <v>0.077</v>
+      </c>
+      <c r="E2000" s="3">
+        <v>39.731</v>
+      </c>
+      <c r="F2000" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2000" s="3">
+        <v>39.808</v>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B2001" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C2001" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2001" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2001" s="3">
+        <v>39.885</v>
+      </c>
+      <c r="F2001" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2001" s="3">
+        <v>39.885</v>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B2002" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C2002" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2002" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2002" s="3">
+        <v>39.066</v>
+      </c>
+      <c r="F2002" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2002" s="3">
+        <v>39.066</v>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B2003" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C2003" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2003" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2003" s="3">
+        <v>37.683</v>
+      </c>
+      <c r="F2003" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2003" s="3">
+        <v>37.683</v>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B2004" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C2004" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2004" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2004" s="3">
+        <v>37.888</v>
+      </c>
+      <c r="F2004" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2004" s="3">
+        <v>37.888</v>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B2005" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C2005" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2005" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2005" s="3">
+        <v>37.734</v>
+      </c>
+      <c r="F2005" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2005" s="3">
+        <v>37.734</v>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B2006" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C2006" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2006" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2006" s="3">
+        <v>37.274</v>
+      </c>
+      <c r="F2006" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2006" s="3">
+        <v>37.274</v>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B2007" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C2007" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2007" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2007" s="3">
+        <v>37.12</v>
+      </c>
+      <c r="F2007" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2007" s="3">
+        <v>37.12</v>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B2008" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C2008" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2008" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2008" s="3">
+        <v>36.659</v>
+      </c>
+      <c r="F2008" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2008" s="3">
+        <v>36.659</v>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B2009" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C2009" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2009" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2009" s="3">
+        <v>36.71</v>
+      </c>
+      <c r="F2009" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2009" s="3">
+        <v>36.71</v>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B2010" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C2010" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2010" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2010" s="3">
+        <v>36.864</v>
+      </c>
+      <c r="F2010" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2010" s="3">
+        <v>36.864</v>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B2011" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C2011" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2011" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2011" s="3">
+        <v>36.71</v>
+      </c>
+      <c r="F2011" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2011" s="3">
+        <v>36.71</v>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B2012" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C2012" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2012" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2012" s="3">
+        <v>36.813</v>
+      </c>
+      <c r="F2012" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2012" s="3">
+        <v>36.813</v>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B2013" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C2013" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2013" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2013" s="3">
+        <v>37.018</v>
+      </c>
+      <c r="F2013" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2013" s="3">
+        <v>37.018</v>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B2014" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C2014" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2014" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2014" s="3">
+        <v>37.222</v>
+      </c>
+      <c r="F2014" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2014" s="3">
+        <v>37.222</v>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B2015" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C2015" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2015" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2015" s="3">
+        <v>36.813</v>
+      </c>
+      <c r="F2015" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2015" s="3">
+        <v>36.813</v>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B2016" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C2016" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2016" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2016" s="3">
+        <v>36.864</v>
+      </c>
+      <c r="F2016" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2016" s="3">
+        <v>36.864</v>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B2017" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C2017" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2017" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2017" s="3">
+        <v>37.171</v>
+      </c>
+      <c r="F2017" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2017" s="3">
+        <v>37.171</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1921"/>
+  <autoFilter ref="A1:G2017"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -646,45 +646,69 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B26" s="4">
+        <v>2232.4</v>
+      </c>
+      <c r="C26" s="4">
+        <v>1497.0</v>
+      </c>
+      <c r="D26" s="4">
+        <v>2215.2</v>
+      </c>
+      <c r="E26" s="4">
+        <v>735.4</v>
+      </c>
+      <c r="F26" s="4">
+        <v>3712.1</v>
+      </c>
+      <c r="G26" s="5">
+        <f>IF(F26&gt;0,C26/F26,"")</f>
+        <v>0.4033</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B26" s="7">
-        <f>SUM(B5:B25)</f>
-        <v>47196.2</v>
-      </c>
-      <c r="C26" s="7">
-        <f>SUM(C5:C25)</f>
-        <v>35059.0</v>
-      </c>
-      <c r="D26" s="7">
-        <f>SUM(D5:D25)</f>
-        <v>123669.9</v>
-      </c>
-      <c r="E26" s="7">
-        <f>SUM(E5:E25)</f>
-        <v>12137.5</v>
-      </c>
-      <c r="F26" s="7">
-        <f>SUM(F5:F25)</f>
-        <v>158728.9</v>
-      </c>
-      <c r="G26" s="8">
-        <f>IF(F26&gt;0,C26/F26,"")</f>
-        <v>0.2209</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B27" s="7">
+        <f>SUM(B5:B26)</f>
+        <v>49428.6</v>
+      </c>
+      <c r="C27" s="7">
+        <f>SUM(C5:C26)</f>
+        <v>36556.0</v>
+      </c>
+      <c r="D27" s="7">
+        <f>SUM(D5:D26)</f>
+        <v>125885.1</v>
+      </c>
+      <c r="E27" s="7">
+        <f>SUM(E5:E26)</f>
+        <v>12872.9</v>
+      </c>
+      <c r="F27" s="7">
+        <f>SUM(F5:F26)</f>
+        <v>162441.1</v>
+      </c>
+      <c r="G27" s="8">
+        <f>IF(F27&gt;0,C27/F27,"")</f>
+        <v>0.225</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -51143,7 +51167,2407 @@
         <v>37.171</v>
       </c>
     </row>
+    <row r="2018">
+      <c r="A2018" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2018" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C2018" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2018" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2018" s="3">
+        <v>36.915</v>
+      </c>
+      <c r="F2018" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2018" s="3">
+        <v>36.915</v>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2019" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C2019" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2019" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2019" s="3">
+        <v>36.966</v>
+      </c>
+      <c r="F2019" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2019" s="3">
+        <v>36.966</v>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2020" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C2020" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2020" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2020" s="3">
+        <v>37.069</v>
+      </c>
+      <c r="F2020" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2020" s="3">
+        <v>37.069</v>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2021" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C2021" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2021" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2021" s="3">
+        <v>36.915</v>
+      </c>
+      <c r="F2021" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2021" s="3">
+        <v>36.915</v>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2022" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C2022" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2022" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2022" s="3">
+        <v>36.915</v>
+      </c>
+      <c r="F2022" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2022" s="3">
+        <v>36.915</v>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2023" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C2023" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2023" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2023" s="3">
+        <v>36.71</v>
+      </c>
+      <c r="F2023" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2023" s="3">
+        <v>36.71</v>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2024" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C2024" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2024" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2024" s="3">
+        <v>36.762</v>
+      </c>
+      <c r="F2024" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2024" s="3">
+        <v>36.762</v>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2025" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C2025" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2025" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2025" s="3">
+        <v>36.966</v>
+      </c>
+      <c r="F2025" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2025" s="3">
+        <v>36.966</v>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2026" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C2026" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2026" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2026" s="3">
+        <v>36.813</v>
+      </c>
+      <c r="F2026" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2026" s="3">
+        <v>36.813</v>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2027" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C2027" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2027" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2027" s="3">
+        <v>36.71</v>
+      </c>
+      <c r="F2027" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2027" s="3">
+        <v>36.71</v>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2028" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C2028" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2028" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2028" s="3">
+        <v>36.813</v>
+      </c>
+      <c r="F2028" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2028" s="3">
+        <v>36.813</v>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2029" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C2029" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2029" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2029" s="3">
+        <v>36.71</v>
+      </c>
+      <c r="F2029" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2029" s="3">
+        <v>36.71</v>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2030" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C2030" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2030" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2030" s="3">
+        <v>37.12</v>
+      </c>
+      <c r="F2030" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2030" s="3">
+        <v>37.12</v>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2031" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C2031" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2031" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2031" s="3">
+        <v>36.864</v>
+      </c>
+      <c r="F2031" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2031" s="3">
+        <v>36.864</v>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2032" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C2032" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2032" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2032" s="3">
+        <v>36.915</v>
+      </c>
+      <c r="F2032" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2032" s="3">
+        <v>36.915</v>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2033" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C2033" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2033" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2033" s="3">
+        <v>37.427</v>
+      </c>
+      <c r="F2033" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2033" s="3">
+        <v>37.427</v>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2034" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C2034" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2034" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2034" s="3">
+        <v>36.71</v>
+      </c>
+      <c r="F2034" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2034" s="3">
+        <v>36.71</v>
+      </c>
+    </row>
+    <row r="2035">
+      <c r="A2035" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2035" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C2035" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2035" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2035" s="3">
+        <v>36.813</v>
+      </c>
+      <c r="F2035" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2035" s="3">
+        <v>36.813</v>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2036" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C2036" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2036" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2036" s="3">
+        <v>36.915</v>
+      </c>
+      <c r="F2036" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2036" s="3">
+        <v>36.915</v>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2037" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C2037" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2037" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2037" s="3">
+        <v>37.12</v>
+      </c>
+      <c r="F2037" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2037" s="3">
+        <v>37.12</v>
+      </c>
+    </row>
+    <row r="2038">
+      <c r="A2038" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2038" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C2038" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2038" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2038" s="3">
+        <v>36.864</v>
+      </c>
+      <c r="F2038" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2038" s="3">
+        <v>36.864</v>
+      </c>
+    </row>
+    <row r="2039">
+      <c r="A2039" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2039" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C2039" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2039" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2039" s="3">
+        <v>36.71</v>
+      </c>
+      <c r="F2039" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2039" s="3">
+        <v>36.71</v>
+      </c>
+    </row>
+    <row r="2040">
+      <c r="A2040" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2040" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C2040" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2040" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2040" s="3">
+        <v>36.762</v>
+      </c>
+      <c r="F2040" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2040" s="3">
+        <v>36.762</v>
+      </c>
+    </row>
+    <row r="2041">
+      <c r="A2041" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2041" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C2041" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2041" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2041" s="3">
+        <v>36.813</v>
+      </c>
+      <c r="F2041" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2041" s="3">
+        <v>36.813</v>
+      </c>
+    </row>
+    <row r="2042">
+      <c r="A2042" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2042" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C2042" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2042" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2042" s="3">
+        <v>37.12</v>
+      </c>
+      <c r="F2042" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2042" s="3">
+        <v>37.12</v>
+      </c>
+    </row>
+    <row r="2043">
+      <c r="A2043" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2043" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C2043" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2043" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2043" s="3">
+        <v>37.222</v>
+      </c>
+      <c r="F2043" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2043" s="3">
+        <v>37.222</v>
+      </c>
+    </row>
+    <row r="2044">
+      <c r="A2044" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2044" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C2044" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="D2044" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="E2044" s="3">
+        <v>37.274</v>
+      </c>
+      <c r="F2044" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2044" s="3">
+        <v>37.287</v>
+      </c>
+    </row>
+    <row r="2045">
+      <c r="A2045" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2045" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C2045" s="3">
+        <v>0.55</v>
+      </c>
+      <c r="D2045" s="3">
+        <v>0.55</v>
+      </c>
+      <c r="E2045" s="3">
+        <v>37.427</v>
+      </c>
+      <c r="F2045" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2045" s="3">
+        <v>37.977</v>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2046" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C2046" s="3">
+        <v>1.651</v>
+      </c>
+      <c r="D2046" s="3">
+        <v>1.651</v>
+      </c>
+      <c r="E2046" s="3">
+        <v>36.301</v>
+      </c>
+      <c r="F2046" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2046" s="3">
+        <v>37.952</v>
+      </c>
+    </row>
+    <row r="2047">
+      <c r="A2047" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2047" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C2047" s="3">
+        <v>4.595</v>
+      </c>
+      <c r="D2047" s="3">
+        <v>4.595</v>
+      </c>
+      <c r="E2047" s="3">
+        <v>32.41</v>
+      </c>
+      <c r="F2047" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2047" s="3">
+        <v>37.005</v>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2048" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C2048" s="3">
+        <v>7.104</v>
+      </c>
+      <c r="D2048" s="3">
+        <v>7.104</v>
+      </c>
+      <c r="E2048" s="3">
+        <v>29.901</v>
+      </c>
+      <c r="F2048" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2048" s="3">
+        <v>37.005</v>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2049" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C2049" s="3">
+        <v>6.374</v>
+      </c>
+      <c r="D2049" s="3">
+        <v>6.374</v>
+      </c>
+      <c r="E2049" s="3">
+        <v>30.72</v>
+      </c>
+      <c r="F2049" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2049" s="3">
+        <v>37.094</v>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2050" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C2050" s="3">
+        <v>16.269</v>
+      </c>
+      <c r="D2050" s="3">
+        <v>16.269</v>
+      </c>
+      <c r="E2050" s="3">
+        <v>20.634</v>
+      </c>
+      <c r="F2050" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2050" s="3">
+        <v>36.903</v>
+      </c>
+    </row>
+    <row r="2051">
+      <c r="A2051" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2051" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C2051" s="3">
+        <v>26.086</v>
+      </c>
+      <c r="D2051" s="3">
+        <v>25.728</v>
+      </c>
+      <c r="E2051" s="3">
+        <v>11.725</v>
+      </c>
+      <c r="F2051" s="3">
+        <v>0.358</v>
+      </c>
+      <c r="G2051" s="3">
+        <v>37.453</v>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2052" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C2052" s="3">
+        <v>26.227</v>
+      </c>
+      <c r="D2052" s="3">
+        <v>24.896</v>
+      </c>
+      <c r="E2052" s="3">
+        <v>11.981</v>
+      </c>
+      <c r="F2052" s="3">
+        <v>1.331</v>
+      </c>
+      <c r="G2052" s="3">
+        <v>36.877</v>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2053" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C2053" s="3">
+        <v>27.238</v>
+      </c>
+      <c r="D2053" s="3">
+        <v>26.06</v>
+      </c>
+      <c r="E2053" s="3">
+        <v>11.315</v>
+      </c>
+      <c r="F2053" s="3">
+        <v>1.178</v>
+      </c>
+      <c r="G2053" s="3">
+        <v>37.375</v>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2054" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C2054" s="3">
+        <v>29.875</v>
+      </c>
+      <c r="D2054" s="3">
+        <v>27.878</v>
+      </c>
+      <c r="E2054" s="3">
+        <v>9.574</v>
+      </c>
+      <c r="F2054" s="3">
+        <v>1.997</v>
+      </c>
+      <c r="G2054" s="3">
+        <v>37.452</v>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2055" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C2055" s="3">
+        <v>21.99</v>
+      </c>
+      <c r="D2055" s="3">
+        <v>21.888</v>
+      </c>
+      <c r="E2055" s="3">
+        <v>15.309</v>
+      </c>
+      <c r="F2055" s="3">
+        <v>0.102</v>
+      </c>
+      <c r="G2055" s="3">
+        <v>37.197</v>
+      </c>
+    </row>
+    <row r="2056">
+      <c r="A2056" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2056" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C2056" s="3">
+        <v>26.867</v>
+      </c>
+      <c r="D2056" s="3">
+        <v>26.867</v>
+      </c>
+      <c r="E2056" s="3">
+        <v>12.39</v>
+      </c>
+      <c r="F2056" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2056" s="3">
+        <v>39.257</v>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2057" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C2057" s="3">
+        <v>45.453</v>
+      </c>
+      <c r="D2057" s="3">
+        <v>34.343</v>
+      </c>
+      <c r="E2057" s="3">
+        <v>5.939</v>
+      </c>
+      <c r="F2057" s="3">
+        <v>11.11</v>
+      </c>
+      <c r="G2057" s="3">
+        <v>40.282</v>
+      </c>
+    </row>
+    <row r="2058">
+      <c r="A2058" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2058" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C2058" s="3">
+        <v>49.024</v>
+      </c>
+      <c r="D2058" s="3">
+        <v>37.146</v>
+      </c>
+      <c r="E2058" s="3">
+        <v>3.635</v>
+      </c>
+      <c r="F2058" s="3">
+        <v>11.878</v>
+      </c>
+      <c r="G2058" s="3">
+        <v>40.781</v>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2059" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C2059" s="3">
+        <v>30.72</v>
+      </c>
+      <c r="D2059" s="3">
+        <v>30.515</v>
+      </c>
+      <c r="E2059" s="3">
+        <v>10.035</v>
+      </c>
+      <c r="F2059" s="3">
+        <v>0.205</v>
+      </c>
+      <c r="G2059" s="3">
+        <v>40.55</v>
+      </c>
+    </row>
+    <row r="2060">
+      <c r="A2060" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2060" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C2060" s="3">
+        <v>27.354</v>
+      </c>
+      <c r="D2060" s="3">
+        <v>25.408</v>
+      </c>
+      <c r="E2060" s="3">
+        <v>15.104</v>
+      </c>
+      <c r="F2060" s="3">
+        <v>1.946</v>
+      </c>
+      <c r="G2060" s="3">
+        <v>40.512</v>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2061" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C2061" s="3">
+        <v>24.397</v>
+      </c>
+      <c r="D2061" s="3">
+        <v>20.403</v>
+      </c>
+      <c r="E2061" s="3">
+        <v>20.275</v>
+      </c>
+      <c r="F2061" s="3">
+        <v>3.994</v>
+      </c>
+      <c r="G2061" s="3">
+        <v>40.678</v>
+      </c>
+    </row>
+    <row r="2062">
+      <c r="A2062" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2062" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C2062" s="3">
+        <v>48.538</v>
+      </c>
+      <c r="D2062" s="3">
+        <v>37.735</v>
+      </c>
+      <c r="E2062" s="3">
+        <v>2.253</v>
+      </c>
+      <c r="F2062" s="3">
+        <v>10.803</v>
+      </c>
+      <c r="G2062" s="3">
+        <v>39.988</v>
+      </c>
+    </row>
+    <row r="2063">
+      <c r="A2063" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2063" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C2063" s="3">
+        <v>32.051</v>
+      </c>
+      <c r="D2063" s="3">
+        <v>31.59</v>
+      </c>
+      <c r="E2063" s="3">
+        <v>8.602</v>
+      </c>
+      <c r="F2063" s="3">
+        <v>0.461</v>
+      </c>
+      <c r="G2063" s="3">
+        <v>40.192</v>
+      </c>
+    </row>
+    <row r="2064">
+      <c r="A2064" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2064" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C2064" s="3">
+        <v>43.597</v>
+      </c>
+      <c r="D2064" s="3">
+        <v>33.357</v>
+      </c>
+      <c r="E2064" s="3">
+        <v>6.4</v>
+      </c>
+      <c r="F2064" s="3">
+        <v>10.24</v>
+      </c>
+      <c r="G2064" s="3">
+        <v>39.757</v>
+      </c>
+    </row>
+    <row r="2065">
+      <c r="A2065" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2065" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C2065" s="3">
+        <v>62.656</v>
+      </c>
+      <c r="D2065" s="3">
+        <v>40.128</v>
+      </c>
+      <c r="E2065" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2065" s="3">
+        <v>22.528</v>
+      </c>
+      <c r="G2065" s="3">
+        <v>40.128</v>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2066" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C2066" s="3">
+        <v>69.338</v>
+      </c>
+      <c r="D2066" s="3">
+        <v>40.052</v>
+      </c>
+      <c r="E2066" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2066" s="3">
+        <v>29.286</v>
+      </c>
+      <c r="G2066" s="3">
+        <v>40.052</v>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2067" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C2067" s="3">
+        <v>82.278</v>
+      </c>
+      <c r="D2067" s="3">
+        <v>40.755</v>
+      </c>
+      <c r="E2067" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2067" s="3">
+        <v>41.523</v>
+      </c>
+      <c r="G2067" s="3">
+        <v>40.755</v>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2068" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C2068" s="3">
+        <v>80.653</v>
+      </c>
+      <c r="D2068" s="3">
+        <v>40.154</v>
+      </c>
+      <c r="E2068" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2068" s="3">
+        <v>40.499</v>
+      </c>
+      <c r="G2068" s="3">
+        <v>40.154</v>
+      </c>
+    </row>
+    <row r="2069">
+      <c r="A2069" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2069" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C2069" s="3">
+        <v>51.52</v>
+      </c>
+      <c r="D2069" s="3">
+        <v>39.949</v>
+      </c>
+      <c r="E2069" s="3">
+        <v>0.205</v>
+      </c>
+      <c r="F2069" s="3">
+        <v>11.571</v>
+      </c>
+      <c r="G2069" s="3">
+        <v>40.154</v>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2070" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C2070" s="3">
+        <v>57.574</v>
+      </c>
+      <c r="D2070" s="3">
+        <v>40.678</v>
+      </c>
+      <c r="E2070" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2070" s="3">
+        <v>16.896</v>
+      </c>
+      <c r="G2070" s="3">
+        <v>40.678</v>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2071" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C2071" s="3">
+        <v>65.741</v>
+      </c>
+      <c r="D2071" s="3">
+        <v>40.397</v>
+      </c>
+      <c r="E2071" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2071" s="3">
+        <v>25.344</v>
+      </c>
+      <c r="G2071" s="3">
+        <v>40.397</v>
+      </c>
+    </row>
+    <row r="2072">
+      <c r="A2072" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2072" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C2072" s="3">
+        <v>49.062</v>
+      </c>
+      <c r="D2072" s="3">
+        <v>39.744</v>
+      </c>
+      <c r="E2072" s="3">
+        <v>0.154</v>
+      </c>
+      <c r="F2072" s="3">
+        <v>9.318</v>
+      </c>
+      <c r="G2072" s="3">
+        <v>39.898</v>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2073" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C2073" s="3">
+        <v>43.11</v>
+      </c>
+      <c r="D2073" s="3">
+        <v>39.372</v>
+      </c>
+      <c r="E2073" s="3">
+        <v>0.307</v>
+      </c>
+      <c r="F2073" s="3">
+        <v>3.738</v>
+      </c>
+      <c r="G2073" s="3">
+        <v>39.679</v>
+      </c>
+    </row>
+    <row r="2074">
+      <c r="A2074" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2074" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C2074" s="3">
+        <v>65.472</v>
+      </c>
+      <c r="D2074" s="3">
+        <v>40.026</v>
+      </c>
+      <c r="E2074" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2074" s="3">
+        <v>25.446</v>
+      </c>
+      <c r="G2074" s="3">
+        <v>40.026</v>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2075" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C2075" s="3">
+        <v>79.539</v>
+      </c>
+      <c r="D2075" s="3">
+        <v>40.473</v>
+      </c>
+      <c r="E2075" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2075" s="3">
+        <v>39.066</v>
+      </c>
+      <c r="G2075" s="3">
+        <v>40.473</v>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2076" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C2076" s="3">
+        <v>63.552</v>
+      </c>
+      <c r="D2076" s="3">
+        <v>39.846</v>
+      </c>
+      <c r="E2076" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2076" s="3">
+        <v>23.706</v>
+      </c>
+      <c r="G2076" s="3">
+        <v>39.846</v>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2077" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C2077" s="3">
+        <v>52.058</v>
+      </c>
+      <c r="D2077" s="3">
+        <v>39.156</v>
+      </c>
+      <c r="E2077" s="3">
+        <v>0.922</v>
+      </c>
+      <c r="F2077" s="3">
+        <v>12.902</v>
+      </c>
+      <c r="G2077" s="3">
+        <v>40.078</v>
+      </c>
+    </row>
+    <row r="2078">
+      <c r="A2078" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2078" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C2078" s="3">
+        <v>84.954</v>
+      </c>
+      <c r="D2078" s="3">
+        <v>40.666</v>
+      </c>
+      <c r="E2078" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2078" s="3">
+        <v>44.288</v>
+      </c>
+      <c r="G2078" s="3">
+        <v>40.666</v>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2079" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C2079" s="3">
+        <v>102.477</v>
+      </c>
+      <c r="D2079" s="3">
+        <v>41.139</v>
+      </c>
+      <c r="E2079" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2079" s="3">
+        <v>61.338</v>
+      </c>
+      <c r="G2079" s="3">
+        <v>41.139</v>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2080" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C2080" s="3">
+        <v>97.357</v>
+      </c>
+      <c r="D2080" s="3">
+        <v>41.395</v>
+      </c>
+      <c r="E2080" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2080" s="3">
+        <v>55.962</v>
+      </c>
+      <c r="G2080" s="3">
+        <v>41.395</v>
+      </c>
+    </row>
+    <row r="2081">
+      <c r="A2081" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2081" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C2081" s="3">
+        <v>93.683</v>
+      </c>
+      <c r="D2081" s="3">
+        <v>41.305</v>
+      </c>
+      <c r="E2081" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2081" s="3">
+        <v>52.378</v>
+      </c>
+      <c r="G2081" s="3">
+        <v>41.305</v>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2082" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C2082" s="3">
+        <v>83.392</v>
+      </c>
+      <c r="D2082" s="3">
+        <v>40.486</v>
+      </c>
+      <c r="E2082" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2082" s="3">
+        <v>42.906</v>
+      </c>
+      <c r="G2082" s="3">
+        <v>40.486</v>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2083" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C2083" s="3">
+        <v>81.088</v>
+      </c>
+      <c r="D2083" s="3">
+        <v>40.64</v>
+      </c>
+      <c r="E2083" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2083" s="3">
+        <v>40.448</v>
+      </c>
+      <c r="G2083" s="3">
+        <v>40.64</v>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2084" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C2084" s="3">
+        <v>55.36</v>
+      </c>
+      <c r="D2084" s="3">
+        <v>33.907</v>
+      </c>
+      <c r="E2084" s="3">
+        <v>6.451</v>
+      </c>
+      <c r="F2084" s="3">
+        <v>21.453</v>
+      </c>
+      <c r="G2084" s="3">
+        <v>40.358</v>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2085" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C2085" s="3">
+        <v>58.547</v>
+      </c>
+      <c r="D2085" s="3">
+        <v>36.736</v>
+      </c>
+      <c r="E2085" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F2085" s="3">
+        <v>21.811</v>
+      </c>
+      <c r="G2085" s="3">
+        <v>40.166</v>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2086" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C2086" s="3">
+        <v>59.494</v>
+      </c>
+      <c r="D2086" s="3">
+        <v>40.089</v>
+      </c>
+      <c r="E2086" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2086" s="3">
+        <v>19.405</v>
+      </c>
+      <c r="G2086" s="3">
+        <v>40.089</v>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2087" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C2087" s="3">
+        <v>47.974</v>
+      </c>
+      <c r="D2087" s="3">
+        <v>34.764</v>
+      </c>
+      <c r="E2087" s="3">
+        <v>5.939</v>
+      </c>
+      <c r="F2087" s="3">
+        <v>13.21</v>
+      </c>
+      <c r="G2087" s="3">
+        <v>40.703</v>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2088" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C2088" s="3">
+        <v>44.173</v>
+      </c>
+      <c r="D2088" s="3">
+        <v>39.565</v>
+      </c>
+      <c r="E2088" s="3">
+        <v>1.024</v>
+      </c>
+      <c r="F2088" s="3">
+        <v>4.608</v>
+      </c>
+      <c r="G2088" s="3">
+        <v>40.589</v>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2089" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C2089" s="3">
+        <v>35.827</v>
+      </c>
+      <c r="D2089" s="3">
+        <v>35.622</v>
+      </c>
+      <c r="E2089" s="3">
+        <v>4.659</v>
+      </c>
+      <c r="F2089" s="3">
+        <v>0.205</v>
+      </c>
+      <c r="G2089" s="3">
+        <v>40.281</v>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2090" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C2090" s="3">
+        <v>27.469</v>
+      </c>
+      <c r="D2090" s="3">
+        <v>27.469</v>
+      </c>
+      <c r="E2090" s="3">
+        <v>12.39</v>
+      </c>
+      <c r="F2090" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2090" s="3">
+        <v>39.859</v>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2091" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C2091" s="3">
+        <v>19.814</v>
+      </c>
+      <c r="D2091" s="3">
+        <v>19.814</v>
+      </c>
+      <c r="E2091" s="3">
+        <v>20.173</v>
+      </c>
+      <c r="F2091" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2091" s="3">
+        <v>39.987</v>
+      </c>
+    </row>
+    <row r="2092">
+      <c r="A2092" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2092" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C2092" s="3">
+        <v>12.429</v>
+      </c>
+      <c r="D2092" s="3">
+        <v>12.429</v>
+      </c>
+      <c r="E2092" s="3">
+        <v>27.699</v>
+      </c>
+      <c r="F2092" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2092" s="3">
+        <v>40.128</v>
+      </c>
+    </row>
+    <row r="2093">
+      <c r="A2093" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2093" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C2093" s="3">
+        <v>6.49</v>
+      </c>
+      <c r="D2093" s="3">
+        <v>6.49</v>
+      </c>
+      <c r="E2093" s="3">
+        <v>33.536</v>
+      </c>
+      <c r="F2093" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2093" s="3">
+        <v>40.026</v>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2094" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C2094" s="3">
+        <v>2.496</v>
+      </c>
+      <c r="D2094" s="3">
+        <v>2.496</v>
+      </c>
+      <c r="E2094" s="3">
+        <v>37.325</v>
+      </c>
+      <c r="F2094" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2094" s="3">
+        <v>39.821</v>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2095" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C2095" s="3">
+        <v>0.704</v>
+      </c>
+      <c r="D2095" s="3">
+        <v>0.704</v>
+      </c>
+      <c r="E2095" s="3">
+        <v>39.014</v>
+      </c>
+      <c r="F2095" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2095" s="3">
+        <v>39.718</v>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2096" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C2096" s="3">
+        <v>0.154</v>
+      </c>
+      <c r="D2096" s="3">
+        <v>0.154</v>
+      </c>
+      <c r="E2096" s="3">
+        <v>39.475</v>
+      </c>
+      <c r="F2096" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2096" s="3">
+        <v>39.629</v>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2097" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C2097" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2097" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2097" s="3">
+        <v>40.141</v>
+      </c>
+      <c r="F2097" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2097" s="3">
+        <v>40.141</v>
+      </c>
+    </row>
+    <row r="2098">
+      <c r="A2098" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2098" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C2098" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2098" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2098" s="3">
+        <v>40.192</v>
+      </c>
+      <c r="F2098" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2098" s="3">
+        <v>40.192</v>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2099" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C2099" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2099" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2099" s="3">
+        <v>39.68</v>
+      </c>
+      <c r="F2099" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2099" s="3">
+        <v>39.68</v>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2100" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C2100" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2100" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2100" s="3">
+        <v>39.782</v>
+      </c>
+      <c r="F2100" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2100" s="3">
+        <v>39.782</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2101" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C2101" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2101" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2101" s="3">
+        <v>39.782</v>
+      </c>
+      <c r="F2101" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2101" s="3">
+        <v>39.782</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2102" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C2102" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2102" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2102" s="3">
+        <v>40.09</v>
+      </c>
+      <c r="F2102" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2102" s="3">
+        <v>40.09</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2103" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C2103" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2103" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2103" s="3">
+        <v>40.038</v>
+      </c>
+      <c r="F2103" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2103" s="3">
+        <v>40.038</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2104" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C2104" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2104" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2104" s="3">
+        <v>39.782</v>
+      </c>
+      <c r="F2104" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2104" s="3">
+        <v>39.782</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2105" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C2105" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2105" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2105" s="3">
+        <v>37.632</v>
+      </c>
+      <c r="F2105" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2105" s="3">
+        <v>37.632</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2106" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C2106" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2106" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2106" s="3">
+        <v>36.71</v>
+      </c>
+      <c r="F2106" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2106" s="3">
+        <v>36.71</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2107" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C2107" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2107" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2107" s="3">
+        <v>36.71</v>
+      </c>
+      <c r="F2107" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2107" s="3">
+        <v>36.71</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2108" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C2108" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2108" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2108" s="3">
+        <v>37.018</v>
+      </c>
+      <c r="F2108" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2108" s="3">
+        <v>37.018</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2109" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C2109" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2109" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2109" s="3">
+        <v>37.376</v>
+      </c>
+      <c r="F2109" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2109" s="3">
+        <v>37.376</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2110" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C2110" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2110" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2110" s="3">
+        <v>37.581</v>
+      </c>
+      <c r="F2110" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2110" s="3">
+        <v>37.581</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2111" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C2111" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2111" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2111" s="3">
+        <v>37.376</v>
+      </c>
+      <c r="F2111" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2111" s="3">
+        <v>37.376</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2112" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C2112" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2112" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2112" s="3">
+        <v>36.762</v>
+      </c>
+      <c r="F2112" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2112" s="3">
+        <v>36.762</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="2">
+        <v>46317</v>
+      </c>
+      <c r="B2113" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C2113" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2113" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2113" s="3">
+        <v>36.966</v>
+      </c>
+      <c r="F2113" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2113" s="3">
+        <v>36.966</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2017"/>
+  <autoFilter ref="A1:G2113"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -670,45 +670,69 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B27" s="4">
+        <v>2735.6</v>
+      </c>
+      <c r="C27" s="4">
+        <v>2072.9</v>
+      </c>
+      <c r="D27" s="4">
+        <v>3184.7</v>
+      </c>
+      <c r="E27" s="4">
+        <v>662.6</v>
+      </c>
+      <c r="F27" s="4">
+        <v>5257.7</v>
+      </c>
+      <c r="G27" s="5">
+        <f>IF(F27&gt;0,C27/F27,"")</f>
+        <v>0.3943</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B27" s="7">
-        <f>SUM(B5:B26)</f>
-        <v>49428.6</v>
-      </c>
-      <c r="C27" s="7">
-        <f>SUM(C5:C26)</f>
-        <v>36556.0</v>
-      </c>
-      <c r="D27" s="7">
-        <f>SUM(D5:D26)</f>
-        <v>125885.1</v>
-      </c>
-      <c r="E27" s="7">
-        <f>SUM(E5:E26)</f>
-        <v>12872.9</v>
-      </c>
-      <c r="F27" s="7">
-        <f>SUM(F5:F26)</f>
-        <v>162441.1</v>
-      </c>
-      <c r="G27" s="8">
-        <f>IF(F27&gt;0,C27/F27,"")</f>
-        <v>0.225</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B28" s="7">
+        <f>SUM(B5:B27)</f>
+        <v>52164.2</v>
+      </c>
+      <c r="C28" s="7">
+        <f>SUM(C5:C27)</f>
+        <v>38628.9</v>
+      </c>
+      <c r="D28" s="7">
+        <f>SUM(D5:D27)</f>
+        <v>129069.8</v>
+      </c>
+      <c r="E28" s="7">
+        <f>SUM(E5:E27)</f>
+        <v>13535.5</v>
+      </c>
+      <c r="F28" s="7">
+        <f>SUM(F5:F27)</f>
+        <v>167698.8</v>
+      </c>
+      <c r="G28" s="8">
+        <f>IF(F28&gt;0,C28/F28,"")</f>
+        <v>0.2303</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -53567,7 +53591,2407 @@
         <v>36.966</v>
       </c>
     </row>
+    <row r="2114">
+      <c r="A2114" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2114" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C2114" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2114" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2114" s="3">
+        <v>37.274</v>
+      </c>
+      <c r="F2114" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2114" s="3">
+        <v>37.274</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2115" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C2115" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2115" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2115" s="3">
+        <v>37.171</v>
+      </c>
+      <c r="F2115" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2115" s="3">
+        <v>37.171</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2116" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C2116" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2116" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2116" s="3">
+        <v>37.376</v>
+      </c>
+      <c r="F2116" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2116" s="3">
+        <v>37.376</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2117" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C2117" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2117" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2117" s="3">
+        <v>37.018</v>
+      </c>
+      <c r="F2117" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2117" s="3">
+        <v>37.018</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2118" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C2118" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2118" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2118" s="3">
+        <v>36.864</v>
+      </c>
+      <c r="F2118" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2118" s="3">
+        <v>36.864</v>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2119" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C2119" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2119" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2119" s="3">
+        <v>37.171</v>
+      </c>
+      <c r="F2119" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2119" s="3">
+        <v>37.171</v>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2120" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C2120" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2120" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2120" s="3">
+        <v>37.222</v>
+      </c>
+      <c r="F2120" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2120" s="3">
+        <v>37.222</v>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2121" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C2121" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2121" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2121" s="3">
+        <v>37.222</v>
+      </c>
+      <c r="F2121" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2121" s="3">
+        <v>37.222</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2122" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C2122" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2122" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2122" s="3">
+        <v>37.222</v>
+      </c>
+      <c r="F2122" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2122" s="3">
+        <v>37.222</v>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2123" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C2123" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2123" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2123" s="3">
+        <v>37.222</v>
+      </c>
+      <c r="F2123" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2123" s="3">
+        <v>37.222</v>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2124" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C2124" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2124" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2124" s="3">
+        <v>37.376</v>
+      </c>
+      <c r="F2124" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2124" s="3">
+        <v>37.376</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2125" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C2125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2125" s="3">
+        <v>37.53</v>
+      </c>
+      <c r="F2125" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2125" s="3">
+        <v>37.53</v>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2126" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C2126" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2126" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2126" s="3">
+        <v>37.376</v>
+      </c>
+      <c r="F2126" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2126" s="3">
+        <v>37.376</v>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2127" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C2127" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2127" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2127" s="3">
+        <v>37.939</v>
+      </c>
+      <c r="F2127" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2127" s="3">
+        <v>37.939</v>
+      </c>
+    </row>
+    <row r="2128">
+      <c r="A2128" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2128" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C2128" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2128" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2128" s="3">
+        <v>37.99</v>
+      </c>
+      <c r="F2128" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2128" s="3">
+        <v>37.99</v>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2129" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C2129" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2129" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2129" s="3">
+        <v>37.325</v>
+      </c>
+      <c r="F2129" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2129" s="3">
+        <v>37.325</v>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2130" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C2130" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2130" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2130" s="3">
+        <v>37.274</v>
+      </c>
+      <c r="F2130" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2130" s="3">
+        <v>37.274</v>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2131" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C2131" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2131" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2131" s="3">
+        <v>37.274</v>
+      </c>
+      <c r="F2131" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2131" s="3">
+        <v>37.274</v>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2132" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C2132" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2132" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2132" s="3">
+        <v>37.274</v>
+      </c>
+      <c r="F2132" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2132" s="3">
+        <v>37.274</v>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2133" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C2133" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2133" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2133" s="3">
+        <v>37.171</v>
+      </c>
+      <c r="F2133" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2133" s="3">
+        <v>37.171</v>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2134" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C2134" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2134" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2134" s="3">
+        <v>37.325</v>
+      </c>
+      <c r="F2134" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2134" s="3">
+        <v>37.325</v>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2135" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C2135" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2135" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2135" s="3">
+        <v>37.274</v>
+      </c>
+      <c r="F2135" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2135" s="3">
+        <v>37.274</v>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2136" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C2136" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2136" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2136" s="3">
+        <v>37.222</v>
+      </c>
+      <c r="F2136" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2136" s="3">
+        <v>37.222</v>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2137" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C2137" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2137" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2137" s="3">
+        <v>37.581</v>
+      </c>
+      <c r="F2137" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2137" s="3">
+        <v>37.581</v>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2138" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C2138" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2138" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2138" s="3">
+        <v>37.786</v>
+      </c>
+      <c r="F2138" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2138" s="3">
+        <v>37.786</v>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2139" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C2139" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2139" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2139" s="3">
+        <v>37.325</v>
+      </c>
+      <c r="F2139" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2139" s="3">
+        <v>37.325</v>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2140" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C2140" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="D2140" s="3">
+        <v>0.23</v>
+      </c>
+      <c r="E2140" s="3">
+        <v>37.53</v>
+      </c>
+      <c r="F2140" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2140" s="3">
+        <v>37.76</v>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2141" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C2141" s="3">
+        <v>1.101</v>
+      </c>
+      <c r="D2141" s="3">
+        <v>1.101</v>
+      </c>
+      <c r="E2141" s="3">
+        <v>36.608</v>
+      </c>
+      <c r="F2141" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2141" s="3">
+        <v>37.709</v>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2142" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C2142" s="3">
+        <v>3.213</v>
+      </c>
+      <c r="D2142" s="3">
+        <v>3.213</v>
+      </c>
+      <c r="E2142" s="3">
+        <v>34.304</v>
+      </c>
+      <c r="F2142" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2142" s="3">
+        <v>37.517</v>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2143" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C2143" s="3">
+        <v>7.936</v>
+      </c>
+      <c r="D2143" s="3">
+        <v>7.936</v>
+      </c>
+      <c r="E2143" s="3">
+        <v>29.133</v>
+      </c>
+      <c r="F2143" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2143" s="3">
+        <v>37.069</v>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2144" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C2144" s="3">
+        <v>17.165</v>
+      </c>
+      <c r="D2144" s="3">
+        <v>17.165</v>
+      </c>
+      <c r="E2144" s="3">
+        <v>19.866</v>
+      </c>
+      <c r="F2144" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2144" s="3">
+        <v>37.031</v>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2145" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C2145" s="3">
+        <v>10.854</v>
+      </c>
+      <c r="D2145" s="3">
+        <v>10.854</v>
+      </c>
+      <c r="E2145" s="3">
+        <v>26.266</v>
+      </c>
+      <c r="F2145" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2145" s="3">
+        <v>37.12</v>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2146" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C2146" s="3">
+        <v>16.102</v>
+      </c>
+      <c r="D2146" s="3">
+        <v>16.051</v>
+      </c>
+      <c r="E2146" s="3">
+        <v>21.197</v>
+      </c>
+      <c r="F2146" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G2146" s="3">
+        <v>37.248</v>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2147" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C2147" s="3">
+        <v>39.654</v>
+      </c>
+      <c r="D2147" s="3">
+        <v>34.432</v>
+      </c>
+      <c r="E2147" s="3">
+        <v>3.328</v>
+      </c>
+      <c r="F2147" s="3">
+        <v>5.222</v>
+      </c>
+      <c r="G2147" s="3">
+        <v>37.76</v>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2148" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C2148" s="3">
+        <v>45.363</v>
+      </c>
+      <c r="D2148" s="3">
+        <v>35.686</v>
+      </c>
+      <c r="E2148" s="3">
+        <v>1.792</v>
+      </c>
+      <c r="F2148" s="3">
+        <v>9.677</v>
+      </c>
+      <c r="G2148" s="3">
+        <v>37.478</v>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2149" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C2149" s="3">
+        <v>60.966</v>
+      </c>
+      <c r="D2149" s="3">
+        <v>37.414</v>
+      </c>
+      <c r="E2149" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2149" s="3">
+        <v>23.552</v>
+      </c>
+      <c r="G2149" s="3">
+        <v>37.414</v>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2150" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C2150" s="3">
+        <v>53.76</v>
+      </c>
+      <c r="D2150" s="3">
+        <v>35.891</v>
+      </c>
+      <c r="E2150" s="3">
+        <v>1.331</v>
+      </c>
+      <c r="F2150" s="3">
+        <v>17.869</v>
+      </c>
+      <c r="G2150" s="3">
+        <v>37.222</v>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2151" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C2151" s="3">
+        <v>53.722</v>
+      </c>
+      <c r="D2151" s="3">
+        <v>35.239</v>
+      </c>
+      <c r="E2151" s="3">
+        <v>1.741</v>
+      </c>
+      <c r="F2151" s="3">
+        <v>18.483</v>
+      </c>
+      <c r="G2151" s="3">
+        <v>36.98</v>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2152" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C2152" s="3">
+        <v>40.474</v>
+      </c>
+      <c r="D2152" s="3">
+        <v>29.773</v>
+      </c>
+      <c r="E2152" s="3">
+        <v>7.629</v>
+      </c>
+      <c r="F2152" s="3">
+        <v>10.701</v>
+      </c>
+      <c r="G2152" s="3">
+        <v>37.402</v>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2153" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C2153" s="3">
+        <v>54.566</v>
+      </c>
+      <c r="D2153" s="3">
+        <v>37.312</v>
+      </c>
+      <c r="E2153" s="3">
+        <v>0.256</v>
+      </c>
+      <c r="F2153" s="3">
+        <v>17.254</v>
+      </c>
+      <c r="G2153" s="3">
+        <v>37.568</v>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2154" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C2154" s="3">
+        <v>69.939</v>
+      </c>
+      <c r="D2154" s="3">
+        <v>36.659</v>
+      </c>
+      <c r="E2154" s="3">
+        <v>0.87</v>
+      </c>
+      <c r="F2154" s="3">
+        <v>33.28</v>
+      </c>
+      <c r="G2154" s="3">
+        <v>37.529</v>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2155" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C2155" s="3">
+        <v>95.206</v>
+      </c>
+      <c r="D2155" s="3">
+        <v>37.913</v>
+      </c>
+      <c r="E2155" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2155" s="3">
+        <v>57.293</v>
+      </c>
+      <c r="G2155" s="3">
+        <v>37.913</v>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2156" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C2156" s="3">
+        <v>101.67</v>
+      </c>
+      <c r="D2156" s="3">
+        <v>40.384</v>
+      </c>
+      <c r="E2156" s="3">
+        <v>0.205</v>
+      </c>
+      <c r="F2156" s="3">
+        <v>61.286</v>
+      </c>
+      <c r="G2156" s="3">
+        <v>40.589</v>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2157" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C2157" s="3">
+        <v>100.326</v>
+      </c>
+      <c r="D2157" s="3">
+        <v>40.576</v>
+      </c>
+      <c r="E2157" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2157" s="3">
+        <v>59.75</v>
+      </c>
+      <c r="G2157" s="3">
+        <v>40.576</v>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2158" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C2158" s="3">
+        <v>47.68</v>
+      </c>
+      <c r="D2158" s="3">
+        <v>39.386</v>
+      </c>
+      <c r="E2158" s="3">
+        <v>0.563</v>
+      </c>
+      <c r="F2158" s="3">
+        <v>8.294</v>
+      </c>
+      <c r="G2158" s="3">
+        <v>39.949</v>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2159" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C2159" s="3">
+        <v>45.914</v>
+      </c>
+      <c r="D2159" s="3">
+        <v>39.616</v>
+      </c>
+      <c r="E2159" s="3">
+        <v>1.024</v>
+      </c>
+      <c r="F2159" s="3">
+        <v>6.298</v>
+      </c>
+      <c r="G2159" s="3">
+        <v>40.64</v>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2160" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C2160" s="3">
+        <v>52.634</v>
+      </c>
+      <c r="D2160" s="3">
+        <v>40.551</v>
+      </c>
+      <c r="E2160" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2160" s="3">
+        <v>12.083</v>
+      </c>
+      <c r="G2160" s="3">
+        <v>40.551</v>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2161" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C2161" s="3">
+        <v>70.758</v>
+      </c>
+      <c r="D2161" s="3">
+        <v>47.411</v>
+      </c>
+      <c r="E2161" s="3">
+        <v>0.666</v>
+      </c>
+      <c r="F2161" s="3">
+        <v>23.347</v>
+      </c>
+      <c r="G2161" s="3">
+        <v>48.077</v>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2162" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C2162" s="3">
+        <v>103.744</v>
+      </c>
+      <c r="D2162" s="3">
+        <v>71.027</v>
+      </c>
+      <c r="E2162" s="3">
+        <v>1.126</v>
+      </c>
+      <c r="F2162" s="3">
+        <v>32.717</v>
+      </c>
+      <c r="G2162" s="3">
+        <v>72.153</v>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2163" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C2163" s="3">
+        <v>96.23</v>
+      </c>
+      <c r="D2163" s="3">
+        <v>71.552</v>
+      </c>
+      <c r="E2163" s="3">
+        <v>1.075</v>
+      </c>
+      <c r="F2163" s="3">
+        <v>24.678</v>
+      </c>
+      <c r="G2163" s="3">
+        <v>72.627</v>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2164" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C2164" s="3">
+        <v>90.291</v>
+      </c>
+      <c r="D2164" s="3">
+        <v>67.149</v>
+      </c>
+      <c r="E2164" s="3">
+        <v>5.939</v>
+      </c>
+      <c r="F2164" s="3">
+        <v>23.142</v>
+      </c>
+      <c r="G2164" s="3">
+        <v>73.088</v>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2165" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C2165" s="3">
+        <v>81.088</v>
+      </c>
+      <c r="D2165" s="3">
+        <v>63.168</v>
+      </c>
+      <c r="E2165" s="3">
+        <v>9.011</v>
+      </c>
+      <c r="F2165" s="3">
+        <v>17.92</v>
+      </c>
+      <c r="G2165" s="3">
+        <v>72.179</v>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2166" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C2166" s="3">
+        <v>109.094</v>
+      </c>
+      <c r="D2166" s="3">
+        <v>72.435</v>
+      </c>
+      <c r="E2166" s="3">
+        <v>0.461</v>
+      </c>
+      <c r="F2166" s="3">
+        <v>36.659</v>
+      </c>
+      <c r="G2166" s="3">
+        <v>72.896</v>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2167" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C2167" s="3">
+        <v>71.642</v>
+      </c>
+      <c r="D2167" s="3">
+        <v>67.751</v>
+      </c>
+      <c r="E2167" s="3">
+        <v>5.12</v>
+      </c>
+      <c r="F2167" s="3">
+        <v>3.891</v>
+      </c>
+      <c r="G2167" s="3">
+        <v>72.871</v>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2168" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C2168" s="3">
+        <v>79.565</v>
+      </c>
+      <c r="D2168" s="3">
+        <v>69.991</v>
+      </c>
+      <c r="E2168" s="3">
+        <v>1.946</v>
+      </c>
+      <c r="F2168" s="3">
+        <v>9.574</v>
+      </c>
+      <c r="G2168" s="3">
+        <v>71.937</v>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2169" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C2169" s="3">
+        <v>50.586</v>
+      </c>
+      <c r="D2169" s="3">
+        <v>50.586</v>
+      </c>
+      <c r="E2169" s="3">
+        <v>21.709</v>
+      </c>
+      <c r="F2169" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2169" s="3">
+        <v>72.295</v>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2170" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C2170" s="3">
+        <v>20.57</v>
+      </c>
+      <c r="D2170" s="3">
+        <v>20.57</v>
+      </c>
+      <c r="E2170" s="3">
+        <v>51.046</v>
+      </c>
+      <c r="F2170" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2170" s="3">
+        <v>71.616</v>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2171" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C2171" s="3">
+        <v>32.115</v>
+      </c>
+      <c r="D2171" s="3">
+        <v>32.115</v>
+      </c>
+      <c r="E2171" s="3">
+        <v>39.475</v>
+      </c>
+      <c r="F2171" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2171" s="3">
+        <v>71.59</v>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2172" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C2172" s="3">
+        <v>60.467</v>
+      </c>
+      <c r="D2172" s="3">
+        <v>55.91</v>
+      </c>
+      <c r="E2172" s="3">
+        <v>16.179</v>
+      </c>
+      <c r="F2172" s="3">
+        <v>4.557</v>
+      </c>
+      <c r="G2172" s="3">
+        <v>72.089</v>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2173" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C2173" s="3">
+        <v>67.827</v>
+      </c>
+      <c r="D2173" s="3">
+        <v>52.774</v>
+      </c>
+      <c r="E2173" s="3">
+        <v>19.149</v>
+      </c>
+      <c r="F2173" s="3">
+        <v>15.053</v>
+      </c>
+      <c r="G2173" s="3">
+        <v>71.923</v>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2174" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C2174" s="3">
+        <v>40.422</v>
+      </c>
+      <c r="D2174" s="3">
+        <v>35.609</v>
+      </c>
+      <c r="E2174" s="3">
+        <v>36.25</v>
+      </c>
+      <c r="F2174" s="3">
+        <v>4.813</v>
+      </c>
+      <c r="G2174" s="3">
+        <v>71.859</v>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2175" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C2175" s="3">
+        <v>98.842</v>
+      </c>
+      <c r="D2175" s="3">
+        <v>67.354</v>
+      </c>
+      <c r="E2175" s="3">
+        <v>4.557</v>
+      </c>
+      <c r="F2175" s="3">
+        <v>31.488</v>
+      </c>
+      <c r="G2175" s="3">
+        <v>71.911</v>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2176" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C2176" s="3">
+        <v>89.907</v>
+      </c>
+      <c r="D2176" s="3">
+        <v>63.693</v>
+      </c>
+      <c r="E2176" s="3">
+        <v>8.755</v>
+      </c>
+      <c r="F2176" s="3">
+        <v>26.214</v>
+      </c>
+      <c r="G2176" s="3">
+        <v>72.448</v>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2177" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C2177" s="3">
+        <v>58.342</v>
+      </c>
+      <c r="D2177" s="3">
+        <v>49.126</v>
+      </c>
+      <c r="E2177" s="3">
+        <v>23.091</v>
+      </c>
+      <c r="F2177" s="3">
+        <v>9.216</v>
+      </c>
+      <c r="G2177" s="3">
+        <v>72.217</v>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2178" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C2178" s="3">
+        <v>73.523</v>
+      </c>
+      <c r="D2178" s="3">
+        <v>58.419</v>
+      </c>
+      <c r="E2178" s="3">
+        <v>13.875</v>
+      </c>
+      <c r="F2178" s="3">
+        <v>15.104</v>
+      </c>
+      <c r="G2178" s="3">
+        <v>72.294</v>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2179" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C2179" s="3">
+        <v>96.947</v>
+      </c>
+      <c r="D2179" s="3">
+        <v>72.678</v>
+      </c>
+      <c r="E2179" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2179" s="3">
+        <v>24.269</v>
+      </c>
+      <c r="G2179" s="3">
+        <v>72.678</v>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2180" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C2180" s="3">
+        <v>59.533</v>
+      </c>
+      <c r="D2180" s="3">
+        <v>51.239</v>
+      </c>
+      <c r="E2180" s="3">
+        <v>21.248</v>
+      </c>
+      <c r="F2180" s="3">
+        <v>8.294</v>
+      </c>
+      <c r="G2180" s="3">
+        <v>72.487</v>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2181" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C2181" s="3">
+        <v>76.928</v>
+      </c>
+      <c r="D2181" s="3">
+        <v>71.347</v>
+      </c>
+      <c r="E2181" s="3">
+        <v>0.922</v>
+      </c>
+      <c r="F2181" s="3">
+        <v>5.581</v>
+      </c>
+      <c r="G2181" s="3">
+        <v>72.269</v>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2182" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C2182" s="3">
+        <v>58.65</v>
+      </c>
+      <c r="D2182" s="3">
+        <v>55.271</v>
+      </c>
+      <c r="E2182" s="3">
+        <v>16.742</v>
+      </c>
+      <c r="F2182" s="3">
+        <v>3.379</v>
+      </c>
+      <c r="G2182" s="3">
+        <v>72.013</v>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2183" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C2183" s="3">
+        <v>69.542</v>
+      </c>
+      <c r="D2183" s="3">
+        <v>67.904</v>
+      </c>
+      <c r="E2183" s="3">
+        <v>4.557</v>
+      </c>
+      <c r="F2183" s="3">
+        <v>1.638</v>
+      </c>
+      <c r="G2183" s="3">
+        <v>72.461</v>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="A2184" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2184" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C2184" s="3">
+        <v>52.352</v>
+      </c>
+      <c r="D2184" s="3">
+        <v>52.352</v>
+      </c>
+      <c r="E2184" s="3">
+        <v>20.275</v>
+      </c>
+      <c r="F2184" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2184" s="3">
+        <v>72.627</v>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="A2185" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2185" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C2185" s="3">
+        <v>38.541</v>
+      </c>
+      <c r="D2185" s="3">
+        <v>38.541</v>
+      </c>
+      <c r="E2185" s="3">
+        <v>33.536</v>
+      </c>
+      <c r="F2185" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2185" s="3">
+        <v>72.077</v>
+      </c>
+    </row>
+    <row r="2186">
+      <c r="A2186" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2186" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C2186" s="3">
+        <v>29.094</v>
+      </c>
+      <c r="D2186" s="3">
+        <v>29.094</v>
+      </c>
+      <c r="E2186" s="3">
+        <v>42.445</v>
+      </c>
+      <c r="F2186" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2186" s="3">
+        <v>71.539</v>
+      </c>
+    </row>
+    <row r="2187">
+      <c r="A2187" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2187" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C2187" s="3">
+        <v>20.454</v>
+      </c>
+      <c r="D2187" s="3">
+        <v>20.454</v>
+      </c>
+      <c r="E2187" s="3">
+        <v>51.098</v>
+      </c>
+      <c r="F2187" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2187" s="3">
+        <v>71.552</v>
+      </c>
+    </row>
+    <row r="2188">
+      <c r="A2188" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2188" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C2188" s="3">
+        <v>13.094</v>
+      </c>
+      <c r="D2188" s="3">
+        <v>13.094</v>
+      </c>
+      <c r="E2188" s="3">
+        <v>58.778</v>
+      </c>
+      <c r="F2188" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2188" s="3">
+        <v>71.872</v>
+      </c>
+    </row>
+    <row r="2189">
+      <c r="A2189" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2189" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C2189" s="3">
+        <v>5.158</v>
+      </c>
+      <c r="D2189" s="3">
+        <v>5.158</v>
+      </c>
+      <c r="E2189" s="3">
+        <v>66.867</v>
+      </c>
+      <c r="F2189" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2189" s="3">
+        <v>72.025</v>
+      </c>
+    </row>
+    <row r="2190">
+      <c r="A2190" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2190" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C2190" s="3">
+        <v>1.331</v>
+      </c>
+      <c r="D2190" s="3">
+        <v>1.331</v>
+      </c>
+      <c r="E2190" s="3">
+        <v>70.912</v>
+      </c>
+      <c r="F2190" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2190" s="3">
+        <v>72.243</v>
+      </c>
+    </row>
+    <row r="2191">
+      <c r="A2191" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2191" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C2191" s="3">
+        <v>0.397</v>
+      </c>
+      <c r="D2191" s="3">
+        <v>0.397</v>
+      </c>
+      <c r="E2191" s="3">
+        <v>71.578</v>
+      </c>
+      <c r="F2191" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2191" s="3">
+        <v>71.975</v>
+      </c>
+    </row>
+    <row r="2192">
+      <c r="A2192" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2192" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C2192" s="3">
+        <v>0.064</v>
+      </c>
+      <c r="D2192" s="3">
+        <v>0.064</v>
+      </c>
+      <c r="E2192" s="3">
+        <v>71.834</v>
+      </c>
+      <c r="F2192" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2192" s="3">
+        <v>71.898</v>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="A2193" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2193" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C2193" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2193" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2193" s="3">
+        <v>71.629</v>
+      </c>
+      <c r="F2193" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2193" s="3">
+        <v>71.629</v>
+      </c>
+    </row>
+    <row r="2194">
+      <c r="A2194" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2194" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C2194" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2194" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2194" s="3">
+        <v>71.68</v>
+      </c>
+      <c r="F2194" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2194" s="3">
+        <v>71.68</v>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="A2195" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2195" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C2195" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2195" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2195" s="3">
+        <v>71.526</v>
+      </c>
+      <c r="F2195" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2195" s="3">
+        <v>71.526</v>
+      </c>
+    </row>
+    <row r="2196">
+      <c r="A2196" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2196" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C2196" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2196" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2196" s="3">
+        <v>72.192</v>
+      </c>
+      <c r="F2196" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2196" s="3">
+        <v>72.192</v>
+      </c>
+    </row>
+    <row r="2197">
+      <c r="A2197" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2197" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C2197" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2197" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2197" s="3">
+        <v>72.09</v>
+      </c>
+      <c r="F2197" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2197" s="3">
+        <v>72.09</v>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="A2198" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2198" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C2198" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2198" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2198" s="3">
+        <v>72.038</v>
+      </c>
+      <c r="F2198" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2198" s="3">
+        <v>72.038</v>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="A2199" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2199" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C2199" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2199" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2199" s="3">
+        <v>71.885</v>
+      </c>
+      <c r="F2199" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2199" s="3">
+        <v>71.885</v>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="A2200" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2200" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C2200" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2200" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2200" s="3">
+        <v>71.731</v>
+      </c>
+      <c r="F2200" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2200" s="3">
+        <v>71.731</v>
+      </c>
+    </row>
+    <row r="2201">
+      <c r="A2201" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2201" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C2201" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2201" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2201" s="3">
+        <v>72.038</v>
+      </c>
+      <c r="F2201" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2201" s="3">
+        <v>72.038</v>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="A2202" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2202" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C2202" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2202" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2202" s="3">
+        <v>69.12</v>
+      </c>
+      <c r="F2202" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2202" s="3">
+        <v>69.12</v>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2203" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C2203" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2203" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2203" s="3">
+        <v>69.581</v>
+      </c>
+      <c r="F2203" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2203" s="3">
+        <v>69.581</v>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2204" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C2204" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2204" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2204" s="3">
+        <v>69.939</v>
+      </c>
+      <c r="F2204" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2204" s="3">
+        <v>69.939</v>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2205" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C2205" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2205" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2205" s="3">
+        <v>69.222</v>
+      </c>
+      <c r="F2205" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2205" s="3">
+        <v>69.222</v>
+      </c>
+    </row>
+    <row r="2206">
+      <c r="A2206" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2206" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C2206" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2206" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2206" s="3">
+        <v>69.018</v>
+      </c>
+      <c r="F2206" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2206" s="3">
+        <v>69.018</v>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2207" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C2207" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2207" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2207" s="3">
+        <v>68.506</v>
+      </c>
+      <c r="F2207" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2207" s="3">
+        <v>68.506</v>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2208" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C2208" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2208" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2208" s="3">
+        <v>68.608</v>
+      </c>
+      <c r="F2208" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2208" s="3">
+        <v>68.608</v>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="A2209" s="2">
+        <v>46318</v>
+      </c>
+      <c r="B2209" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C2209" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2209" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2209" s="3">
+        <v>69.274</v>
+      </c>
+      <c r="F2209" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2209" s="3">
+        <v>69.274</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2113"/>
+  <autoFilter ref="A1:G2209"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -694,45 +694,69 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B28" s="4">
+        <v>3487.7</v>
+      </c>
+      <c r="C28" s="4">
+        <v>861.8</v>
+      </c>
+      <c r="D28" s="4">
+        <v>2354.9</v>
+      </c>
+      <c r="E28" s="4">
+        <v>2625.9</v>
+      </c>
+      <c r="F28" s="4">
+        <v>3216.8</v>
+      </c>
+      <c r="G28" s="5">
+        <f>IF(F28&gt;0,C28/F28,"")</f>
+        <v>0.2679</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B28" s="7">
-        <f>SUM(B5:B27)</f>
-        <v>52164.2</v>
-      </c>
-      <c r="C28" s="7">
-        <f>SUM(C5:C27)</f>
-        <v>38628.9</v>
-      </c>
-      <c r="D28" s="7">
-        <f>SUM(D5:D27)</f>
-        <v>129069.8</v>
-      </c>
-      <c r="E28" s="7">
-        <f>SUM(E5:E27)</f>
-        <v>13535.5</v>
-      </c>
-      <c r="F28" s="7">
-        <f>SUM(F5:F27)</f>
-        <v>167698.8</v>
-      </c>
-      <c r="G28" s="8">
-        <f>IF(F28&gt;0,C28/F28,"")</f>
-        <v>0.2303</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B29" s="7">
+        <f>SUM(B5:B28)</f>
+        <v>55651.8</v>
+      </c>
+      <c r="C29" s="7">
+        <f>SUM(C5:C28)</f>
+        <v>39490.7</v>
+      </c>
+      <c r="D29" s="7">
+        <f>SUM(D5:D28)</f>
+        <v>131424.8</v>
+      </c>
+      <c r="E29" s="7">
+        <f>SUM(E5:E28)</f>
+        <v>16161.4</v>
+      </c>
+      <c r="F29" s="7">
+        <f>SUM(F5:F28)</f>
+        <v>170915.5</v>
+      </c>
+      <c r="G29" s="8">
+        <f>IF(F29&gt;0,C29/F29,"")</f>
+        <v>0.2311</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -55991,7 +56015,2407 @@
         <v>69.274</v>
       </c>
     </row>
+    <row r="2210">
+      <c r="A2210" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2210" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C2210" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2210" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2210" s="3">
+        <v>68.557</v>
+      </c>
+      <c r="F2210" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2210" s="3">
+        <v>68.557</v>
+      </c>
+    </row>
+    <row r="2211">
+      <c r="A2211" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2211" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C2211" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2211" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2211" s="3">
+        <v>68.813</v>
+      </c>
+      <c r="F2211" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2211" s="3">
+        <v>68.813</v>
+      </c>
+    </row>
+    <row r="2212">
+      <c r="A2212" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2212" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C2212" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2212" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2212" s="3">
+        <v>68.557</v>
+      </c>
+      <c r="F2212" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2212" s="3">
+        <v>68.557</v>
+      </c>
+    </row>
+    <row r="2213">
+      <c r="A2213" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2213" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C2213" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2213" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2213" s="3">
+        <v>68.659</v>
+      </c>
+      <c r="F2213" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2213" s="3">
+        <v>68.659</v>
+      </c>
+    </row>
+    <row r="2214">
+      <c r="A2214" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2214" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C2214" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2214" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2214" s="3">
+        <v>69.018</v>
+      </c>
+      <c r="F2214" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2214" s="3">
+        <v>69.018</v>
+      </c>
+    </row>
+    <row r="2215">
+      <c r="A2215" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2215" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C2215" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2215" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2215" s="3">
+        <v>68.506</v>
+      </c>
+      <c r="F2215" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2215" s="3">
+        <v>68.506</v>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="A2216" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2216" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C2216" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2216" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2216" s="3">
+        <v>68.71</v>
+      </c>
+      <c r="F2216" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2216" s="3">
+        <v>68.71</v>
+      </c>
+    </row>
+    <row r="2217">
+      <c r="A2217" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2217" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C2217" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2217" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2217" s="3">
+        <v>68.454</v>
+      </c>
+      <c r="F2217" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2217" s="3">
+        <v>68.454</v>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="A2218" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2218" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C2218" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2218" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2218" s="3">
+        <v>68.864</v>
+      </c>
+      <c r="F2218" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2218" s="3">
+        <v>68.864</v>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2219" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C2219" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2219" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2219" s="3">
+        <v>68.864</v>
+      </c>
+      <c r="F2219" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2219" s="3">
+        <v>68.864</v>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="A2220" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2220" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C2220" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2220" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2220" s="3">
+        <v>68.506</v>
+      </c>
+      <c r="F2220" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2220" s="3">
+        <v>68.506</v>
+      </c>
+    </row>
+    <row r="2221">
+      <c r="A2221" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2221" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C2221" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2221" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2221" s="3">
+        <v>68.659</v>
+      </c>
+      <c r="F2221" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2221" s="3">
+        <v>68.659</v>
+      </c>
+    </row>
+    <row r="2222">
+      <c r="A2222" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2222" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C2222" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2222" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2222" s="3">
+        <v>68.454</v>
+      </c>
+      <c r="F2222" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2222" s="3">
+        <v>68.454</v>
+      </c>
+    </row>
+    <row r="2223">
+      <c r="A2223" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2223" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C2223" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2223" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2223" s="3">
+        <v>68.915</v>
+      </c>
+      <c r="F2223" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2223" s="3">
+        <v>68.915</v>
+      </c>
+    </row>
+    <row r="2224">
+      <c r="A2224" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2224" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C2224" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2224" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2224" s="3">
+        <v>68.915</v>
+      </c>
+      <c r="F2224" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2224" s="3">
+        <v>68.915</v>
+      </c>
+    </row>
+    <row r="2225">
+      <c r="A2225" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2225" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C2225" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2225" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2225" s="3">
+        <v>68.403</v>
+      </c>
+      <c r="F2225" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2225" s="3">
+        <v>68.403</v>
+      </c>
+    </row>
+    <row r="2226">
+      <c r="A2226" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2226" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C2226" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2226" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2226" s="3">
+        <v>68.659</v>
+      </c>
+      <c r="F2226" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2226" s="3">
+        <v>68.659</v>
+      </c>
+    </row>
+    <row r="2227">
+      <c r="A2227" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2227" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C2227" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2227" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2227" s="3">
+        <v>68.557</v>
+      </c>
+      <c r="F2227" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2227" s="3">
+        <v>68.557</v>
+      </c>
+    </row>
+    <row r="2228">
+      <c r="A2228" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2228" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C2228" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2228" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2228" s="3">
+        <v>68.454</v>
+      </c>
+      <c r="F2228" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2228" s="3">
+        <v>68.454</v>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="A2229" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2229" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C2229" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2229" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2229" s="3">
+        <v>68.813</v>
+      </c>
+      <c r="F2229" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2229" s="3">
+        <v>68.813</v>
+      </c>
+    </row>
+    <row r="2230">
+      <c r="A2230" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2230" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C2230" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2230" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2230" s="3">
+        <v>68.506</v>
+      </c>
+      <c r="F2230" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2230" s="3">
+        <v>68.506</v>
+      </c>
+    </row>
+    <row r="2231">
+      <c r="A2231" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2231" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C2231" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2231" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2231" s="3">
+        <v>68.506</v>
+      </c>
+      <c r="F2231" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2231" s="3">
+        <v>68.506</v>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="A2232" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2232" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C2232" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2232" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2232" s="3">
+        <v>68.915</v>
+      </c>
+      <c r="F2232" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2232" s="3">
+        <v>68.915</v>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="A2233" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2233" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C2233" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2233" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2233" s="3">
+        <v>69.069</v>
+      </c>
+      <c r="F2233" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2233" s="3">
+        <v>69.069</v>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="A2234" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2234" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C2234" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2234" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2234" s="3">
+        <v>68.71</v>
+      </c>
+      <c r="F2234" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2234" s="3">
+        <v>68.71</v>
+      </c>
+    </row>
+    <row r="2235">
+      <c r="A2235" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2235" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C2235" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2235" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2235" s="3">
+        <v>68.915</v>
+      </c>
+      <c r="F2235" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2235" s="3">
+        <v>68.915</v>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="A2236" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2236" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C2236" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="D2236" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="E2236" s="3">
+        <v>69.581</v>
+      </c>
+      <c r="F2236" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2236" s="3">
+        <v>69.632</v>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2237" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C2237" s="3">
+        <v>1.011</v>
+      </c>
+      <c r="D2237" s="3">
+        <v>1.011</v>
+      </c>
+      <c r="E2237" s="3">
+        <v>68.25</v>
+      </c>
+      <c r="F2237" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2237" s="3">
+        <v>69.261</v>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2238" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C2238" s="3">
+        <v>2.624</v>
+      </c>
+      <c r="D2238" s="3">
+        <v>2.624</v>
+      </c>
+      <c r="E2238" s="3">
+        <v>66.202</v>
+      </c>
+      <c r="F2238" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2238" s="3">
+        <v>68.826</v>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="A2239" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2239" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C2239" s="3">
+        <v>4.723</v>
+      </c>
+      <c r="D2239" s="3">
+        <v>4.723</v>
+      </c>
+      <c r="E2239" s="3">
+        <v>64.307</v>
+      </c>
+      <c r="F2239" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2239" s="3">
+        <v>69.03</v>
+      </c>
+    </row>
+    <row r="2240">
+      <c r="A2240" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2240" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C2240" s="3">
+        <v>17.28</v>
+      </c>
+      <c r="D2240" s="3">
+        <v>17.28</v>
+      </c>
+      <c r="E2240" s="3">
+        <v>51.149</v>
+      </c>
+      <c r="F2240" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2240" s="3">
+        <v>68.429</v>
+      </c>
+    </row>
+    <row r="2241">
+      <c r="A2241" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2241" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C2241" s="3">
+        <v>19.93</v>
+      </c>
+      <c r="D2241" s="3">
+        <v>19.93</v>
+      </c>
+      <c r="E2241" s="3">
+        <v>49.101</v>
+      </c>
+      <c r="F2241" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2241" s="3">
+        <v>69.031</v>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="A2242" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2242" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C2242" s="3">
+        <v>34.662</v>
+      </c>
+      <c r="D2242" s="3">
+        <v>34.662</v>
+      </c>
+      <c r="E2242" s="3">
+        <v>34.355</v>
+      </c>
+      <c r="F2242" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2242" s="3">
+        <v>69.017</v>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="A2243" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2243" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C2243" s="3">
+        <v>40.934</v>
+      </c>
+      <c r="D2243" s="3">
+        <v>40.934</v>
+      </c>
+      <c r="E2243" s="3">
+        <v>28.109</v>
+      </c>
+      <c r="F2243" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2243" s="3">
+        <v>69.043</v>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="A2244" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2244" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C2244" s="3">
+        <v>55.245</v>
+      </c>
+      <c r="D2244" s="3">
+        <v>55.245</v>
+      </c>
+      <c r="E2244" s="3">
+        <v>14.746</v>
+      </c>
+      <c r="F2244" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2244" s="3">
+        <v>69.991</v>
+      </c>
+    </row>
+    <row r="2245">
+      <c r="A2245" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2245" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C2245" s="3">
+        <v>58.739</v>
+      </c>
+      <c r="D2245" s="3">
+        <v>58.739</v>
+      </c>
+      <c r="E2245" s="3">
+        <v>11.264</v>
+      </c>
+      <c r="F2245" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2245" s="3">
+        <v>70.003</v>
+      </c>
+    </row>
+    <row r="2246">
+      <c r="A2246" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2246" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C2246" s="3">
+        <v>67.136</v>
+      </c>
+      <c r="D2246" s="3">
+        <v>66.266</v>
+      </c>
+      <c r="E2246" s="3">
+        <v>3.379</v>
+      </c>
+      <c r="F2246" s="3">
+        <v>0.87</v>
+      </c>
+      <c r="G2246" s="3">
+        <v>69.645</v>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="A2247" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2247" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C2247" s="3">
+        <v>75.123</v>
+      </c>
+      <c r="D2247" s="3">
+        <v>69.235</v>
+      </c>
+      <c r="E2247" s="3">
+        <v>0.307</v>
+      </c>
+      <c r="F2247" s="3">
+        <v>5.888</v>
+      </c>
+      <c r="G2247" s="3">
+        <v>69.542</v>
+      </c>
+    </row>
+    <row r="2248">
+      <c r="A2248" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2248" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C2248" s="3">
+        <v>70.822</v>
+      </c>
+      <c r="D2248" s="3">
+        <v>48.55</v>
+      </c>
+      <c r="E2248" s="3">
+        <v>1.075</v>
+      </c>
+      <c r="F2248" s="3">
+        <v>22.272</v>
+      </c>
+      <c r="G2248" s="3">
+        <v>49.625</v>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="A2249" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2249" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C2249" s="3">
+        <v>55.987</v>
+      </c>
+      <c r="D2249" s="3">
+        <v>33.766</v>
+      </c>
+      <c r="E2249" s="3">
+        <v>2.202</v>
+      </c>
+      <c r="F2249" s="3">
+        <v>22.221</v>
+      </c>
+      <c r="G2249" s="3">
+        <v>35.968</v>
+      </c>
+    </row>
+    <row r="2250">
+      <c r="A2250" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2250" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C2250" s="3">
+        <v>68.826</v>
+      </c>
+      <c r="D2250" s="3">
+        <v>36.519</v>
+      </c>
+      <c r="E2250" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2250" s="3">
+        <v>32.307</v>
+      </c>
+      <c r="G2250" s="3">
+        <v>36.519</v>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="A2251" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2251" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C2251" s="3">
+        <v>82.842</v>
+      </c>
+      <c r="D2251" s="3">
+        <v>38.298</v>
+      </c>
+      <c r="E2251" s="3">
+        <v>0.256</v>
+      </c>
+      <c r="F2251" s="3">
+        <v>44.544</v>
+      </c>
+      <c r="G2251" s="3">
+        <v>38.554</v>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2252" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C2252" s="3">
+        <v>61.146</v>
+      </c>
+      <c r="D2252" s="3">
+        <v>38.362</v>
+      </c>
+      <c r="E2252" s="3">
+        <v>0.154</v>
+      </c>
+      <c r="F2252" s="3">
+        <v>22.784</v>
+      </c>
+      <c r="G2252" s="3">
+        <v>38.516</v>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2253" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C2253" s="3">
+        <v>103.322</v>
+      </c>
+      <c r="D2253" s="3">
+        <v>39.322</v>
+      </c>
+      <c r="E2253" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2253" s="3">
+        <v>64.0</v>
+      </c>
+      <c r="G2253" s="3">
+        <v>39.322</v>
+      </c>
+    </row>
+    <row r="2254">
+      <c r="A2254" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2254" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C2254" s="3">
+        <v>107.994</v>
+      </c>
+      <c r="D2254" s="3">
+        <v>29.658</v>
+      </c>
+      <c r="E2254" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2254" s="3">
+        <v>78.336</v>
+      </c>
+      <c r="G2254" s="3">
+        <v>29.658</v>
+      </c>
+    </row>
+    <row r="2255">
+      <c r="A2255" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2255" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C2255" s="3">
+        <v>106.586</v>
+      </c>
+      <c r="D2255" s="3">
+        <v>7.924</v>
+      </c>
+      <c r="E2255" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2255" s="3">
+        <v>98.662</v>
+      </c>
+      <c r="G2255" s="3">
+        <v>7.924</v>
+      </c>
+    </row>
+    <row r="2256">
+      <c r="A2256" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2256" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C2256" s="3">
+        <v>108.006</v>
+      </c>
+      <c r="D2256" s="3">
+        <v>7.756</v>
+      </c>
+      <c r="E2256" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2256" s="3">
+        <v>100.25</v>
+      </c>
+      <c r="G2256" s="3">
+        <v>7.756</v>
+      </c>
+    </row>
+    <row r="2257">
+      <c r="A2257" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2257" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C2257" s="3">
+        <v>104.806</v>
+      </c>
+      <c r="D2257" s="3">
+        <v>7.628</v>
+      </c>
+      <c r="E2257" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2257" s="3">
+        <v>97.178</v>
+      </c>
+      <c r="G2257" s="3">
+        <v>7.628</v>
+      </c>
+    </row>
+    <row r="2258">
+      <c r="A2258" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2258" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C2258" s="3">
+        <v>106.112</v>
+      </c>
+      <c r="D2258" s="3">
+        <v>7.757</v>
+      </c>
+      <c r="E2258" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2258" s="3">
+        <v>98.355</v>
+      </c>
+      <c r="G2258" s="3">
+        <v>7.757</v>
+      </c>
+    </row>
+    <row r="2259">
+      <c r="A2259" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2259" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C2259" s="3">
+        <v>109.197</v>
+      </c>
+      <c r="D2259" s="3">
+        <v>7.309</v>
+      </c>
+      <c r="E2259" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2259" s="3">
+        <v>101.888</v>
+      </c>
+      <c r="G2259" s="3">
+        <v>7.309</v>
+      </c>
+    </row>
+    <row r="2260">
+      <c r="A2260" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2260" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C2260" s="3">
+        <v>108.48</v>
+      </c>
+      <c r="D2260" s="3">
+        <v>7.309</v>
+      </c>
+      <c r="E2260" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2260" s="3">
+        <v>101.171</v>
+      </c>
+      <c r="G2260" s="3">
+        <v>7.309</v>
+      </c>
+    </row>
+    <row r="2261">
+      <c r="A2261" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2261" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C2261" s="3">
+        <v>109.274</v>
+      </c>
+      <c r="D2261" s="3">
+        <v>7.898</v>
+      </c>
+      <c r="E2261" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2261" s="3">
+        <v>101.376</v>
+      </c>
+      <c r="G2261" s="3">
+        <v>7.898</v>
+      </c>
+    </row>
+    <row r="2262">
+      <c r="A2262" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2262" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C2262" s="3">
+        <v>93.837</v>
+      </c>
+      <c r="D2262" s="3">
+        <v>7.207</v>
+      </c>
+      <c r="E2262" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2262" s="3">
+        <v>86.63</v>
+      </c>
+      <c r="G2262" s="3">
+        <v>7.207</v>
+      </c>
+    </row>
+    <row r="2263">
+      <c r="A2263" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2263" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C2263" s="3">
+        <v>91.917</v>
+      </c>
+      <c r="D2263" s="3">
+        <v>7.079</v>
+      </c>
+      <c r="E2263" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2263" s="3">
+        <v>84.838</v>
+      </c>
+      <c r="G2263" s="3">
+        <v>7.079</v>
+      </c>
+    </row>
+    <row r="2264">
+      <c r="A2264" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2264" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C2264" s="3">
+        <v>106.189</v>
+      </c>
+      <c r="D2264" s="3">
+        <v>8.397</v>
+      </c>
+      <c r="E2264" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2264" s="3">
+        <v>97.792</v>
+      </c>
+      <c r="G2264" s="3">
+        <v>8.397</v>
+      </c>
+    </row>
+    <row r="2265">
+      <c r="A2265" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2265" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C2265" s="3">
+        <v>109.197</v>
+      </c>
+      <c r="D2265" s="3">
+        <v>7.821</v>
+      </c>
+      <c r="E2265" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2265" s="3">
+        <v>101.376</v>
+      </c>
+      <c r="G2265" s="3">
+        <v>7.821</v>
+      </c>
+    </row>
+    <row r="2266">
+      <c r="A2266" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2266" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C2266" s="3">
+        <v>109.12</v>
+      </c>
+      <c r="D2266" s="3">
+        <v>7.795</v>
+      </c>
+      <c r="E2266" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2266" s="3">
+        <v>101.325</v>
+      </c>
+      <c r="G2266" s="3">
+        <v>7.795</v>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2267" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C2267" s="3">
+        <v>108.966</v>
+      </c>
+      <c r="D2267" s="3">
+        <v>7.436</v>
+      </c>
+      <c r="E2267" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2267" s="3">
+        <v>101.53</v>
+      </c>
+      <c r="G2267" s="3">
+        <v>7.436</v>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="A2268" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2268" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C2268" s="3">
+        <v>109.043</v>
+      </c>
+      <c r="D2268" s="3">
+        <v>7.309</v>
+      </c>
+      <c r="E2268" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2268" s="3">
+        <v>101.734</v>
+      </c>
+      <c r="G2268" s="3">
+        <v>7.309</v>
+      </c>
+    </row>
+    <row r="2269">
+      <c r="A2269" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2269" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C2269" s="3">
+        <v>108.442</v>
+      </c>
+      <c r="D2269" s="3">
+        <v>7.22</v>
+      </c>
+      <c r="E2269" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2269" s="3">
+        <v>101.222</v>
+      </c>
+      <c r="G2269" s="3">
+        <v>7.22</v>
+      </c>
+    </row>
+    <row r="2270">
+      <c r="A2270" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2270" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C2270" s="3">
+        <v>106.88</v>
+      </c>
+      <c r="D2270" s="3">
+        <v>7.398</v>
+      </c>
+      <c r="E2270" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2270" s="3">
+        <v>99.482</v>
+      </c>
+      <c r="G2270" s="3">
+        <v>7.398</v>
+      </c>
+    </row>
+    <row r="2271">
+      <c r="A2271" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2271" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C2271" s="3">
+        <v>104.717</v>
+      </c>
+      <c r="D2271" s="3">
+        <v>7.232</v>
+      </c>
+      <c r="E2271" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2271" s="3">
+        <v>97.485</v>
+      </c>
+      <c r="G2271" s="3">
+        <v>7.232</v>
+      </c>
+    </row>
+    <row r="2272">
+      <c r="A2272" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2272" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C2272" s="3">
+        <v>103.616</v>
+      </c>
+      <c r="D2272" s="3">
+        <v>7.206</v>
+      </c>
+      <c r="E2272" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2272" s="3">
+        <v>96.41</v>
+      </c>
+      <c r="G2272" s="3">
+        <v>7.206</v>
+      </c>
+    </row>
+    <row r="2273">
+      <c r="A2273" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2273" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C2273" s="3">
+        <v>101.709</v>
+      </c>
+      <c r="D2273" s="3">
+        <v>7.245</v>
+      </c>
+      <c r="E2273" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2273" s="3">
+        <v>94.464</v>
+      </c>
+      <c r="G2273" s="3">
+        <v>7.245</v>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="A2274" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2274" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C2274" s="3">
+        <v>96.166</v>
+      </c>
+      <c r="D2274" s="3">
+        <v>7.334</v>
+      </c>
+      <c r="E2274" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2274" s="3">
+        <v>88.832</v>
+      </c>
+      <c r="G2274" s="3">
+        <v>7.334</v>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="A2275" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2275" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C2275" s="3">
+        <v>88.154</v>
+      </c>
+      <c r="D2275" s="3">
+        <v>6.9</v>
+      </c>
+      <c r="E2275" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2275" s="3">
+        <v>81.254</v>
+      </c>
+      <c r="G2275" s="3">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="A2276" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2276" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C2276" s="3">
+        <v>69.85</v>
+      </c>
+      <c r="D2276" s="3">
+        <v>6.72</v>
+      </c>
+      <c r="E2276" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2276" s="3">
+        <v>63.13</v>
+      </c>
+      <c r="G2276" s="3">
+        <v>6.72</v>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2277" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C2277" s="3">
+        <v>74.854</v>
+      </c>
+      <c r="D2277" s="3">
+        <v>6.963</v>
+      </c>
+      <c r="E2277" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2277" s="3">
+        <v>67.891</v>
+      </c>
+      <c r="G2277" s="3">
+        <v>6.963</v>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2278" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C2278" s="3">
+        <v>60.89</v>
+      </c>
+      <c r="D2278" s="3">
+        <v>6.772</v>
+      </c>
+      <c r="E2278" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2278" s="3">
+        <v>54.118</v>
+      </c>
+      <c r="G2278" s="3">
+        <v>6.772</v>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2279" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C2279" s="3">
+        <v>52.467</v>
+      </c>
+      <c r="D2279" s="3">
+        <v>6.797</v>
+      </c>
+      <c r="E2279" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2279" s="3">
+        <v>45.67</v>
+      </c>
+      <c r="G2279" s="3">
+        <v>6.797</v>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2280" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C2280" s="3">
+        <v>30.771</v>
+      </c>
+      <c r="D2280" s="3">
+        <v>6.605</v>
+      </c>
+      <c r="E2280" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2280" s="3">
+        <v>24.166</v>
+      </c>
+      <c r="G2280" s="3">
+        <v>6.605</v>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2281" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C2281" s="3">
+        <v>27.546</v>
+      </c>
+      <c r="D2281" s="3">
+        <v>6.656</v>
+      </c>
+      <c r="E2281" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2281" s="3">
+        <v>20.89</v>
+      </c>
+      <c r="G2281" s="3">
+        <v>6.656</v>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2282" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C2282" s="3">
+        <v>17.805</v>
+      </c>
+      <c r="D2282" s="3">
+        <v>6.183</v>
+      </c>
+      <c r="E2282" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2282" s="3">
+        <v>11.622</v>
+      </c>
+      <c r="G2282" s="3">
+        <v>6.183</v>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2283" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C2283" s="3">
+        <v>14.605</v>
+      </c>
+      <c r="D2283" s="3">
+        <v>6.669</v>
+      </c>
+      <c r="E2283" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2283" s="3">
+        <v>7.936</v>
+      </c>
+      <c r="G2283" s="3">
+        <v>6.669</v>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2284" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C2284" s="3">
+        <v>10.317</v>
+      </c>
+      <c r="D2284" s="3">
+        <v>6.835</v>
+      </c>
+      <c r="E2284" s="3">
+        <v>0.102</v>
+      </c>
+      <c r="F2284" s="3">
+        <v>3.482</v>
+      </c>
+      <c r="G2284" s="3">
+        <v>6.937</v>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2285" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C2285" s="3">
+        <v>5.555</v>
+      </c>
+      <c r="D2285" s="3">
+        <v>5.094</v>
+      </c>
+      <c r="E2285" s="3">
+        <v>2.355</v>
+      </c>
+      <c r="F2285" s="3">
+        <v>0.461</v>
+      </c>
+      <c r="G2285" s="3">
+        <v>7.449</v>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2286" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C2286" s="3">
+        <v>3.686</v>
+      </c>
+      <c r="D2286" s="3">
+        <v>3.686</v>
+      </c>
+      <c r="E2286" s="3">
+        <v>3.994</v>
+      </c>
+      <c r="F2286" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2286" s="3">
+        <v>7.68</v>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2287" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C2287" s="3">
+        <v>0.461</v>
+      </c>
+      <c r="D2287" s="3">
+        <v>0.461</v>
+      </c>
+      <c r="E2287" s="3">
+        <v>6.4</v>
+      </c>
+      <c r="F2287" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2287" s="3">
+        <v>6.861</v>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2288" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C2288" s="3">
+        <v>0.038</v>
+      </c>
+      <c r="D2288" s="3">
+        <v>0.038</v>
+      </c>
+      <c r="E2288" s="3">
+        <v>6.656</v>
+      </c>
+      <c r="F2288" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2288" s="3">
+        <v>6.694</v>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2289" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C2289" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2289" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2289" s="3">
+        <v>6.912</v>
+      </c>
+      <c r="F2289" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2289" s="3">
+        <v>6.912</v>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2290" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C2290" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2290" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2290" s="3">
+        <v>6.554</v>
+      </c>
+      <c r="F2290" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2290" s="3">
+        <v>6.554</v>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2291" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C2291" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2291" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2291" s="3">
+        <v>6.298</v>
+      </c>
+      <c r="F2291" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2291" s="3">
+        <v>6.298</v>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2292" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C2292" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2292" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2292" s="3">
+        <v>6.605</v>
+      </c>
+      <c r="F2292" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2292" s="3">
+        <v>6.605</v>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2293" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C2293" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2293" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2293" s="3">
+        <v>6.605</v>
+      </c>
+      <c r="F2293" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2293" s="3">
+        <v>6.605</v>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2294" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C2294" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2294" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2294" s="3">
+        <v>6.4</v>
+      </c>
+      <c r="F2294" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2294" s="3">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2295" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C2295" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2295" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2295" s="3">
+        <v>6.758</v>
+      </c>
+      <c r="F2295" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2295" s="3">
+        <v>6.758</v>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2296" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C2296" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2296" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2296" s="3">
+        <v>6.298</v>
+      </c>
+      <c r="F2296" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2296" s="3">
+        <v>6.298</v>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2297" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C2297" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2297" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2297" s="3">
+        <v>4.096</v>
+      </c>
+      <c r="F2297" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2297" s="3">
+        <v>4.096</v>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2298" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C2298" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2298" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2298" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F2298" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2298" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2299" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C2299" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2299" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2299" s="3">
+        <v>3.482</v>
+      </c>
+      <c r="F2299" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2299" s="3">
+        <v>3.482</v>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2300" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C2300" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2300" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2300" s="3">
+        <v>3.738</v>
+      </c>
+      <c r="F2300" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2300" s="3">
+        <v>3.738</v>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2301" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C2301" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2301" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2301" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F2301" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G2301" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2302" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C2302" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2302" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2302" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="F2302" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2302" s="3">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2303" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C2303" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2303" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2303" s="3">
+        <v>3.379</v>
+      </c>
+      <c r="F2303" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2303" s="3">
+        <v>3.379</v>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="A2304" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2304" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C2304" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2304" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2304" s="3">
+        <v>3.328</v>
+      </c>
+      <c r="F2304" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2304" s="3">
+        <v>3.328</v>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" s="2">
+        <v>46319</v>
+      </c>
+      <c r="B2305" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C2305" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2305" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2305" s="3">
+        <v>3.891</v>
+      </c>
+      <c r="F2305" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2305" s="3">
+        <v>3.891</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2209"/>
+  <autoFilter ref="A1:G2305"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -718,45 +718,69 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B29" s="4">
+        <v>2834.3</v>
+      </c>
+      <c r="C29" s="4">
+        <v>303.4</v>
+      </c>
+      <c r="D29" s="4">
+        <v>212.0</v>
+      </c>
+      <c r="E29" s="4">
+        <v>2531.1</v>
+      </c>
+      <c r="F29" s="4">
+        <v>515.5</v>
+      </c>
+      <c r="G29" s="5">
+        <f>IF(F29&gt;0,C29/F29,"")</f>
+        <v>0.5887</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B29" s="7">
-        <f>SUM(B5:B28)</f>
-        <v>55651.8</v>
-      </c>
-      <c r="C29" s="7">
-        <f>SUM(C5:C28)</f>
-        <v>39490.7</v>
-      </c>
-      <c r="D29" s="7">
-        <f>SUM(D5:D28)</f>
-        <v>131424.8</v>
-      </c>
-      <c r="E29" s="7">
-        <f>SUM(E5:E28)</f>
-        <v>16161.4</v>
-      </c>
-      <c r="F29" s="7">
-        <f>SUM(F5:F28)</f>
-        <v>170915.5</v>
-      </c>
-      <c r="G29" s="8">
-        <f>IF(F29&gt;0,C29/F29,"")</f>
-        <v>0.2311</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B30" s="7">
+        <f>SUM(B5:B29)</f>
+        <v>58486.1</v>
+      </c>
+      <c r="C30" s="7">
+        <f>SUM(C5:C29)</f>
+        <v>39794.2</v>
+      </c>
+      <c r="D30" s="7">
+        <f>SUM(D5:D29)</f>
+        <v>131636.8</v>
+      </c>
+      <c r="E30" s="7">
+        <f>SUM(E5:E29)</f>
+        <v>18692.5</v>
+      </c>
+      <c r="F30" s="7">
+        <f>SUM(F5:F29)</f>
+        <v>171431.0</v>
+      </c>
+      <c r="G30" s="8">
+        <f>IF(F30&gt;0,C30/F30,"")</f>
+        <v>0.2321</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -58415,7 +58439,2407 @@
         <v>3.891</v>
       </c>
     </row>
+    <row r="2306">
+      <c r="A2306" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2306" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C2306" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2306" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2306" s="3">
+        <v>3.328</v>
+      </c>
+      <c r="F2306" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2306" s="3">
+        <v>3.328</v>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2307" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C2307" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2307" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2307" s="3">
+        <v>3.533</v>
+      </c>
+      <c r="F2307" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2307" s="3">
+        <v>3.533</v>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2308" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C2308" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2308" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2308" s="3">
+        <v>3.482</v>
+      </c>
+      <c r="F2308" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2308" s="3">
+        <v>3.482</v>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2309" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C2309" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2309" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2309" s="3">
+        <v>3.584</v>
+      </c>
+      <c r="F2309" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2309" s="3">
+        <v>3.584</v>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2310" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C2310" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2310" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2310" s="3">
+        <v>3.379</v>
+      </c>
+      <c r="F2310" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2310" s="3">
+        <v>3.379</v>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2311" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C2311" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2311" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2311" s="3">
+        <v>3.328</v>
+      </c>
+      <c r="F2311" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2311" s="3">
+        <v>3.328</v>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2312" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C2312" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2312" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2312" s="3">
+        <v>3.738</v>
+      </c>
+      <c r="F2312" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2312" s="3">
+        <v>3.738</v>
+      </c>
+    </row>
+    <row r="2313">
+      <c r="A2313" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2313" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C2313" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2313" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2313" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F2313" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2313" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="2314">
+      <c r="A2314" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2314" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C2314" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2314" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2314" s="3">
+        <v>3.328</v>
+      </c>
+      <c r="F2314" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2314" s="3">
+        <v>3.328</v>
+      </c>
+    </row>
+    <row r="2315">
+      <c r="A2315" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2315" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C2315" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2315" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2315" s="3">
+        <v>3.328</v>
+      </c>
+      <c r="F2315" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2315" s="3">
+        <v>3.328</v>
+      </c>
+    </row>
+    <row r="2316">
+      <c r="A2316" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2316" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C2316" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2316" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2316" s="3">
+        <v>3.533</v>
+      </c>
+      <c r="F2316" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2316" s="3">
+        <v>3.533</v>
+      </c>
+    </row>
+    <row r="2317">
+      <c r="A2317" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2317" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C2317" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2317" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2317" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="F2317" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2317" s="3">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="2318">
+      <c r="A2318" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2318" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C2318" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2318" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2318" s="3">
+        <v>3.686</v>
+      </c>
+      <c r="F2318" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G2318" s="3">
+        <v>3.686</v>
+      </c>
+    </row>
+    <row r="2319">
+      <c r="A2319" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2319" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C2319" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2319" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2319" s="3">
+        <v>3.379</v>
+      </c>
+      <c r="F2319" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2319" s="3">
+        <v>3.379</v>
+      </c>
+    </row>
+    <row r="2320">
+      <c r="A2320" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2320" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C2320" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2320" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2320" s="3">
+        <v>3.482</v>
+      </c>
+      <c r="F2320" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G2320" s="3">
+        <v>3.482</v>
+      </c>
+    </row>
+    <row r="2321">
+      <c r="A2321" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2321" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C2321" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2321" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2321" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F2321" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2321" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="2322">
+      <c r="A2322" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2322" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C2322" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2322" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2322" s="3">
+        <v>3.328</v>
+      </c>
+      <c r="F2322" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2322" s="3">
+        <v>3.328</v>
+      </c>
+    </row>
+    <row r="2323">
+      <c r="A2323" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2323" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C2323" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2323" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2323" s="3">
+        <v>3.328</v>
+      </c>
+      <c r="F2323" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G2323" s="3">
+        <v>3.328</v>
+      </c>
+    </row>
+    <row r="2324">
+      <c r="A2324" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2324" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C2324" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2324" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2324" s="3">
+        <v>3.994</v>
+      </c>
+      <c r="F2324" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2324" s="3">
+        <v>3.994</v>
+      </c>
+    </row>
+    <row r="2325">
+      <c r="A2325" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2325" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C2325" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2325" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2325" s="3">
+        <v>4.506</v>
+      </c>
+      <c r="F2325" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2325" s="3">
+        <v>4.506</v>
+      </c>
+    </row>
+    <row r="2326">
+      <c r="A2326" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2326" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C2326" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2326" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2326" s="3">
+        <v>4.045</v>
+      </c>
+      <c r="F2326" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2326" s="3">
+        <v>4.045</v>
+      </c>
+    </row>
+    <row r="2327">
+      <c r="A2327" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2327" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C2327" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2327" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2327" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F2327" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2327" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="2328">
+      <c r="A2328" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2328" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C2328" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2328" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2328" s="3">
+        <v>3.635</v>
+      </c>
+      <c r="F2328" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2328" s="3">
+        <v>3.635</v>
+      </c>
+    </row>
+    <row r="2329">
+      <c r="A2329" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2329" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C2329" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2329" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2329" s="3">
+        <v>3.686</v>
+      </c>
+      <c r="F2329" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2329" s="3">
+        <v>3.686</v>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="A2330" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2330" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C2330" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2330" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2330" s="3">
+        <v>3.686</v>
+      </c>
+      <c r="F2330" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2330" s="3">
+        <v>3.686</v>
+      </c>
+    </row>
+    <row r="2331">
+      <c r="A2331" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2331" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C2331" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="D2331" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="E2331" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F2331" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2331" s="3">
+        <v>3.443</v>
+      </c>
+    </row>
+    <row r="2332">
+      <c r="A2332" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2332" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C2332" s="3">
+        <v>0.256</v>
+      </c>
+      <c r="D2332" s="3">
+        <v>0.205</v>
+      </c>
+      <c r="E2332" s="3">
+        <v>3.328</v>
+      </c>
+      <c r="F2332" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G2332" s="3">
+        <v>3.533</v>
+      </c>
+    </row>
+    <row r="2333">
+      <c r="A2333" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2333" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C2333" s="3">
+        <v>0.819</v>
+      </c>
+      <c r="D2333" s="3">
+        <v>0.512</v>
+      </c>
+      <c r="E2333" s="3">
+        <v>2.816</v>
+      </c>
+      <c r="F2333" s="3">
+        <v>0.307</v>
+      </c>
+      <c r="G2333" s="3">
+        <v>3.328</v>
+      </c>
+    </row>
+    <row r="2334">
+      <c r="A2334" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2334" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C2334" s="3">
+        <v>2.112</v>
+      </c>
+      <c r="D2334" s="3">
+        <v>1.549</v>
+      </c>
+      <c r="E2334" s="3">
+        <v>1.997</v>
+      </c>
+      <c r="F2334" s="3">
+        <v>0.563</v>
+      </c>
+      <c r="G2334" s="3">
+        <v>3.546</v>
+      </c>
+    </row>
+    <row r="2335">
+      <c r="A2335" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2335" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C2335" s="3">
+        <v>7.027</v>
+      </c>
+      <c r="D2335" s="3">
+        <v>3.955</v>
+      </c>
+      <c r="E2335" s="3">
+        <v>0.256</v>
+      </c>
+      <c r="F2335" s="3">
+        <v>3.072</v>
+      </c>
+      <c r="G2335" s="3">
+        <v>4.211</v>
+      </c>
+    </row>
+    <row r="2336">
+      <c r="A2336" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2336" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C2336" s="3">
+        <v>13.85</v>
+      </c>
+      <c r="D2336" s="3">
+        <v>3.712</v>
+      </c>
+      <c r="E2336" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2336" s="3">
+        <v>10.138</v>
+      </c>
+      <c r="G2336" s="3">
+        <v>3.712</v>
+      </c>
+    </row>
+    <row r="2337">
+      <c r="A2337" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2337" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C2337" s="3">
+        <v>22.182</v>
+      </c>
+      <c r="D2337" s="3">
+        <v>3.289</v>
+      </c>
+      <c r="E2337" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2337" s="3">
+        <v>18.893</v>
+      </c>
+      <c r="G2337" s="3">
+        <v>3.289</v>
+      </c>
+    </row>
+    <row r="2338">
+      <c r="A2338" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2338" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C2338" s="3">
+        <v>31.13</v>
+      </c>
+      <c r="D2338" s="3">
+        <v>3.277</v>
+      </c>
+      <c r="E2338" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2338" s="3">
+        <v>27.853</v>
+      </c>
+      <c r="G2338" s="3">
+        <v>3.277</v>
+      </c>
+    </row>
+    <row r="2339">
+      <c r="A2339" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2339" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C2339" s="3">
+        <v>40.422</v>
+      </c>
+      <c r="D2339" s="3">
+        <v>3.66</v>
+      </c>
+      <c r="E2339" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2339" s="3">
+        <v>36.762</v>
+      </c>
+      <c r="G2339" s="3">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="2340">
+      <c r="A2340" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2340" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C2340" s="3">
+        <v>49.485</v>
+      </c>
+      <c r="D2340" s="3">
+        <v>3.917</v>
+      </c>
+      <c r="E2340" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2340" s="3">
+        <v>45.568</v>
+      </c>
+      <c r="G2340" s="3">
+        <v>3.917</v>
+      </c>
+    </row>
+    <row r="2341">
+      <c r="A2341" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2341" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C2341" s="3">
+        <v>57.997</v>
+      </c>
+      <c r="D2341" s="3">
+        <v>3.776</v>
+      </c>
+      <c r="E2341" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2341" s="3">
+        <v>54.221</v>
+      </c>
+      <c r="G2341" s="3">
+        <v>3.776</v>
+      </c>
+    </row>
+    <row r="2342">
+      <c r="A2342" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2342" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C2342" s="3">
+        <v>66.214</v>
+      </c>
+      <c r="D2342" s="3">
+        <v>4.569</v>
+      </c>
+      <c r="E2342" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2342" s="3">
+        <v>61.645</v>
+      </c>
+      <c r="G2342" s="3">
+        <v>4.569</v>
+      </c>
+    </row>
+    <row r="2343">
+      <c r="A2343" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2343" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C2343" s="3">
+        <v>74.445</v>
+      </c>
+      <c r="D2343" s="3">
+        <v>4.096</v>
+      </c>
+      <c r="E2343" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2343" s="3">
+        <v>70.349</v>
+      </c>
+      <c r="G2343" s="3">
+        <v>4.096</v>
+      </c>
+    </row>
+    <row r="2344">
+      <c r="A2344" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2344" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C2344" s="3">
+        <v>81.574</v>
+      </c>
+      <c r="D2344" s="3">
+        <v>3.904</v>
+      </c>
+      <c r="E2344" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2344" s="3">
+        <v>77.67</v>
+      </c>
+      <c r="G2344" s="3">
+        <v>3.904</v>
+      </c>
+    </row>
+    <row r="2345">
+      <c r="A2345" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2345" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C2345" s="3">
+        <v>88.115</v>
+      </c>
+      <c r="D2345" s="3">
+        <v>4.147</v>
+      </c>
+      <c r="E2345" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2345" s="3">
+        <v>83.968</v>
+      </c>
+      <c r="G2345" s="3">
+        <v>4.147</v>
+      </c>
+    </row>
+    <row r="2346">
+      <c r="A2346" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2346" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C2346" s="3">
+        <v>94.566</v>
+      </c>
+      <c r="D2346" s="3">
+        <v>5.939</v>
+      </c>
+      <c r="E2346" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2346" s="3">
+        <v>88.627</v>
+      </c>
+      <c r="G2346" s="3">
+        <v>5.939</v>
+      </c>
+    </row>
+    <row r="2347">
+      <c r="A2347" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2347" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C2347" s="3">
+        <v>103.002</v>
+      </c>
+      <c r="D2347" s="3">
+        <v>7.616</v>
+      </c>
+      <c r="E2347" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2347" s="3">
+        <v>95.386</v>
+      </c>
+      <c r="G2347" s="3">
+        <v>7.616</v>
+      </c>
+    </row>
+    <row r="2348">
+      <c r="A2348" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2348" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C2348" s="3">
+        <v>104.794</v>
+      </c>
+      <c r="D2348" s="3">
+        <v>7.719</v>
+      </c>
+      <c r="E2348" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2348" s="3">
+        <v>97.075</v>
+      </c>
+      <c r="G2348" s="3">
+        <v>7.719</v>
+      </c>
+    </row>
+    <row r="2349">
+      <c r="A2349" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2349" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C2349" s="3">
+        <v>67.674</v>
+      </c>
+      <c r="D2349" s="3">
+        <v>6.746</v>
+      </c>
+      <c r="E2349" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2349" s="3">
+        <v>60.928</v>
+      </c>
+      <c r="G2349" s="3">
+        <v>6.746</v>
+      </c>
+    </row>
+    <row r="2350">
+      <c r="A2350" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2350" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C2350" s="3">
+        <v>47.066</v>
+      </c>
+      <c r="D2350" s="3">
+        <v>6.669</v>
+      </c>
+      <c r="E2350" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2350" s="3">
+        <v>40.397</v>
+      </c>
+      <c r="G2350" s="3">
+        <v>6.669</v>
+      </c>
+    </row>
+    <row r="2351">
+      <c r="A2351" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2351" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C2351" s="3">
+        <v>63.859</v>
+      </c>
+      <c r="D2351" s="3">
+        <v>6.976</v>
+      </c>
+      <c r="E2351" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2351" s="3">
+        <v>56.883</v>
+      </c>
+      <c r="G2351" s="3">
+        <v>6.976</v>
+      </c>
+    </row>
+    <row r="2352">
+      <c r="A2352" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2352" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C2352" s="3">
+        <v>75.136</v>
+      </c>
+      <c r="D2352" s="3">
+        <v>7.45</v>
+      </c>
+      <c r="E2352" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2352" s="3">
+        <v>67.686</v>
+      </c>
+      <c r="G2352" s="3">
+        <v>7.45</v>
+      </c>
+    </row>
+    <row r="2353">
+      <c r="A2353" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2353" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C2353" s="3">
+        <v>66.355</v>
+      </c>
+      <c r="D2353" s="3">
+        <v>7.373</v>
+      </c>
+      <c r="E2353" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2353" s="3">
+        <v>58.982</v>
+      </c>
+      <c r="G2353" s="3">
+        <v>7.373</v>
+      </c>
+    </row>
+    <row r="2354">
+      <c r="A2354" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2354" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C2354" s="3">
+        <v>71.091</v>
+      </c>
+      <c r="D2354" s="3">
+        <v>7.757</v>
+      </c>
+      <c r="E2354" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2354" s="3">
+        <v>63.334</v>
+      </c>
+      <c r="G2354" s="3">
+        <v>7.757</v>
+      </c>
+    </row>
+    <row r="2355">
+      <c r="A2355" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2355" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C2355" s="3">
+        <v>91.366</v>
+      </c>
+      <c r="D2355" s="3">
+        <v>7.449</v>
+      </c>
+      <c r="E2355" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2355" s="3">
+        <v>83.917</v>
+      </c>
+      <c r="G2355" s="3">
+        <v>7.449</v>
+      </c>
+    </row>
+    <row r="2356">
+      <c r="A2356" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2356" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C2356" s="3">
+        <v>67.597</v>
+      </c>
+      <c r="D2356" s="3">
+        <v>7.283</v>
+      </c>
+      <c r="E2356" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2356" s="3">
+        <v>60.314</v>
+      </c>
+      <c r="G2356" s="3">
+        <v>7.283</v>
+      </c>
+    </row>
+    <row r="2357">
+      <c r="A2357" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2357" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C2357" s="3">
+        <v>38.771</v>
+      </c>
+      <c r="D2357" s="3">
+        <v>6.72</v>
+      </c>
+      <c r="E2357" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2357" s="3">
+        <v>32.051</v>
+      </c>
+      <c r="G2357" s="3">
+        <v>6.72</v>
+      </c>
+    </row>
+    <row r="2358">
+      <c r="A2358" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2358" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C2358" s="3">
+        <v>102.182</v>
+      </c>
+      <c r="D2358" s="3">
+        <v>7.308</v>
+      </c>
+      <c r="E2358" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2358" s="3">
+        <v>94.874</v>
+      </c>
+      <c r="G2358" s="3">
+        <v>7.308</v>
+      </c>
+    </row>
+    <row r="2359">
+      <c r="A2359" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2359" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C2359" s="3">
+        <v>76.928</v>
+      </c>
+      <c r="D2359" s="3">
+        <v>7.296</v>
+      </c>
+      <c r="E2359" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2359" s="3">
+        <v>69.632</v>
+      </c>
+      <c r="G2359" s="3">
+        <v>7.296</v>
+      </c>
+    </row>
+    <row r="2360">
+      <c r="A2360" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2360" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C2360" s="3">
+        <v>47.795</v>
+      </c>
+      <c r="D2360" s="3">
+        <v>6.937</v>
+      </c>
+      <c r="E2360" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2360" s="3">
+        <v>40.858</v>
+      </c>
+      <c r="G2360" s="3">
+        <v>6.937</v>
+      </c>
+    </row>
+    <row r="2361">
+      <c r="A2361" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2361" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C2361" s="3">
+        <v>60.352</v>
+      </c>
+      <c r="D2361" s="3">
+        <v>7.002</v>
+      </c>
+      <c r="E2361" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2361" s="3">
+        <v>53.35</v>
+      </c>
+      <c r="G2361" s="3">
+        <v>7.002</v>
+      </c>
+    </row>
+    <row r="2362">
+      <c r="A2362" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2362" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C2362" s="3">
+        <v>60.954</v>
+      </c>
+      <c r="D2362" s="3">
+        <v>6.58</v>
+      </c>
+      <c r="E2362" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2362" s="3">
+        <v>54.374</v>
+      </c>
+      <c r="G2362" s="3">
+        <v>6.58</v>
+      </c>
+    </row>
+    <row r="2363">
+      <c r="A2363" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2363" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C2363" s="3">
+        <v>74.893</v>
+      </c>
+      <c r="D2363" s="3">
+        <v>6.695</v>
+      </c>
+      <c r="E2363" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2363" s="3">
+        <v>68.198</v>
+      </c>
+      <c r="G2363" s="3">
+        <v>6.695</v>
+      </c>
+    </row>
+    <row r="2364">
+      <c r="A2364" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2364" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C2364" s="3">
+        <v>110.618</v>
+      </c>
+      <c r="D2364" s="3">
+        <v>7.962</v>
+      </c>
+      <c r="E2364" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2364" s="3">
+        <v>102.656</v>
+      </c>
+      <c r="G2364" s="3">
+        <v>7.962</v>
+      </c>
+    </row>
+    <row r="2365">
+      <c r="A2365" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2365" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C2365" s="3">
+        <v>37.491</v>
+      </c>
+      <c r="D2365" s="3">
+        <v>7.59</v>
+      </c>
+      <c r="E2365" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2365" s="3">
+        <v>29.901</v>
+      </c>
+      <c r="G2365" s="3">
+        <v>7.59</v>
+      </c>
+    </row>
+    <row r="2366">
+      <c r="A2366" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2366" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C2366" s="3">
+        <v>47.475</v>
+      </c>
+      <c r="D2366" s="3">
+        <v>7.129</v>
+      </c>
+      <c r="E2366" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2366" s="3">
+        <v>40.346</v>
+      </c>
+      <c r="G2366" s="3">
+        <v>7.129</v>
+      </c>
+    </row>
+    <row r="2367">
+      <c r="A2367" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2367" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C2367" s="3">
+        <v>41.408</v>
+      </c>
+      <c r="D2367" s="3">
+        <v>6.797</v>
+      </c>
+      <c r="E2367" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2367" s="3">
+        <v>34.611</v>
+      </c>
+      <c r="G2367" s="3">
+        <v>6.797</v>
+      </c>
+    </row>
+    <row r="2368">
+      <c r="A2368" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2368" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C2368" s="3">
+        <v>19.123</v>
+      </c>
+      <c r="D2368" s="3">
+        <v>6.323</v>
+      </c>
+      <c r="E2368" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2368" s="3">
+        <v>12.8</v>
+      </c>
+      <c r="G2368" s="3">
+        <v>6.323</v>
+      </c>
+    </row>
+    <row r="2369">
+      <c r="A2369" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2369" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C2369" s="3">
+        <v>21.786</v>
+      </c>
+      <c r="D2369" s="3">
+        <v>6.784</v>
+      </c>
+      <c r="E2369" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2369" s="3">
+        <v>15.002</v>
+      </c>
+      <c r="G2369" s="3">
+        <v>6.784</v>
+      </c>
+    </row>
+    <row r="2370">
+      <c r="A2370" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2370" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C2370" s="3">
+        <v>102.336</v>
+      </c>
+      <c r="D2370" s="3">
+        <v>7.462</v>
+      </c>
+      <c r="E2370" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2370" s="3">
+        <v>94.874</v>
+      </c>
+      <c r="G2370" s="3">
+        <v>7.462</v>
+      </c>
+    </row>
+    <row r="2371">
+      <c r="A2371" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2371" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C2371" s="3">
+        <v>91.136</v>
+      </c>
+      <c r="D2371" s="3">
+        <v>6.963</v>
+      </c>
+      <c r="E2371" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2371" s="3">
+        <v>84.173</v>
+      </c>
+      <c r="G2371" s="3">
+        <v>6.963</v>
+      </c>
+    </row>
+    <row r="2372">
+      <c r="A2372" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2372" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C2372" s="3">
+        <v>81.907</v>
+      </c>
+      <c r="D2372" s="3">
+        <v>6.899</v>
+      </c>
+      <c r="E2372" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2372" s="3">
+        <v>75.008</v>
+      </c>
+      <c r="G2372" s="3">
+        <v>6.899</v>
+      </c>
+    </row>
+    <row r="2373">
+      <c r="A2373" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2373" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C2373" s="3">
+        <v>74.701</v>
+      </c>
+      <c r="D2373" s="3">
+        <v>6.759</v>
+      </c>
+      <c r="E2373" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2373" s="3">
+        <v>67.942</v>
+      </c>
+      <c r="G2373" s="3">
+        <v>6.759</v>
+      </c>
+    </row>
+    <row r="2374">
+      <c r="A2374" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2374" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C2374" s="3">
+        <v>69.619</v>
+      </c>
+      <c r="D2374" s="3">
+        <v>6.694</v>
+      </c>
+      <c r="E2374" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2374" s="3">
+        <v>62.925</v>
+      </c>
+      <c r="G2374" s="3">
+        <v>6.694</v>
+      </c>
+    </row>
+    <row r="2375">
+      <c r="A2375" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2375" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C2375" s="3">
+        <v>68.339</v>
+      </c>
+      <c r="D2375" s="3">
+        <v>6.797</v>
+      </c>
+      <c r="E2375" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2375" s="3">
+        <v>61.542</v>
+      </c>
+      <c r="G2375" s="3">
+        <v>6.797</v>
+      </c>
+    </row>
+    <row r="2376">
+      <c r="A2376" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2376" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C2376" s="3">
+        <v>59.661</v>
+      </c>
+      <c r="D2376" s="3">
+        <v>6.823</v>
+      </c>
+      <c r="E2376" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2376" s="3">
+        <v>52.838</v>
+      </c>
+      <c r="G2376" s="3">
+        <v>6.823</v>
+      </c>
+    </row>
+    <row r="2377">
+      <c r="A2377" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2377" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C2377" s="3">
+        <v>50.931</v>
+      </c>
+      <c r="D2377" s="3">
+        <v>6.592</v>
+      </c>
+      <c r="E2377" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2377" s="3">
+        <v>44.339</v>
+      </c>
+      <c r="G2377" s="3">
+        <v>6.592</v>
+      </c>
+    </row>
+    <row r="2378">
+      <c r="A2378" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2378" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C2378" s="3">
+        <v>38.784</v>
+      </c>
+      <c r="D2378" s="3">
+        <v>6.477</v>
+      </c>
+      <c r="E2378" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2378" s="3">
+        <v>32.307</v>
+      </c>
+      <c r="G2378" s="3">
+        <v>6.477</v>
+      </c>
+    </row>
+    <row r="2379">
+      <c r="A2379" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2379" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C2379" s="3">
+        <v>29.03</v>
+      </c>
+      <c r="D2379" s="3">
+        <v>6.348</v>
+      </c>
+      <c r="E2379" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2379" s="3">
+        <v>22.682</v>
+      </c>
+      <c r="G2379" s="3">
+        <v>6.348</v>
+      </c>
+    </row>
+    <row r="2380">
+      <c r="A2380" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2380" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C2380" s="3">
+        <v>18.842</v>
+      </c>
+      <c r="D2380" s="3">
+        <v>6.247</v>
+      </c>
+      <c r="E2380" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2380" s="3">
+        <v>12.595</v>
+      </c>
+      <c r="G2380" s="3">
+        <v>6.247</v>
+      </c>
+    </row>
+    <row r="2381">
+      <c r="A2381" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2381" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C2381" s="3">
+        <v>11.52</v>
+      </c>
+      <c r="D2381" s="3">
+        <v>6.502</v>
+      </c>
+      <c r="E2381" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="F2381" s="3">
+        <v>5.018</v>
+      </c>
+      <c r="G2381" s="3">
+        <v>6.553</v>
+      </c>
+    </row>
+    <row r="2382">
+      <c r="A2382" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2382" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C2382" s="3">
+        <v>6.528</v>
+      </c>
+      <c r="D2382" s="3">
+        <v>5.299</v>
+      </c>
+      <c r="E2382" s="3">
+        <v>1.28</v>
+      </c>
+      <c r="F2382" s="3">
+        <v>1.229</v>
+      </c>
+      <c r="G2382" s="3">
+        <v>6.579</v>
+      </c>
+    </row>
+    <row r="2383">
+      <c r="A2383" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2383" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C2383" s="3">
+        <v>2.739</v>
+      </c>
+      <c r="D2383" s="3">
+        <v>2.585</v>
+      </c>
+      <c r="E2383" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="F2383" s="3">
+        <v>0.154</v>
+      </c>
+      <c r="G2383" s="3">
+        <v>6.425</v>
+      </c>
+    </row>
+    <row r="2384">
+      <c r="A2384" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2384" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C2384" s="3">
+        <v>0.294</v>
+      </c>
+      <c r="D2384" s="3">
+        <v>0.294</v>
+      </c>
+      <c r="E2384" s="3">
+        <v>6.042</v>
+      </c>
+      <c r="F2384" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2384" s="3">
+        <v>6.336</v>
+      </c>
+    </row>
+    <row r="2385">
+      <c r="A2385" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2385" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C2385" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="D2385" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="E2385" s="3">
+        <v>6.502</v>
+      </c>
+      <c r="F2385" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2385" s="3">
+        <v>6.515</v>
+      </c>
+    </row>
+    <row r="2386">
+      <c r="A2386" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2386" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C2386" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2386" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2386" s="3">
+        <v>6.502</v>
+      </c>
+      <c r="F2386" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2386" s="3">
+        <v>6.502</v>
+      </c>
+    </row>
+    <row r="2387">
+      <c r="A2387" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2387" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C2387" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2387" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2387" s="3">
+        <v>6.298</v>
+      </c>
+      <c r="F2387" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2387" s="3">
+        <v>6.298</v>
+      </c>
+    </row>
+    <row r="2388">
+      <c r="A2388" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2388" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C2388" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2388" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2388" s="3">
+        <v>6.298</v>
+      </c>
+      <c r="F2388" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2388" s="3">
+        <v>6.298</v>
+      </c>
+    </row>
+    <row r="2389">
+      <c r="A2389" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2389" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C2389" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2389" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2389" s="3">
+        <v>6.298</v>
+      </c>
+      <c r="F2389" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2389" s="3">
+        <v>6.298</v>
+      </c>
+    </row>
+    <row r="2390">
+      <c r="A2390" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2390" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C2390" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2390" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2390" s="3">
+        <v>6.605</v>
+      </c>
+      <c r="F2390" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2390" s="3">
+        <v>6.605</v>
+      </c>
+    </row>
+    <row r="2391">
+      <c r="A2391" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2391" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C2391" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2391" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2391" s="3">
+        <v>6.758</v>
+      </c>
+      <c r="F2391" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2391" s="3">
+        <v>6.758</v>
+      </c>
+    </row>
+    <row r="2392">
+      <c r="A2392" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2392" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C2392" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2392" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2392" s="3">
+        <v>6.861</v>
+      </c>
+      <c r="F2392" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2392" s="3">
+        <v>6.861</v>
+      </c>
+    </row>
+    <row r="2393">
+      <c r="A2393" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2393" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C2393" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2393" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2393" s="3">
+        <v>6.707</v>
+      </c>
+      <c r="F2393" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2393" s="3">
+        <v>6.707</v>
+      </c>
+    </row>
+    <row r="2394">
+      <c r="A2394" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2394" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C2394" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2394" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2394" s="3">
+        <v>6.656</v>
+      </c>
+      <c r="F2394" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2394" s="3">
+        <v>6.656</v>
+      </c>
+    </row>
+    <row r="2395">
+      <c r="A2395" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2395" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C2395" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2395" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2395" s="3">
+        <v>6.605</v>
+      </c>
+      <c r="F2395" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2395" s="3">
+        <v>6.605</v>
+      </c>
+    </row>
+    <row r="2396">
+      <c r="A2396" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2396" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C2396" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2396" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2396" s="3">
+        <v>6.912</v>
+      </c>
+      <c r="F2396" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2396" s="3">
+        <v>6.912</v>
+      </c>
+    </row>
+    <row r="2397">
+      <c r="A2397" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2397" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C2397" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2397" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2397" s="3">
+        <v>5.939</v>
+      </c>
+      <c r="F2397" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2397" s="3">
+        <v>5.939</v>
+      </c>
+    </row>
+    <row r="2398">
+      <c r="A2398" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2398" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C2398" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2398" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2398" s="3">
+        <v>3.789</v>
+      </c>
+      <c r="F2398" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2398" s="3">
+        <v>3.789</v>
+      </c>
+    </row>
+    <row r="2399">
+      <c r="A2399" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2399" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C2399" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2399" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2399" s="3">
+        <v>3.994</v>
+      </c>
+      <c r="F2399" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2399" s="3">
+        <v>3.994</v>
+      </c>
+    </row>
+    <row r="2400">
+      <c r="A2400" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2400" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C2400" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2400" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2400" s="3">
+        <v>3.482</v>
+      </c>
+      <c r="F2400" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G2400" s="3">
+        <v>3.482</v>
+      </c>
+    </row>
+    <row r="2401">
+      <c r="A2401" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B2401" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C2401" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2401" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2401" s="3">
+        <v>3.328</v>
+      </c>
+      <c r="F2401" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2401" s="3">
+        <v>3.328</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2305"/>
+  <autoFilter ref="A1:G2401"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -742,45 +742,69 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B30" s="4">
+        <v>2823.6</v>
+      </c>
+      <c r="C30" s="4">
+        <v>384.5</v>
+      </c>
+      <c r="D30" s="4">
+        <v>244.0</v>
+      </c>
+      <c r="E30" s="4">
+        <v>2439.1</v>
+      </c>
+      <c r="F30" s="4">
+        <v>628.5</v>
+      </c>
+      <c r="G30" s="5">
+        <f>IF(F30&gt;0,C30/F30,"")</f>
+        <v>0.6118</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B30" s="7">
-        <f>SUM(B5:B29)</f>
-        <v>58486.1</v>
-      </c>
-      <c r="C30" s="7">
-        <f>SUM(C5:C29)</f>
-        <v>39794.2</v>
-      </c>
-      <c r="D30" s="7">
-        <f>SUM(D5:D29)</f>
-        <v>131636.8</v>
-      </c>
-      <c r="E30" s="7">
-        <f>SUM(E5:E29)</f>
-        <v>18692.5</v>
-      </c>
-      <c r="F30" s="7">
-        <f>SUM(F5:F29)</f>
-        <v>171431.0</v>
-      </c>
-      <c r="G30" s="8">
-        <f>IF(F30&gt;0,C30/F30,"")</f>
-        <v>0.2321</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B31" s="7">
+        <f>SUM(B5:B30)</f>
+        <v>61309.7</v>
+      </c>
+      <c r="C31" s="7">
+        <f>SUM(C5:C30)</f>
+        <v>40178.7</v>
+      </c>
+      <c r="D31" s="7">
+        <f>SUM(D5:D30)</f>
+        <v>131880.8</v>
+      </c>
+      <c r="E31" s="7">
+        <f>SUM(E5:E30)</f>
+        <v>21131.6</v>
+      </c>
+      <c r="F31" s="7">
+        <f>SUM(F5:F30)</f>
+        <v>172059.4</v>
+      </c>
+      <c r="G31" s="8">
+        <f>IF(F31&gt;0,C31/F31,"")</f>
+        <v>0.2335</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -60839,7 +60863,2407 @@
         <v>3.328</v>
       </c>
     </row>
+    <row r="2402">
+      <c r="A2402" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2402" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C2402" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2402" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2402" s="3">
+        <v>3.328</v>
+      </c>
+      <c r="F2402" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2402" s="3">
+        <v>3.328</v>
+      </c>
+    </row>
+    <row r="2403">
+      <c r="A2403" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2403" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C2403" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2403" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2403" s="3">
+        <v>3.328</v>
+      </c>
+      <c r="F2403" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2403" s="3">
+        <v>3.328</v>
+      </c>
+    </row>
+    <row r="2404">
+      <c r="A2404" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2404" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C2404" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2404" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2404" s="3">
+        <v>3.379</v>
+      </c>
+      <c r="F2404" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2404" s="3">
+        <v>3.379</v>
+      </c>
+    </row>
+    <row r="2405">
+      <c r="A2405" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2405" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C2405" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2405" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2405" s="3">
+        <v>3.533</v>
+      </c>
+      <c r="F2405" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2405" s="3">
+        <v>3.533</v>
+      </c>
+    </row>
+    <row r="2406">
+      <c r="A2406" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2406" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C2406" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2406" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2406" s="3">
+        <v>3.482</v>
+      </c>
+      <c r="F2406" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2406" s="3">
+        <v>3.482</v>
+      </c>
+    </row>
+    <row r="2407">
+      <c r="A2407" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2407" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C2407" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2407" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2407" s="3">
+        <v>4.096</v>
+      </c>
+      <c r="F2407" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2407" s="3">
+        <v>4.096</v>
+      </c>
+    </row>
+    <row r="2408">
+      <c r="A2408" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2408" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C2408" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2408" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2408" s="3">
+        <v>4.147</v>
+      </c>
+      <c r="F2408" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2408" s="3">
+        <v>4.147</v>
+      </c>
+    </row>
+    <row r="2409">
+      <c r="A2409" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2409" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C2409" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2409" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2409" s="3">
+        <v>3.482</v>
+      </c>
+      <c r="F2409" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2409" s="3">
+        <v>3.482</v>
+      </c>
+    </row>
+    <row r="2410">
+      <c r="A2410" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2410" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C2410" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2410" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2410" s="3">
+        <v>3.738</v>
+      </c>
+      <c r="F2410" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2410" s="3">
+        <v>3.738</v>
+      </c>
+    </row>
+    <row r="2411">
+      <c r="A2411" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2411" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C2411" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2411" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2411" s="3">
+        <v>3.686</v>
+      </c>
+      <c r="F2411" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2411" s="3">
+        <v>3.686</v>
+      </c>
+    </row>
+    <row r="2412">
+      <c r="A2412" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2412" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C2412" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2412" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2412" s="3">
+        <v>3.379</v>
+      </c>
+      <c r="F2412" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2412" s="3">
+        <v>3.379</v>
+      </c>
+    </row>
+    <row r="2413">
+      <c r="A2413" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2413" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C2413" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2413" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2413" s="3">
+        <v>3.277</v>
+      </c>
+      <c r="F2413" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2413" s="3">
+        <v>3.277</v>
+      </c>
+    </row>
+    <row r="2414">
+      <c r="A2414" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2414" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C2414" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2414" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2414" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F2414" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2414" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="2415">
+      <c r="A2415" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2415" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C2415" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2415" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2415" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F2415" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G2415" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="2416">
+      <c r="A2416" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2416" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C2416" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2416" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2416" s="3">
+        <v>3.635</v>
+      </c>
+      <c r="F2416" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2416" s="3">
+        <v>3.635</v>
+      </c>
+    </row>
+    <row r="2417">
+      <c r="A2417" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2417" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C2417" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2417" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2417" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F2417" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2417" s="3">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="2418">
+      <c r="A2418" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2418" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C2418" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2418" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2418" s="3">
+        <v>3.379</v>
+      </c>
+      <c r="F2418" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2418" s="3">
+        <v>3.379</v>
+      </c>
+    </row>
+    <row r="2419">
+      <c r="A2419" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2419" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C2419" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2419" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2419" s="3">
+        <v>3.328</v>
+      </c>
+      <c r="F2419" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2419" s="3">
+        <v>3.328</v>
+      </c>
+    </row>
+    <row r="2420">
+      <c r="A2420" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2420" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C2420" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2420" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2420" s="3">
+        <v>3.379</v>
+      </c>
+      <c r="F2420" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2420" s="3">
+        <v>3.379</v>
+      </c>
+    </row>
+    <row r="2421">
+      <c r="A2421" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2421" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C2421" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2421" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2421" s="3">
+        <v>3.328</v>
+      </c>
+      <c r="F2421" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2421" s="3">
+        <v>3.328</v>
+      </c>
+    </row>
+    <row r="2422">
+      <c r="A2422" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2422" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C2422" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2422" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2422" s="3">
+        <v>4.045</v>
+      </c>
+      <c r="F2422" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2422" s="3">
+        <v>4.045</v>
+      </c>
+    </row>
+    <row r="2423">
+      <c r="A2423" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2423" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C2423" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2423" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2423" s="3">
+        <v>4.198</v>
+      </c>
+      <c r="F2423" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2423" s="3">
+        <v>4.198</v>
+      </c>
+    </row>
+    <row r="2424">
+      <c r="A2424" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2424" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C2424" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2424" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2424" s="3">
+        <v>3.379</v>
+      </c>
+      <c r="F2424" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2424" s="3">
+        <v>3.379</v>
+      </c>
+    </row>
+    <row r="2425">
+      <c r="A2425" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2425" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C2425" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2425" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2425" s="3">
+        <v>3.482</v>
+      </c>
+      <c r="F2425" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2425" s="3">
+        <v>3.482</v>
+      </c>
+    </row>
+    <row r="2426">
+      <c r="A2426" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2426" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C2426" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2426" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2426" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="F2426" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2426" s="3">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="2427">
+      <c r="A2427" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2427" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C2427" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="D2427" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="E2427" s="3">
+        <v>3.789</v>
+      </c>
+      <c r="F2427" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2427" s="3">
+        <v>3.802</v>
+      </c>
+    </row>
+    <row r="2428">
+      <c r="A2428" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2428" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C2428" s="3">
+        <v>0.371</v>
+      </c>
+      <c r="D2428" s="3">
+        <v>0.32</v>
+      </c>
+      <c r="E2428" s="3">
+        <v>3.379</v>
+      </c>
+      <c r="F2428" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G2428" s="3">
+        <v>3.699</v>
+      </c>
+    </row>
+    <row r="2429">
+      <c r="A2429" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2429" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C2429" s="3">
+        <v>1.395</v>
+      </c>
+      <c r="D2429" s="3">
+        <v>1.241</v>
+      </c>
+      <c r="E2429" s="3">
+        <v>2.714</v>
+      </c>
+      <c r="F2429" s="3">
+        <v>0.154</v>
+      </c>
+      <c r="G2429" s="3">
+        <v>3.955</v>
+      </c>
+    </row>
+    <row r="2430">
+      <c r="A2430" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2430" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C2430" s="3">
+        <v>2.56</v>
+      </c>
+      <c r="D2430" s="3">
+        <v>2.099</v>
+      </c>
+      <c r="E2430" s="3">
+        <v>1.997</v>
+      </c>
+      <c r="F2430" s="3">
+        <v>0.461</v>
+      </c>
+      <c r="G2430" s="3">
+        <v>4.096</v>
+      </c>
+    </row>
+    <row r="2431">
+      <c r="A2431" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2431" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C2431" s="3">
+        <v>5.325</v>
+      </c>
+      <c r="D2431" s="3">
+        <v>3.431</v>
+      </c>
+      <c r="E2431" s="3">
+        <v>0.461</v>
+      </c>
+      <c r="F2431" s="3">
+        <v>1.894</v>
+      </c>
+      <c r="G2431" s="3">
+        <v>3.892</v>
+      </c>
+    </row>
+    <row r="2432">
+      <c r="A2432" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2432" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C2432" s="3">
+        <v>11.226</v>
+      </c>
+      <c r="D2432" s="3">
+        <v>3.802</v>
+      </c>
+      <c r="E2432" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2432" s="3">
+        <v>7.424</v>
+      </c>
+      <c r="G2432" s="3">
+        <v>3.802</v>
+      </c>
+    </row>
+    <row r="2433">
+      <c r="A2433" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2433" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C2433" s="3">
+        <v>19.738</v>
+      </c>
+      <c r="D2433" s="3">
+        <v>4.02</v>
+      </c>
+      <c r="E2433" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2433" s="3">
+        <v>15.718</v>
+      </c>
+      <c r="G2433" s="3">
+        <v>4.02</v>
+      </c>
+    </row>
+    <row r="2434">
+      <c r="A2434" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2434" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C2434" s="3">
+        <v>18.739</v>
+      </c>
+      <c r="D2434" s="3">
+        <v>3.789</v>
+      </c>
+      <c r="E2434" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2434" s="3">
+        <v>14.95</v>
+      </c>
+      <c r="G2434" s="3">
+        <v>3.789</v>
+      </c>
+    </row>
+    <row r="2435">
+      <c r="A2435" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2435" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C2435" s="3">
+        <v>22.605</v>
+      </c>
+      <c r="D2435" s="3">
+        <v>4.429</v>
+      </c>
+      <c r="E2435" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2435" s="3">
+        <v>18.176</v>
+      </c>
+      <c r="G2435" s="3">
+        <v>4.429</v>
+      </c>
+    </row>
+    <row r="2436">
+      <c r="A2436" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2436" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C2436" s="3">
+        <v>33.754</v>
+      </c>
+      <c r="D2436" s="3">
+        <v>4.365</v>
+      </c>
+      <c r="E2436" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2436" s="3">
+        <v>29.389</v>
+      </c>
+      <c r="G2436" s="3">
+        <v>4.365</v>
+      </c>
+    </row>
+    <row r="2437">
+      <c r="A2437" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2437" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C2437" s="3">
+        <v>35.392</v>
+      </c>
+      <c r="D2437" s="3">
+        <v>11.584</v>
+      </c>
+      <c r="E2437" s="3">
+        <v>0.256</v>
+      </c>
+      <c r="F2437" s="3">
+        <v>23.808</v>
+      </c>
+      <c r="G2437" s="3">
+        <v>11.84</v>
+      </c>
+    </row>
+    <row r="2438">
+      <c r="A2438" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2438" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C2438" s="3">
+        <v>46.387</v>
+      </c>
+      <c r="D2438" s="3">
+        <v>6.656</v>
+      </c>
+      <c r="E2438" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2438" s="3">
+        <v>39.731</v>
+      </c>
+      <c r="G2438" s="3">
+        <v>6.656</v>
+      </c>
+    </row>
+    <row r="2439">
+      <c r="A2439" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2439" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C2439" s="3">
+        <v>45.338</v>
+      </c>
+      <c r="D2439" s="3">
+        <v>7.501</v>
+      </c>
+      <c r="E2439" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2439" s="3">
+        <v>37.837</v>
+      </c>
+      <c r="G2439" s="3">
+        <v>7.501</v>
+      </c>
+    </row>
+    <row r="2440">
+      <c r="A2440" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2440" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C2440" s="3">
+        <v>77.261</v>
+      </c>
+      <c r="D2440" s="3">
+        <v>8.346</v>
+      </c>
+      <c r="E2440" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2440" s="3">
+        <v>68.915</v>
+      </c>
+      <c r="G2440" s="3">
+        <v>8.346</v>
+      </c>
+    </row>
+    <row r="2441">
+      <c r="A2441" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2441" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C2441" s="3">
+        <v>55.821</v>
+      </c>
+      <c r="D2441" s="3">
+        <v>7.642</v>
+      </c>
+      <c r="E2441" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2441" s="3">
+        <v>48.179</v>
+      </c>
+      <c r="G2441" s="3">
+        <v>7.642</v>
+      </c>
+    </row>
+    <row r="2442">
+      <c r="A2442" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2442" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C2442" s="3">
+        <v>44.019</v>
+      </c>
+      <c r="D2442" s="3">
+        <v>7.667</v>
+      </c>
+      <c r="E2442" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2442" s="3">
+        <v>36.352</v>
+      </c>
+      <c r="G2442" s="3">
+        <v>7.667</v>
+      </c>
+    </row>
+    <row r="2443">
+      <c r="A2443" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2443" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C2443" s="3">
+        <v>66.432</v>
+      </c>
+      <c r="D2443" s="3">
+        <v>7.757</v>
+      </c>
+      <c r="E2443" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2443" s="3">
+        <v>58.675</v>
+      </c>
+      <c r="G2443" s="3">
+        <v>7.757</v>
+      </c>
+    </row>
+    <row r="2444">
+      <c r="A2444" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2444" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C2444" s="3">
+        <v>75.981</v>
+      </c>
+      <c r="D2444" s="3">
+        <v>8.346</v>
+      </c>
+      <c r="E2444" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2444" s="3">
+        <v>67.635</v>
+      </c>
+      <c r="G2444" s="3">
+        <v>8.346</v>
+      </c>
+    </row>
+    <row r="2445">
+      <c r="A2445" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2445" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C2445" s="3">
+        <v>77.978</v>
+      </c>
+      <c r="D2445" s="3">
+        <v>8.653</v>
+      </c>
+      <c r="E2445" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2445" s="3">
+        <v>69.325</v>
+      </c>
+      <c r="G2445" s="3">
+        <v>8.653</v>
+      </c>
+    </row>
+    <row r="2446">
+      <c r="A2446" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2446" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C2446" s="3">
+        <v>80.23</v>
+      </c>
+      <c r="D2446" s="3">
+        <v>8.857</v>
+      </c>
+      <c r="E2446" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2446" s="3">
+        <v>71.373</v>
+      </c>
+      <c r="G2446" s="3">
+        <v>8.857</v>
+      </c>
+    </row>
+    <row r="2447">
+      <c r="A2447" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2447" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C2447" s="3">
+        <v>87.386</v>
+      </c>
+      <c r="D2447" s="3">
+        <v>8.18</v>
+      </c>
+      <c r="E2447" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2447" s="3">
+        <v>79.206</v>
+      </c>
+      <c r="G2447" s="3">
+        <v>8.18</v>
+      </c>
+    </row>
+    <row r="2448">
+      <c r="A2448" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2448" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C2448" s="3">
+        <v>94.976</v>
+      </c>
+      <c r="D2448" s="3">
+        <v>8.192</v>
+      </c>
+      <c r="E2448" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2448" s="3">
+        <v>86.784</v>
+      </c>
+      <c r="G2448" s="3">
+        <v>8.192</v>
+      </c>
+    </row>
+    <row r="2449">
+      <c r="A2449" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2449" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C2449" s="3">
+        <v>83.789</v>
+      </c>
+      <c r="D2449" s="3">
+        <v>7.859</v>
+      </c>
+      <c r="E2449" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2449" s="3">
+        <v>75.93</v>
+      </c>
+      <c r="G2449" s="3">
+        <v>7.859</v>
+      </c>
+    </row>
+    <row r="2450">
+      <c r="A2450" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2450" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C2450" s="3">
+        <v>97.011</v>
+      </c>
+      <c r="D2450" s="3">
+        <v>8.281</v>
+      </c>
+      <c r="E2450" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2450" s="3">
+        <v>88.73</v>
+      </c>
+      <c r="G2450" s="3">
+        <v>8.281</v>
+      </c>
+    </row>
+    <row r="2451">
+      <c r="A2451" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2451" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C2451" s="3">
+        <v>107.648</v>
+      </c>
+      <c r="D2451" s="3">
+        <v>8.064</v>
+      </c>
+      <c r="E2451" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2451" s="3">
+        <v>99.584</v>
+      </c>
+      <c r="G2451" s="3">
+        <v>8.064</v>
+      </c>
+    </row>
+    <row r="2452">
+      <c r="A2452" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2452" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C2452" s="3">
+        <v>111.386</v>
+      </c>
+      <c r="D2452" s="3">
+        <v>8.781</v>
+      </c>
+      <c r="E2452" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2452" s="3">
+        <v>102.605</v>
+      </c>
+      <c r="G2452" s="3">
+        <v>8.781</v>
+      </c>
+    </row>
+    <row r="2453">
+      <c r="A2453" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2453" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C2453" s="3">
+        <v>111.872</v>
+      </c>
+      <c r="D2453" s="3">
+        <v>9.421</v>
+      </c>
+      <c r="E2453" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2453" s="3">
+        <v>102.451</v>
+      </c>
+      <c r="G2453" s="3">
+        <v>9.421</v>
+      </c>
+    </row>
+    <row r="2454">
+      <c r="A2454" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2454" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C2454" s="3">
+        <v>109.645</v>
+      </c>
+      <c r="D2454" s="3">
+        <v>8.423</v>
+      </c>
+      <c r="E2454" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2454" s="3">
+        <v>101.222</v>
+      </c>
+      <c r="G2454" s="3">
+        <v>8.423</v>
+      </c>
+    </row>
+    <row r="2455">
+      <c r="A2455" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2455" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C2455" s="3">
+        <v>101.453</v>
+      </c>
+      <c r="D2455" s="3">
+        <v>8.167</v>
+      </c>
+      <c r="E2455" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2455" s="3">
+        <v>93.286</v>
+      </c>
+      <c r="G2455" s="3">
+        <v>8.167</v>
+      </c>
+    </row>
+    <row r="2456">
+      <c r="A2456" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2456" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C2456" s="3">
+        <v>107.174</v>
+      </c>
+      <c r="D2456" s="3">
+        <v>8.409</v>
+      </c>
+      <c r="E2456" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2456" s="3">
+        <v>98.765</v>
+      </c>
+      <c r="G2456" s="3">
+        <v>8.409</v>
+      </c>
+    </row>
+    <row r="2457">
+      <c r="A2457" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2457" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C2457" s="3">
+        <v>109.568</v>
+      </c>
+      <c r="D2457" s="3">
+        <v>8.397</v>
+      </c>
+      <c r="E2457" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2457" s="3">
+        <v>101.171</v>
+      </c>
+      <c r="G2457" s="3">
+        <v>8.397</v>
+      </c>
+    </row>
+    <row r="2458">
+      <c r="A2458" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2458" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C2458" s="3">
+        <v>99.674</v>
+      </c>
+      <c r="D2458" s="3">
+        <v>8.333</v>
+      </c>
+      <c r="E2458" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2458" s="3">
+        <v>91.341</v>
+      </c>
+      <c r="G2458" s="3">
+        <v>8.333</v>
+      </c>
+    </row>
+    <row r="2459">
+      <c r="A2459" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2459" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C2459" s="3">
+        <v>100.48</v>
+      </c>
+      <c r="D2459" s="3">
+        <v>7.91</v>
+      </c>
+      <c r="E2459" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2459" s="3">
+        <v>92.57</v>
+      </c>
+      <c r="G2459" s="3">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="2460">
+      <c r="A2460" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2460" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C2460" s="3">
+        <v>111.834</v>
+      </c>
+      <c r="D2460" s="3">
+        <v>8.103</v>
+      </c>
+      <c r="E2460" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2460" s="3">
+        <v>103.731</v>
+      </c>
+      <c r="G2460" s="3">
+        <v>8.103</v>
+      </c>
+    </row>
+    <row r="2461">
+      <c r="A2461" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2461" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C2461" s="3">
+        <v>104.883</v>
+      </c>
+      <c r="D2461" s="3">
+        <v>20.505</v>
+      </c>
+      <c r="E2461" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2461" s="3">
+        <v>84.378</v>
+      </c>
+      <c r="G2461" s="3">
+        <v>20.505</v>
+      </c>
+    </row>
+    <row r="2462">
+      <c r="A2462" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2462" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C2462" s="3">
+        <v>78.554</v>
+      </c>
+      <c r="D2462" s="3">
+        <v>25.46</v>
+      </c>
+      <c r="E2462" s="3">
+        <v>0.205</v>
+      </c>
+      <c r="F2462" s="3">
+        <v>53.094</v>
+      </c>
+      <c r="G2462" s="3">
+        <v>25.665</v>
+      </c>
+    </row>
+    <row r="2463">
+      <c r="A2463" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2463" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C2463" s="3">
+        <v>79.642</v>
+      </c>
+      <c r="D2463" s="3">
+        <v>7.45</v>
+      </c>
+      <c r="E2463" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2463" s="3">
+        <v>72.192</v>
+      </c>
+      <c r="G2463" s="3">
+        <v>7.45</v>
+      </c>
+    </row>
+    <row r="2464">
+      <c r="A2464" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2464" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C2464" s="3">
+        <v>35.533</v>
+      </c>
+      <c r="D2464" s="3">
+        <v>7.015</v>
+      </c>
+      <c r="E2464" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2464" s="3">
+        <v>28.518</v>
+      </c>
+      <c r="G2464" s="3">
+        <v>7.015</v>
+      </c>
+    </row>
+    <row r="2465">
+      <c r="A2465" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2465" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C2465" s="3">
+        <v>61.094</v>
+      </c>
+      <c r="D2465" s="3">
+        <v>8.153</v>
+      </c>
+      <c r="E2465" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2465" s="3">
+        <v>52.941</v>
+      </c>
+      <c r="G2465" s="3">
+        <v>8.153</v>
+      </c>
+    </row>
+    <row r="2466">
+      <c r="A2466" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2466" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C2466" s="3">
+        <v>63.885</v>
+      </c>
+      <c r="D2466" s="3">
+        <v>7.975</v>
+      </c>
+      <c r="E2466" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2466" s="3">
+        <v>55.91</v>
+      </c>
+      <c r="G2466" s="3">
+        <v>7.975</v>
+      </c>
+    </row>
+    <row r="2467">
+      <c r="A2467" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2467" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C2467" s="3">
+        <v>36.403</v>
+      </c>
+      <c r="D2467" s="3">
+        <v>7.321</v>
+      </c>
+      <c r="E2467" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2467" s="3">
+        <v>29.082</v>
+      </c>
+      <c r="G2467" s="3">
+        <v>7.321</v>
+      </c>
+    </row>
+    <row r="2468">
+      <c r="A2468" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2468" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C2468" s="3">
+        <v>39.782</v>
+      </c>
+      <c r="D2468" s="3">
+        <v>8.601</v>
+      </c>
+      <c r="E2468" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2468" s="3">
+        <v>31.181</v>
+      </c>
+      <c r="G2468" s="3">
+        <v>8.601</v>
+      </c>
+    </row>
+    <row r="2469">
+      <c r="A2469" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2469" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C2469" s="3">
+        <v>33.357</v>
+      </c>
+      <c r="D2469" s="3">
+        <v>8.218</v>
+      </c>
+      <c r="E2469" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2469" s="3">
+        <v>25.139</v>
+      </c>
+      <c r="G2469" s="3">
+        <v>8.218</v>
+      </c>
+    </row>
+    <row r="2470">
+      <c r="A2470" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2470" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C2470" s="3">
+        <v>38.362</v>
+      </c>
+      <c r="D2470" s="3">
+        <v>7.693</v>
+      </c>
+      <c r="E2470" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2470" s="3">
+        <v>30.669</v>
+      </c>
+      <c r="G2470" s="3">
+        <v>7.693</v>
+      </c>
+    </row>
+    <row r="2471">
+      <c r="A2471" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2471" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C2471" s="3">
+        <v>23.718</v>
+      </c>
+      <c r="D2471" s="3">
+        <v>8.819</v>
+      </c>
+      <c r="E2471" s="3">
+        <v>1.382</v>
+      </c>
+      <c r="F2471" s="3">
+        <v>14.899</v>
+      </c>
+      <c r="G2471" s="3">
+        <v>10.201</v>
+      </c>
+    </row>
+    <row r="2472">
+      <c r="A2472" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2472" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C2472" s="3">
+        <v>21.35</v>
+      </c>
+      <c r="D2472" s="3">
+        <v>7.782</v>
+      </c>
+      <c r="E2472" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2472" s="3">
+        <v>13.568</v>
+      </c>
+      <c r="G2472" s="3">
+        <v>7.782</v>
+      </c>
+    </row>
+    <row r="2473">
+      <c r="A2473" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2473" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C2473" s="3">
+        <v>16.384</v>
+      </c>
+      <c r="D2473" s="3">
+        <v>6.912</v>
+      </c>
+      <c r="E2473" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2473" s="3">
+        <v>9.472</v>
+      </c>
+      <c r="G2473" s="3">
+        <v>6.912</v>
+      </c>
+    </row>
+    <row r="2474">
+      <c r="A2474" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2474" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C2474" s="3">
+        <v>12.813</v>
+      </c>
+      <c r="D2474" s="3">
+        <v>7.232</v>
+      </c>
+      <c r="E2474" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2474" s="3">
+        <v>5.581</v>
+      </c>
+      <c r="G2474" s="3">
+        <v>7.232</v>
+      </c>
+    </row>
+    <row r="2475">
+      <c r="A2475" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2475" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C2475" s="3">
+        <v>12.698</v>
+      </c>
+      <c r="D2475" s="3">
+        <v>7.885</v>
+      </c>
+      <c r="E2475" s="3">
+        <v>0.154</v>
+      </c>
+      <c r="F2475" s="3">
+        <v>4.813</v>
+      </c>
+      <c r="G2475" s="3">
+        <v>8.039</v>
+      </c>
+    </row>
+    <row r="2476">
+      <c r="A2476" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2476" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C2476" s="3">
+        <v>5.376</v>
+      </c>
+      <c r="D2476" s="3">
+        <v>5.171</v>
+      </c>
+      <c r="E2476" s="3">
+        <v>2.765</v>
+      </c>
+      <c r="F2476" s="3">
+        <v>0.205</v>
+      </c>
+      <c r="G2476" s="3">
+        <v>7.936</v>
+      </c>
+    </row>
+    <row r="2477">
+      <c r="A2477" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2477" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C2477" s="3">
+        <v>2.803</v>
+      </c>
+      <c r="D2477" s="3">
+        <v>2.803</v>
+      </c>
+      <c r="E2477" s="3">
+        <v>5.069</v>
+      </c>
+      <c r="F2477" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2477" s="3">
+        <v>7.872</v>
+      </c>
+    </row>
+    <row r="2478">
+      <c r="A2478" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2478" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C2478" s="3">
+        <v>1.587</v>
+      </c>
+      <c r="D2478" s="3">
+        <v>1.587</v>
+      </c>
+      <c r="E2478" s="3">
+        <v>5.786</v>
+      </c>
+      <c r="F2478" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2478" s="3">
+        <v>7.373</v>
+      </c>
+    </row>
+    <row r="2479">
+      <c r="A2479" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2479" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C2479" s="3">
+        <v>0.819</v>
+      </c>
+      <c r="D2479" s="3">
+        <v>0.819</v>
+      </c>
+      <c r="E2479" s="3">
+        <v>6.554</v>
+      </c>
+      <c r="F2479" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2479" s="3">
+        <v>7.373</v>
+      </c>
+    </row>
+    <row r="2480">
+      <c r="A2480" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2480" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C2480" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="D2480" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="E2480" s="3">
+        <v>6.707</v>
+      </c>
+      <c r="F2480" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2480" s="3">
+        <v>6.758</v>
+      </c>
+    </row>
+    <row r="2481">
+      <c r="A2481" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2481" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C2481" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2481" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2481" s="3">
+        <v>6.451</v>
+      </c>
+      <c r="F2481" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2481" s="3">
+        <v>6.451</v>
+      </c>
+    </row>
+    <row r="2482">
+      <c r="A2482" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2482" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C2482" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2482" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2482" s="3">
+        <v>6.605</v>
+      </c>
+      <c r="F2482" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2482" s="3">
+        <v>6.605</v>
+      </c>
+    </row>
+    <row r="2483">
+      <c r="A2483" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2483" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C2483" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2483" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2483" s="3">
+        <v>6.349</v>
+      </c>
+      <c r="F2483" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2483" s="3">
+        <v>6.349</v>
+      </c>
+    </row>
+    <row r="2484">
+      <c r="A2484" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2484" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C2484" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2484" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2484" s="3">
+        <v>6.4</v>
+      </c>
+      <c r="F2484" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2484" s="3">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="2485">
+      <c r="A2485" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2485" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C2485" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2485" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2485" s="3">
+        <v>6.349</v>
+      </c>
+      <c r="F2485" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2485" s="3">
+        <v>6.349</v>
+      </c>
+    </row>
+    <row r="2486">
+      <c r="A2486" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2486" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C2486" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2486" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2486" s="3">
+        <v>6.656</v>
+      </c>
+      <c r="F2486" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2486" s="3">
+        <v>6.656</v>
+      </c>
+    </row>
+    <row r="2487">
+      <c r="A2487" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2487" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C2487" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2487" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2487" s="3">
+        <v>6.912</v>
+      </c>
+      <c r="F2487" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2487" s="3">
+        <v>6.912</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2488" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C2488" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2488" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2488" s="3">
+        <v>6.758</v>
+      </c>
+      <c r="F2488" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2488" s="3">
+        <v>6.758</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2489" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C2489" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2489" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2489" s="3">
+        <v>6.861</v>
+      </c>
+      <c r="F2489" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2489" s="3">
+        <v>6.861</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2490" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C2490" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2490" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2490" s="3">
+        <v>6.656</v>
+      </c>
+      <c r="F2490" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2490" s="3">
+        <v>6.656</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2491" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C2491" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2491" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2491" s="3">
+        <v>6.349</v>
+      </c>
+      <c r="F2491" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2491" s="3">
+        <v>6.349</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2492" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C2492" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2492" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2492" s="3">
+        <v>6.554</v>
+      </c>
+      <c r="F2492" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2492" s="3">
+        <v>6.554</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2493" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C2493" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2493" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2493" s="3">
+        <v>6.81</v>
+      </c>
+      <c r="F2493" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2493" s="3">
+        <v>6.81</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2494" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C2494" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2494" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2494" s="3">
+        <v>6.81</v>
+      </c>
+      <c r="F2494" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2494" s="3">
+        <v>6.81</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2495" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C2495" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2495" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2495" s="3">
+        <v>7.117</v>
+      </c>
+      <c r="F2495" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2495" s="3">
+        <v>7.117</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2496" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C2496" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2496" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2496" s="3">
+        <v>7.373</v>
+      </c>
+      <c r="F2496" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2496" s="3">
+        <v>7.373</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="2">
+        <v>46321</v>
+      </c>
+      <c r="B2497" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C2497" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2497" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2497" s="3">
+        <v>6.605</v>
+      </c>
+      <c r="F2497" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2497" s="3">
+        <v>6.605</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2401"/>
+  <autoFilter ref="A1:G2497"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -766,45 +766,69 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B31" s="4">
+        <v>1723.3</v>
+      </c>
+      <c r="C31" s="4">
+        <v>1648.6</v>
+      </c>
+      <c r="D31" s="4">
+        <v>6819.1</v>
+      </c>
+      <c r="E31" s="4">
+        <v>74.7</v>
+      </c>
+      <c r="F31" s="4">
+        <v>8467.7</v>
+      </c>
+      <c r="G31" s="5">
+        <f>IF(F31&gt;0,C31/F31,"")</f>
+        <v>0.1947</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B31" s="7">
-        <f>SUM(B5:B30)</f>
-        <v>61309.7</v>
-      </c>
-      <c r="C31" s="7">
-        <f>SUM(C5:C30)</f>
-        <v>40178.7</v>
-      </c>
-      <c r="D31" s="7">
-        <f>SUM(D5:D30)</f>
-        <v>131880.8</v>
-      </c>
-      <c r="E31" s="7">
-        <f>SUM(E5:E30)</f>
-        <v>21131.6</v>
-      </c>
-      <c r="F31" s="7">
-        <f>SUM(F5:F30)</f>
-        <v>172059.4</v>
-      </c>
-      <c r="G31" s="8">
-        <f>IF(F31&gt;0,C31/F31,"")</f>
-        <v>0.2335</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B32" s="7">
+        <f>SUM(B5:B31)</f>
+        <v>63033.0</v>
+      </c>
+      <c r="C32" s="7">
+        <f>SUM(C5:C31)</f>
+        <v>41827.3</v>
+      </c>
+      <c r="D32" s="7">
+        <f>SUM(D5:D31)</f>
+        <v>138699.9</v>
+      </c>
+      <c r="E32" s="7">
+        <f>SUM(E5:E31)</f>
+        <v>21206.3</v>
+      </c>
+      <c r="F32" s="7">
+        <f>SUM(F5:F31)</f>
+        <v>180527.2</v>
+      </c>
+      <c r="G32" s="8">
+        <f>IF(F32&gt;0,C32/F32,"")</f>
+        <v>0.2317</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -63263,7 +63287,2407 @@
         <v>6.605</v>
       </c>
     </row>
+    <row r="2498">
+      <c r="A2498" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2498" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C2498" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2498" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2498" s="3">
+        <v>6.349</v>
+      </c>
+      <c r="F2498" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2498" s="3">
+        <v>6.349</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2499" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C2499" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2499" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2499" s="3">
+        <v>6.451</v>
+      </c>
+      <c r="F2499" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2499" s="3">
+        <v>6.451</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2500" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C2500" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2500" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2500" s="3">
+        <v>7.168</v>
+      </c>
+      <c r="F2500" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2500" s="3">
+        <v>7.168</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2501" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C2501" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2501" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2501" s="3">
+        <v>6.349</v>
+      </c>
+      <c r="F2501" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2501" s="3">
+        <v>6.349</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2502" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C2502" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2502" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2502" s="3">
+        <v>6.349</v>
+      </c>
+      <c r="F2502" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2502" s="3">
+        <v>6.349</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2503" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C2503" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2503" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2503" s="3">
+        <v>6.349</v>
+      </c>
+      <c r="F2503" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2503" s="3">
+        <v>6.349</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2504" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C2504" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2504" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2504" s="3">
+        <v>6.502</v>
+      </c>
+      <c r="F2504" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2504" s="3">
+        <v>6.502</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2505" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C2505" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2505" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2505" s="3">
+        <v>6.298</v>
+      </c>
+      <c r="F2505" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2505" s="3">
+        <v>6.298</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2506" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C2506" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2506" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2506" s="3">
+        <v>6.451</v>
+      </c>
+      <c r="F2506" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2506" s="3">
+        <v>6.451</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2507" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C2507" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2507" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2507" s="3">
+        <v>6.554</v>
+      </c>
+      <c r="F2507" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2507" s="3">
+        <v>6.554</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2508" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C2508" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2508" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2508" s="3">
+        <v>6.554</v>
+      </c>
+      <c r="F2508" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2508" s="3">
+        <v>6.554</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2509" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C2509" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2509" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2509" s="3">
+        <v>6.298</v>
+      </c>
+      <c r="F2509" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2509" s="3">
+        <v>6.298</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2510" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C2510" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2510" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2510" s="3">
+        <v>6.246</v>
+      </c>
+      <c r="F2510" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2510" s="3">
+        <v>6.246</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2511" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C2511" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2511" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2511" s="3">
+        <v>6.502</v>
+      </c>
+      <c r="F2511" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2511" s="3">
+        <v>6.502</v>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2512" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C2512" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2512" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2512" s="3">
+        <v>6.349</v>
+      </c>
+      <c r="F2512" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2512" s="3">
+        <v>6.349</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2513" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C2513" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2513" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2513" s="3">
+        <v>6.81</v>
+      </c>
+      <c r="F2513" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2513" s="3">
+        <v>6.81</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2514" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C2514" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2514" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2514" s="3">
+        <v>6.502</v>
+      </c>
+      <c r="F2514" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2514" s="3">
+        <v>6.502</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2515" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C2515" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2515" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2515" s="3">
+        <v>6.502</v>
+      </c>
+      <c r="F2515" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2515" s="3">
+        <v>6.502</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2516" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C2516" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2516" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2516" s="3">
+        <v>6.298</v>
+      </c>
+      <c r="F2516" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2516" s="3">
+        <v>6.298</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2517" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C2517" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2517" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2517" s="3">
+        <v>4.557</v>
+      </c>
+      <c r="F2517" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2517" s="3">
+        <v>4.557</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2518" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C2518" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2518" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2518" s="3">
+        <v>3.482</v>
+      </c>
+      <c r="F2518" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2518" s="3">
+        <v>3.482</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2519" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C2519" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2519" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2519" s="3">
+        <v>3.789</v>
+      </c>
+      <c r="F2519" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2519" s="3">
+        <v>3.789</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2520" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C2520" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2520" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2520" s="3">
+        <v>3.891</v>
+      </c>
+      <c r="F2520" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2520" s="3">
+        <v>3.891</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2521" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C2521" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2521" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2521" s="3">
+        <v>4.659</v>
+      </c>
+      <c r="F2521" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2521" s="3">
+        <v>4.659</v>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2522" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C2522" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2522" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2522" s="3">
+        <v>4.659</v>
+      </c>
+      <c r="F2522" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2522" s="3">
+        <v>4.659</v>
+      </c>
+    </row>
+    <row r="2523">
+      <c r="A2523" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2523" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C2523" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2523" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2523" s="3">
+        <v>1.434</v>
+      </c>
+      <c r="F2523" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2523" s="3">
+        <v>1.434</v>
+      </c>
+    </row>
+    <row r="2524">
+      <c r="A2524" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2524" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C2524" s="3">
+        <v>0.077</v>
+      </c>
+      <c r="D2524" s="3">
+        <v>0.077</v>
+      </c>
+      <c r="E2524" s="3">
+        <v>3.533</v>
+      </c>
+      <c r="F2524" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2524" s="3">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="2525">
+      <c r="A2525" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2525" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C2525" s="3">
+        <v>0.742</v>
+      </c>
+      <c r="D2525" s="3">
+        <v>0.691</v>
+      </c>
+      <c r="E2525" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="F2525" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G2525" s="3">
+        <v>4.121</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2526" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C2526" s="3">
+        <v>0.64</v>
+      </c>
+      <c r="D2526" s="3">
+        <v>0.64</v>
+      </c>
+      <c r="E2526" s="3">
+        <v>3.738</v>
+      </c>
+      <c r="F2526" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2526" s="3">
+        <v>4.378</v>
+      </c>
+    </row>
+    <row r="2527">
+      <c r="A2527" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2527" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C2527" s="3">
+        <v>2.816</v>
+      </c>
+      <c r="D2527" s="3">
+        <v>1.843</v>
+      </c>
+      <c r="E2527" s="3">
+        <v>1.69</v>
+      </c>
+      <c r="F2527" s="3">
+        <v>0.973</v>
+      </c>
+      <c r="G2527" s="3">
+        <v>3.533</v>
+      </c>
+    </row>
+    <row r="2528">
+      <c r="A2528" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2528" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C2528" s="3">
+        <v>11.366</v>
+      </c>
+      <c r="D2528" s="3">
+        <v>6.86</v>
+      </c>
+      <c r="E2528" s="3">
+        <v>11.674</v>
+      </c>
+      <c r="F2528" s="3">
+        <v>4.506</v>
+      </c>
+      <c r="G2528" s="3">
+        <v>18.534</v>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2529" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C2529" s="3">
+        <v>6.054</v>
+      </c>
+      <c r="D2529" s="3">
+        <v>6.054</v>
+      </c>
+      <c r="E2529" s="3">
+        <v>31.437</v>
+      </c>
+      <c r="F2529" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2529" s="3">
+        <v>37.491</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2530" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C2530" s="3">
+        <v>11.494</v>
+      </c>
+      <c r="D2530" s="3">
+        <v>11.494</v>
+      </c>
+      <c r="E2530" s="3">
+        <v>26.778</v>
+      </c>
+      <c r="F2530" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2530" s="3">
+        <v>38.272</v>
+      </c>
+    </row>
+    <row r="2531">
+      <c r="A2531" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2531" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C2531" s="3">
+        <v>11.75</v>
+      </c>
+      <c r="D2531" s="3">
+        <v>11.75</v>
+      </c>
+      <c r="E2531" s="3">
+        <v>26.112</v>
+      </c>
+      <c r="F2531" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2531" s="3">
+        <v>37.862</v>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2532" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C2532" s="3">
+        <v>13.299</v>
+      </c>
+      <c r="D2532" s="3">
+        <v>13.299</v>
+      </c>
+      <c r="E2532" s="3">
+        <v>24.218</v>
+      </c>
+      <c r="F2532" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2532" s="3">
+        <v>37.517</v>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2533" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C2533" s="3">
+        <v>28.275</v>
+      </c>
+      <c r="D2533" s="3">
+        <v>26.739</v>
+      </c>
+      <c r="E2533" s="3">
+        <v>11.264</v>
+      </c>
+      <c r="F2533" s="3">
+        <v>1.536</v>
+      </c>
+      <c r="G2533" s="3">
+        <v>38.003</v>
+      </c>
+    </row>
+    <row r="2534">
+      <c r="A2534" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2534" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C2534" s="3">
+        <v>43.955</v>
+      </c>
+      <c r="D2534" s="3">
+        <v>36.429</v>
+      </c>
+      <c r="E2534" s="3">
+        <v>1.178</v>
+      </c>
+      <c r="F2534" s="3">
+        <v>7.526</v>
+      </c>
+      <c r="G2534" s="3">
+        <v>37.607</v>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2535" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C2535" s="3">
+        <v>28.582</v>
+      </c>
+      <c r="D2535" s="3">
+        <v>27.456</v>
+      </c>
+      <c r="E2535" s="3">
+        <v>9.933</v>
+      </c>
+      <c r="F2535" s="3">
+        <v>1.126</v>
+      </c>
+      <c r="G2535" s="3">
+        <v>37.389</v>
+      </c>
+    </row>
+    <row r="2536">
+      <c r="A2536" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2536" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C2536" s="3">
+        <v>64.806</v>
+      </c>
+      <c r="D2536" s="3">
+        <v>36.185</v>
+      </c>
+      <c r="E2536" s="3">
+        <v>1.638</v>
+      </c>
+      <c r="F2536" s="3">
+        <v>28.621</v>
+      </c>
+      <c r="G2536" s="3">
+        <v>37.823</v>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2537" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C2537" s="3">
+        <v>34.304</v>
+      </c>
+      <c r="D2537" s="3">
+        <v>33.178</v>
+      </c>
+      <c r="E2537" s="3">
+        <v>5.018</v>
+      </c>
+      <c r="F2537" s="3">
+        <v>1.126</v>
+      </c>
+      <c r="G2537" s="3">
+        <v>38.196</v>
+      </c>
+    </row>
+    <row r="2538">
+      <c r="A2538" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2538" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C2538" s="3">
+        <v>23.309</v>
+      </c>
+      <c r="D2538" s="3">
+        <v>23.309</v>
+      </c>
+      <c r="E2538" s="3">
+        <v>14.899</v>
+      </c>
+      <c r="F2538" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2538" s="3">
+        <v>38.208</v>
+      </c>
+    </row>
+    <row r="2539">
+      <c r="A2539" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2539" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C2539" s="3">
+        <v>20.621</v>
+      </c>
+      <c r="D2539" s="3">
+        <v>20.621</v>
+      </c>
+      <c r="E2539" s="3">
+        <v>16.947</v>
+      </c>
+      <c r="F2539" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2539" s="3">
+        <v>37.568</v>
+      </c>
+    </row>
+    <row r="2540">
+      <c r="A2540" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2540" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C2540" s="3">
+        <v>13.363</v>
+      </c>
+      <c r="D2540" s="3">
+        <v>13.363</v>
+      </c>
+      <c r="E2540" s="3">
+        <v>26.01</v>
+      </c>
+      <c r="F2540" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2540" s="3">
+        <v>39.373</v>
+      </c>
+    </row>
+    <row r="2541">
+      <c r="A2541" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2541" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C2541" s="3">
+        <v>10.598</v>
+      </c>
+      <c r="D2541" s="3">
+        <v>10.598</v>
+      </c>
+      <c r="E2541" s="3">
+        <v>31.949</v>
+      </c>
+      <c r="F2541" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2541" s="3">
+        <v>42.547</v>
+      </c>
+    </row>
+    <row r="2542">
+      <c r="A2542" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2542" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C2542" s="3">
+        <v>12.826</v>
+      </c>
+      <c r="D2542" s="3">
+        <v>12.826</v>
+      </c>
+      <c r="E2542" s="3">
+        <v>59.853</v>
+      </c>
+      <c r="F2542" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2542" s="3">
+        <v>72.679</v>
+      </c>
+    </row>
+    <row r="2543">
+      <c r="A2543" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2543" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C2543" s="3">
+        <v>41.05</v>
+      </c>
+      <c r="D2543" s="3">
+        <v>41.05</v>
+      </c>
+      <c r="E2543" s="3">
+        <v>31.334</v>
+      </c>
+      <c r="F2543" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2543" s="3">
+        <v>72.384</v>
+      </c>
+    </row>
+    <row r="2544">
+      <c r="A2544" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2544" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C2544" s="3">
+        <v>52.006</v>
+      </c>
+      <c r="D2544" s="3">
+        <v>52.006</v>
+      </c>
+      <c r="E2544" s="3">
+        <v>21.094</v>
+      </c>
+      <c r="F2544" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2544" s="3">
+        <v>73.1</v>
+      </c>
+    </row>
+    <row r="2545">
+      <c r="A2545" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2545" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C2545" s="3">
+        <v>84.275</v>
+      </c>
+      <c r="D2545" s="3">
+        <v>69.12</v>
+      </c>
+      <c r="E2545" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="F2545" s="3">
+        <v>15.155</v>
+      </c>
+      <c r="G2545" s="3">
+        <v>72.96</v>
+      </c>
+    </row>
+    <row r="2546">
+      <c r="A2546" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2546" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C2546" s="3">
+        <v>92.211</v>
+      </c>
+      <c r="D2546" s="3">
+        <v>78.233</v>
+      </c>
+      <c r="E2546" s="3">
+        <v>8.448</v>
+      </c>
+      <c r="F2546" s="3">
+        <v>13.978</v>
+      </c>
+      <c r="G2546" s="3">
+        <v>86.681</v>
+      </c>
+    </row>
+    <row r="2547">
+      <c r="A2547" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2547" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C2547" s="3">
+        <v>50.304</v>
+      </c>
+      <c r="D2547" s="3">
+        <v>50.304</v>
+      </c>
+      <c r="E2547" s="3">
+        <v>57.139</v>
+      </c>
+      <c r="F2547" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2547" s="3">
+        <v>107.443</v>
+      </c>
+    </row>
+    <row r="2548">
+      <c r="A2548" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2548" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C2548" s="3">
+        <v>41.677</v>
+      </c>
+      <c r="D2548" s="3">
+        <v>41.677</v>
+      </c>
+      <c r="E2548" s="3">
+        <v>66.406</v>
+      </c>
+      <c r="F2548" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2548" s="3">
+        <v>108.083</v>
+      </c>
+    </row>
+    <row r="2549">
+      <c r="A2549" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2549" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C2549" s="3">
+        <v>43.494</v>
+      </c>
+      <c r="D2549" s="3">
+        <v>43.443</v>
+      </c>
+      <c r="E2549" s="3">
+        <v>64.256</v>
+      </c>
+      <c r="F2549" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G2549" s="3">
+        <v>107.699</v>
+      </c>
+    </row>
+    <row r="2550">
+      <c r="A2550" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2550" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C2550" s="3">
+        <v>49.165</v>
+      </c>
+      <c r="D2550" s="3">
+        <v>49.114</v>
+      </c>
+      <c r="E2550" s="3">
+        <v>69.325</v>
+      </c>
+      <c r="F2550" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="G2550" s="3">
+        <v>118.439</v>
+      </c>
+    </row>
+    <row r="2551">
+      <c r="A2551" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2551" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C2551" s="3">
+        <v>25.229</v>
+      </c>
+      <c r="D2551" s="3">
+        <v>25.229</v>
+      </c>
+      <c r="E2551" s="3">
+        <v>111.411</v>
+      </c>
+      <c r="F2551" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2551" s="3">
+        <v>136.64</v>
+      </c>
+    </row>
+    <row r="2552">
+      <c r="A2552" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2552" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C2552" s="3">
+        <v>15.667</v>
+      </c>
+      <c r="D2552" s="3">
+        <v>15.667</v>
+      </c>
+      <c r="E2552" s="3">
+        <v>92.16</v>
+      </c>
+      <c r="F2552" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2552" s="3">
+        <v>107.827</v>
+      </c>
+    </row>
+    <row r="2553">
+      <c r="A2553" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2553" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C2553" s="3">
+        <v>13.235</v>
+      </c>
+      <c r="D2553" s="3">
+        <v>13.235</v>
+      </c>
+      <c r="E2553" s="3">
+        <v>94.515</v>
+      </c>
+      <c r="F2553" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2553" s="3">
+        <v>107.75</v>
+      </c>
+    </row>
+    <row r="2554">
+      <c r="A2554" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2554" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C2554" s="3">
+        <v>32.243</v>
+      </c>
+      <c r="D2554" s="3">
+        <v>32.243</v>
+      </c>
+      <c r="E2554" s="3">
+        <v>80.23</v>
+      </c>
+      <c r="F2554" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2554" s="3">
+        <v>112.473</v>
+      </c>
+    </row>
+    <row r="2555">
+      <c r="A2555" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2555" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C2555" s="3">
+        <v>78.566</v>
+      </c>
+      <c r="D2555" s="3">
+        <v>78.566</v>
+      </c>
+      <c r="E2555" s="3">
+        <v>63.795</v>
+      </c>
+      <c r="F2555" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2555" s="3">
+        <v>142.361</v>
+      </c>
+    </row>
+    <row r="2556">
+      <c r="A2556" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2556" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C2556" s="3">
+        <v>27.725</v>
+      </c>
+      <c r="D2556" s="3">
+        <v>27.725</v>
+      </c>
+      <c r="E2556" s="3">
+        <v>114.074</v>
+      </c>
+      <c r="F2556" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2556" s="3">
+        <v>141.799</v>
+      </c>
+    </row>
+    <row r="2557">
+      <c r="A2557" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2557" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C2557" s="3">
+        <v>17.984</v>
+      </c>
+      <c r="D2557" s="3">
+        <v>17.984</v>
+      </c>
+      <c r="E2557" s="3">
+        <v>123.904</v>
+      </c>
+      <c r="F2557" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2557" s="3">
+        <v>141.888</v>
+      </c>
+    </row>
+    <row r="2558">
+      <c r="A2558" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2558" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C2558" s="3">
+        <v>18.24</v>
+      </c>
+      <c r="D2558" s="3">
+        <v>18.24</v>
+      </c>
+      <c r="E2558" s="3">
+        <v>123.955</v>
+      </c>
+      <c r="F2558" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2558" s="3">
+        <v>142.195</v>
+      </c>
+    </row>
+    <row r="2559">
+      <c r="A2559" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2559" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C2559" s="3">
+        <v>22.144</v>
+      </c>
+      <c r="D2559" s="3">
+        <v>22.144</v>
+      </c>
+      <c r="E2559" s="3">
+        <v>119.45</v>
+      </c>
+      <c r="F2559" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2559" s="3">
+        <v>141.594</v>
+      </c>
+    </row>
+    <row r="2560">
+      <c r="A2560" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2560" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C2560" s="3">
+        <v>54.784</v>
+      </c>
+      <c r="D2560" s="3">
+        <v>54.784</v>
+      </c>
+      <c r="E2560" s="3">
+        <v>86.682</v>
+      </c>
+      <c r="F2560" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2560" s="3">
+        <v>141.466</v>
+      </c>
+    </row>
+    <row r="2561">
+      <c r="A2561" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2561" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C2561" s="3">
+        <v>99.469</v>
+      </c>
+      <c r="D2561" s="3">
+        <v>99.469</v>
+      </c>
+      <c r="E2561" s="3">
+        <v>42.035</v>
+      </c>
+      <c r="F2561" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2561" s="3">
+        <v>141.504</v>
+      </c>
+    </row>
+    <row r="2562">
+      <c r="A2562" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2562" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C2562" s="3">
+        <v>94.861</v>
+      </c>
+      <c r="D2562" s="3">
+        <v>94.861</v>
+      </c>
+      <c r="E2562" s="3">
+        <v>46.49</v>
+      </c>
+      <c r="F2562" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2562" s="3">
+        <v>141.351</v>
+      </c>
+    </row>
+    <row r="2563">
+      <c r="A2563" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2563" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C2563" s="3">
+        <v>91.853</v>
+      </c>
+      <c r="D2563" s="3">
+        <v>91.853</v>
+      </c>
+      <c r="E2563" s="3">
+        <v>54.374</v>
+      </c>
+      <c r="F2563" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2563" s="3">
+        <v>146.227</v>
+      </c>
+    </row>
+    <row r="2564">
+      <c r="A2564" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2564" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C2564" s="3">
+        <v>82.061</v>
+      </c>
+      <c r="D2564" s="3">
+        <v>82.061</v>
+      </c>
+      <c r="E2564" s="3">
+        <v>91.904</v>
+      </c>
+      <c r="F2564" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2564" s="3">
+        <v>173.965</v>
+      </c>
+    </row>
+    <row r="2565">
+      <c r="A2565" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2565" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C2565" s="3">
+        <v>25.293</v>
+      </c>
+      <c r="D2565" s="3">
+        <v>25.293</v>
+      </c>
+      <c r="E2565" s="3">
+        <v>148.736</v>
+      </c>
+      <c r="F2565" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2565" s="3">
+        <v>174.029</v>
+      </c>
+    </row>
+    <row r="2566">
+      <c r="A2566" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2566" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C2566" s="3">
+        <v>59.238</v>
+      </c>
+      <c r="D2566" s="3">
+        <v>59.238</v>
+      </c>
+      <c r="E2566" s="3">
+        <v>115.2</v>
+      </c>
+      <c r="F2566" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2566" s="3">
+        <v>174.438</v>
+      </c>
+    </row>
+    <row r="2567">
+      <c r="A2567" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2567" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C2567" s="3">
+        <v>43.123</v>
+      </c>
+      <c r="D2567" s="3">
+        <v>43.123</v>
+      </c>
+      <c r="E2567" s="3">
+        <v>130.662</v>
+      </c>
+      <c r="F2567" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2567" s="3">
+        <v>173.785</v>
+      </c>
+    </row>
+    <row r="2568">
+      <c r="A2568" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2568" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C2568" s="3">
+        <v>36.109</v>
+      </c>
+      <c r="D2568" s="3">
+        <v>36.109</v>
+      </c>
+      <c r="E2568" s="3">
+        <v>138.138</v>
+      </c>
+      <c r="F2568" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2568" s="3">
+        <v>174.247</v>
+      </c>
+    </row>
+    <row r="2569">
+      <c r="A2569" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2569" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C2569" s="3">
+        <v>32.55</v>
+      </c>
+      <c r="D2569" s="3">
+        <v>32.55</v>
+      </c>
+      <c r="E2569" s="3">
+        <v>141.722</v>
+      </c>
+      <c r="F2569" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2569" s="3">
+        <v>174.272</v>
+      </c>
+    </row>
+    <row r="2570">
+      <c r="A2570" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2570" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C2570" s="3">
+        <v>18.202</v>
+      </c>
+      <c r="D2570" s="3">
+        <v>18.202</v>
+      </c>
+      <c r="E2570" s="3">
+        <v>155.904</v>
+      </c>
+      <c r="F2570" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2570" s="3">
+        <v>174.106</v>
+      </c>
+    </row>
+    <row r="2571">
+      <c r="A2571" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2571" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C2571" s="3">
+        <v>15.642</v>
+      </c>
+      <c r="D2571" s="3">
+        <v>15.642</v>
+      </c>
+      <c r="E2571" s="3">
+        <v>158.771</v>
+      </c>
+      <c r="F2571" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2571" s="3">
+        <v>174.413</v>
+      </c>
+    </row>
+    <row r="2572">
+      <c r="A2572" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2572" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C2572" s="3">
+        <v>13.581</v>
+      </c>
+      <c r="D2572" s="3">
+        <v>13.581</v>
+      </c>
+      <c r="E2572" s="3">
+        <v>159.949</v>
+      </c>
+      <c r="F2572" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2572" s="3">
+        <v>173.53</v>
+      </c>
+    </row>
+    <row r="2573">
+      <c r="A2573" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2573" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C2573" s="3">
+        <v>7.462</v>
+      </c>
+      <c r="D2573" s="3">
+        <v>7.462</v>
+      </c>
+      <c r="E2573" s="3">
+        <v>166.298</v>
+      </c>
+      <c r="F2573" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2573" s="3">
+        <v>173.76</v>
+      </c>
+    </row>
+    <row r="2574">
+      <c r="A2574" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2574" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C2574" s="3">
+        <v>3.482</v>
+      </c>
+      <c r="D2574" s="3">
+        <v>3.482</v>
+      </c>
+      <c r="E2574" s="3">
+        <v>170.445</v>
+      </c>
+      <c r="F2574" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2574" s="3">
+        <v>173.927</v>
+      </c>
+    </row>
+    <row r="2575">
+      <c r="A2575" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2575" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C2575" s="3">
+        <v>1.242</v>
+      </c>
+      <c r="D2575" s="3">
+        <v>1.242</v>
+      </c>
+      <c r="E2575" s="3">
+        <v>173.158</v>
+      </c>
+      <c r="F2575" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2575" s="3">
+        <v>174.4</v>
+      </c>
+    </row>
+    <row r="2576">
+      <c r="A2576" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2576" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C2576" s="3">
+        <v>0.269</v>
+      </c>
+      <c r="D2576" s="3">
+        <v>0.269</v>
+      </c>
+      <c r="E2576" s="3">
+        <v>175.565</v>
+      </c>
+      <c r="F2576" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2576" s="3">
+        <v>175.834</v>
+      </c>
+    </row>
+    <row r="2577">
+      <c r="A2577" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2577" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C2577" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2577" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2577" s="3">
+        <v>175.155</v>
+      </c>
+      <c r="F2577" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2577" s="3">
+        <v>175.155</v>
+      </c>
+    </row>
+    <row r="2578">
+      <c r="A2578" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2578" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C2578" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2578" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2578" s="3">
+        <v>174.336</v>
+      </c>
+      <c r="F2578" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2578" s="3">
+        <v>174.336</v>
+      </c>
+    </row>
+    <row r="2579">
+      <c r="A2579" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2579" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C2579" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2579" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2579" s="3">
+        <v>174.234</v>
+      </c>
+      <c r="F2579" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2579" s="3">
+        <v>174.234</v>
+      </c>
+    </row>
+    <row r="2580">
+      <c r="A2580" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2580" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C2580" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2580" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2580" s="3">
+        <v>173.773</v>
+      </c>
+      <c r="F2580" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2580" s="3">
+        <v>173.773</v>
+      </c>
+    </row>
+    <row r="2581">
+      <c r="A2581" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2581" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C2581" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2581" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2581" s="3">
+        <v>174.131</v>
+      </c>
+      <c r="F2581" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2581" s="3">
+        <v>174.131</v>
+      </c>
+    </row>
+    <row r="2582">
+      <c r="A2582" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2582" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C2582" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2582" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2582" s="3">
+        <v>174.08</v>
+      </c>
+      <c r="F2582" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2582" s="3">
+        <v>174.08</v>
+      </c>
+    </row>
+    <row r="2583">
+      <c r="A2583" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2583" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C2583" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2583" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2583" s="3">
+        <v>173.466</v>
+      </c>
+      <c r="F2583" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2583" s="3">
+        <v>173.466</v>
+      </c>
+    </row>
+    <row r="2584">
+      <c r="A2584" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2584" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C2584" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2584" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2584" s="3">
+        <v>174.131</v>
+      </c>
+      <c r="F2584" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2584" s="3">
+        <v>174.131</v>
+      </c>
+    </row>
+    <row r="2585">
+      <c r="A2585" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2585" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C2585" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2585" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2585" s="3">
+        <v>173.568</v>
+      </c>
+      <c r="F2585" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2585" s="3">
+        <v>173.568</v>
+      </c>
+    </row>
+    <row r="2586">
+      <c r="A2586" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2586" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C2586" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2586" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2586" s="3">
+        <v>173.926</v>
+      </c>
+      <c r="F2586" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2586" s="3">
+        <v>173.926</v>
+      </c>
+    </row>
+    <row r="2587">
+      <c r="A2587" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2587" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C2587" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2587" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2587" s="3">
+        <v>173.773</v>
+      </c>
+      <c r="F2587" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2587" s="3">
+        <v>173.773</v>
+      </c>
+    </row>
+    <row r="2588">
+      <c r="A2588" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2588" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C2588" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2588" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2588" s="3">
+        <v>173.926</v>
+      </c>
+      <c r="F2588" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2588" s="3">
+        <v>173.926</v>
+      </c>
+    </row>
+    <row r="2589">
+      <c r="A2589" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2589" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C2589" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2589" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2589" s="3">
+        <v>173.722</v>
+      </c>
+      <c r="F2589" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2589" s="3">
+        <v>173.722</v>
+      </c>
+    </row>
+    <row r="2590">
+      <c r="A2590" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2590" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C2590" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2590" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2590" s="3">
+        <v>173.568</v>
+      </c>
+      <c r="F2590" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2590" s="3">
+        <v>173.568</v>
+      </c>
+    </row>
+    <row r="2591">
+      <c r="A2591" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2591" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C2591" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2591" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2591" s="3">
+        <v>173.67</v>
+      </c>
+      <c r="F2591" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2591" s="3">
+        <v>173.67</v>
+      </c>
+    </row>
+    <row r="2592">
+      <c r="A2592" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2592" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C2592" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2592" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2592" s="3">
+        <v>173.722</v>
+      </c>
+      <c r="F2592" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2592" s="3">
+        <v>173.722</v>
+      </c>
+    </row>
+    <row r="2593">
+      <c r="A2593" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B2593" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C2593" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2593" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2593" s="3">
+        <v>173.926</v>
+      </c>
+      <c r="F2593" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2593" s="3">
+        <v>173.926</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2497"/>
+  <autoFilter ref="A1:G2593"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -790,45 +790,69 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B32" s="4">
+        <v>3632.5</v>
+      </c>
+      <c r="C32" s="4">
+        <v>3267.8</v>
+      </c>
+      <c r="D32" s="4">
+        <v>10106.0</v>
+      </c>
+      <c r="E32" s="4">
+        <v>364.8</v>
+      </c>
+      <c r="F32" s="4">
+        <v>13373.7</v>
+      </c>
+      <c r="G32" s="5">
+        <f>IF(F32&gt;0,C32/F32,"")</f>
+        <v>0.2443</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B32" s="7">
-        <f>SUM(B5:B31)</f>
-        <v>63033.0</v>
-      </c>
-      <c r="C32" s="7">
-        <f>SUM(C5:C31)</f>
-        <v>41827.3</v>
-      </c>
-      <c r="D32" s="7">
-        <f>SUM(D5:D31)</f>
-        <v>138699.9</v>
-      </c>
-      <c r="E32" s="7">
-        <f>SUM(E5:E31)</f>
-        <v>21206.3</v>
-      </c>
-      <c r="F32" s="7">
-        <f>SUM(F5:F31)</f>
-        <v>180527.2</v>
-      </c>
-      <c r="G32" s="8">
-        <f>IF(F32&gt;0,C32/F32,"")</f>
-        <v>0.2317</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B33" s="7">
+        <f>SUM(B5:B32)</f>
+        <v>66665.5</v>
+      </c>
+      <c r="C33" s="7">
+        <f>SUM(C5:C32)</f>
+        <v>45095.0</v>
+      </c>
+      <c r="D33" s="7">
+        <f>SUM(D5:D32)</f>
+        <v>148805.8</v>
+      </c>
+      <c r="E33" s="7">
+        <f>SUM(E5:E32)</f>
+        <v>21571.1</v>
+      </c>
+      <c r="F33" s="7">
+        <f>SUM(F5:F32)</f>
+        <v>193900.9</v>
+      </c>
+      <c r="G33" s="8">
+        <f>IF(F33&gt;0,C33/F33,"")</f>
+        <v>0.2326</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -65687,7 +65711,2407 @@
         <v>173.926</v>
       </c>
     </row>
+    <row r="2594">
+      <c r="A2594" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2594" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C2594" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2594" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2594" s="3">
+        <v>173.926</v>
+      </c>
+      <c r="F2594" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2594" s="3">
+        <v>173.926</v>
+      </c>
+    </row>
+    <row r="2595">
+      <c r="A2595" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2595" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C2595" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2595" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2595" s="3">
+        <v>173.824</v>
+      </c>
+      <c r="F2595" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2595" s="3">
+        <v>173.824</v>
+      </c>
+    </row>
+    <row r="2596">
+      <c r="A2596" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2596" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C2596" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2596" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2596" s="3">
+        <v>173.414</v>
+      </c>
+      <c r="F2596" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2596" s="3">
+        <v>173.414</v>
+      </c>
+    </row>
+    <row r="2597">
+      <c r="A2597" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2597" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C2597" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2597" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2597" s="3">
+        <v>173.312</v>
+      </c>
+      <c r="F2597" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2597" s="3">
+        <v>173.312</v>
+      </c>
+    </row>
+    <row r="2598">
+      <c r="A2598" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2598" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C2598" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2598" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2598" s="3">
+        <v>173.568</v>
+      </c>
+      <c r="F2598" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2598" s="3">
+        <v>173.568</v>
+      </c>
+    </row>
+    <row r="2599">
+      <c r="A2599" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2599" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C2599" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2599" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2599" s="3">
+        <v>173.926</v>
+      </c>
+      <c r="F2599" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2599" s="3">
+        <v>173.926</v>
+      </c>
+    </row>
+    <row r="2600">
+      <c r="A2600" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2600" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C2600" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2600" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2600" s="3">
+        <v>173.978</v>
+      </c>
+      <c r="F2600" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2600" s="3">
+        <v>173.978</v>
+      </c>
+    </row>
+    <row r="2601">
+      <c r="A2601" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2601" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C2601" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2601" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2601" s="3">
+        <v>173.978</v>
+      </c>
+      <c r="F2601" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2601" s="3">
+        <v>173.978</v>
+      </c>
+    </row>
+    <row r="2602">
+      <c r="A2602" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2602" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C2602" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2602" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2602" s="3">
+        <v>173.926</v>
+      </c>
+      <c r="F2602" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2602" s="3">
+        <v>173.926</v>
+      </c>
+    </row>
+    <row r="2603">
+      <c r="A2603" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2603" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C2603" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2603" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2603" s="3">
+        <v>174.029</v>
+      </c>
+      <c r="F2603" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2603" s="3">
+        <v>174.029</v>
+      </c>
+    </row>
+    <row r="2604">
+      <c r="A2604" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2604" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C2604" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2604" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2604" s="3">
+        <v>174.234</v>
+      </c>
+      <c r="F2604" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2604" s="3">
+        <v>174.234</v>
+      </c>
+    </row>
+    <row r="2605">
+      <c r="A2605" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2605" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C2605" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2605" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2605" s="3">
+        <v>174.08</v>
+      </c>
+      <c r="F2605" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2605" s="3">
+        <v>174.08</v>
+      </c>
+    </row>
+    <row r="2606">
+      <c r="A2606" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2606" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C2606" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2606" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2606" s="3">
+        <v>173.67</v>
+      </c>
+      <c r="F2606" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2606" s="3">
+        <v>173.67</v>
+      </c>
+    </row>
+    <row r="2607">
+      <c r="A2607" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2607" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C2607" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2607" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2607" s="3">
+        <v>173.619</v>
+      </c>
+      <c r="F2607" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2607" s="3">
+        <v>173.619</v>
+      </c>
+    </row>
+    <row r="2608">
+      <c r="A2608" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2608" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C2608" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2608" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2608" s="3">
+        <v>173.619</v>
+      </c>
+      <c r="F2608" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2608" s="3">
+        <v>173.619</v>
+      </c>
+    </row>
+    <row r="2609">
+      <c r="A2609" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2609" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C2609" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2609" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2609" s="3">
+        <v>173.67</v>
+      </c>
+      <c r="F2609" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2609" s="3">
+        <v>173.67</v>
+      </c>
+    </row>
+    <row r="2610">
+      <c r="A2610" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2610" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C2610" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2610" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2610" s="3">
+        <v>173.773</v>
+      </c>
+      <c r="F2610" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2610" s="3">
+        <v>173.773</v>
+      </c>
+    </row>
+    <row r="2611">
+      <c r="A2611" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2611" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C2611" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2611" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2611" s="3">
+        <v>173.722</v>
+      </c>
+      <c r="F2611" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2611" s="3">
+        <v>173.722</v>
+      </c>
+    </row>
+    <row r="2612">
+      <c r="A2612" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2612" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C2612" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2612" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2612" s="3">
+        <v>173.67</v>
+      </c>
+      <c r="F2612" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2612" s="3">
+        <v>173.67</v>
+      </c>
+    </row>
+    <row r="2613">
+      <c r="A2613" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2613" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C2613" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2613" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2613" s="3">
+        <v>173.466</v>
+      </c>
+      <c r="F2613" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2613" s="3">
+        <v>173.466</v>
+      </c>
+    </row>
+    <row r="2614">
+      <c r="A2614" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2614" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C2614" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2614" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2614" s="3">
+        <v>173.722</v>
+      </c>
+      <c r="F2614" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2614" s="3">
+        <v>173.722</v>
+      </c>
+    </row>
+    <row r="2615">
+      <c r="A2615" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2615" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C2615" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2615" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2615" s="3">
+        <v>173.926</v>
+      </c>
+      <c r="F2615" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2615" s="3">
+        <v>173.926</v>
+      </c>
+    </row>
+    <row r="2616">
+      <c r="A2616" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2616" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C2616" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2616" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2616" s="3">
+        <v>173.466</v>
+      </c>
+      <c r="F2616" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2616" s="3">
+        <v>173.466</v>
+      </c>
+    </row>
+    <row r="2617">
+      <c r="A2617" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2617" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C2617" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2617" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2617" s="3">
+        <v>173.773</v>
+      </c>
+      <c r="F2617" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2617" s="3">
+        <v>173.773</v>
+      </c>
+    </row>
+    <row r="2618">
+      <c r="A2618" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2618" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C2618" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2618" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2618" s="3">
+        <v>174.08</v>
+      </c>
+      <c r="F2618" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2618" s="3">
+        <v>174.08</v>
+      </c>
+    </row>
+    <row r="2619">
+      <c r="A2619" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2619" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C2619" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="D2619" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="E2619" s="3">
+        <v>174.234</v>
+      </c>
+      <c r="F2619" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2619" s="3">
+        <v>174.247</v>
+      </c>
+    </row>
+    <row r="2620">
+      <c r="A2620" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2620" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C2620" s="3">
+        <v>0.422</v>
+      </c>
+      <c r="D2620" s="3">
+        <v>0.422</v>
+      </c>
+      <c r="E2620" s="3">
+        <v>173.363</v>
+      </c>
+      <c r="F2620" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2620" s="3">
+        <v>173.785</v>
+      </c>
+    </row>
+    <row r="2621">
+      <c r="A2621" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2621" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C2621" s="3">
+        <v>1.203</v>
+      </c>
+      <c r="D2621" s="3">
+        <v>1.203</v>
+      </c>
+      <c r="E2621" s="3">
+        <v>172.8</v>
+      </c>
+      <c r="F2621" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2621" s="3">
+        <v>174.003</v>
+      </c>
+    </row>
+    <row r="2622">
+      <c r="A2622" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2622" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C2622" s="3">
+        <v>3.366</v>
+      </c>
+      <c r="D2622" s="3">
+        <v>3.366</v>
+      </c>
+      <c r="E2622" s="3">
+        <v>170.803</v>
+      </c>
+      <c r="F2622" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2622" s="3">
+        <v>174.169</v>
+      </c>
+    </row>
+    <row r="2623">
+      <c r="A2623" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2623" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C2623" s="3">
+        <v>7.667</v>
+      </c>
+      <c r="D2623" s="3">
+        <v>7.667</v>
+      </c>
+      <c r="E2623" s="3">
+        <v>166.451</v>
+      </c>
+      <c r="F2623" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2623" s="3">
+        <v>174.118</v>
+      </c>
+    </row>
+    <row r="2624">
+      <c r="A2624" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2624" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C2624" s="3">
+        <v>14.029</v>
+      </c>
+      <c r="D2624" s="3">
+        <v>14.029</v>
+      </c>
+      <c r="E2624" s="3">
+        <v>159.949</v>
+      </c>
+      <c r="F2624" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2624" s="3">
+        <v>173.978</v>
+      </c>
+    </row>
+    <row r="2625">
+      <c r="A2625" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2625" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C2625" s="3">
+        <v>21.683</v>
+      </c>
+      <c r="D2625" s="3">
+        <v>21.683</v>
+      </c>
+      <c r="E2625" s="3">
+        <v>181.094</v>
+      </c>
+      <c r="F2625" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2625" s="3">
+        <v>202.777</v>
+      </c>
+    </row>
+    <row r="2626">
+      <c r="A2626" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2626" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C2626" s="3">
+        <v>29.76</v>
+      </c>
+      <c r="D2626" s="3">
+        <v>29.76</v>
+      </c>
+      <c r="E2626" s="3">
+        <v>177.357</v>
+      </c>
+      <c r="F2626" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2626" s="3">
+        <v>207.117</v>
+      </c>
+    </row>
+    <row r="2627">
+      <c r="A2627" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2627" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C2627" s="3">
+        <v>38.272</v>
+      </c>
+      <c r="D2627" s="3">
+        <v>38.272</v>
+      </c>
+      <c r="E2627" s="3">
+        <v>169.062</v>
+      </c>
+      <c r="F2627" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2627" s="3">
+        <v>207.334</v>
+      </c>
+    </row>
+    <row r="2628">
+      <c r="A2628" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2628" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C2628" s="3">
+        <v>46.899</v>
+      </c>
+      <c r="D2628" s="3">
+        <v>46.899</v>
+      </c>
+      <c r="E2628" s="3">
+        <v>160.666</v>
+      </c>
+      <c r="F2628" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2628" s="3">
+        <v>207.565</v>
+      </c>
+    </row>
+    <row r="2629">
+      <c r="A2629" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2629" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C2629" s="3">
+        <v>54.861</v>
+      </c>
+      <c r="D2629" s="3">
+        <v>54.861</v>
+      </c>
+      <c r="E2629" s="3">
+        <v>152.986</v>
+      </c>
+      <c r="F2629" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2629" s="3">
+        <v>207.847</v>
+      </c>
+    </row>
+    <row r="2630">
+      <c r="A2630" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2630" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C2630" s="3">
+        <v>62.541</v>
+      </c>
+      <c r="D2630" s="3">
+        <v>62.541</v>
+      </c>
+      <c r="E2630" s="3">
+        <v>113.357</v>
+      </c>
+      <c r="F2630" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2630" s="3">
+        <v>175.898</v>
+      </c>
+    </row>
+    <row r="2631">
+      <c r="A2631" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2631" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C2631" s="3">
+        <v>69.76</v>
+      </c>
+      <c r="D2631" s="3">
+        <v>69.76</v>
+      </c>
+      <c r="E2631" s="3">
+        <v>104.602</v>
+      </c>
+      <c r="F2631" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2631" s="3">
+        <v>174.362</v>
+      </c>
+    </row>
+    <row r="2632">
+      <c r="A2632" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2632" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C2632" s="3">
+        <v>76.506</v>
+      </c>
+      <c r="D2632" s="3">
+        <v>76.506</v>
+      </c>
+      <c r="E2632" s="3">
+        <v>98.765</v>
+      </c>
+      <c r="F2632" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2632" s="3">
+        <v>175.271</v>
+      </c>
+    </row>
+    <row r="2633">
+      <c r="A2633" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2633" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C2633" s="3">
+        <v>83.162</v>
+      </c>
+      <c r="D2633" s="3">
+        <v>83.162</v>
+      </c>
+      <c r="E2633" s="3">
+        <v>91.341</v>
+      </c>
+      <c r="F2633" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2633" s="3">
+        <v>174.503</v>
+      </c>
+    </row>
+    <row r="2634">
+      <c r="A2634" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2634" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C2634" s="3">
+        <v>88.96</v>
+      </c>
+      <c r="D2634" s="3">
+        <v>88.96</v>
+      </c>
+      <c r="E2634" s="3">
+        <v>84.787</v>
+      </c>
+      <c r="F2634" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2634" s="3">
+        <v>173.747</v>
+      </c>
+    </row>
+    <row r="2635">
+      <c r="A2635" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2635" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C2635" s="3">
+        <v>94.49</v>
+      </c>
+      <c r="D2635" s="3">
+        <v>94.49</v>
+      </c>
+      <c r="E2635" s="3">
+        <v>79.872</v>
+      </c>
+      <c r="F2635" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2635" s="3">
+        <v>174.362</v>
+      </c>
+    </row>
+    <row r="2636">
+      <c r="A2636" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2636" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C2636" s="3">
+        <v>99.418</v>
+      </c>
+      <c r="D2636" s="3">
+        <v>99.418</v>
+      </c>
+      <c r="E2636" s="3">
+        <v>74.445</v>
+      </c>
+      <c r="F2636" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2636" s="3">
+        <v>173.863</v>
+      </c>
+    </row>
+    <row r="2637">
+      <c r="A2637" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2637" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C2637" s="3">
+        <v>102.131</v>
+      </c>
+      <c r="D2637" s="3">
+        <v>102.131</v>
+      </c>
+      <c r="E2637" s="3">
+        <v>72.141</v>
+      </c>
+      <c r="F2637" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2637" s="3">
+        <v>174.272</v>
+      </c>
+    </row>
+    <row r="2638">
+      <c r="A2638" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2638" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C2638" s="3">
+        <v>108.058</v>
+      </c>
+      <c r="D2638" s="3">
+        <v>108.058</v>
+      </c>
+      <c r="E2638" s="3">
+        <v>66.867</v>
+      </c>
+      <c r="F2638" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2638" s="3">
+        <v>174.925</v>
+      </c>
+    </row>
+    <row r="2639">
+      <c r="A2639" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2639" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C2639" s="3">
+        <v>111.706</v>
+      </c>
+      <c r="D2639" s="3">
+        <v>111.706</v>
+      </c>
+      <c r="E2639" s="3">
+        <v>63.13</v>
+      </c>
+      <c r="F2639" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2639" s="3">
+        <v>174.836</v>
+      </c>
+    </row>
+    <row r="2640">
+      <c r="A2640" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2640" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C2640" s="3">
+        <v>113.766</v>
+      </c>
+      <c r="D2640" s="3">
+        <v>113.766</v>
+      </c>
+      <c r="E2640" s="3">
+        <v>60.518</v>
+      </c>
+      <c r="F2640" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2640" s="3">
+        <v>174.284</v>
+      </c>
+    </row>
+    <row r="2641">
+      <c r="A2641" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2641" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C2641" s="3">
+        <v>114.419</v>
+      </c>
+      <c r="D2641" s="3">
+        <v>114.419</v>
+      </c>
+      <c r="E2641" s="3">
+        <v>60.109</v>
+      </c>
+      <c r="F2641" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2641" s="3">
+        <v>174.528</v>
+      </c>
+    </row>
+    <row r="2642">
+      <c r="A2642" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2642" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C2642" s="3">
+        <v>106.189</v>
+      </c>
+      <c r="D2642" s="3">
+        <v>106.189</v>
+      </c>
+      <c r="E2642" s="3">
+        <v>46.848</v>
+      </c>
+      <c r="F2642" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2642" s="3">
+        <v>153.037</v>
+      </c>
+    </row>
+    <row r="2643">
+      <c r="A2643" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2643" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C2643" s="3">
+        <v>115.699</v>
+      </c>
+      <c r="D2643" s="3">
+        <v>113.497</v>
+      </c>
+      <c r="E2643" s="3">
+        <v>17.152</v>
+      </c>
+      <c r="F2643" s="3">
+        <v>2.202</v>
+      </c>
+      <c r="G2643" s="3">
+        <v>130.649</v>
+      </c>
+    </row>
+    <row r="2644">
+      <c r="A2644" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2644" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C2644" s="3">
+        <v>116.032</v>
+      </c>
+      <c r="D2644" s="3">
+        <v>96.525</v>
+      </c>
+      <c r="E2644" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2644" s="3">
+        <v>19.507</v>
+      </c>
+      <c r="G2644" s="3">
+        <v>96.525</v>
+      </c>
+    </row>
+    <row r="2645">
+      <c r="A2645" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2645" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C2645" s="3">
+        <v>115.93</v>
+      </c>
+      <c r="D2645" s="3">
+        <v>76.813</v>
+      </c>
+      <c r="E2645" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2645" s="3">
+        <v>39.117</v>
+      </c>
+      <c r="G2645" s="3">
+        <v>76.813</v>
+      </c>
+    </row>
+    <row r="2646">
+      <c r="A2646" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2646" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C2646" s="3">
+        <v>115.738</v>
+      </c>
+      <c r="D2646" s="3">
+        <v>76.724</v>
+      </c>
+      <c r="E2646" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2646" s="3">
+        <v>39.014</v>
+      </c>
+      <c r="G2646" s="3">
+        <v>76.724</v>
+      </c>
+    </row>
+    <row r="2647">
+      <c r="A2647" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2647" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C2647" s="3">
+        <v>115.443</v>
+      </c>
+      <c r="D2647" s="3">
+        <v>77.248</v>
+      </c>
+      <c r="E2647" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2647" s="3">
+        <v>38.195</v>
+      </c>
+      <c r="G2647" s="3">
+        <v>77.248</v>
+      </c>
+    </row>
+    <row r="2648">
+      <c r="A2648" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2648" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C2648" s="3">
+        <v>108.902</v>
+      </c>
+      <c r="D2648" s="3">
+        <v>76.185</v>
+      </c>
+      <c r="E2648" s="3">
+        <v>0.614</v>
+      </c>
+      <c r="F2648" s="3">
+        <v>32.717</v>
+      </c>
+      <c r="G2648" s="3">
+        <v>76.799</v>
+      </c>
+    </row>
+    <row r="2649">
+      <c r="A2649" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2649" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C2649" s="3">
+        <v>115.2</v>
+      </c>
+      <c r="D2649" s="3">
+        <v>76.851</v>
+      </c>
+      <c r="E2649" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2649" s="3">
+        <v>38.349</v>
+      </c>
+      <c r="G2649" s="3">
+        <v>76.851</v>
+      </c>
+    </row>
+    <row r="2650">
+      <c r="A2650" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2650" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C2650" s="3">
+        <v>114.534</v>
+      </c>
+      <c r="D2650" s="3">
+        <v>76.953</v>
+      </c>
+      <c r="E2650" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2650" s="3">
+        <v>37.581</v>
+      </c>
+      <c r="G2650" s="3">
+        <v>76.953</v>
+      </c>
+    </row>
+    <row r="2651">
+      <c r="A2651" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2651" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C2651" s="3">
+        <v>113.062</v>
+      </c>
+      <c r="D2651" s="3">
+        <v>77.12</v>
+      </c>
+      <c r="E2651" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2651" s="3">
+        <v>35.942</v>
+      </c>
+      <c r="G2651" s="3">
+        <v>77.12</v>
+      </c>
+    </row>
+    <row r="2652">
+      <c r="A2652" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2652" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C2652" s="3">
+        <v>111.398</v>
+      </c>
+      <c r="D2652" s="3">
+        <v>77.708</v>
+      </c>
+      <c r="E2652" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2652" s="3">
+        <v>33.69</v>
+      </c>
+      <c r="G2652" s="3">
+        <v>77.708</v>
+      </c>
+    </row>
+    <row r="2653">
+      <c r="A2653" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2653" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C2653" s="3">
+        <v>110.886</v>
+      </c>
+      <c r="D2653" s="3">
+        <v>77.196</v>
+      </c>
+      <c r="E2653" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2653" s="3">
+        <v>33.69</v>
+      </c>
+      <c r="G2653" s="3">
+        <v>77.196</v>
+      </c>
+    </row>
+    <row r="2654">
+      <c r="A2654" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2654" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C2654" s="3">
+        <v>108.595</v>
+      </c>
+      <c r="D2654" s="3">
+        <v>96.307</v>
+      </c>
+      <c r="E2654" s="3">
+        <v>1.382</v>
+      </c>
+      <c r="F2654" s="3">
+        <v>12.288</v>
+      </c>
+      <c r="G2654" s="3">
+        <v>97.689</v>
+      </c>
+    </row>
+    <row r="2655">
+      <c r="A2655" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2655" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C2655" s="3">
+        <v>104.013</v>
+      </c>
+      <c r="D2655" s="3">
+        <v>103.603</v>
+      </c>
+      <c r="E2655" s="3">
+        <v>4.045</v>
+      </c>
+      <c r="F2655" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="G2655" s="3">
+        <v>107.648</v>
+      </c>
+    </row>
+    <row r="2656">
+      <c r="A2656" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2656" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C2656" s="3">
+        <v>98.24</v>
+      </c>
+      <c r="D2656" s="3">
+        <v>98.24</v>
+      </c>
+      <c r="E2656" s="3">
+        <v>9.882</v>
+      </c>
+      <c r="F2656" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2656" s="3">
+        <v>108.122</v>
+      </c>
+    </row>
+    <row r="2657">
+      <c r="A2657" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2657" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C2657" s="3">
+        <v>86.579</v>
+      </c>
+      <c r="D2657" s="3">
+        <v>86.579</v>
+      </c>
+      <c r="E2657" s="3">
+        <v>21.453</v>
+      </c>
+      <c r="F2657" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2657" s="3">
+        <v>108.032</v>
+      </c>
+    </row>
+    <row r="2658">
+      <c r="A2658" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2658" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C2658" s="3">
+        <v>78.874</v>
+      </c>
+      <c r="D2658" s="3">
+        <v>78.874</v>
+      </c>
+      <c r="E2658" s="3">
+        <v>28.774</v>
+      </c>
+      <c r="F2658" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2658" s="3">
+        <v>107.648</v>
+      </c>
+    </row>
+    <row r="2659">
+      <c r="A2659" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2659" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C2659" s="3">
+        <v>82.445</v>
+      </c>
+      <c r="D2659" s="3">
+        <v>82.445</v>
+      </c>
+      <c r="E2659" s="3">
+        <v>25.293</v>
+      </c>
+      <c r="F2659" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2659" s="3">
+        <v>107.738</v>
+      </c>
+    </row>
+    <row r="2660">
+      <c r="A2660" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2660" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C2660" s="3">
+        <v>75.418</v>
+      </c>
+      <c r="D2660" s="3">
+        <v>73.37</v>
+      </c>
+      <c r="E2660" s="3">
+        <v>11.776</v>
+      </c>
+      <c r="F2660" s="3">
+        <v>2.048</v>
+      </c>
+      <c r="G2660" s="3">
+        <v>85.146</v>
+      </c>
+    </row>
+    <row r="2661">
+      <c r="A2661" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2661" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C2661" s="3">
+        <v>62.899</v>
+      </c>
+      <c r="D2661" s="3">
+        <v>62.899</v>
+      </c>
+      <c r="E2661" s="3">
+        <v>42.752</v>
+      </c>
+      <c r="F2661" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2661" s="3">
+        <v>105.651</v>
+      </c>
+    </row>
+    <row r="2662">
+      <c r="A2662" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2662" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C2662" s="3">
+        <v>29.363</v>
+      </c>
+      <c r="D2662" s="3">
+        <v>29.363</v>
+      </c>
+      <c r="E2662" s="3">
+        <v>75.981</v>
+      </c>
+      <c r="F2662" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2662" s="3">
+        <v>105.344</v>
+      </c>
+    </row>
+    <row r="2663">
+      <c r="A2663" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2663" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C2663" s="3">
+        <v>46.17</v>
+      </c>
+      <c r="D2663" s="3">
+        <v>46.17</v>
+      </c>
+      <c r="E2663" s="3">
+        <v>59.341</v>
+      </c>
+      <c r="F2663" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2663" s="3">
+        <v>105.511</v>
+      </c>
+    </row>
+    <row r="2664">
+      <c r="A2664" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2664" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C2664" s="3">
+        <v>46.746</v>
+      </c>
+      <c r="D2664" s="3">
+        <v>46.746</v>
+      </c>
+      <c r="E2664" s="3">
+        <v>58.47</v>
+      </c>
+      <c r="F2664" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2664" s="3">
+        <v>105.216</v>
+      </c>
+    </row>
+    <row r="2665">
+      <c r="A2665" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2665" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C2665" s="3">
+        <v>37.184</v>
+      </c>
+      <c r="D2665" s="3">
+        <v>37.184</v>
+      </c>
+      <c r="E2665" s="3">
+        <v>67.942</v>
+      </c>
+      <c r="F2665" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2665" s="3">
+        <v>105.126</v>
+      </c>
+    </row>
+    <row r="2666">
+      <c r="A2666" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2666" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C2666" s="3">
+        <v>28.672</v>
+      </c>
+      <c r="D2666" s="3">
+        <v>28.672</v>
+      </c>
+      <c r="E2666" s="3">
+        <v>76.851</v>
+      </c>
+      <c r="F2666" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2666" s="3">
+        <v>105.523</v>
+      </c>
+    </row>
+    <row r="2667">
+      <c r="A2667" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2667" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C2667" s="3">
+        <v>20.506</v>
+      </c>
+      <c r="D2667" s="3">
+        <v>20.506</v>
+      </c>
+      <c r="E2667" s="3">
+        <v>85.094</v>
+      </c>
+      <c r="F2667" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2667" s="3">
+        <v>105.6</v>
+      </c>
+    </row>
+    <row r="2668">
+      <c r="A2668" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2668" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C2668" s="3">
+        <v>13.248</v>
+      </c>
+      <c r="D2668" s="3">
+        <v>13.248</v>
+      </c>
+      <c r="E2668" s="3">
+        <v>92.314</v>
+      </c>
+      <c r="F2668" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2668" s="3">
+        <v>105.562</v>
+      </c>
+    </row>
+    <row r="2669">
+      <c r="A2669" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2669" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C2669" s="3">
+        <v>7.283</v>
+      </c>
+      <c r="D2669" s="3">
+        <v>7.283</v>
+      </c>
+      <c r="E2669" s="3">
+        <v>98.15</v>
+      </c>
+      <c r="F2669" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2669" s="3">
+        <v>105.433</v>
+      </c>
+    </row>
+    <row r="2670">
+      <c r="A2670" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2670" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C2670" s="3">
+        <v>2.957</v>
+      </c>
+      <c r="D2670" s="3">
+        <v>2.957</v>
+      </c>
+      <c r="E2670" s="3">
+        <v>102.502</v>
+      </c>
+      <c r="F2670" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2670" s="3">
+        <v>105.459</v>
+      </c>
+    </row>
+    <row r="2671">
+      <c r="A2671" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2671" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C2671" s="3">
+        <v>1.037</v>
+      </c>
+      <c r="D2671" s="3">
+        <v>1.037</v>
+      </c>
+      <c r="E2671" s="3">
+        <v>104.038</v>
+      </c>
+      <c r="F2671" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2671" s="3">
+        <v>105.075</v>
+      </c>
+    </row>
+    <row r="2672">
+      <c r="A2672" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2672" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C2672" s="3">
+        <v>0.166</v>
+      </c>
+      <c r="D2672" s="3">
+        <v>0.166</v>
+      </c>
+      <c r="E2672" s="3">
+        <v>104.96</v>
+      </c>
+      <c r="F2672" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2672" s="3">
+        <v>105.126</v>
+      </c>
+    </row>
+    <row r="2673">
+      <c r="A2673" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2673" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C2673" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2673" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2673" s="3">
+        <v>105.114</v>
+      </c>
+      <c r="F2673" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2673" s="3">
+        <v>105.114</v>
+      </c>
+    </row>
+    <row r="2674">
+      <c r="A2674" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2674" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C2674" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2674" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2674" s="3">
+        <v>105.114</v>
+      </c>
+      <c r="F2674" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2674" s="3">
+        <v>105.114</v>
+      </c>
+    </row>
+    <row r="2675">
+      <c r="A2675" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2675" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C2675" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2675" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2675" s="3">
+        <v>105.779</v>
+      </c>
+      <c r="F2675" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2675" s="3">
+        <v>105.779</v>
+      </c>
+    </row>
+    <row r="2676">
+      <c r="A2676" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2676" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C2676" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2676" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2676" s="3">
+        <v>106.138</v>
+      </c>
+      <c r="F2676" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2676" s="3">
+        <v>106.138</v>
+      </c>
+    </row>
+    <row r="2677">
+      <c r="A2677" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2677" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C2677" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2677" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2677" s="3">
+        <v>106.086</v>
+      </c>
+      <c r="F2677" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2677" s="3">
+        <v>106.086</v>
+      </c>
+    </row>
+    <row r="2678">
+      <c r="A2678" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2678" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C2678" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2678" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2678" s="3">
+        <v>105.882</v>
+      </c>
+      <c r="F2678" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2678" s="3">
+        <v>105.882</v>
+      </c>
+    </row>
+    <row r="2679">
+      <c r="A2679" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2679" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C2679" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2679" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2679" s="3">
+        <v>105.574</v>
+      </c>
+      <c r="F2679" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2679" s="3">
+        <v>105.574</v>
+      </c>
+    </row>
+    <row r="2680">
+      <c r="A2680" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2680" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C2680" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2680" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2680" s="3">
+        <v>105.626</v>
+      </c>
+      <c r="F2680" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2680" s="3">
+        <v>105.626</v>
+      </c>
+    </row>
+    <row r="2681">
+      <c r="A2681" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2681" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C2681" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2681" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2681" s="3">
+        <v>105.472</v>
+      </c>
+      <c r="F2681" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2681" s="3">
+        <v>105.472</v>
+      </c>
+    </row>
+    <row r="2682">
+      <c r="A2682" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2682" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C2682" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2682" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2682" s="3">
+        <v>105.574</v>
+      </c>
+      <c r="F2682" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2682" s="3">
+        <v>105.574</v>
+      </c>
+    </row>
+    <row r="2683">
+      <c r="A2683" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2683" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C2683" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2683" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2683" s="3">
+        <v>106.342</v>
+      </c>
+      <c r="F2683" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2683" s="3">
+        <v>106.342</v>
+      </c>
+    </row>
+    <row r="2684">
+      <c r="A2684" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2684" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C2684" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2684" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2684" s="3">
+        <v>106.394</v>
+      </c>
+      <c r="F2684" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2684" s="3">
+        <v>106.394</v>
+      </c>
+    </row>
+    <row r="2685">
+      <c r="A2685" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2685" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C2685" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2685" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2685" s="3">
+        <v>105.37</v>
+      </c>
+      <c r="F2685" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2685" s="3">
+        <v>105.37</v>
+      </c>
+    </row>
+    <row r="2686">
+      <c r="A2686" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2686" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C2686" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2686" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2686" s="3">
+        <v>106.24</v>
+      </c>
+      <c r="F2686" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2686" s="3">
+        <v>106.24</v>
+      </c>
+    </row>
+    <row r="2687">
+      <c r="A2687" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2687" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C2687" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2687" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2687" s="3">
+        <v>105.574</v>
+      </c>
+      <c r="F2687" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2687" s="3">
+        <v>105.574</v>
+      </c>
+    </row>
+    <row r="2688">
+      <c r="A2688" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2688" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C2688" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2688" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2688" s="3">
+        <v>105.523</v>
+      </c>
+      <c r="F2688" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2688" s="3">
+        <v>105.523</v>
+      </c>
+    </row>
+    <row r="2689">
+      <c r="A2689" s="2">
+        <v>46323</v>
+      </c>
+      <c r="B2689" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C2689" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2689" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2689" s="3">
+        <v>105.472</v>
+      </c>
+      <c r="F2689" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2689" s="3">
+        <v>105.472</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2593"/>
+  <autoFilter ref="A1:G2689"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -814,45 +814,69 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B33" s="4">
+        <v>2657.9</v>
+      </c>
+      <c r="C33" s="4">
+        <v>2299.9</v>
+      </c>
+      <c r="D33" s="4">
+        <v>5589.4</v>
+      </c>
+      <c r="E33" s="4">
+        <v>357.9</v>
+      </c>
+      <c r="F33" s="4">
+        <v>7889.4</v>
+      </c>
+      <c r="G33" s="5">
+        <f>IF(F33&gt;0,C33/F33,"")</f>
+        <v>0.2915</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B33" s="7">
-        <f>SUM(B5:B32)</f>
-        <v>66665.5</v>
-      </c>
-      <c r="C33" s="7">
-        <f>SUM(C5:C32)</f>
-        <v>45095.0</v>
-      </c>
-      <c r="D33" s="7">
-        <f>SUM(D5:D32)</f>
-        <v>148805.8</v>
-      </c>
-      <c r="E33" s="7">
-        <f>SUM(E5:E32)</f>
-        <v>21571.1</v>
-      </c>
-      <c r="F33" s="7">
-        <f>SUM(F5:F32)</f>
-        <v>193900.9</v>
-      </c>
-      <c r="G33" s="8">
-        <f>IF(F33&gt;0,C33/F33,"")</f>
-        <v>0.2326</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B34" s="7">
+        <f>SUM(B5:B33)</f>
+        <v>69323.4</v>
+      </c>
+      <c r="C34" s="7">
+        <f>SUM(C5:C33)</f>
+        <v>47395.0</v>
+      </c>
+      <c r="D34" s="7">
+        <f>SUM(D5:D33)</f>
+        <v>154395.3</v>
+      </c>
+      <c r="E34" s="7">
+        <f>SUM(E5:E33)</f>
+        <v>21929.0</v>
+      </c>
+      <c r="F34" s="7">
+        <f>SUM(F5:F33)</f>
+        <v>201790.3</v>
+      </c>
+      <c r="G34" s="8">
+        <f>IF(F34&gt;0,C34/F34,"")</f>
+        <v>0.2349</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -68111,7 +68135,2407 @@
         <v>105.472</v>
       </c>
     </row>
+    <row r="2690">
+      <c r="A2690" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2690" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C2690" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2690" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2690" s="3">
+        <v>105.318</v>
+      </c>
+      <c r="F2690" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2690" s="3">
+        <v>105.318</v>
+      </c>
+    </row>
+    <row r="2691">
+      <c r="A2691" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2691" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C2691" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2691" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2691" s="3">
+        <v>105.626</v>
+      </c>
+      <c r="F2691" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2691" s="3">
+        <v>105.626</v>
+      </c>
+    </row>
+    <row r="2692">
+      <c r="A2692" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2692" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C2692" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2692" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2692" s="3">
+        <v>105.728</v>
+      </c>
+      <c r="F2692" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2692" s="3">
+        <v>105.728</v>
+      </c>
+    </row>
+    <row r="2693">
+      <c r="A2693" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2693" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C2693" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2693" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2693" s="3">
+        <v>105.165</v>
+      </c>
+      <c r="F2693" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2693" s="3">
+        <v>105.165</v>
+      </c>
+    </row>
+    <row r="2694">
+      <c r="A2694" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2694" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C2694" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2694" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2694" s="3">
+        <v>105.267</v>
+      </c>
+      <c r="F2694" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2694" s="3">
+        <v>105.267</v>
+      </c>
+    </row>
+    <row r="2695">
+      <c r="A2695" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2695" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C2695" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2695" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2695" s="3">
+        <v>105.062</v>
+      </c>
+      <c r="F2695" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2695" s="3">
+        <v>105.062</v>
+      </c>
+    </row>
+    <row r="2696">
+      <c r="A2696" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2696" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C2696" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2696" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2696" s="3">
+        <v>105.37</v>
+      </c>
+      <c r="F2696" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2696" s="3">
+        <v>105.37</v>
+      </c>
+    </row>
+    <row r="2697">
+      <c r="A2697" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2697" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C2697" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2697" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2697" s="3">
+        <v>105.216</v>
+      </c>
+      <c r="F2697" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2697" s="3">
+        <v>105.216</v>
+      </c>
+    </row>
+    <row r="2698">
+      <c r="A2698" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2698" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C2698" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2698" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2698" s="3">
+        <v>105.267</v>
+      </c>
+      <c r="F2698" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2698" s="3">
+        <v>105.267</v>
+      </c>
+    </row>
+    <row r="2699">
+      <c r="A2699" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2699" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C2699" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2699" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2699" s="3">
+        <v>104.96</v>
+      </c>
+      <c r="F2699" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2699" s="3">
+        <v>104.96</v>
+      </c>
+    </row>
+    <row r="2700">
+      <c r="A2700" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2700" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C2700" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2700" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2700" s="3">
+        <v>104.96</v>
+      </c>
+      <c r="F2700" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2700" s="3">
+        <v>104.96</v>
+      </c>
+    </row>
+    <row r="2701">
+      <c r="A2701" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2701" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C2701" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2701" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2701" s="3">
+        <v>102.246</v>
+      </c>
+      <c r="F2701" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2701" s="3">
+        <v>102.246</v>
+      </c>
+    </row>
+    <row r="2702">
+      <c r="A2702" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2702" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C2702" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2702" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2702" s="3">
+        <v>102.093</v>
+      </c>
+      <c r="F2702" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2702" s="3">
+        <v>102.093</v>
+      </c>
+    </row>
+    <row r="2703">
+      <c r="A2703" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2703" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C2703" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2703" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2703" s="3">
+        <v>102.298</v>
+      </c>
+      <c r="F2703" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2703" s="3">
+        <v>102.298</v>
+      </c>
+    </row>
+    <row r="2704">
+      <c r="A2704" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2704" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C2704" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2704" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2704" s="3">
+        <v>102.4</v>
+      </c>
+      <c r="F2704" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2704" s="3">
+        <v>102.4</v>
+      </c>
+    </row>
+    <row r="2705">
+      <c r="A2705" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2705" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C2705" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2705" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2705" s="3">
+        <v>102.349</v>
+      </c>
+      <c r="F2705" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2705" s="3">
+        <v>102.349</v>
+      </c>
+    </row>
+    <row r="2706">
+      <c r="A2706" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2706" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C2706" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2706" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2706" s="3">
+        <v>102.502</v>
+      </c>
+      <c r="F2706" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2706" s="3">
+        <v>102.502</v>
+      </c>
+    </row>
+    <row r="2707">
+      <c r="A2707" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2707" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C2707" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2707" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2707" s="3">
+        <v>102.093</v>
+      </c>
+      <c r="F2707" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2707" s="3">
+        <v>102.093</v>
+      </c>
+    </row>
+    <row r="2708">
+      <c r="A2708" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2708" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C2708" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2708" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2708" s="3">
+        <v>102.502</v>
+      </c>
+      <c r="F2708" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2708" s="3">
+        <v>102.502</v>
+      </c>
+    </row>
+    <row r="2709">
+      <c r="A2709" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2709" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C2709" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2709" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2709" s="3">
+        <v>103.014</v>
+      </c>
+      <c r="F2709" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2709" s="3">
+        <v>103.014</v>
+      </c>
+    </row>
+    <row r="2710">
+      <c r="A2710" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2710" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C2710" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2710" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2710" s="3">
+        <v>102.656</v>
+      </c>
+      <c r="F2710" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2710" s="3">
+        <v>102.656</v>
+      </c>
+    </row>
+    <row r="2711">
+      <c r="A2711" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2711" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C2711" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2711" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2711" s="3">
+        <v>102.195</v>
+      </c>
+      <c r="F2711" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2711" s="3">
+        <v>102.195</v>
+      </c>
+    </row>
+    <row r="2712">
+      <c r="A2712" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2712" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C2712" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2712" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2712" s="3">
+        <v>102.605</v>
+      </c>
+      <c r="F2712" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2712" s="3">
+        <v>102.605</v>
+      </c>
+    </row>
+    <row r="2713">
+      <c r="A2713" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2713" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C2713" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2713" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2713" s="3">
+        <v>102.195</v>
+      </c>
+      <c r="F2713" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2713" s="3">
+        <v>102.195</v>
+      </c>
+    </row>
+    <row r="2714">
+      <c r="A2714" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2714" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C2714" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2714" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2714" s="3">
+        <v>102.195</v>
+      </c>
+      <c r="F2714" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2714" s="3">
+        <v>102.195</v>
+      </c>
+    </row>
+    <row r="2715">
+      <c r="A2715" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2715" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C2715" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="D2715" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="E2715" s="3">
+        <v>102.451</v>
+      </c>
+      <c r="F2715" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2715" s="3">
+        <v>102.464</v>
+      </c>
+    </row>
+    <row r="2716">
+      <c r="A2716" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2716" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C2716" s="3">
+        <v>0.435</v>
+      </c>
+      <c r="D2716" s="3">
+        <v>0.435</v>
+      </c>
+      <c r="E2716" s="3">
+        <v>102.4</v>
+      </c>
+      <c r="F2716" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2716" s="3">
+        <v>102.835</v>
+      </c>
+    </row>
+    <row r="2717">
+      <c r="A2717" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2717" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C2717" s="3">
+        <v>1.229</v>
+      </c>
+      <c r="D2717" s="3">
+        <v>1.229</v>
+      </c>
+      <c r="E2717" s="3">
+        <v>101.274</v>
+      </c>
+      <c r="F2717" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2717" s="3">
+        <v>102.503</v>
+      </c>
+    </row>
+    <row r="2718">
+      <c r="A2718" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2718" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C2718" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="D2718" s="3">
+        <v>2.79</v>
+      </c>
+      <c r="E2718" s="3">
+        <v>99.533</v>
+      </c>
+      <c r="F2718" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2718" s="3">
+        <v>102.323</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2719" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C2719" s="3">
+        <v>7.68</v>
+      </c>
+      <c r="D2719" s="3">
+        <v>7.68</v>
+      </c>
+      <c r="E2719" s="3">
+        <v>95.334</v>
+      </c>
+      <c r="F2719" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2719" s="3">
+        <v>103.014</v>
+      </c>
+    </row>
+    <row r="2720">
+      <c r="A2720" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2720" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C2720" s="3">
+        <v>13.76</v>
+      </c>
+      <c r="D2720" s="3">
+        <v>13.76</v>
+      </c>
+      <c r="E2720" s="3">
+        <v>90.01</v>
+      </c>
+      <c r="F2720" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2720" s="3">
+        <v>103.77</v>
+      </c>
+    </row>
+    <row r="2721">
+      <c r="A2721" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2721" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C2721" s="3">
+        <v>21.338</v>
+      </c>
+      <c r="D2721" s="3">
+        <v>21.338</v>
+      </c>
+      <c r="E2721" s="3">
+        <v>81.715</v>
+      </c>
+      <c r="F2721" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2721" s="3">
+        <v>103.053</v>
+      </c>
+    </row>
+    <row r="2722">
+      <c r="A2722" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2722" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C2722" s="3">
+        <v>29.632</v>
+      </c>
+      <c r="D2722" s="3">
+        <v>29.632</v>
+      </c>
+      <c r="E2722" s="3">
+        <v>72.909</v>
+      </c>
+      <c r="F2722" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2722" s="3">
+        <v>102.541</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2723" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C2723" s="3">
+        <v>38.234</v>
+      </c>
+      <c r="D2723" s="3">
+        <v>38.234</v>
+      </c>
+      <c r="E2723" s="3">
+        <v>64.154</v>
+      </c>
+      <c r="F2723" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2723" s="3">
+        <v>102.388</v>
+      </c>
+    </row>
+    <row r="2724">
+      <c r="A2724" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2724" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C2724" s="3">
+        <v>46.528</v>
+      </c>
+      <c r="D2724" s="3">
+        <v>46.528</v>
+      </c>
+      <c r="E2724" s="3">
+        <v>55.91</v>
+      </c>
+      <c r="F2724" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2724" s="3">
+        <v>102.438</v>
+      </c>
+    </row>
+    <row r="2725">
+      <c r="A2725" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2725" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C2725" s="3">
+        <v>54.477</v>
+      </c>
+      <c r="D2725" s="3">
+        <v>54.477</v>
+      </c>
+      <c r="E2725" s="3">
+        <v>48.435</v>
+      </c>
+      <c r="F2725" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2725" s="3">
+        <v>102.912</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2726" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C2726" s="3">
+        <v>62.157</v>
+      </c>
+      <c r="D2726" s="3">
+        <v>62.157</v>
+      </c>
+      <c r="E2726" s="3">
+        <v>40.448</v>
+      </c>
+      <c r="F2726" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2726" s="3">
+        <v>102.605</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2727" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C2727" s="3">
+        <v>69.338</v>
+      </c>
+      <c r="D2727" s="3">
+        <v>69.338</v>
+      </c>
+      <c r="E2727" s="3">
+        <v>34.304</v>
+      </c>
+      <c r="F2727" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2727" s="3">
+        <v>103.642</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2728" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C2728" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2728" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2728" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2728" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2728" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2729" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C2729" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2729" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2729" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2729" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2729" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="2730">
+      <c r="A2730" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2730" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C2730" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2730" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2730" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2730" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2730" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="2731">
+      <c r="A2731" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2731" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C2731" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2731" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2731" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2731" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2731" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2732" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C2732" s="3">
+        <v>43.379</v>
+      </c>
+      <c r="D2732" s="3">
+        <v>38.515</v>
+      </c>
+      <c r="E2732" s="3">
+        <v>13.517</v>
+      </c>
+      <c r="F2732" s="3">
+        <v>4.864</v>
+      </c>
+      <c r="G2732" s="3">
+        <v>52.032</v>
+      </c>
+    </row>
+    <row r="2733">
+      <c r="A2733" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2733" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C2733" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2733" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2733" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2733" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2733" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="2734">
+      <c r="A2734" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2734" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C2734" s="3">
+        <v>1.728</v>
+      </c>
+      <c r="D2734" s="3">
+        <v>1.728</v>
+      </c>
+      <c r="E2734" s="3">
+        <v>14.899</v>
+      </c>
+      <c r="F2734" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2734" s="3">
+        <v>16.627</v>
+      </c>
+    </row>
+    <row r="2735">
+      <c r="A2735" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2735" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C2735" s="3">
+        <v>7.488</v>
+      </c>
+      <c r="D2735" s="3">
+        <v>7.488</v>
+      </c>
+      <c r="E2735" s="3">
+        <v>32.0</v>
+      </c>
+      <c r="F2735" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2735" s="3">
+        <v>39.488</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2736" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C2736" s="3">
+        <v>66.202</v>
+      </c>
+      <c r="D2736" s="3">
+        <v>65.588</v>
+      </c>
+      <c r="E2736" s="3">
+        <v>24.166</v>
+      </c>
+      <c r="F2736" s="3">
+        <v>0.614</v>
+      </c>
+      <c r="G2736" s="3">
+        <v>89.754</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2737" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C2737" s="3">
+        <v>112.678</v>
+      </c>
+      <c r="D2737" s="3">
+        <v>107.148</v>
+      </c>
+      <c r="E2737" s="3">
+        <v>0.154</v>
+      </c>
+      <c r="F2737" s="3">
+        <v>5.53</v>
+      </c>
+      <c r="G2737" s="3">
+        <v>107.302</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2738" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C2738" s="3">
+        <v>113.28</v>
+      </c>
+      <c r="D2738" s="3">
+        <v>107.443</v>
+      </c>
+      <c r="E2738" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="F2738" s="3">
+        <v>5.837</v>
+      </c>
+      <c r="G2738" s="3">
+        <v>107.494</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2739" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C2739" s="3">
+        <v>112.499</v>
+      </c>
+      <c r="D2739" s="3">
+        <v>106.304</v>
+      </c>
+      <c r="E2739" s="3">
+        <v>1.024</v>
+      </c>
+      <c r="F2739" s="3">
+        <v>6.195</v>
+      </c>
+      <c r="G2739" s="3">
+        <v>107.328</v>
+      </c>
+    </row>
+    <row r="2740">
+      <c r="A2740" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2740" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C2740" s="3">
+        <v>78.643</v>
+      </c>
+      <c r="D2740" s="3">
+        <v>74.905</v>
+      </c>
+      <c r="E2740" s="3">
+        <v>32.256</v>
+      </c>
+      <c r="F2740" s="3">
+        <v>3.738</v>
+      </c>
+      <c r="G2740" s="3">
+        <v>107.161</v>
+      </c>
+    </row>
+    <row r="2741">
+      <c r="A2741" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2741" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C2741" s="3">
+        <v>79.629</v>
+      </c>
+      <c r="D2741" s="3">
+        <v>75.328</v>
+      </c>
+      <c r="E2741" s="3">
+        <v>31.744</v>
+      </c>
+      <c r="F2741" s="3">
+        <v>4.301</v>
+      </c>
+      <c r="G2741" s="3">
+        <v>107.072</v>
+      </c>
+    </row>
+    <row r="2742">
+      <c r="A2742" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2742" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C2742" s="3">
+        <v>114.445</v>
+      </c>
+      <c r="D2742" s="3">
+        <v>87.719</v>
+      </c>
+      <c r="E2742" s="3">
+        <v>0.205</v>
+      </c>
+      <c r="F2742" s="3">
+        <v>26.726</v>
+      </c>
+      <c r="G2742" s="3">
+        <v>87.924</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2743" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C2743" s="3">
+        <v>68.659</v>
+      </c>
+      <c r="D2743" s="3">
+        <v>51.507</v>
+      </c>
+      <c r="E2743" s="3">
+        <v>22.374</v>
+      </c>
+      <c r="F2743" s="3">
+        <v>17.152</v>
+      </c>
+      <c r="G2743" s="3">
+        <v>73.881</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2744" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C2744" s="3">
+        <v>114.278</v>
+      </c>
+      <c r="D2744" s="3">
+        <v>74.547</v>
+      </c>
+      <c r="E2744" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2744" s="3">
+        <v>39.731</v>
+      </c>
+      <c r="G2744" s="3">
+        <v>74.547</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2745" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C2745" s="3">
+        <v>111.104</v>
+      </c>
+      <c r="D2745" s="3">
+        <v>74.957</v>
+      </c>
+      <c r="E2745" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2745" s="3">
+        <v>36.147</v>
+      </c>
+      <c r="G2745" s="3">
+        <v>74.957</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2746" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C2746" s="3">
+        <v>91.712</v>
+      </c>
+      <c r="D2746" s="3">
+        <v>77.837</v>
+      </c>
+      <c r="E2746" s="3">
+        <v>12.493</v>
+      </c>
+      <c r="F2746" s="3">
+        <v>13.875</v>
+      </c>
+      <c r="G2746" s="3">
+        <v>90.33</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2747" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C2747" s="3">
+        <v>88.346</v>
+      </c>
+      <c r="D2747" s="3">
+        <v>86.554</v>
+      </c>
+      <c r="E2747" s="3">
+        <v>20.48</v>
+      </c>
+      <c r="F2747" s="3">
+        <v>1.792</v>
+      </c>
+      <c r="G2747" s="3">
+        <v>107.034</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2748" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C2748" s="3">
+        <v>93.824</v>
+      </c>
+      <c r="D2748" s="3">
+        <v>79.232</v>
+      </c>
+      <c r="E2748" s="3">
+        <v>15.155</v>
+      </c>
+      <c r="F2748" s="3">
+        <v>14.592</v>
+      </c>
+      <c r="G2748" s="3">
+        <v>94.387</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2749" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C2749" s="3">
+        <v>74.266</v>
+      </c>
+      <c r="D2749" s="3">
+        <v>38.221</v>
+      </c>
+      <c r="E2749" s="3">
+        <v>6.246</v>
+      </c>
+      <c r="F2749" s="3">
+        <v>36.045</v>
+      </c>
+      <c r="G2749" s="3">
+        <v>44.467</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2750" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C2750" s="3">
+        <v>107.635</v>
+      </c>
+      <c r="D2750" s="3">
+        <v>68.313</v>
+      </c>
+      <c r="E2750" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2750" s="3">
+        <v>39.322</v>
+      </c>
+      <c r="G2750" s="3">
+        <v>68.313</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2751" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C2751" s="3">
+        <v>105.485</v>
+      </c>
+      <c r="D2751" s="3">
+        <v>73.331</v>
+      </c>
+      <c r="E2751" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2751" s="3">
+        <v>32.154</v>
+      </c>
+      <c r="G2751" s="3">
+        <v>73.331</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2752" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C2752" s="3">
+        <v>50.829</v>
+      </c>
+      <c r="D2752" s="3">
+        <v>40.794</v>
+      </c>
+      <c r="E2752" s="3">
+        <v>30.259</v>
+      </c>
+      <c r="F2752" s="3">
+        <v>10.035</v>
+      </c>
+      <c r="G2752" s="3">
+        <v>71.053</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2753" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C2753" s="3">
+        <v>76.045</v>
+      </c>
+      <c r="D2753" s="3">
+        <v>57.613</v>
+      </c>
+      <c r="E2753" s="3">
+        <v>14.541</v>
+      </c>
+      <c r="F2753" s="3">
+        <v>18.432</v>
+      </c>
+      <c r="G2753" s="3">
+        <v>72.154</v>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2754" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C2754" s="3">
+        <v>93.12</v>
+      </c>
+      <c r="D2754" s="3">
+        <v>72.23</v>
+      </c>
+      <c r="E2754" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2754" s="3">
+        <v>20.89</v>
+      </c>
+      <c r="G2754" s="3">
+        <v>72.23</v>
+      </c>
+    </row>
+    <row r="2755">
+      <c r="A2755" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2755" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C2755" s="3">
+        <v>85.427</v>
+      </c>
+      <c r="D2755" s="3">
+        <v>71.654</v>
+      </c>
+      <c r="E2755" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2755" s="3">
+        <v>13.773</v>
+      </c>
+      <c r="G2755" s="3">
+        <v>71.654</v>
+      </c>
+    </row>
+    <row r="2756">
+      <c r="A2756" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2756" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C2756" s="3">
+        <v>77.312</v>
+      </c>
+      <c r="D2756" s="3">
+        <v>71.68</v>
+      </c>
+      <c r="E2756" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2756" s="3">
+        <v>5.632</v>
+      </c>
+      <c r="G2756" s="3">
+        <v>71.68</v>
+      </c>
+    </row>
+    <row r="2757">
+      <c r="A2757" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2757" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C2757" s="3">
+        <v>69.824</v>
+      </c>
+      <c r="D2757" s="3">
+        <v>69.261</v>
+      </c>
+      <c r="E2757" s="3">
+        <v>3.635</v>
+      </c>
+      <c r="F2757" s="3">
+        <v>0.563</v>
+      </c>
+      <c r="G2757" s="3">
+        <v>72.896</v>
+      </c>
+    </row>
+    <row r="2758">
+      <c r="A2758" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2758" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C2758" s="3">
+        <v>61.734</v>
+      </c>
+      <c r="D2758" s="3">
+        <v>61.734</v>
+      </c>
+      <c r="E2758" s="3">
+        <v>10.752</v>
+      </c>
+      <c r="F2758" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2758" s="3">
+        <v>72.486</v>
+      </c>
+    </row>
+    <row r="2759">
+      <c r="A2759" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2759" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C2759" s="3">
+        <v>53.632</v>
+      </c>
+      <c r="D2759" s="3">
+        <v>53.632</v>
+      </c>
+      <c r="E2759" s="3">
+        <v>18.995</v>
+      </c>
+      <c r="F2759" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2759" s="3">
+        <v>72.627</v>
+      </c>
+    </row>
+    <row r="2760">
+      <c r="A2760" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2760" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C2760" s="3">
+        <v>45.158</v>
+      </c>
+      <c r="D2760" s="3">
+        <v>45.158</v>
+      </c>
+      <c r="E2760" s="3">
+        <v>26.726</v>
+      </c>
+      <c r="F2760" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2760" s="3">
+        <v>71.884</v>
+      </c>
+    </row>
+    <row r="2761">
+      <c r="A2761" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2761" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C2761" s="3">
+        <v>37.197</v>
+      </c>
+      <c r="D2761" s="3">
+        <v>37.197</v>
+      </c>
+      <c r="E2761" s="3">
+        <v>34.458</v>
+      </c>
+      <c r="F2761" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2761" s="3">
+        <v>71.655</v>
+      </c>
+    </row>
+    <row r="2762">
+      <c r="A2762" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2762" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C2762" s="3">
+        <v>29.222</v>
+      </c>
+      <c r="D2762" s="3">
+        <v>29.222</v>
+      </c>
+      <c r="E2762" s="3">
+        <v>43.981</v>
+      </c>
+      <c r="F2762" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2762" s="3">
+        <v>73.203</v>
+      </c>
+    </row>
+    <row r="2763">
+      <c r="A2763" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2763" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C2763" s="3">
+        <v>20.646</v>
+      </c>
+      <c r="D2763" s="3">
+        <v>20.646</v>
+      </c>
+      <c r="E2763" s="3">
+        <v>52.582</v>
+      </c>
+      <c r="F2763" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2763" s="3">
+        <v>73.228</v>
+      </c>
+    </row>
+    <row r="2764">
+      <c r="A2764" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2764" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C2764" s="3">
+        <v>13.286</v>
+      </c>
+      <c r="D2764" s="3">
+        <v>13.286</v>
+      </c>
+      <c r="E2764" s="3">
+        <v>59.648</v>
+      </c>
+      <c r="F2764" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2764" s="3">
+        <v>72.934</v>
+      </c>
+    </row>
+    <row r="2765">
+      <c r="A2765" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2765" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C2765" s="3">
+        <v>7.206</v>
+      </c>
+      <c r="D2765" s="3">
+        <v>7.206</v>
+      </c>
+      <c r="E2765" s="3">
+        <v>65.229</v>
+      </c>
+      <c r="F2765" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2765" s="3">
+        <v>72.435</v>
+      </c>
+    </row>
+    <row r="2766">
+      <c r="A2766" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2766" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C2766" s="3">
+        <v>2.944</v>
+      </c>
+      <c r="D2766" s="3">
+        <v>2.944</v>
+      </c>
+      <c r="E2766" s="3">
+        <v>68.454</v>
+      </c>
+      <c r="F2766" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2766" s="3">
+        <v>71.398</v>
+      </c>
+    </row>
+    <row r="2767">
+      <c r="A2767" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2767" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C2767" s="3">
+        <v>1.075</v>
+      </c>
+      <c r="D2767" s="3">
+        <v>1.075</v>
+      </c>
+      <c r="E2767" s="3">
+        <v>70.298</v>
+      </c>
+      <c r="F2767" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2767" s="3">
+        <v>71.373</v>
+      </c>
+    </row>
+    <row r="2768">
+      <c r="A2768" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2768" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C2768" s="3">
+        <v>0.307</v>
+      </c>
+      <c r="D2768" s="3">
+        <v>0.307</v>
+      </c>
+      <c r="E2768" s="3">
+        <v>71.27</v>
+      </c>
+      <c r="F2768" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2768" s="3">
+        <v>71.577</v>
+      </c>
+    </row>
+    <row r="2769">
+      <c r="A2769" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2769" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C2769" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="D2769" s="3">
+        <v>0.013</v>
+      </c>
+      <c r="E2769" s="3">
+        <v>71.014</v>
+      </c>
+      <c r="F2769" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2769" s="3">
+        <v>71.027</v>
+      </c>
+    </row>
+    <row r="2770">
+      <c r="A2770" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2770" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C2770" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2770" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2770" s="3">
+        <v>71.117</v>
+      </c>
+      <c r="F2770" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2770" s="3">
+        <v>71.117</v>
+      </c>
+    </row>
+    <row r="2771">
+      <c r="A2771" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2771" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C2771" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2771" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2771" s="3">
+        <v>71.834</v>
+      </c>
+      <c r="F2771" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2771" s="3">
+        <v>71.834</v>
+      </c>
+    </row>
+    <row r="2772">
+      <c r="A2772" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2772" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C2772" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2772" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2772" s="3">
+        <v>71.987</v>
+      </c>
+      <c r="F2772" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2772" s="3">
+        <v>71.987</v>
+      </c>
+    </row>
+    <row r="2773">
+      <c r="A2773" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2773" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C2773" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2773" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2773" s="3">
+        <v>72.038</v>
+      </c>
+      <c r="F2773" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2773" s="3">
+        <v>72.038</v>
+      </c>
+    </row>
+    <row r="2774">
+      <c r="A2774" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2774" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C2774" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2774" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2774" s="3">
+        <v>71.936</v>
+      </c>
+      <c r="F2774" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2774" s="3">
+        <v>71.936</v>
+      </c>
+    </row>
+    <row r="2775">
+      <c r="A2775" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2775" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C2775" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2775" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2775" s="3">
+        <v>71.27</v>
+      </c>
+      <c r="F2775" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2775" s="3">
+        <v>71.27</v>
+      </c>
+    </row>
+    <row r="2776">
+      <c r="A2776" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2776" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C2776" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2776" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2776" s="3">
+        <v>71.117</v>
+      </c>
+      <c r="F2776" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2776" s="3">
+        <v>71.117</v>
+      </c>
+    </row>
+    <row r="2777">
+      <c r="A2777" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2777" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C2777" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2777" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2777" s="3">
+        <v>71.014</v>
+      </c>
+      <c r="F2777" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2777" s="3">
+        <v>71.014</v>
+      </c>
+    </row>
+    <row r="2778">
+      <c r="A2778" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2778" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C2778" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2778" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2778" s="3">
+        <v>71.27</v>
+      </c>
+      <c r="F2778" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2778" s="3">
+        <v>71.27</v>
+      </c>
+    </row>
+    <row r="2779">
+      <c r="A2779" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2779" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C2779" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2779" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2779" s="3">
+        <v>70.861</v>
+      </c>
+      <c r="F2779" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2779" s="3">
+        <v>70.861</v>
+      </c>
+    </row>
+    <row r="2780">
+      <c r="A2780" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2780" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C2780" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2780" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2780" s="3">
+        <v>71.117</v>
+      </c>
+      <c r="F2780" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2780" s="3">
+        <v>71.117</v>
+      </c>
+    </row>
+    <row r="2781">
+      <c r="A2781" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2781" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C2781" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2781" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2781" s="3">
+        <v>70.912</v>
+      </c>
+      <c r="F2781" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2781" s="3">
+        <v>70.912</v>
+      </c>
+    </row>
+    <row r="2782">
+      <c r="A2782" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2782" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C2782" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2782" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2782" s="3">
+        <v>70.861</v>
+      </c>
+      <c r="F2782" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2782" s="3">
+        <v>70.861</v>
+      </c>
+    </row>
+    <row r="2783">
+      <c r="A2783" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2783" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C2783" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2783" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2783" s="3">
+        <v>71.475</v>
+      </c>
+      <c r="F2783" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2783" s="3">
+        <v>71.475</v>
+      </c>
+    </row>
+    <row r="2784">
+      <c r="A2784" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2784" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C2784" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2784" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2784" s="3">
+        <v>70.912</v>
+      </c>
+      <c r="F2784" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2784" s="3">
+        <v>70.912</v>
+      </c>
+    </row>
+    <row r="2785">
+      <c r="A2785" s="2">
+        <v>46324</v>
+      </c>
+      <c r="B2785" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C2785" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2785" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2785" s="3">
+        <v>70.963</v>
+      </c>
+      <c r="F2785" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2785" s="3">
+        <v>70.963</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2689"/>
+  <autoFilter ref="A1:G2785"/>
 </worksheet>
 </file>
--- a/nube/excel/2026-10.xlsx
+++ b/nube/excel/2026-10.xlsx
@@ -838,45 +838,69 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B34" s="4">
+        <v>2927.9</v>
+      </c>
+      <c r="C34" s="4">
+        <v>1378.4</v>
+      </c>
+      <c r="D34" s="4">
+        <v>3486.2</v>
+      </c>
+      <c r="E34" s="4">
+        <v>1549.5</v>
+      </c>
+      <c r="F34" s="4">
+        <v>4864.6</v>
+      </c>
+      <c r="G34" s="5">
+        <f>IF(F34&gt;0,C34/F34,"")</f>
+        <v>0.2834</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Total del mes</t>
         </is>
       </c>
-      <c r="B34" s="7">
-        <f>SUM(B5:B33)</f>
-        <v>69323.4</v>
-      </c>
-      <c r="C34" s="7">
-        <f>SUM(C5:C33)</f>
-        <v>47395.0</v>
-      </c>
-      <c r="D34" s="7">
-        <f>SUM(D5:D33)</f>
-        <v>154395.3</v>
-      </c>
-      <c r="E34" s="7">
-        <f>SUM(E5:E33)</f>
-        <v>21929.0</v>
-      </c>
-      <c r="F34" s="7">
-        <f>SUM(F5:F33)</f>
-        <v>201790.3</v>
-      </c>
-      <c r="G34" s="8">
-        <f>IF(F34&gt;0,C34/F34,"")</f>
-        <v>0.2349</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
-        </is>
+      <c r="B35" s="7">
+        <f>SUM(B5:B34)</f>
+        <v>72251.2</v>
+      </c>
+      <c r="C35" s="7">
+        <f>SUM(C5:C34)</f>
+        <v>48773.4</v>
+      </c>
+      <c r="D35" s="7">
+        <f>SUM(D5:D34)</f>
+        <v>157881.5</v>
+      </c>
+      <c r="E35" s="7">
+        <f>SUM(E5:E34)</f>
+        <v>23478.5</v>
+      </c>
+      <c r="F35" s="7">
+        <f>SUM(F5:F34)</f>
+        <v>206654.9</v>
+      </c>
+      <c r="G35" s="8">
+        <f>IF(F35&gt;0,C35/F35,"")</f>
+        <v>0.236</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solar consumida en sitio = producción solar − inyectada a la red (por intervalo de 15 minutos). Consumo total = solar consumida en sitio + comprada a la red.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">El detalle de cada 15 minutos está en la hoja «Lecturas 15 min».</t>
         </is>
@@ -70535,7 +70559,2407 @@
         <v>70.963</v>
       </c>
     </row>
+    <row r="2786">
+      <c r="A2786" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2786" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:00–00:15</t>
+        </is>
+      </c>
+      <c r="C2786" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2786" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2786" s="3">
+        <v>71.373</v>
+      </c>
+      <c r="F2786" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2786" s="3">
+        <v>71.373</v>
+      </c>
+    </row>
+    <row r="2787">
+      <c r="A2787" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2787" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:15–00:30</t>
+        </is>
+      </c>
+      <c r="C2787" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2787" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2787" s="3">
+        <v>70.861</v>
+      </c>
+      <c r="F2787" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2787" s="3">
+        <v>70.861</v>
+      </c>
+    </row>
+    <row r="2788">
+      <c r="A2788" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2788" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:30–00:45</t>
+        </is>
+      </c>
+      <c r="C2788" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2788" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2788" s="3">
+        <v>70.912</v>
+      </c>
+      <c r="F2788" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2788" s="3">
+        <v>70.912</v>
+      </c>
+    </row>
+    <row r="2789">
+      <c r="A2789" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2789" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00:45–01:00</t>
+        </is>
+      </c>
+      <c r="C2789" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2789" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2789" s="3">
+        <v>71.27</v>
+      </c>
+      <c r="F2789" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2789" s="3">
+        <v>71.27</v>
+      </c>
+    </row>
+    <row r="2790">
+      <c r="A2790" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2790" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:00–01:15</t>
+        </is>
+      </c>
+      <c r="C2790" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2790" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2790" s="3">
+        <v>71.219</v>
+      </c>
+      <c r="F2790" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2790" s="3">
+        <v>71.219</v>
+      </c>
+    </row>
+    <row r="2791">
+      <c r="A2791" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2791" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:15–01:30</t>
+        </is>
+      </c>
+      <c r="C2791" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2791" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2791" s="3">
+        <v>72.192</v>
+      </c>
+      <c r="F2791" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2791" s="3">
+        <v>72.192</v>
+      </c>
+    </row>
+    <row r="2792">
+      <c r="A2792" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2792" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:30–01:45</t>
+        </is>
+      </c>
+      <c r="C2792" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2792" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2792" s="3">
+        <v>72.294</v>
+      </c>
+      <c r="F2792" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2792" s="3">
+        <v>72.294</v>
+      </c>
+    </row>
+    <row r="2793">
+      <c r="A2793" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2793" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01:45–02:00</t>
+        </is>
+      </c>
+      <c r="C2793" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2793" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2793" s="3">
+        <v>71.731</v>
+      </c>
+      <c r="F2793" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2793" s="3">
+        <v>71.731</v>
+      </c>
+    </row>
+    <row r="2794">
+      <c r="A2794" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2794" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:00–02:15</t>
+        </is>
+      </c>
+      <c r="C2794" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2794" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2794" s="3">
+        <v>71.424</v>
+      </c>
+      <c r="F2794" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2794" s="3">
+        <v>71.424</v>
+      </c>
+    </row>
+    <row r="2795">
+      <c r="A2795" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2795" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:15–02:30</t>
+        </is>
+      </c>
+      <c r="C2795" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2795" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2795" s="3">
+        <v>71.629</v>
+      </c>
+      <c r="F2795" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2795" s="3">
+        <v>71.629</v>
+      </c>
+    </row>
+    <row r="2796">
+      <c r="A2796" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2796" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:30–02:45</t>
+        </is>
+      </c>
+      <c r="C2796" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2796" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2796" s="3">
+        <v>71.629</v>
+      </c>
+      <c r="F2796" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2796" s="3">
+        <v>71.629</v>
+      </c>
+    </row>
+    <row r="2797">
+      <c r="A2797" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2797" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02:45–03:00</t>
+        </is>
+      </c>
+      <c r="C2797" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2797" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2797" s="3">
+        <v>71.782</v>
+      </c>
+      <c r="F2797" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2797" s="3">
+        <v>71.782</v>
+      </c>
+    </row>
+    <row r="2798">
+      <c r="A2798" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2798" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:00–03:15</t>
+        </is>
+      </c>
+      <c r="C2798" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2798" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2798" s="3">
+        <v>71.629</v>
+      </c>
+      <c r="F2798" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2798" s="3">
+        <v>71.629</v>
+      </c>
+    </row>
+    <row r="2799">
+      <c r="A2799" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2799" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:15–03:30</t>
+        </is>
+      </c>
+      <c r="C2799" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2799" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2799" s="3">
+        <v>71.936</v>
+      </c>
+      <c r="F2799" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2799" s="3">
+        <v>71.936</v>
+      </c>
+    </row>
+    <row r="2800">
+      <c r="A2800" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2800" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:30–03:45</t>
+        </is>
+      </c>
+      <c r="C2800" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2800" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2800" s="3">
+        <v>71.578</v>
+      </c>
+      <c r="F2800" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2800" s="3">
+        <v>71.578</v>
+      </c>
+    </row>
+    <row r="2801">
+      <c r="A2801" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2801" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03:45–04:00</t>
+        </is>
+      </c>
+      <c r="C2801" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2801" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2801" s="3">
+        <v>71.629</v>
+      </c>
+      <c r="F2801" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2801" s="3">
+        <v>71.629</v>
+      </c>
+    </row>
+    <row r="2802">
+      <c r="A2802" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2802" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:00–04:15</t>
+        </is>
+      </c>
+      <c r="C2802" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2802" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2802" s="3">
+        <v>71.424</v>
+      </c>
+      <c r="F2802" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2802" s="3">
+        <v>71.424</v>
+      </c>
+    </row>
+    <row r="2803">
+      <c r="A2803" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2803" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:15–04:30</t>
+        </is>
+      </c>
+      <c r="C2803" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2803" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2803" s="3">
+        <v>71.578</v>
+      </c>
+      <c r="F2803" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2803" s="3">
+        <v>71.578</v>
+      </c>
+    </row>
+    <row r="2804">
+      <c r="A2804" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2804" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:30–04:45</t>
+        </is>
+      </c>
+      <c r="C2804" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2804" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2804" s="3">
+        <v>71.68</v>
+      </c>
+      <c r="F2804" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2804" s="3">
+        <v>71.68</v>
+      </c>
+    </row>
+    <row r="2805">
+      <c r="A2805" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2805" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04:45–05:00</t>
+        </is>
+      </c>
+      <c r="C2805" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2805" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2805" s="3">
+        <v>71.424</v>
+      </c>
+      <c r="F2805" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2805" s="3">
+        <v>71.424</v>
+      </c>
+    </row>
+    <row r="2806">
+      <c r="A2806" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2806" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:00–05:15</t>
+        </is>
+      </c>
+      <c r="C2806" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2806" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2806" s="3">
+        <v>71.629</v>
+      </c>
+      <c r="F2806" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2806" s="3">
+        <v>71.629</v>
+      </c>
+    </row>
+    <row r="2807">
+      <c r="A2807" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2807" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:15–05:30</t>
+        </is>
+      </c>
+      <c r="C2807" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2807" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2807" s="3">
+        <v>71.629</v>
+      </c>
+      <c r="F2807" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2807" s="3">
+        <v>71.629</v>
+      </c>
+    </row>
+    <row r="2808">
+      <c r="A2808" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2808" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:30–05:45</t>
+        </is>
+      </c>
+      <c r="C2808" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2808" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2808" s="3">
+        <v>71.373</v>
+      </c>
+      <c r="F2808" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2808" s="3">
+        <v>71.373</v>
+      </c>
+    </row>
+    <row r="2809">
+      <c r="A2809" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2809" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05:45–06:00</t>
+        </is>
+      </c>
+      <c r="C2809" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2809" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2809" s="3">
+        <v>71.936</v>
+      </c>
+      <c r="F2809" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2809" s="3">
+        <v>71.936</v>
+      </c>
+    </row>
+    <row r="2810">
+      <c r="A2810" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2810" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:00–06:15</t>
+        </is>
+      </c>
+      <c r="C2810" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2810" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2810" s="3">
+        <v>72.038</v>
+      </c>
+      <c r="F2810" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2810" s="3">
+        <v>72.038</v>
+      </c>
+    </row>
+    <row r="2811">
+      <c r="A2811" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2811" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:15–06:30</t>
+        </is>
+      </c>
+      <c r="C2811" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2811" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2811" s="3">
+        <v>71.731</v>
+      </c>
+      <c r="F2811" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2811" s="3">
+        <v>71.731</v>
+      </c>
+    </row>
+    <row r="2812">
+      <c r="A2812" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2812" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:30–06:45</t>
+        </is>
+      </c>
+      <c r="C2812" s="3">
+        <v>0.179</v>
+      </c>
+      <c r="D2812" s="3">
+        <v>0.179</v>
+      </c>
+      <c r="E2812" s="3">
+        <v>71.475</v>
+      </c>
+      <c r="F2812" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2812" s="3">
+        <v>71.654</v>
+      </c>
+    </row>
+    <row r="2813">
+      <c r="A2813" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2813" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06:45–07:00</t>
+        </is>
+      </c>
+      <c r="C2813" s="3">
+        <v>1.446</v>
+      </c>
+      <c r="D2813" s="3">
+        <v>1.446</v>
+      </c>
+      <c r="E2813" s="3">
+        <v>70.144</v>
+      </c>
+      <c r="F2813" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2813" s="3">
+        <v>71.59</v>
+      </c>
+    </row>
+    <row r="2814">
+      <c r="A2814" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2814" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:00–07:15</t>
+        </is>
+      </c>
+      <c r="C2814" s="3">
+        <v>2.995</v>
+      </c>
+      <c r="D2814" s="3">
+        <v>2.995</v>
+      </c>
+      <c r="E2814" s="3">
+        <v>69.683</v>
+      </c>
+      <c r="F2814" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2814" s="3">
+        <v>72.678</v>
+      </c>
+    </row>
+    <row r="2815">
+      <c r="A2815" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2815" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:15–07:30</t>
+        </is>
+      </c>
+      <c r="C2815" s="3">
+        <v>4.454</v>
+      </c>
+      <c r="D2815" s="3">
+        <v>4.454</v>
+      </c>
+      <c r="E2815" s="3">
+        <v>68.403</v>
+      </c>
+      <c r="F2815" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2815" s="3">
+        <v>72.857</v>
+      </c>
+    </row>
+    <row r="2816">
+      <c r="A2816" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2816" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:30–07:45</t>
+        </is>
+      </c>
+      <c r="C2816" s="3">
+        <v>6.938</v>
+      </c>
+      <c r="D2816" s="3">
+        <v>6.938</v>
+      </c>
+      <c r="E2816" s="3">
+        <v>66.048</v>
+      </c>
+      <c r="F2816" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2816" s="3">
+        <v>72.986</v>
+      </c>
+    </row>
+    <row r="2817">
+      <c r="A2817" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2817" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07:45–08:00</t>
+        </is>
+      </c>
+      <c r="C2817" s="3">
+        <v>5.299</v>
+      </c>
+      <c r="D2817" s="3">
+        <v>5.299</v>
+      </c>
+      <c r="E2817" s="3">
+        <v>68.454</v>
+      </c>
+      <c r="F2817" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2817" s="3">
+        <v>73.753</v>
+      </c>
+    </row>
+    <row r="2818">
+      <c r="A2818" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2818" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:00–08:15</t>
+        </is>
+      </c>
+      <c r="C2818" s="3">
+        <v>5.696</v>
+      </c>
+      <c r="D2818" s="3">
+        <v>5.696</v>
+      </c>
+      <c r="E2818" s="3">
+        <v>67.789</v>
+      </c>
+      <c r="F2818" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2818" s="3">
+        <v>73.485</v>
+      </c>
+    </row>
+    <row r="2819">
+      <c r="A2819" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2819" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:15–08:30</t>
+        </is>
+      </c>
+      <c r="C2819" s="3">
+        <v>9.152</v>
+      </c>
+      <c r="D2819" s="3">
+        <v>9.152</v>
+      </c>
+      <c r="E2819" s="3">
+        <v>63.539</v>
+      </c>
+      <c r="F2819" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2819" s="3">
+        <v>72.691</v>
+      </c>
+    </row>
+    <row r="2820">
+      <c r="A2820" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2820" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:30–08:45</t>
+        </is>
+      </c>
+      <c r="C2820" s="3">
+        <v>13.555</v>
+      </c>
+      <c r="D2820" s="3">
+        <v>13.555</v>
+      </c>
+      <c r="E2820" s="3">
+        <v>33.126</v>
+      </c>
+      <c r="F2820" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2820" s="3">
+        <v>46.681</v>
+      </c>
+    </row>
+    <row r="2821">
+      <c r="A2821" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2821" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08:45–09:00</t>
+        </is>
+      </c>
+      <c r="C2821" s="3">
+        <v>18.368</v>
+      </c>
+      <c r="D2821" s="3">
+        <v>18.368</v>
+      </c>
+      <c r="E2821" s="3">
+        <v>20.838</v>
+      </c>
+      <c r="F2821" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2821" s="3">
+        <v>39.206</v>
+      </c>
+    </row>
+    <row r="2822">
+      <c r="A2822" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2822" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:00–09:15</t>
+        </is>
+      </c>
+      <c r="C2822" s="3">
+        <v>34.099</v>
+      </c>
+      <c r="D2822" s="3">
+        <v>31.795</v>
+      </c>
+      <c r="E2822" s="3">
+        <v>6.861</v>
+      </c>
+      <c r="F2822" s="3">
+        <v>2.304</v>
+      </c>
+      <c r="G2822" s="3">
+        <v>38.656</v>
+      </c>
+    </row>
+    <row r="2823">
+      <c r="A2823" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2823" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:15–09:30</t>
+        </is>
+      </c>
+      <c r="C2823" s="3">
+        <v>48.141</v>
+      </c>
+      <c r="D2823" s="3">
+        <v>36.263</v>
+      </c>
+      <c r="E2823" s="3">
+        <v>2.458</v>
+      </c>
+      <c r="F2823" s="3">
+        <v>11.878</v>
+      </c>
+      <c r="G2823" s="3">
+        <v>38.721</v>
+      </c>
+    </row>
+    <row r="2824">
+      <c r="A2824" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2824" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:30–09:45</t>
+        </is>
+      </c>
+      <c r="C2824" s="3">
+        <v>76.813</v>
+      </c>
+      <c r="D2824" s="3">
+        <v>39.13</v>
+      </c>
+      <c r="E2824" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2824" s="3">
+        <v>37.683</v>
+      </c>
+      <c r="G2824" s="3">
+        <v>39.13</v>
+      </c>
+    </row>
+    <row r="2825">
+      <c r="A2825" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2825" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09:45–10:00</t>
+        </is>
+      </c>
+      <c r="C2825" s="3">
+        <v>86.797</v>
+      </c>
+      <c r="D2825" s="3">
+        <v>38.72</v>
+      </c>
+      <c r="E2825" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2825" s="3">
+        <v>48.077</v>
+      </c>
+      <c r="G2825" s="3">
+        <v>38.72</v>
+      </c>
+    </row>
+    <row r="2826">
+      <c r="A2826" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2826" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:00–10:15</t>
+        </is>
+      </c>
+      <c r="C2826" s="3">
+        <v>91.61</v>
+      </c>
+      <c r="D2826" s="3">
+        <v>38.72</v>
+      </c>
+      <c r="E2826" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2826" s="3">
+        <v>52.89</v>
+      </c>
+      <c r="G2826" s="3">
+        <v>38.72</v>
+      </c>
+    </row>
+    <row r="2827">
+      <c r="A2827" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2827" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:15–10:30</t>
+        </is>
+      </c>
+      <c r="C2827" s="3">
+        <v>96.192</v>
+      </c>
+      <c r="D2827" s="3">
+        <v>39.053</v>
+      </c>
+      <c r="E2827" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2827" s="3">
+        <v>57.139</v>
+      </c>
+      <c r="G2827" s="3">
+        <v>39.053</v>
+      </c>
+    </row>
+    <row r="2828">
+      <c r="A2828" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2828" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:30–10:45</t>
+        </is>
+      </c>
+      <c r="C2828" s="3">
+        <v>100.211</v>
+      </c>
+      <c r="D2828" s="3">
+        <v>39.385</v>
+      </c>
+      <c r="E2828" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2828" s="3">
+        <v>60.826</v>
+      </c>
+      <c r="G2828" s="3">
+        <v>39.385</v>
+      </c>
+    </row>
+    <row r="2829">
+      <c r="A2829" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2829" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10:45–11:00</t>
+        </is>
+      </c>
+      <c r="C2829" s="3">
+        <v>105.446</v>
+      </c>
+      <c r="D2829" s="3">
+        <v>39.552</v>
+      </c>
+      <c r="E2829" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2829" s="3">
+        <v>65.894</v>
+      </c>
+      <c r="G2829" s="3">
+        <v>39.552</v>
+      </c>
+    </row>
+    <row r="2830">
+      <c r="A2830" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2830" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:00–11:15</t>
+        </is>
+      </c>
+      <c r="C2830" s="3">
+        <v>110.221</v>
+      </c>
+      <c r="D2830" s="3">
+        <v>39.514</v>
+      </c>
+      <c r="E2830" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2830" s="3">
+        <v>70.707</v>
+      </c>
+      <c r="G2830" s="3">
+        <v>39.514</v>
+      </c>
+    </row>
+    <row r="2831">
+      <c r="A2831" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2831" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:15–11:30</t>
+        </is>
+      </c>
+      <c r="C2831" s="3">
+        <v>71.117</v>
+      </c>
+      <c r="D2831" s="3">
+        <v>38.963</v>
+      </c>
+      <c r="E2831" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2831" s="3">
+        <v>32.154</v>
+      </c>
+      <c r="G2831" s="3">
+        <v>38.963</v>
+      </c>
+    </row>
+    <row r="2832">
+      <c r="A2832" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2832" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:30–11:45</t>
+        </is>
+      </c>
+      <c r="C2832" s="3">
+        <v>48.435</v>
+      </c>
+      <c r="D2832" s="3">
+        <v>38.707</v>
+      </c>
+      <c r="E2832" s="3">
+        <v>0.051</v>
+      </c>
+      <c r="F2832" s="3">
+        <v>9.728</v>
+      </c>
+      <c r="G2832" s="3">
+        <v>38.758</v>
+      </c>
+    </row>
+    <row r="2833">
+      <c r="A2833" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2833" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11:45–12:00</t>
+        </is>
+      </c>
+      <c r="C2833" s="3">
+        <v>103.68</v>
+      </c>
+      <c r="D2833" s="3">
+        <v>39.014</v>
+      </c>
+      <c r="E2833" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2833" s="3">
+        <v>64.666</v>
+      </c>
+      <c r="G2833" s="3">
+        <v>39.014</v>
+      </c>
+    </row>
+    <row r="2834">
+      <c r="A2834" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2834" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:00–12:15</t>
+        </is>
+      </c>
+      <c r="C2834" s="3">
+        <v>114.65</v>
+      </c>
+      <c r="D2834" s="3">
+        <v>39.181</v>
+      </c>
+      <c r="E2834" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2834" s="3">
+        <v>75.469</v>
+      </c>
+      <c r="G2834" s="3">
+        <v>39.181</v>
+      </c>
+    </row>
+    <row r="2835">
+      <c r="A2835" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2835" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:15–12:30</t>
+        </is>
+      </c>
+      <c r="C2835" s="3">
+        <v>114.394</v>
+      </c>
+      <c r="D2835" s="3">
+        <v>39.642</v>
+      </c>
+      <c r="E2835" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2835" s="3">
+        <v>74.752</v>
+      </c>
+      <c r="G2835" s="3">
+        <v>39.642</v>
+      </c>
+    </row>
+    <row r="2836">
+      <c r="A2836" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2836" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:30–12:45</t>
+        </is>
+      </c>
+      <c r="C2836" s="3">
+        <v>83.328</v>
+      </c>
+      <c r="D2836" s="3">
+        <v>39.194</v>
+      </c>
+      <c r="E2836" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2836" s="3">
+        <v>44.134</v>
+      </c>
+      <c r="G2836" s="3">
+        <v>39.194</v>
+      </c>
+    </row>
+    <row r="2837">
+      <c r="A2837" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2837" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12:45–13:00</t>
+        </is>
+      </c>
+      <c r="C2837" s="3">
+        <v>80.448</v>
+      </c>
+      <c r="D2837" s="3">
+        <v>39.693</v>
+      </c>
+      <c r="E2837" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2837" s="3">
+        <v>40.755</v>
+      </c>
+      <c r="G2837" s="3">
+        <v>39.693</v>
+      </c>
+    </row>
+    <row r="2838">
+      <c r="A2838" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2838" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:00–13:15</t>
+        </is>
+      </c>
+      <c r="C2838" s="3">
+        <v>57.574</v>
+      </c>
+      <c r="D2838" s="3">
+        <v>38.732</v>
+      </c>
+      <c r="E2838" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2838" s="3">
+        <v>18.842</v>
+      </c>
+      <c r="G2838" s="3">
+        <v>38.732</v>
+      </c>
+    </row>
+    <row r="2839">
+      <c r="A2839" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2839" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:15–13:30</t>
+        </is>
+      </c>
+      <c r="C2839" s="3">
+        <v>45.453</v>
+      </c>
+      <c r="D2839" s="3">
+        <v>38.592</v>
+      </c>
+      <c r="E2839" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2839" s="3">
+        <v>6.861</v>
+      </c>
+      <c r="G2839" s="3">
+        <v>38.592</v>
+      </c>
+    </row>
+    <row r="2840">
+      <c r="A2840" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2840" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:30–13:45</t>
+        </is>
+      </c>
+      <c r="C2840" s="3">
+        <v>89.382</v>
+      </c>
+      <c r="D2840" s="3">
+        <v>38.95</v>
+      </c>
+      <c r="E2840" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2840" s="3">
+        <v>50.432</v>
+      </c>
+      <c r="G2840" s="3">
+        <v>38.95</v>
+      </c>
+    </row>
+    <row r="2841">
+      <c r="A2841" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2841" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13:45–14:00</t>
+        </is>
+      </c>
+      <c r="C2841" s="3">
+        <v>109.338</v>
+      </c>
+      <c r="D2841" s="3">
+        <v>39.245</v>
+      </c>
+      <c r="E2841" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2841" s="3">
+        <v>70.093</v>
+      </c>
+      <c r="G2841" s="3">
+        <v>39.245</v>
+      </c>
+    </row>
+    <row r="2842">
+      <c r="A2842" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2842" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:00–14:15</t>
+        </is>
+      </c>
+      <c r="C2842" s="3">
+        <v>107.891</v>
+      </c>
+      <c r="D2842" s="3">
+        <v>40.153</v>
+      </c>
+      <c r="E2842" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2842" s="3">
+        <v>67.738</v>
+      </c>
+      <c r="G2842" s="3">
+        <v>40.153</v>
+      </c>
+    </row>
+    <row r="2843">
+      <c r="A2843" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2843" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:15–14:30</t>
+        </is>
+      </c>
+      <c r="C2843" s="3">
+        <v>93.158</v>
+      </c>
+      <c r="D2843" s="3">
+        <v>40.524</v>
+      </c>
+      <c r="E2843" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2843" s="3">
+        <v>52.634</v>
+      </c>
+      <c r="G2843" s="3">
+        <v>40.524</v>
+      </c>
+    </row>
+    <row r="2844">
+      <c r="A2844" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2844" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:30–14:45</t>
+        </is>
+      </c>
+      <c r="C2844" s="3">
+        <v>100.07</v>
+      </c>
+      <c r="D2844" s="3">
+        <v>40.115</v>
+      </c>
+      <c r="E2844" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2844" s="3">
+        <v>59.955</v>
+      </c>
+      <c r="G2844" s="3">
+        <v>40.115</v>
+      </c>
+    </row>
+    <row r="2845">
+      <c r="A2845" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2845" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14:45–15:00</t>
+        </is>
+      </c>
+      <c r="C2845" s="3">
+        <v>108.954</v>
+      </c>
+      <c r="D2845" s="3">
+        <v>39.732</v>
+      </c>
+      <c r="E2845" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2845" s="3">
+        <v>69.222</v>
+      </c>
+      <c r="G2845" s="3">
+        <v>39.732</v>
+      </c>
+    </row>
+    <row r="2846">
+      <c r="A2846" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2846" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:00–15:15</t>
+        </is>
+      </c>
+      <c r="C2846" s="3">
+        <v>105.754</v>
+      </c>
+      <c r="D2846" s="3">
+        <v>39.655</v>
+      </c>
+      <c r="E2846" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2846" s="3">
+        <v>66.099</v>
+      </c>
+      <c r="G2846" s="3">
+        <v>39.655</v>
+      </c>
+    </row>
+    <row r="2847">
+      <c r="A2847" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2847" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:15–15:30</t>
+        </is>
+      </c>
+      <c r="C2847" s="3">
+        <v>101.965</v>
+      </c>
+      <c r="D2847" s="3">
+        <v>39.091</v>
+      </c>
+      <c r="E2847" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2847" s="3">
+        <v>62.874</v>
+      </c>
+      <c r="G2847" s="3">
+        <v>39.091</v>
+      </c>
+    </row>
+    <row r="2848">
+      <c r="A2848" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2848" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:30–15:45</t>
+        </is>
+      </c>
+      <c r="C2848" s="3">
+        <v>97.024</v>
+      </c>
+      <c r="D2848" s="3">
+        <v>39.424</v>
+      </c>
+      <c r="E2848" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2848" s="3">
+        <v>57.6</v>
+      </c>
+      <c r="G2848" s="3">
+        <v>39.424</v>
+      </c>
+    </row>
+    <row r="2849">
+      <c r="A2849" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2849" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15:45–16:00</t>
+        </is>
+      </c>
+      <c r="C2849" s="3">
+        <v>91.75</v>
+      </c>
+      <c r="D2849" s="3">
+        <v>39.884</v>
+      </c>
+      <c r="E2849" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2849" s="3">
+        <v>51.866</v>
+      </c>
+      <c r="G2849" s="3">
+        <v>39.884</v>
+      </c>
+    </row>
+    <row r="2850">
+      <c r="A2850" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2850" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:00–16:15</t>
+        </is>
+      </c>
+      <c r="C2850" s="3">
+        <v>86.362</v>
+      </c>
+      <c r="D2850" s="3">
+        <v>40.077</v>
+      </c>
+      <c r="E2850" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2850" s="3">
+        <v>46.285</v>
+      </c>
+      <c r="G2850" s="3">
+        <v>40.077</v>
+      </c>
+    </row>
+    <row r="2851">
+      <c r="A2851" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2851" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:15–16:30</t>
+        </is>
+      </c>
+      <c r="C2851" s="3">
+        <v>80.896</v>
+      </c>
+      <c r="D2851" s="3">
+        <v>39.27</v>
+      </c>
+      <c r="E2851" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2851" s="3">
+        <v>41.626</v>
+      </c>
+      <c r="G2851" s="3">
+        <v>39.27</v>
+      </c>
+    </row>
+    <row r="2852">
+      <c r="A2852" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2852" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:30–16:45</t>
+        </is>
+      </c>
+      <c r="C2852" s="3">
+        <v>74.534</v>
+      </c>
+      <c r="D2852" s="3">
+        <v>38.95</v>
+      </c>
+      <c r="E2852" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2852" s="3">
+        <v>35.584</v>
+      </c>
+      <c r="G2852" s="3">
+        <v>38.95</v>
+      </c>
+    </row>
+    <row r="2853">
+      <c r="A2853" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2853" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16:45–17:00</t>
+        </is>
+      </c>
+      <c r="C2853" s="3">
+        <v>68.851</v>
+      </c>
+      <c r="D2853" s="3">
+        <v>38.95</v>
+      </c>
+      <c r="E2853" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F2853" s="3">
+        <v>29.901</v>
+      </c>
+      <c r="G2853" s="3">
+        <v>38.95</v>
+      </c>
+    </row>
+    <row r="2854">
+      <c r="A2854" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2854" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:00–17:15</t>
+        </is>
+      </c>
+      <c r="C2854" s="3">
+        <v>42.867</v>
+      </c>
+      <c r="D2854" s="3">
+        <v>30.067</v>
+      </c>
+      <c r="E2854" s="3">
+        <v>8.602</v>
+      </c>
+      <c r="F2854" s="3">
+        <v>12.8</v>
+      </c>
+      <c r="G2854" s="3">
+        <v>38.669</v>
+      </c>
+    </row>
+    <row r="2855">
+      <c r="A2855" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2855" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:15–17:30</t>
+        </is>
+      </c>
+      <c r="C2855" s="3">
+        <v>10.394</v>
+      </c>
+      <c r="D2855" s="3">
+        <v>10.394</v>
+      </c>
+      <c r="E2855" s="3">
+        <v>28.211</v>
+      </c>
+      <c r="F2855" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2855" s="3">
+        <v>38.605</v>
+      </c>
+    </row>
+    <row r="2856">
+      <c r="A2856" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2856" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:30–17:45</t>
+        </is>
+      </c>
+      <c r="C2856" s="3">
+        <v>7.987</v>
+      </c>
+      <c r="D2856" s="3">
+        <v>7.987</v>
+      </c>
+      <c r="E2856" s="3">
+        <v>30.464</v>
+      </c>
+      <c r="F2856" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2856" s="3">
+        <v>38.451</v>
+      </c>
+    </row>
+    <row r="2857">
+      <c r="A2857" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2857" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17:45–18:00</t>
+        </is>
+      </c>
+      <c r="C2857" s="3">
+        <v>4.16</v>
+      </c>
+      <c r="D2857" s="3">
+        <v>4.16</v>
+      </c>
+      <c r="E2857" s="3">
+        <v>34.253</v>
+      </c>
+      <c r="F2857" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2857" s="3">
+        <v>38.413</v>
+      </c>
+    </row>
+    <row r="2858">
+      <c r="A2858" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2858" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:00–18:15</t>
+        </is>
+      </c>
+      <c r="C2858" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="D2858" s="3">
+        <v>3.43</v>
+      </c>
+      <c r="E2858" s="3">
+        <v>34.765</v>
+      </c>
+      <c r="F2858" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2858" s="3">
+        <v>38.195</v>
+      </c>
+    </row>
+    <row r="2859">
+      <c r="A2859" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2859" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:15–18:30</t>
+        </is>
+      </c>
+      <c r="C2859" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="D2859" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="E2859" s="3">
+        <v>35.379</v>
+      </c>
+      <c r="F2859" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2859" s="3">
+        <v>38.579</v>
+      </c>
+    </row>
+    <row r="2860">
+      <c r="A2860" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2860" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:30–18:45</t>
+        </is>
+      </c>
+      <c r="C2860" s="3">
+        <v>1.638</v>
+      </c>
+      <c r="D2860" s="3">
+        <v>1.638</v>
+      </c>
+      <c r="E2860" s="3">
+        <v>36.71</v>
+      </c>
+      <c r="F2860" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2860" s="3">
+        <v>38.348</v>
+      </c>
+    </row>
+    <row r="2861">
+      <c r="A2861" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2861" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18:45–19:00</t>
+        </is>
+      </c>
+      <c r="C2861" s="3">
+        <v>0.755</v>
+      </c>
+      <c r="D2861" s="3">
+        <v>0.755</v>
+      </c>
+      <c r="E2861" s="3">
+        <v>37.939</v>
+      </c>
+      <c r="F2861" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2861" s="3">
+        <v>38.694</v>
+      </c>
+    </row>
+    <row r="2862">
+      <c r="A2862" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2862" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:00–19:15</t>
+        </is>
+      </c>
+      <c r="C2862" s="3">
+        <v>0.678</v>
+      </c>
+      <c r="D2862" s="3">
+        <v>0.678</v>
+      </c>
+      <c r="E2862" s="3">
+        <v>38.246</v>
+      </c>
+      <c r="F2862" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2862" s="3">
+        <v>38.924</v>
+      </c>
+    </row>
+    <row r="2863">
+      <c r="A2863" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2863" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:15–19:30</t>
+        </is>
+      </c>
+      <c r="C2863" s="3">
+        <v>0.141</v>
+      </c>
+      <c r="D2863" s="3">
+        <v>0.141</v>
+      </c>
+      <c r="E2863" s="3">
+        <v>38.4</v>
+      </c>
+      <c r="F2863" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2863" s="3">
+        <v>38.541</v>
+      </c>
+    </row>
+    <row r="2864">
+      <c r="A2864" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2864" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:30–19:45</t>
+        </is>
+      </c>
+      <c r="C2864" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2864" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2864" s="3">
+        <v>38.861</v>
+      </c>
+      <c r="F2864" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2864" s="3">
+        <v>38.861</v>
+      </c>
+    </row>
+    <row r="2865">
+      <c r="A2865" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2865" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19:45–20:00</t>
+        </is>
+      </c>
+      <c r="C2865" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2865" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2865" s="3">
+        <v>38.349</v>
+      </c>
+      <c r="F2865" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2865" s="3">
+        <v>38.349</v>
+      </c>
+    </row>
+    <row r="2866">
+      <c r="A2866" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2866" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:00–20:15</t>
+        </is>
+      </c>
+      <c r="C2866" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2866" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2866" s="3">
+        <v>38.195</v>
+      </c>
+      <c r="F2866" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2866" s="3">
+        <v>38.195</v>
+      </c>
+    </row>
+    <row r="2867">
+      <c r="A2867" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2867" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:15–20:30</t>
+        </is>
+      </c>
+      <c r="C2867" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2867" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2867" s="3">
+        <v>38.246</v>
+      </c>
+      <c r="F2867" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2867" s="3">
+        <v>38.246</v>
+      </c>
+    </row>
+    <row r="2868">
+      <c r="A2868" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2868" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:30–20:45</t>
+        </is>
+      </c>
+      <c r="C2868" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2868" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2868" s="3">
+        <v>38.656</v>
+      </c>
+      <c r="F2868" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2868" s="3">
+        <v>38.656</v>
+      </c>
+    </row>
+    <row r="2869">
+      <c r="A2869" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2869" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20:45–21:00</t>
+        </is>
+      </c>
+      <c r="C2869" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2869" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2869" s="3">
+        <v>38.451</v>
+      </c>
+      <c r="F2869" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2869" s="3">
+        <v>38.451</v>
+      </c>
+    </row>
+    <row r="2870">
+      <c r="A2870" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2870" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:00–21:15</t>
+        </is>
+      </c>
+      <c r="C2870" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2870" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2870" s="3">
+        <v>38.298</v>
+      </c>
+      <c r="F2870" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2870" s="3">
+        <v>38.298</v>
+      </c>
+    </row>
+    <row r="2871">
+      <c r="A2871" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2871" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:15–21:30</t>
+        </is>
+      </c>
+      <c r="C2871" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2871" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2871" s="3">
+        <v>39.27</v>
+      </c>
+      <c r="F2871" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2871" s="3">
+        <v>39.27</v>
+      </c>
+    </row>
+    <row r="2872">
+      <c r="A2872" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2872" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:30–21:45</t>
+        </is>
+      </c>
+      <c r="C2872" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2872" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2872" s="3">
+        <v>39.219</v>
+      </c>
+      <c r="F2872" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2872" s="3">
+        <v>39.219</v>
+      </c>
+    </row>
+    <row r="2873">
+      <c r="A2873" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2873" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21:45–22:00</t>
+        </is>
+      </c>
+      <c r="C2873" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2873" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2873" s="3">
+        <v>38.707</v>
+      </c>
+      <c r="F2873" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2873" s="3">
+        <v>38.707</v>
+      </c>
+    </row>
+    <row r="2874">
+      <c r="A2874" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2874" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:00–22:15</t>
+        </is>
+      </c>
+      <c r="C2874" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2874" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2874" s="3">
+        <v>38.246</v>
+      </c>
+      <c r="F2874" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2874" s="3">
+        <v>38.246</v>
+      </c>
+    </row>
+    <row r="2875">
+      <c r="A2875" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2875" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:15–22:30</t>
+        </is>
+      </c>
+      <c r="C2875" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2875" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2875" s="3">
+        <v>38.195</v>
+      </c>
+      <c r="F2875" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2875" s="3">
+        <v>38.195</v>
+      </c>
+    </row>
+    <row r="2876">
+      <c r="A2876" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2876" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:30–22:45</t>
+        </is>
+      </c>
+      <c r="C2876" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2876" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2876" s="3">
+        <v>38.195</v>
+      </c>
+      <c r="F2876" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2876" s="3">
+        <v>38.195</v>
+      </c>
+    </row>
+    <row r="2877">
+      <c r="A2877" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2877" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22:45–23:00</t>
+        </is>
+      </c>
+      <c r="C2877" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2877" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2877" s="3">
+        <v>38.349</v>
+      </c>
+      <c r="F2877" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2877" s="3">
+        <v>38.349</v>
+      </c>
+    </row>
+    <row r="2878">
+      <c r="A2878" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2878" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:00–23:15</t>
+        </is>
+      </c>
+      <c r="C2878" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2878" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2878" s="3">
+        <v>38.4</v>
+      </c>
+      <c r="F2878" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2878" s="3">
+        <v>38.4</v>
+      </c>
+    </row>
+    <row r="2879">
+      <c r="A2879" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2879" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:15–23:30</t>
+        </is>
+      </c>
+      <c r="C2879" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2879" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2879" s="3">
+        <v>38.298</v>
+      </c>
+      <c r="F2879" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2879" s="3">
+        <v>38.298</v>
+      </c>
+    </row>
+    <row r="2880">
+      <c r="A2880" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2880" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:30–23:45</t>
+        </is>
+      </c>
+      <c r="C2880" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2880" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2880" s="3">
+        <v>38.195</v>
+      </c>
+      <c r="F2880" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2880" s="3">
+        <v>38.195</v>
+      </c>
+    </row>
+    <row r="2881">
+      <c r="A2881" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B2881" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23:45–24:00</t>
+        </is>
+      </c>
+      <c r="C2881" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="D2881" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E2881" s="3">
+        <v>38.707</v>
+      </c>
+      <c r="F2881" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G2881" s="3">
+        <v>38.707</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2785"/>
+  <autoFilter ref="A1:G2881"/>
 </worksheet>
 </file>